--- a/school_lublino/lublino_KP.xlsx
+++ b/school_lublino/lublino_KP.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\МирзаяновИИ\Documents\projects\school_lublino\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10425" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ТКП" sheetId="1" r:id="rId1"/>
@@ -13,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ТКП!$A$7:$U$7</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -3709,7 +3714,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3822,6 +3827,39 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3852,40 +3890,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3896,6 +3901,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4285,79 +4299,79 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="42"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="54"/>
+      <c r="Q3" s="54"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54"/>
+      <c r="U3" s="54"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="44"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="55"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="55"/>
+      <c r="U4" s="55"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="51" t="s">
@@ -4387,115 +4401,115 @@
       <c r="I5" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="45" t="s">
+      <c r="J5" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="47"/>
-      <c r="P5" s="48" t="s">
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="58"/>
+      <c r="P5" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="48" t="s">
+      <c r="Q5" s="60"/>
+      <c r="R5" s="61"/>
+      <c r="S5" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="49"/>
-      <c r="U5" s="50"/>
+      <c r="T5" s="60"/>
+      <c r="U5" s="61"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="52"/>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="54" t="s">
+      <c r="A6" s="62"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="55"/>
+      <c r="K6" s="44"/>
       <c r="L6" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="54" t="s">
+      <c r="M6" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="55"/>
+      <c r="N6" s="44"/>
       <c r="O6" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="54" t="s">
+      <c r="P6" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="55"/>
+      <c r="Q6" s="44"/>
       <c r="R6" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="S6" s="54" t="s">
+      <c r="S6" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="55"/>
+      <c r="T6" s="44"/>
       <c r="U6" s="51" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="53"/>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
+      <c r="A7" s="52"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
       <c r="J7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="53"/>
+      <c r="L7" s="52"/>
       <c r="M7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="53"/>
+      <c r="O7" s="52"/>
       <c r="P7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="53"/>
+      <c r="R7" s="52"/>
       <c r="S7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="U7" s="53"/>
+      <c r="U7" s="52"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="58"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="50"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -4537,15 +4551,15 @@
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="61"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="47"/>
       <c r="M9" s="6">
         <f>SUM(M10,M20)</f>
         <v>18303819.899999999</v>
@@ -4581,15 +4595,15 @@
       <c r="B10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="61"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="47"/>
       <c r="M10" s="6">
         <f t="shared" ref="M10:O14" si="0">SUM(M11)</f>
         <v>126283.29</v>
@@ -4625,15 +4639,15 @@
       <c r="B11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="61"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="47"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4669,15 +4683,15 @@
       <c r="B12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="61"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="47"/>
       <c r="M12" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4713,15 +4727,15 @@
       <c r="B13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="61"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="47"/>
       <c r="M13" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4757,15 +4771,15 @@
       <c r="B14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="61"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="47"/>
       <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -5056,15 +5070,15 @@
       <c r="B20" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="59" t="s">
+      <c r="C20" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="61"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="47"/>
       <c r="M20" s="6">
         <f t="shared" ref="M20:O21" si="1">SUM(M21)</f>
         <v>18177536.609999999</v>
@@ -5100,15 +5114,15 @@
       <c r="B21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="59" t="s">
+      <c r="C21" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="61"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="47"/>
       <c r="M21" s="6">
         <f t="shared" si="1"/>
         <v>18177536.609999999</v>
@@ -5144,15 +5158,15 @@
       <c r="B22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="59" t="s">
+      <c r="C22" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="61"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="47"/>
       <c r="M22" s="6">
         <f>SUM(M23,M122,M163,M203,M248)</f>
         <v>18177536.609999999</v>
@@ -5188,15 +5202,15 @@
       <c r="B23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="61"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="47"/>
       <c r="M23" s="6">
         <f>SUM(M24,M67,M76,M119)</f>
         <v>12831032.07</v>
@@ -5232,15 +5246,15 @@
       <c r="B24" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="60"/>
-      <c r="E24" s="60"/>
-      <c r="F24" s="60"/>
-      <c r="G24" s="60"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="61"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="47"/>
       <c r="M24" s="6">
         <f>SUM(M25,M29,M31,M34,M36,M41,M46,M51,M57,M62)</f>
         <v>7808423.3099999996</v>
@@ -7464,15 +7478,15 @@
       <c r="B67" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="59" t="s">
+      <c r="C67" s="45" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="60"/>
-      <c r="E67" s="60"/>
-      <c r="F67" s="60"/>
-      <c r="G67" s="60"/>
-      <c r="H67" s="60"/>
-      <c r="I67" s="61"/>
+      <c r="D67" s="46"/>
+      <c r="E67" s="46"/>
+      <c r="F67" s="46"/>
+      <c r="G67" s="46"/>
+      <c r="H67" s="46"/>
+      <c r="I67" s="47"/>
       <c r="M67" s="6">
         <f>SUM(M68,M72,M74)</f>
         <v>748533.11</v>
@@ -7970,15 +7984,15 @@
       <c r="B76" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C76" s="59" t="s">
+      <c r="C76" s="45" t="s">
         <v>325</v>
       </c>
-      <c r="D76" s="60"/>
-      <c r="E76" s="60"/>
-      <c r="F76" s="60"/>
-      <c r="G76" s="60"/>
-      <c r="H76" s="60"/>
-      <c r="I76" s="61"/>
+      <c r="D76" s="46"/>
+      <c r="E76" s="46"/>
+      <c r="F76" s="46"/>
+      <c r="G76" s="46"/>
+      <c r="H76" s="46"/>
+      <c r="I76" s="47"/>
       <c r="M76" s="6">
         <f>SUM(M77,M82,M87,M93,M96,M99,M104,M109,M114,M117)</f>
         <v>3831185.6499999994</v>
@@ -10228,15 +10242,15 @@
       <c r="B119" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C119" s="59" t="s">
+      <c r="C119" s="45" t="s">
         <v>526</v>
       </c>
-      <c r="D119" s="60"/>
-      <c r="E119" s="60"/>
-      <c r="F119" s="60"/>
-      <c r="G119" s="60"/>
-      <c r="H119" s="60"/>
-      <c r="I119" s="61"/>
+      <c r="D119" s="46"/>
+      <c r="E119" s="46"/>
+      <c r="F119" s="46"/>
+      <c r="G119" s="46"/>
+      <c r="H119" s="46"/>
+      <c r="I119" s="47"/>
       <c r="M119" s="6">
         <f>SUM(M120)</f>
         <v>442890</v>
@@ -10398,15 +10412,15 @@
       <c r="B122" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="C122" s="59" t="s">
+      <c r="C122" s="45" t="s">
         <v>541</v>
       </c>
-      <c r="D122" s="60"/>
-      <c r="E122" s="60"/>
-      <c r="F122" s="60"/>
-      <c r="G122" s="60"/>
-      <c r="H122" s="60"/>
-      <c r="I122" s="61"/>
+      <c r="D122" s="46"/>
+      <c r="E122" s="46"/>
+      <c r="F122" s="46"/>
+      <c r="G122" s="46"/>
+      <c r="H122" s="46"/>
+      <c r="I122" s="47"/>
       <c r="M122" s="6">
         <f>SUM(M123)</f>
         <v>4016037.31</v>
@@ -10442,15 +10456,15 @@
       <c r="B123" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="C123" s="59" t="s">
+      <c r="C123" s="45" t="s">
         <v>544</v>
       </c>
-      <c r="D123" s="60"/>
-      <c r="E123" s="60"/>
-      <c r="F123" s="60"/>
-      <c r="G123" s="60"/>
-      <c r="H123" s="60"/>
-      <c r="I123" s="61"/>
+      <c r="D123" s="46"/>
+      <c r="E123" s="46"/>
+      <c r="F123" s="46"/>
+      <c r="G123" s="46"/>
+      <c r="H123" s="46"/>
+      <c r="I123" s="47"/>
       <c r="M123" s="6">
         <f>SUM(M124,M127,M131,M136,M140,M143,M148,M153,M158)</f>
         <v>4016037.31</v>
@@ -10558,7 +10572,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="125" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A125" s="9" t="s">
         <v>550</v>
       </c>
@@ -11192,7 +11206,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="137" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A137" s="9" t="s">
         <v>613</v>
       </c>
@@ -12531,15 +12545,15 @@
       <c r="B163" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C163" s="59" t="s">
+      <c r="C163" s="45" t="s">
         <v>710</v>
       </c>
-      <c r="D163" s="60"/>
-      <c r="E163" s="60"/>
-      <c r="F163" s="60"/>
-      <c r="G163" s="60"/>
-      <c r="H163" s="60"/>
-      <c r="I163" s="61"/>
+      <c r="D163" s="46"/>
+      <c r="E163" s="46"/>
+      <c r="F163" s="46"/>
+      <c r="G163" s="46"/>
+      <c r="H163" s="46"/>
+      <c r="I163" s="47"/>
       <c r="M163" s="6">
         <f>SUM(M164,M184)</f>
         <v>611422.71999999997</v>
@@ -12575,15 +12589,15 @@
       <c r="B164" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="C164" s="59" t="s">
+      <c r="C164" s="45" t="s">
         <v>713</v>
       </c>
-      <c r="D164" s="60"/>
-      <c r="E164" s="60"/>
-      <c r="F164" s="60"/>
-      <c r="G164" s="60"/>
-      <c r="H164" s="60"/>
-      <c r="I164" s="61"/>
+      <c r="D164" s="46"/>
+      <c r="E164" s="46"/>
+      <c r="F164" s="46"/>
+      <c r="G164" s="46"/>
+      <c r="H164" s="46"/>
+      <c r="I164" s="47"/>
       <c r="M164" s="6">
         <f>SUM(M165,M171,M174,M178,M182)</f>
         <v>415021.23999999993</v>
@@ -13630,15 +13644,15 @@
       <c r="B184" s="9" t="s">
         <v>789</v>
       </c>
-      <c r="C184" s="59" t="s">
+      <c r="C184" s="45" t="s">
         <v>790</v>
       </c>
-      <c r="D184" s="60"/>
-      <c r="E184" s="60"/>
-      <c r="F184" s="60"/>
-      <c r="G184" s="60"/>
-      <c r="H184" s="60"/>
-      <c r="I184" s="61"/>
+      <c r="D184" s="46"/>
+      <c r="E184" s="46"/>
+      <c r="F184" s="46"/>
+      <c r="G184" s="46"/>
+      <c r="H184" s="46"/>
+      <c r="I184" s="47"/>
       <c r="M184" s="6">
         <f>SUM(M185,M188,M191,M194,M197,M200)</f>
         <v>196401.48</v>
@@ -14688,15 +14702,15 @@
       <c r="B203" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="C203" s="59" t="s">
+      <c r="C203" s="45" t="s">
         <v>856</v>
       </c>
-      <c r="D203" s="60"/>
-      <c r="E203" s="60"/>
-      <c r="F203" s="60"/>
-      <c r="G203" s="60"/>
-      <c r="H203" s="60"/>
-      <c r="I203" s="61"/>
+      <c r="D203" s="46"/>
+      <c r="E203" s="46"/>
+      <c r="F203" s="46"/>
+      <c r="G203" s="46"/>
+      <c r="H203" s="46"/>
+      <c r="I203" s="47"/>
       <c r="M203" s="6">
         <f>SUM(M204,M206,M221,M236,M238,M240,M242,M243,M244,M245,M246,M247)</f>
         <v>719044.50999999989</v>
@@ -16426,7 +16440,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="239" spans="1:35" ht="375" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:35" ht="393.75" x14ac:dyDescent="0.25">
       <c r="A239" s="9" t="s">
         <v>1004</v>
       </c>
@@ -17078,15 +17092,15 @@
       <c r="B248" s="9" t="s">
         <v>1031</v>
       </c>
-      <c r="C248" s="59" t="s">
+      <c r="C248" s="45" t="s">
         <v>1032</v>
       </c>
-      <c r="D248" s="60"/>
-      <c r="E248" s="60"/>
-      <c r="F248" s="60"/>
-      <c r="G248" s="60"/>
-      <c r="H248" s="60"/>
-      <c r="I248" s="61"/>
+      <c r="D248" s="46"/>
+      <c r="E248" s="46"/>
+      <c r="F248" s="46"/>
+      <c r="G248" s="46"/>
+      <c r="H248" s="46"/>
+      <c r="I248" s="47"/>
       <c r="M248" s="6">
         <f>SUM(M249,M250,M251,M252)</f>
         <v>0</v>
@@ -17473,29 +17487,29 @@
       </c>
     </row>
     <row r="254" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="56" t="s">
+      <c r="A254" s="48" t="s">
         <v>1050</v>
       </c>
-      <c r="B254" s="57"/>
-      <c r="C254" s="57"/>
-      <c r="D254" s="57"/>
-      <c r="E254" s="57"/>
-      <c r="F254" s="57"/>
-      <c r="G254" s="57"/>
-      <c r="H254" s="57"/>
-      <c r="I254" s="57"/>
-      <c r="J254" s="57"/>
-      <c r="K254" s="57"/>
-      <c r="L254" s="57"/>
-      <c r="M254" s="57"/>
-      <c r="N254" s="57"/>
-      <c r="O254" s="57"/>
-      <c r="P254" s="57"/>
-      <c r="Q254" s="57"/>
-      <c r="R254" s="57"/>
-      <c r="S254" s="57"/>
-      <c r="T254" s="57"/>
-      <c r="U254" s="58"/>
+      <c r="B254" s="49"/>
+      <c r="C254" s="49"/>
+      <c r="D254" s="49"/>
+      <c r="E254" s="49"/>
+      <c r="F254" s="49"/>
+      <c r="G254" s="49"/>
+      <c r="H254" s="49"/>
+      <c r="I254" s="49"/>
+      <c r="J254" s="49"/>
+      <c r="K254" s="49"/>
+      <c r="L254" s="49"/>
+      <c r="M254" s="49"/>
+      <c r="N254" s="49"/>
+      <c r="O254" s="49"/>
+      <c r="P254" s="49"/>
+      <c r="Q254" s="49"/>
+      <c r="R254" s="49"/>
+      <c r="S254" s="49"/>
+      <c r="T254" s="49"/>
+      <c r="U254" s="50"/>
     </row>
     <row r="255" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="27"/>
@@ -17511,20 +17525,20 @@
       <c r="E255" s="28"/>
       <c r="F255" s="28"/>
       <c r="G255" s="28"/>
-      <c r="H255" s="54"/>
-      <c r="I255" s="62"/>
-      <c r="J255" s="62"/>
-      <c r="K255" s="62"/>
-      <c r="L255" s="62"/>
-      <c r="M255" s="62"/>
-      <c r="N255" s="62"/>
-      <c r="O255" s="62"/>
-      <c r="P255" s="62"/>
-      <c r="Q255" s="62"/>
-      <c r="R255" s="62"/>
-      <c r="S255" s="62"/>
-      <c r="T255" s="62"/>
-      <c r="U255" s="55"/>
+      <c r="H255" s="42"/>
+      <c r="I255" s="43"/>
+      <c r="J255" s="43"/>
+      <c r="K255" s="43"/>
+      <c r="L255" s="43"/>
+      <c r="M255" s="43"/>
+      <c r="N255" s="43"/>
+      <c r="O255" s="43"/>
+      <c r="P255" s="43"/>
+      <c r="Q255" s="43"/>
+      <c r="R255" s="43"/>
+      <c r="S255" s="43"/>
+      <c r="T255" s="43"/>
+      <c r="U255" s="44"/>
     </row>
     <row r="256" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="27"/>
@@ -17540,20 +17554,20 @@
       <c r="E256" s="28"/>
       <c r="F256" s="28"/>
       <c r="G256" s="28"/>
-      <c r="H256" s="54"/>
-      <c r="I256" s="62"/>
-      <c r="J256" s="62"/>
-      <c r="K256" s="62"/>
-      <c r="L256" s="62"/>
-      <c r="M256" s="62"/>
-      <c r="N256" s="62"/>
-      <c r="O256" s="62"/>
-      <c r="P256" s="62"/>
-      <c r="Q256" s="62"/>
-      <c r="R256" s="62"/>
-      <c r="S256" s="62"/>
-      <c r="T256" s="62"/>
-      <c r="U256" s="55"/>
+      <c r="H256" s="42"/>
+      <c r="I256" s="43"/>
+      <c r="J256" s="43"/>
+      <c r="K256" s="43"/>
+      <c r="L256" s="43"/>
+      <c r="M256" s="43"/>
+      <c r="N256" s="43"/>
+      <c r="O256" s="43"/>
+      <c r="P256" s="43"/>
+      <c r="Q256" s="43"/>
+      <c r="R256" s="43"/>
+      <c r="S256" s="43"/>
+      <c r="T256" s="43"/>
+      <c r="U256" s="44"/>
     </row>
     <row r="257" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A257" s="27"/>
@@ -17569,20 +17583,20 @@
       <c r="E257" s="28"/>
       <c r="F257" s="28"/>
       <c r="G257" s="28"/>
-      <c r="H257" s="54"/>
-      <c r="I257" s="62"/>
-      <c r="J257" s="62"/>
-      <c r="K257" s="62"/>
-      <c r="L257" s="62"/>
-      <c r="M257" s="62"/>
-      <c r="N257" s="62"/>
-      <c r="O257" s="62"/>
-      <c r="P257" s="62"/>
-      <c r="Q257" s="62"/>
-      <c r="R257" s="62"/>
-      <c r="S257" s="62"/>
-      <c r="T257" s="62"/>
-      <c r="U257" s="55"/>
+      <c r="H257" s="42"/>
+      <c r="I257" s="43"/>
+      <c r="J257" s="43"/>
+      <c r="K257" s="43"/>
+      <c r="L257" s="43"/>
+      <c r="M257" s="43"/>
+      <c r="N257" s="43"/>
+      <c r="O257" s="43"/>
+      <c r="P257" s="43"/>
+      <c r="Q257" s="43"/>
+      <c r="R257" s="43"/>
+      <c r="S257" s="43"/>
+      <c r="T257" s="43"/>
+      <c r="U257" s="44"/>
     </row>
     <row r="258" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="27"/>
@@ -17598,20 +17612,20 @@
       <c r="E258" s="28"/>
       <c r="F258" s="28"/>
       <c r="G258" s="28"/>
-      <c r="H258" s="54"/>
-      <c r="I258" s="62"/>
-      <c r="J258" s="62"/>
-      <c r="K258" s="62"/>
-      <c r="L258" s="62"/>
-      <c r="M258" s="62"/>
-      <c r="N258" s="62"/>
-      <c r="O258" s="62"/>
-      <c r="P258" s="62"/>
-      <c r="Q258" s="62"/>
-      <c r="R258" s="62"/>
-      <c r="S258" s="62"/>
-      <c r="T258" s="62"/>
-      <c r="U258" s="55"/>
+      <c r="H258" s="42"/>
+      <c r="I258" s="43"/>
+      <c r="J258" s="43"/>
+      <c r="K258" s="43"/>
+      <c r="L258" s="43"/>
+      <c r="M258" s="43"/>
+      <c r="N258" s="43"/>
+      <c r="O258" s="43"/>
+      <c r="P258" s="43"/>
+      <c r="Q258" s="43"/>
+      <c r="R258" s="43"/>
+      <c r="S258" s="43"/>
+      <c r="T258" s="43"/>
+      <c r="U258" s="44"/>
     </row>
     <row r="259" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="27"/>
@@ -17627,20 +17641,20 @@
       <c r="E259" s="28"/>
       <c r="F259" s="28"/>
       <c r="G259" s="28"/>
-      <c r="H259" s="54"/>
-      <c r="I259" s="62"/>
-      <c r="J259" s="62"/>
-      <c r="K259" s="62"/>
-      <c r="L259" s="62"/>
-      <c r="M259" s="62"/>
-      <c r="N259" s="62"/>
-      <c r="O259" s="62"/>
-      <c r="P259" s="62"/>
-      <c r="Q259" s="62"/>
-      <c r="R259" s="62"/>
-      <c r="S259" s="62"/>
-      <c r="T259" s="62"/>
-      <c r="U259" s="55"/>
+      <c r="H259" s="42"/>
+      <c r="I259" s="43"/>
+      <c r="J259" s="43"/>
+      <c r="K259" s="43"/>
+      <c r="L259" s="43"/>
+      <c r="M259" s="43"/>
+      <c r="N259" s="43"/>
+      <c r="O259" s="43"/>
+      <c r="P259" s="43"/>
+      <c r="Q259" s="43"/>
+      <c r="R259" s="43"/>
+      <c r="S259" s="43"/>
+      <c r="T259" s="43"/>
+      <c r="U259" s="44"/>
     </row>
     <row r="260" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A260" s="27"/>
@@ -17656,20 +17670,20 @@
       <c r="E260" s="28"/>
       <c r="F260" s="28"/>
       <c r="G260" s="28"/>
-      <c r="H260" s="54"/>
-      <c r="I260" s="62"/>
-      <c r="J260" s="62"/>
-      <c r="K260" s="62"/>
-      <c r="L260" s="62"/>
-      <c r="M260" s="62"/>
-      <c r="N260" s="62"/>
-      <c r="O260" s="62"/>
-      <c r="P260" s="62"/>
-      <c r="Q260" s="62"/>
-      <c r="R260" s="62"/>
-      <c r="S260" s="62"/>
-      <c r="T260" s="62"/>
-      <c r="U260" s="55"/>
+      <c r="H260" s="42"/>
+      <c r="I260" s="43"/>
+      <c r="J260" s="43"/>
+      <c r="K260" s="43"/>
+      <c r="L260" s="43"/>
+      <c r="M260" s="43"/>
+      <c r="N260" s="43"/>
+      <c r="O260" s="43"/>
+      <c r="P260" s="43"/>
+      <c r="Q260" s="43"/>
+      <c r="R260" s="43"/>
+      <c r="S260" s="43"/>
+      <c r="T260" s="43"/>
+      <c r="U260" s="44"/>
     </row>
     <row r="261" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A261" s="27"/>
@@ -17685,20 +17699,20 @@
       <c r="E261" s="28"/>
       <c r="F261" s="28"/>
       <c r="G261" s="28"/>
-      <c r="H261" s="54"/>
-      <c r="I261" s="62"/>
-      <c r="J261" s="62"/>
-      <c r="K261" s="62"/>
-      <c r="L261" s="62"/>
-      <c r="M261" s="62"/>
-      <c r="N261" s="62"/>
-      <c r="O261" s="62"/>
-      <c r="P261" s="62"/>
-      <c r="Q261" s="62"/>
-      <c r="R261" s="62"/>
-      <c r="S261" s="62"/>
-      <c r="T261" s="62"/>
-      <c r="U261" s="55"/>
+      <c r="H261" s="42"/>
+      <c r="I261" s="43"/>
+      <c r="J261" s="43"/>
+      <c r="K261" s="43"/>
+      <c r="L261" s="43"/>
+      <c r="M261" s="43"/>
+      <c r="N261" s="43"/>
+      <c r="O261" s="43"/>
+      <c r="P261" s="43"/>
+      <c r="Q261" s="43"/>
+      <c r="R261" s="43"/>
+      <c r="S261" s="43"/>
+      <c r="T261" s="43"/>
+      <c r="U261" s="44"/>
     </row>
     <row r="262" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="27"/>
@@ -17714,20 +17728,20 @@
       <c r="E262" s="28"/>
       <c r="F262" s="28"/>
       <c r="G262" s="28"/>
-      <c r="H262" s="54"/>
-      <c r="I262" s="62"/>
-      <c r="J262" s="62"/>
-      <c r="K262" s="62"/>
-      <c r="L262" s="62"/>
-      <c r="M262" s="62"/>
-      <c r="N262" s="62"/>
-      <c r="O262" s="62"/>
-      <c r="P262" s="62"/>
-      <c r="Q262" s="62"/>
-      <c r="R262" s="62"/>
-      <c r="S262" s="62"/>
-      <c r="T262" s="62"/>
-      <c r="U262" s="55"/>
+      <c r="H262" s="42"/>
+      <c r="I262" s="43"/>
+      <c r="J262" s="43"/>
+      <c r="K262" s="43"/>
+      <c r="L262" s="43"/>
+      <c r="M262" s="43"/>
+      <c r="N262" s="43"/>
+      <c r="O262" s="43"/>
+      <c r="P262" s="43"/>
+      <c r="Q262" s="43"/>
+      <c r="R262" s="43"/>
+      <c r="S262" s="43"/>
+      <c r="T262" s="43"/>
+      <c r="U262" s="44"/>
     </row>
     <row r="263" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="27"/>
@@ -17743,20 +17757,20 @@
       <c r="E263" s="28"/>
       <c r="F263" s="28"/>
       <c r="G263" s="28"/>
-      <c r="H263" s="54"/>
-      <c r="I263" s="62"/>
-      <c r="J263" s="62"/>
-      <c r="K263" s="62"/>
-      <c r="L263" s="62"/>
-      <c r="M263" s="62"/>
-      <c r="N263" s="62"/>
-      <c r="O263" s="62"/>
-      <c r="P263" s="62"/>
-      <c r="Q263" s="62"/>
-      <c r="R263" s="62"/>
-      <c r="S263" s="62"/>
-      <c r="T263" s="62"/>
-      <c r="U263" s="55"/>
+      <c r="H263" s="42"/>
+      <c r="I263" s="43"/>
+      <c r="J263" s="43"/>
+      <c r="K263" s="43"/>
+      <c r="L263" s="43"/>
+      <c r="M263" s="43"/>
+      <c r="N263" s="43"/>
+      <c r="O263" s="43"/>
+      <c r="P263" s="43"/>
+      <c r="Q263" s="43"/>
+      <c r="R263" s="43"/>
+      <c r="S263" s="43"/>
+      <c r="T263" s="43"/>
+      <c r="U263" s="44"/>
     </row>
     <row r="264" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A264" s="27"/>
@@ -17772,20 +17786,20 @@
       <c r="E264" s="28"/>
       <c r="F264" s="28"/>
       <c r="G264" s="28"/>
-      <c r="H264" s="54"/>
-      <c r="I264" s="62"/>
-      <c r="J264" s="62"/>
-      <c r="K264" s="62"/>
-      <c r="L264" s="62"/>
-      <c r="M264" s="62"/>
-      <c r="N264" s="62"/>
-      <c r="O264" s="62"/>
-      <c r="P264" s="62"/>
-      <c r="Q264" s="62"/>
-      <c r="R264" s="62"/>
-      <c r="S264" s="62"/>
-      <c r="T264" s="62"/>
-      <c r="U264" s="55"/>
+      <c r="H264" s="42"/>
+      <c r="I264" s="43"/>
+      <c r="J264" s="43"/>
+      <c r="K264" s="43"/>
+      <c r="L264" s="43"/>
+      <c r="M264" s="43"/>
+      <c r="N264" s="43"/>
+      <c r="O264" s="43"/>
+      <c r="P264" s="43"/>
+      <c r="Q264" s="43"/>
+      <c r="R264" s="43"/>
+      <c r="S264" s="43"/>
+      <c r="T264" s="43"/>
+      <c r="U264" s="44"/>
     </row>
     <row r="265" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A265" s="27"/>
@@ -17801,20 +17815,20 @@
       <c r="E265" s="28"/>
       <c r="F265" s="28"/>
       <c r="G265" s="28"/>
-      <c r="H265" s="54"/>
-      <c r="I265" s="62"/>
-      <c r="J265" s="62"/>
-      <c r="K265" s="62"/>
-      <c r="L265" s="62"/>
-      <c r="M265" s="62"/>
-      <c r="N265" s="62"/>
-      <c r="O265" s="62"/>
-      <c r="P265" s="62"/>
-      <c r="Q265" s="62"/>
-      <c r="R265" s="62"/>
-      <c r="S265" s="62"/>
-      <c r="T265" s="62"/>
-      <c r="U265" s="55"/>
+      <c r="H265" s="42"/>
+      <c r="I265" s="43"/>
+      <c r="J265" s="43"/>
+      <c r="K265" s="43"/>
+      <c r="L265" s="43"/>
+      <c r="M265" s="43"/>
+      <c r="N265" s="43"/>
+      <c r="O265" s="43"/>
+      <c r="P265" s="43"/>
+      <c r="Q265" s="43"/>
+      <c r="R265" s="43"/>
+      <c r="S265" s="43"/>
+      <c r="T265" s="43"/>
+      <c r="U265" s="44"/>
     </row>
     <row r="266" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A266" s="27"/>
@@ -17830,20 +17844,20 @@
       <c r="E266" s="28"/>
       <c r="F266" s="28"/>
       <c r="G266" s="28"/>
-      <c r="H266" s="54"/>
-      <c r="I266" s="62"/>
-      <c r="J266" s="62"/>
-      <c r="K266" s="62"/>
-      <c r="L266" s="62"/>
-      <c r="M266" s="62"/>
-      <c r="N266" s="62"/>
-      <c r="O266" s="62"/>
-      <c r="P266" s="62"/>
-      <c r="Q266" s="62"/>
-      <c r="R266" s="62"/>
-      <c r="S266" s="62"/>
-      <c r="T266" s="62"/>
-      <c r="U266" s="55"/>
+      <c r="H266" s="42"/>
+      <c r="I266" s="43"/>
+      <c r="J266" s="43"/>
+      <c r="K266" s="43"/>
+      <c r="L266" s="43"/>
+      <c r="M266" s="43"/>
+      <c r="N266" s="43"/>
+      <c r="O266" s="43"/>
+      <c r="P266" s="43"/>
+      <c r="Q266" s="43"/>
+      <c r="R266" s="43"/>
+      <c r="S266" s="43"/>
+      <c r="T266" s="43"/>
+      <c r="U266" s="44"/>
     </row>
     <row r="267" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="27"/>
@@ -17859,20 +17873,20 @@
       <c r="E267" s="28"/>
       <c r="F267" s="28"/>
       <c r="G267" s="28"/>
-      <c r="H267" s="54"/>
-      <c r="I267" s="62"/>
-      <c r="J267" s="62"/>
-      <c r="K267" s="62"/>
-      <c r="L267" s="62"/>
-      <c r="M267" s="62"/>
-      <c r="N267" s="62"/>
-      <c r="O267" s="62"/>
-      <c r="P267" s="62"/>
-      <c r="Q267" s="62"/>
-      <c r="R267" s="62"/>
-      <c r="S267" s="62"/>
-      <c r="T267" s="62"/>
-      <c r="U267" s="55"/>
+      <c r="H267" s="42"/>
+      <c r="I267" s="43"/>
+      <c r="J267" s="43"/>
+      <c r="K267" s="43"/>
+      <c r="L267" s="43"/>
+      <c r="M267" s="43"/>
+      <c r="N267" s="43"/>
+      <c r="O267" s="43"/>
+      <c r="P267" s="43"/>
+      <c r="Q267" s="43"/>
+      <c r="R267" s="43"/>
+      <c r="S267" s="43"/>
+      <c r="T267" s="43"/>
+      <c r="U267" s="44"/>
     </row>
     <row r="268" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="27"/>
@@ -17888,22 +17902,22 @@
       <c r="E268" s="28"/>
       <c r="F268" s="28"/>
       <c r="G268" s="28"/>
-      <c r="H268" s="54" t="s">
+      <c r="H268" s="42" t="s">
         <v>1092</v>
       </c>
-      <c r="I268" s="62"/>
-      <c r="J268" s="62"/>
-      <c r="K268" s="62"/>
-      <c r="L268" s="62"/>
-      <c r="M268" s="62"/>
-      <c r="N268" s="62"/>
-      <c r="O268" s="62"/>
-      <c r="P268" s="62"/>
-      <c r="Q268" s="62"/>
-      <c r="R268" s="62"/>
-      <c r="S268" s="62"/>
-      <c r="T268" s="62"/>
-      <c r="U268" s="55"/>
+      <c r="I268" s="43"/>
+      <c r="J268" s="43"/>
+      <c r="K268" s="43"/>
+      <c r="L268" s="43"/>
+      <c r="M268" s="43"/>
+      <c r="N268" s="43"/>
+      <c r="O268" s="43"/>
+      <c r="P268" s="43"/>
+      <c r="Q268" s="43"/>
+      <c r="R268" s="43"/>
+      <c r="S268" s="43"/>
+      <c r="T268" s="43"/>
+      <c r="U268" s="44"/>
     </row>
     <row r="269" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="27"/>
@@ -17919,20 +17933,20 @@
       <c r="E269" s="28"/>
       <c r="F269" s="28"/>
       <c r="G269" s="28"/>
-      <c r="H269" s="54"/>
-      <c r="I269" s="62"/>
-      <c r="J269" s="62"/>
-      <c r="K269" s="62"/>
-      <c r="L269" s="62"/>
-      <c r="M269" s="62"/>
-      <c r="N269" s="62"/>
-      <c r="O269" s="62"/>
-      <c r="P269" s="62"/>
-      <c r="Q269" s="62"/>
-      <c r="R269" s="62"/>
-      <c r="S269" s="62"/>
-      <c r="T269" s="62"/>
-      <c r="U269" s="55"/>
+      <c r="H269" s="42"/>
+      <c r="I269" s="43"/>
+      <c r="J269" s="43"/>
+      <c r="K269" s="43"/>
+      <c r="L269" s="43"/>
+      <c r="M269" s="43"/>
+      <c r="N269" s="43"/>
+      <c r="O269" s="43"/>
+      <c r="P269" s="43"/>
+      <c r="Q269" s="43"/>
+      <c r="R269" s="43"/>
+      <c r="S269" s="43"/>
+      <c r="T269" s="43"/>
+      <c r="U269" s="44"/>
     </row>
     <row r="270" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A270" s="27"/>
@@ -17946,20 +17960,20 @@
       <c r="E270" s="28"/>
       <c r="F270" s="28"/>
       <c r="G270" s="28"/>
-      <c r="H270" s="54"/>
-      <c r="I270" s="62"/>
-      <c r="J270" s="62"/>
-      <c r="K270" s="62"/>
-      <c r="L270" s="62"/>
-      <c r="M270" s="62"/>
-      <c r="N270" s="62"/>
-      <c r="O270" s="62"/>
-      <c r="P270" s="62"/>
-      <c r="Q270" s="62"/>
-      <c r="R270" s="62"/>
-      <c r="S270" s="62"/>
-      <c r="T270" s="62"/>
-      <c r="U270" s="55"/>
+      <c r="H270" s="42"/>
+      <c r="I270" s="43"/>
+      <c r="J270" s="43"/>
+      <c r="K270" s="43"/>
+      <c r="L270" s="43"/>
+      <c r="M270" s="43"/>
+      <c r="N270" s="43"/>
+      <c r="O270" s="43"/>
+      <c r="P270" s="43"/>
+      <c r="Q270" s="43"/>
+      <c r="R270" s="43"/>
+      <c r="S270" s="43"/>
+      <c r="T270" s="43"/>
+      <c r="U270" s="44"/>
     </row>
     <row r="271" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="27"/>
@@ -17973,20 +17987,20 @@
       <c r="E271" s="28"/>
       <c r="F271" s="28"/>
       <c r="G271" s="28"/>
-      <c r="H271" s="54"/>
-      <c r="I271" s="62"/>
-      <c r="J271" s="62"/>
-      <c r="K271" s="62"/>
-      <c r="L271" s="62"/>
-      <c r="M271" s="62"/>
-      <c r="N271" s="62"/>
-      <c r="O271" s="62"/>
-      <c r="P271" s="62"/>
-      <c r="Q271" s="62"/>
-      <c r="R271" s="62"/>
-      <c r="S271" s="62"/>
-      <c r="T271" s="62"/>
-      <c r="U271" s="55"/>
+      <c r="H271" s="42"/>
+      <c r="I271" s="43"/>
+      <c r="J271" s="43"/>
+      <c r="K271" s="43"/>
+      <c r="L271" s="43"/>
+      <c r="M271" s="43"/>
+      <c r="N271" s="43"/>
+      <c r="O271" s="43"/>
+      <c r="P271" s="43"/>
+      <c r="Q271" s="43"/>
+      <c r="R271" s="43"/>
+      <c r="S271" s="43"/>
+      <c r="T271" s="43"/>
+      <c r="U271" s="44"/>
     </row>
     <row r="272" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="27"/>
@@ -18000,73 +18014,25 @@
       <c r="E272" s="28"/>
       <c r="F272" s="28"/>
       <c r="G272" s="28"/>
-      <c r="H272" s="54"/>
-      <c r="I272" s="62"/>
-      <c r="J272" s="62"/>
-      <c r="K272" s="62"/>
-      <c r="L272" s="62"/>
-      <c r="M272" s="62"/>
-      <c r="N272" s="62"/>
-      <c r="O272" s="62"/>
-      <c r="P272" s="62"/>
-      <c r="Q272" s="62"/>
-      <c r="R272" s="62"/>
-      <c r="S272" s="62"/>
-      <c r="T272" s="62"/>
-      <c r="U272" s="55"/>
+      <c r="H272" s="42"/>
+      <c r="I272" s="43"/>
+      <c r="J272" s="43"/>
+      <c r="K272" s="43"/>
+      <c r="L272" s="43"/>
+      <c r="M272" s="43"/>
+      <c r="N272" s="43"/>
+      <c r="O272" s="43"/>
+      <c r="P272" s="43"/>
+      <c r="Q272" s="43"/>
+      <c r="R272" s="43"/>
+      <c r="S272" s="43"/>
+      <c r="T272" s="43"/>
+      <c r="U272" s="44"/>
     </row>
   </sheetData>
   <sheetProtection password="C644" sheet="1" formatColumns="0" autoFilter="0"/>
   <autoFilter ref="A7:U7"/>
   <mergeCells count="64">
-    <mergeCell ref="H270:U270"/>
-    <mergeCell ref="H271:U271"/>
-    <mergeCell ref="H272:U272"/>
-    <mergeCell ref="H265:U265"/>
-    <mergeCell ref="H266:U266"/>
-    <mergeCell ref="H267:U267"/>
-    <mergeCell ref="H268:U268"/>
-    <mergeCell ref="H269:U269"/>
-    <mergeCell ref="H260:U260"/>
-    <mergeCell ref="H261:U261"/>
-    <mergeCell ref="H262:U262"/>
-    <mergeCell ref="H263:U263"/>
-    <mergeCell ref="H264:U264"/>
-    <mergeCell ref="H255:U255"/>
-    <mergeCell ref="H256:U256"/>
-    <mergeCell ref="H257:U257"/>
-    <mergeCell ref="H258:U258"/>
-    <mergeCell ref="H259:U259"/>
-    <mergeCell ref="C164:I164"/>
-    <mergeCell ref="C184:I184"/>
-    <mergeCell ref="C203:I203"/>
-    <mergeCell ref="C248:I248"/>
-    <mergeCell ref="A254:U254"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C119:I119"/>
-    <mergeCell ref="C122:I122"/>
-    <mergeCell ref="C123:I123"/>
-    <mergeCell ref="C163:I163"/>
-    <mergeCell ref="C21:I21"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:R7"/>
     <mergeCell ref="A2:U2"/>
     <mergeCell ref="A3:U3"/>
     <mergeCell ref="A4:U4"/>
@@ -18083,6 +18049,54 @@
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="I5:I7"/>
     <mergeCell ref="J6:K6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C119:I119"/>
+    <mergeCell ref="C122:I122"/>
+    <mergeCell ref="C123:I123"/>
+    <mergeCell ref="C163:I163"/>
+    <mergeCell ref="C164:I164"/>
+    <mergeCell ref="C184:I184"/>
+    <mergeCell ref="C203:I203"/>
+    <mergeCell ref="C248:I248"/>
+    <mergeCell ref="A254:U254"/>
+    <mergeCell ref="H255:U255"/>
+    <mergeCell ref="H256:U256"/>
+    <mergeCell ref="H257:U257"/>
+    <mergeCell ref="H258:U258"/>
+    <mergeCell ref="H259:U259"/>
+    <mergeCell ref="H260:U260"/>
+    <mergeCell ref="H261:U261"/>
+    <mergeCell ref="H262:U262"/>
+    <mergeCell ref="H263:U263"/>
+    <mergeCell ref="H264:U264"/>
+    <mergeCell ref="H270:U270"/>
+    <mergeCell ref="H271:U271"/>
+    <mergeCell ref="H272:U272"/>
+    <mergeCell ref="H265:U265"/>
+    <mergeCell ref="H266:U266"/>
+    <mergeCell ref="H267:U267"/>
+    <mergeCell ref="H268:U268"/>
+    <mergeCell ref="H269:U269"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18173,79 +18187,79 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="42"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="54"/>
+      <c r="Q3" s="54"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54"/>
+      <c r="U3" s="54"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="44"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="55"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="55"/>
+      <c r="U4" s="55"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="51" t="s">
@@ -18275,115 +18289,115 @@
       <c r="I5" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="45" t="s">
+      <c r="J5" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="47"/>
-      <c r="P5" s="48" t="s">
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="58"/>
+      <c r="P5" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="48" t="s">
+      <c r="Q5" s="60"/>
+      <c r="R5" s="61"/>
+      <c r="S5" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="49"/>
-      <c r="U5" s="50"/>
+      <c r="T5" s="60"/>
+      <c r="U5" s="61"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="52"/>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="54" t="s">
+      <c r="A6" s="62"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="55"/>
+      <c r="K6" s="44"/>
       <c r="L6" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="54" t="s">
+      <c r="M6" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="55"/>
+      <c r="N6" s="44"/>
       <c r="O6" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="54" t="s">
+      <c r="P6" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="55"/>
+      <c r="Q6" s="44"/>
       <c r="R6" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="S6" s="54" t="s">
+      <c r="S6" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="55"/>
+      <c r="T6" s="44"/>
       <c r="U6" s="51" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="53"/>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
+      <c r="A7" s="52"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
       <c r="J7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="53"/>
+      <c r="L7" s="52"/>
       <c r="M7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="53"/>
+      <c r="O7" s="52"/>
       <c r="P7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="53"/>
+      <c r="R7" s="52"/>
       <c r="S7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="U7" s="53"/>
+      <c r="U7" s="52"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="58"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="50"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -18425,15 +18439,15 @@
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="61"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="47"/>
       <c r="M9" s="6">
         <f>SUM(M10,M20)</f>
         <v>18303819.899999999</v>
@@ -18469,15 +18483,15 @@
       <c r="B10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="61"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="47"/>
       <c r="M10" s="6">
         <f t="shared" ref="M10:O14" si="0">SUM(M11)</f>
         <v>126283.29</v>
@@ -18513,15 +18527,15 @@
       <c r="B11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="61"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="47"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18557,15 +18571,15 @@
       <c r="B12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="61"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="47"/>
       <c r="M12" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18601,15 +18615,15 @@
       <c r="B13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="61"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="47"/>
       <c r="M13" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18645,15 +18659,15 @@
       <c r="B14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="61"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="47"/>
       <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18944,15 +18958,15 @@
       <c r="B20" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="59" t="s">
+      <c r="C20" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="61"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="47"/>
       <c r="M20" s="6">
         <f t="shared" ref="M20:O21" si="1">SUM(M21)</f>
         <v>18177536.609999999</v>
@@ -18988,15 +19002,15 @@
       <c r="B21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="59" t="s">
+      <c r="C21" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="61"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="47"/>
       <c r="M21" s="6">
         <f t="shared" si="1"/>
         <v>18177536.609999999</v>
@@ -19032,15 +19046,15 @@
       <c r="B22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="59" t="s">
+      <c r="C22" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="61"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="47"/>
       <c r="M22" s="6">
         <f>SUM(M23,M122,M163,M203,M248)</f>
         <v>18177536.609999999</v>
@@ -19076,15 +19090,15 @@
       <c r="B23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="61"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="47"/>
       <c r="M23" s="6">
         <f>SUM(M24,M67,M76,M119)</f>
         <v>12831032.07</v>
@@ -19120,15 +19134,15 @@
       <c r="B24" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="60"/>
-      <c r="E24" s="60"/>
-      <c r="F24" s="60"/>
-      <c r="G24" s="60"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="61"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="47"/>
       <c r="M24" s="6">
         <f>SUM(M25,M29,M31,M34,M36,M41,M46,M51,M57,M62)</f>
         <v>7808423.3099999996</v>
@@ -21352,15 +21366,15 @@
       <c r="B67" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="59" t="s">
+      <c r="C67" s="45" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="60"/>
-      <c r="E67" s="60"/>
-      <c r="F67" s="60"/>
-      <c r="G67" s="60"/>
-      <c r="H67" s="60"/>
-      <c r="I67" s="61"/>
+      <c r="D67" s="46"/>
+      <c r="E67" s="46"/>
+      <c r="F67" s="46"/>
+      <c r="G67" s="46"/>
+      <c r="H67" s="46"/>
+      <c r="I67" s="47"/>
       <c r="M67" s="6">
         <f>SUM(M68,M72,M74)</f>
         <v>748533.11</v>
@@ -21858,15 +21872,15 @@
       <c r="B76" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C76" s="59" t="s">
+      <c r="C76" s="45" t="s">
         <v>325</v>
       </c>
-      <c r="D76" s="60"/>
-      <c r="E76" s="60"/>
-      <c r="F76" s="60"/>
-      <c r="G76" s="60"/>
-      <c r="H76" s="60"/>
-      <c r="I76" s="61"/>
+      <c r="D76" s="46"/>
+      <c r="E76" s="46"/>
+      <c r="F76" s="46"/>
+      <c r="G76" s="46"/>
+      <c r="H76" s="46"/>
+      <c r="I76" s="47"/>
       <c r="M76" s="6">
         <f>SUM(M77,M82,M87,M93,M96,M99,M104,M109,M114,M117)</f>
         <v>3831185.6499999994</v>
@@ -24116,15 +24130,15 @@
       <c r="B119" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C119" s="59" t="s">
+      <c r="C119" s="45" t="s">
         <v>526</v>
       </c>
-      <c r="D119" s="60"/>
-      <c r="E119" s="60"/>
-      <c r="F119" s="60"/>
-      <c r="G119" s="60"/>
-      <c r="H119" s="60"/>
-      <c r="I119" s="61"/>
+      <c r="D119" s="46"/>
+      <c r="E119" s="46"/>
+      <c r="F119" s="46"/>
+      <c r="G119" s="46"/>
+      <c r="H119" s="46"/>
+      <c r="I119" s="47"/>
       <c r="M119" s="6">
         <f>SUM(M120)</f>
         <v>442890</v>
@@ -24448,7 +24462,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="125" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A125" s="9" t="s">
         <v>550</v>
       </c>
@@ -25082,7 +25096,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="137" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A137" s="9" t="s">
         <v>613</v>
       </c>
@@ -26421,15 +26435,15 @@
       <c r="B163" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C163" s="59" t="s">
+      <c r="C163" s="45" t="s">
         <v>710</v>
       </c>
-      <c r="D163" s="60"/>
-      <c r="E163" s="60"/>
-      <c r="F163" s="60"/>
-      <c r="G163" s="60"/>
-      <c r="H163" s="60"/>
-      <c r="I163" s="61"/>
+      <c r="D163" s="46"/>
+      <c r="E163" s="46"/>
+      <c r="F163" s="46"/>
+      <c r="G163" s="46"/>
+      <c r="H163" s="46"/>
+      <c r="I163" s="47"/>
       <c r="M163" s="6">
         <f>SUM(M164,M184)</f>
         <v>611422.71999999997</v>
@@ -26465,15 +26479,15 @@
       <c r="B164" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="C164" s="59" t="s">
+      <c r="C164" s="45" t="s">
         <v>713</v>
       </c>
-      <c r="D164" s="60"/>
-      <c r="E164" s="60"/>
-      <c r="F164" s="60"/>
-      <c r="G164" s="60"/>
-      <c r="H164" s="60"/>
-      <c r="I164" s="61"/>
+      <c r="D164" s="46"/>
+      <c r="E164" s="46"/>
+      <c r="F164" s="46"/>
+      <c r="G164" s="46"/>
+      <c r="H164" s="46"/>
+      <c r="I164" s="47"/>
       <c r="M164" s="6">
         <f>SUM(M165,M171,M174,M178,M182)</f>
         <v>415021.23999999993</v>
@@ -26806,24 +26820,24 @@
       <c r="A171" s="9" t="s">
         <v>743</v>
       </c>
-      <c r="B171" s="9" t="s">
+      <c r="B171" s="29" t="s">
         <v>744</v>
       </c>
-      <c r="C171" s="39" t="s">
+      <c r="C171" s="66" t="s">
         <v>745</v>
       </c>
-      <c r="D171" s="11"/>
-      <c r="E171" s="11" t="s">
+      <c r="D171" s="67"/>
+      <c r="E171" s="67" t="s">
         <v>746</v>
       </c>
-      <c r="F171" s="11" t="s">
+      <c r="F171" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="G171" s="12">
+      <c r="G171" s="68">
         <v>1</v>
       </c>
-      <c r="H171" s="12"/>
-      <c r="I171" s="12">
+      <c r="H171" s="68"/>
+      <c r="I171" s="68">
         <v>3246.61</v>
       </c>
       <c r="J171" s="13">
@@ -26883,7 +26897,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="172" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A172" s="9" t="s">
         <v>749</v>
       </c>
@@ -27050,7 +27064,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="175" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A175" s="9" t="s">
         <v>759</v>
       </c>
@@ -27346,7 +27360,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="181" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
         <v>776</v>
       </c>
@@ -27520,15 +27534,15 @@
       <c r="B184" s="9" t="s">
         <v>789</v>
       </c>
-      <c r="C184" s="59" t="s">
+      <c r="C184" s="45" t="s">
         <v>790</v>
       </c>
-      <c r="D184" s="60"/>
-      <c r="E184" s="60"/>
-      <c r="F184" s="60"/>
-      <c r="G184" s="60"/>
-      <c r="H184" s="60"/>
-      <c r="I184" s="61"/>
+      <c r="D184" s="46"/>
+      <c r="E184" s="46"/>
+      <c r="F184" s="46"/>
+      <c r="G184" s="46"/>
+      <c r="H184" s="46"/>
+      <c r="I184" s="47"/>
       <c r="M184" s="6">
         <f>SUM(M185,M188,M191,M194,M197,M200)</f>
         <v>196401.48</v>
@@ -27976,7 +27990,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="192" spans="1:35" ht="206.25" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:35" ht="187.5" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
         <v>819</v>
       </c>
@@ -28578,15 +28592,15 @@
       <c r="B203" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="C203" s="59" t="s">
+      <c r="C203" s="45" t="s">
         <v>856</v>
       </c>
-      <c r="D203" s="60"/>
-      <c r="E203" s="60"/>
-      <c r="F203" s="60"/>
-      <c r="G203" s="60"/>
-      <c r="H203" s="60"/>
-      <c r="I203" s="61"/>
+      <c r="D203" s="46"/>
+      <c r="E203" s="46"/>
+      <c r="F203" s="46"/>
+      <c r="G203" s="46"/>
+      <c r="H203" s="46"/>
+      <c r="I203" s="47"/>
       <c r="M203" s="6">
         <f>SUM(M204,M206,M221,M236,M238,M240,M242,M243,M244,M245,M246,M247)</f>
         <v>719044.50999999989</v>
@@ -30968,15 +30982,15 @@
       <c r="B248" s="9" t="s">
         <v>1031</v>
       </c>
-      <c r="C248" s="59" t="s">
+      <c r="C248" s="45" t="s">
         <v>1032</v>
       </c>
-      <c r="D248" s="60"/>
-      <c r="E248" s="60"/>
-      <c r="F248" s="60"/>
-      <c r="G248" s="60"/>
-      <c r="H248" s="60"/>
-      <c r="I248" s="61"/>
+      <c r="D248" s="46"/>
+      <c r="E248" s="46"/>
+      <c r="F248" s="46"/>
+      <c r="G248" s="46"/>
+      <c r="H248" s="46"/>
+      <c r="I248" s="47"/>
       <c r="M248" s="6">
         <f>SUM(M249,M250,M251,M252)</f>
         <v>0</v>
@@ -31363,29 +31377,29 @@
       </c>
     </row>
     <row r="254" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="56" t="s">
+      <c r="A254" s="48" t="s">
         <v>1050</v>
       </c>
-      <c r="B254" s="57"/>
-      <c r="C254" s="57"/>
-      <c r="D254" s="57"/>
-      <c r="E254" s="57"/>
-      <c r="F254" s="57"/>
-      <c r="G254" s="57"/>
-      <c r="H254" s="57"/>
-      <c r="I254" s="57"/>
-      <c r="J254" s="57"/>
-      <c r="K254" s="57"/>
-      <c r="L254" s="57"/>
-      <c r="M254" s="57"/>
-      <c r="N254" s="57"/>
-      <c r="O254" s="57"/>
-      <c r="P254" s="57"/>
-      <c r="Q254" s="57"/>
-      <c r="R254" s="57"/>
-      <c r="S254" s="57"/>
-      <c r="T254" s="57"/>
-      <c r="U254" s="58"/>
+      <c r="B254" s="49"/>
+      <c r="C254" s="49"/>
+      <c r="D254" s="49"/>
+      <c r="E254" s="49"/>
+      <c r="F254" s="49"/>
+      <c r="G254" s="49"/>
+      <c r="H254" s="49"/>
+      <c r="I254" s="49"/>
+      <c r="J254" s="49"/>
+      <c r="K254" s="49"/>
+      <c r="L254" s="49"/>
+      <c r="M254" s="49"/>
+      <c r="N254" s="49"/>
+      <c r="O254" s="49"/>
+      <c r="P254" s="49"/>
+      <c r="Q254" s="49"/>
+      <c r="R254" s="49"/>
+      <c r="S254" s="49"/>
+      <c r="T254" s="49"/>
+      <c r="U254" s="50"/>
     </row>
     <row r="255" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="27"/>
@@ -31401,20 +31415,20 @@
       <c r="E255" s="28"/>
       <c r="F255" s="28"/>
       <c r="G255" s="28"/>
-      <c r="H255" s="54"/>
-      <c r="I255" s="62"/>
-      <c r="J255" s="62"/>
-      <c r="K255" s="62"/>
-      <c r="L255" s="62"/>
-      <c r="M255" s="62"/>
-      <c r="N255" s="62"/>
-      <c r="O255" s="62"/>
-      <c r="P255" s="62"/>
-      <c r="Q255" s="62"/>
-      <c r="R255" s="62"/>
-      <c r="S255" s="62"/>
-      <c r="T255" s="62"/>
-      <c r="U255" s="55"/>
+      <c r="H255" s="42"/>
+      <c r="I255" s="43"/>
+      <c r="J255" s="43"/>
+      <c r="K255" s="43"/>
+      <c r="L255" s="43"/>
+      <c r="M255" s="43"/>
+      <c r="N255" s="43"/>
+      <c r="O255" s="43"/>
+      <c r="P255" s="43"/>
+      <c r="Q255" s="43"/>
+      <c r="R255" s="43"/>
+      <c r="S255" s="43"/>
+      <c r="T255" s="43"/>
+      <c r="U255" s="44"/>
     </row>
     <row r="256" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="27"/>
@@ -31430,20 +31444,20 @@
       <c r="E256" s="28"/>
       <c r="F256" s="28"/>
       <c r="G256" s="28"/>
-      <c r="H256" s="54"/>
-      <c r="I256" s="62"/>
-      <c r="J256" s="62"/>
-      <c r="K256" s="62"/>
-      <c r="L256" s="62"/>
-      <c r="M256" s="62"/>
-      <c r="N256" s="62"/>
-      <c r="O256" s="62"/>
-      <c r="P256" s="62"/>
-      <c r="Q256" s="62"/>
-      <c r="R256" s="62"/>
-      <c r="S256" s="62"/>
-      <c r="T256" s="62"/>
-      <c r="U256" s="55"/>
+      <c r="H256" s="42"/>
+      <c r="I256" s="43"/>
+      <c r="J256" s="43"/>
+      <c r="K256" s="43"/>
+      <c r="L256" s="43"/>
+      <c r="M256" s="43"/>
+      <c r="N256" s="43"/>
+      <c r="O256" s="43"/>
+      <c r="P256" s="43"/>
+      <c r="Q256" s="43"/>
+      <c r="R256" s="43"/>
+      <c r="S256" s="43"/>
+      <c r="T256" s="43"/>
+      <c r="U256" s="44"/>
     </row>
     <row r="257" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A257" s="27"/>
@@ -31459,20 +31473,20 @@
       <c r="E257" s="28"/>
       <c r="F257" s="28"/>
       <c r="G257" s="28"/>
-      <c r="H257" s="54"/>
-      <c r="I257" s="62"/>
-      <c r="J257" s="62"/>
-      <c r="K257" s="62"/>
-      <c r="L257" s="62"/>
-      <c r="M257" s="62"/>
-      <c r="N257" s="62"/>
-      <c r="O257" s="62"/>
-      <c r="P257" s="62"/>
-      <c r="Q257" s="62"/>
-      <c r="R257" s="62"/>
-      <c r="S257" s="62"/>
-      <c r="T257" s="62"/>
-      <c r="U257" s="55"/>
+      <c r="H257" s="42"/>
+      <c r="I257" s="43"/>
+      <c r="J257" s="43"/>
+      <c r="K257" s="43"/>
+      <c r="L257" s="43"/>
+      <c r="M257" s="43"/>
+      <c r="N257" s="43"/>
+      <c r="O257" s="43"/>
+      <c r="P257" s="43"/>
+      <c r="Q257" s="43"/>
+      <c r="R257" s="43"/>
+      <c r="S257" s="43"/>
+      <c r="T257" s="43"/>
+      <c r="U257" s="44"/>
     </row>
     <row r="258" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="27"/>
@@ -31488,20 +31502,20 @@
       <c r="E258" s="28"/>
       <c r="F258" s="28"/>
       <c r="G258" s="28"/>
-      <c r="H258" s="54"/>
-      <c r="I258" s="62"/>
-      <c r="J258" s="62"/>
-      <c r="K258" s="62"/>
-      <c r="L258" s="62"/>
-      <c r="M258" s="62"/>
-      <c r="N258" s="62"/>
-      <c r="O258" s="62"/>
-      <c r="P258" s="62"/>
-      <c r="Q258" s="62"/>
-      <c r="R258" s="62"/>
-      <c r="S258" s="62"/>
-      <c r="T258" s="62"/>
-      <c r="U258" s="55"/>
+      <c r="H258" s="42"/>
+      <c r="I258" s="43"/>
+      <c r="J258" s="43"/>
+      <c r="K258" s="43"/>
+      <c r="L258" s="43"/>
+      <c r="M258" s="43"/>
+      <c r="N258" s="43"/>
+      <c r="O258" s="43"/>
+      <c r="P258" s="43"/>
+      <c r="Q258" s="43"/>
+      <c r="R258" s="43"/>
+      <c r="S258" s="43"/>
+      <c r="T258" s="43"/>
+      <c r="U258" s="44"/>
     </row>
     <row r="259" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="27"/>
@@ -31517,20 +31531,20 @@
       <c r="E259" s="28"/>
       <c r="F259" s="28"/>
       <c r="G259" s="28"/>
-      <c r="H259" s="54"/>
-      <c r="I259" s="62"/>
-      <c r="J259" s="62"/>
-      <c r="K259" s="62"/>
-      <c r="L259" s="62"/>
-      <c r="M259" s="62"/>
-      <c r="N259" s="62"/>
-      <c r="O259" s="62"/>
-      <c r="P259" s="62"/>
-      <c r="Q259" s="62"/>
-      <c r="R259" s="62"/>
-      <c r="S259" s="62"/>
-      <c r="T259" s="62"/>
-      <c r="U259" s="55"/>
+      <c r="H259" s="42"/>
+      <c r="I259" s="43"/>
+      <c r="J259" s="43"/>
+      <c r="K259" s="43"/>
+      <c r="L259" s="43"/>
+      <c r="M259" s="43"/>
+      <c r="N259" s="43"/>
+      <c r="O259" s="43"/>
+      <c r="P259" s="43"/>
+      <c r="Q259" s="43"/>
+      <c r="R259" s="43"/>
+      <c r="S259" s="43"/>
+      <c r="T259" s="43"/>
+      <c r="U259" s="44"/>
     </row>
     <row r="260" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A260" s="27"/>
@@ -31546,20 +31560,20 @@
       <c r="E260" s="28"/>
       <c r="F260" s="28"/>
       <c r="G260" s="28"/>
-      <c r="H260" s="54"/>
-      <c r="I260" s="62"/>
-      <c r="J260" s="62"/>
-      <c r="K260" s="62"/>
-      <c r="L260" s="62"/>
-      <c r="M260" s="62"/>
-      <c r="N260" s="62"/>
-      <c r="O260" s="62"/>
-      <c r="P260" s="62"/>
-      <c r="Q260" s="62"/>
-      <c r="R260" s="62"/>
-      <c r="S260" s="62"/>
-      <c r="T260" s="62"/>
-      <c r="U260" s="55"/>
+      <c r="H260" s="42"/>
+      <c r="I260" s="43"/>
+      <c r="J260" s="43"/>
+      <c r="K260" s="43"/>
+      <c r="L260" s="43"/>
+      <c r="M260" s="43"/>
+      <c r="N260" s="43"/>
+      <c r="O260" s="43"/>
+      <c r="P260" s="43"/>
+      <c r="Q260" s="43"/>
+      <c r="R260" s="43"/>
+      <c r="S260" s="43"/>
+      <c r="T260" s="43"/>
+      <c r="U260" s="44"/>
     </row>
     <row r="261" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A261" s="27"/>
@@ -31575,20 +31589,20 @@
       <c r="E261" s="28"/>
       <c r="F261" s="28"/>
       <c r="G261" s="28"/>
-      <c r="H261" s="54"/>
-      <c r="I261" s="62"/>
-      <c r="J261" s="62"/>
-      <c r="K261" s="62"/>
-      <c r="L261" s="62"/>
-      <c r="M261" s="62"/>
-      <c r="N261" s="62"/>
-      <c r="O261" s="62"/>
-      <c r="P261" s="62"/>
-      <c r="Q261" s="62"/>
-      <c r="R261" s="62"/>
-      <c r="S261" s="62"/>
-      <c r="T261" s="62"/>
-      <c r="U261" s="55"/>
+      <c r="H261" s="42"/>
+      <c r="I261" s="43"/>
+      <c r="J261" s="43"/>
+      <c r="K261" s="43"/>
+      <c r="L261" s="43"/>
+      <c r="M261" s="43"/>
+      <c r="N261" s="43"/>
+      <c r="O261" s="43"/>
+      <c r="P261" s="43"/>
+      <c r="Q261" s="43"/>
+      <c r="R261" s="43"/>
+      <c r="S261" s="43"/>
+      <c r="T261" s="43"/>
+      <c r="U261" s="44"/>
     </row>
     <row r="262" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="27"/>
@@ -31604,20 +31618,20 @@
       <c r="E262" s="28"/>
       <c r="F262" s="28"/>
       <c r="G262" s="28"/>
-      <c r="H262" s="54"/>
-      <c r="I262" s="62"/>
-      <c r="J262" s="62"/>
-      <c r="K262" s="62"/>
-      <c r="L262" s="62"/>
-      <c r="M262" s="62"/>
-      <c r="N262" s="62"/>
-      <c r="O262" s="62"/>
-      <c r="P262" s="62"/>
-      <c r="Q262" s="62"/>
-      <c r="R262" s="62"/>
-      <c r="S262" s="62"/>
-      <c r="T262" s="62"/>
-      <c r="U262" s="55"/>
+      <c r="H262" s="42"/>
+      <c r="I262" s="43"/>
+      <c r="J262" s="43"/>
+      <c r="K262" s="43"/>
+      <c r="L262" s="43"/>
+      <c r="M262" s="43"/>
+      <c r="N262" s="43"/>
+      <c r="O262" s="43"/>
+      <c r="P262" s="43"/>
+      <c r="Q262" s="43"/>
+      <c r="R262" s="43"/>
+      <c r="S262" s="43"/>
+      <c r="T262" s="43"/>
+      <c r="U262" s="44"/>
     </row>
     <row r="263" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="27"/>
@@ -31633,20 +31647,20 @@
       <c r="E263" s="28"/>
       <c r="F263" s="28"/>
       <c r="G263" s="28"/>
-      <c r="H263" s="54"/>
-      <c r="I263" s="62"/>
-      <c r="J263" s="62"/>
-      <c r="K263" s="62"/>
-      <c r="L263" s="62"/>
-      <c r="M263" s="62"/>
-      <c r="N263" s="62"/>
-      <c r="O263" s="62"/>
-      <c r="P263" s="62"/>
-      <c r="Q263" s="62"/>
-      <c r="R263" s="62"/>
-      <c r="S263" s="62"/>
-      <c r="T263" s="62"/>
-      <c r="U263" s="55"/>
+      <c r="H263" s="42"/>
+      <c r="I263" s="43"/>
+      <c r="J263" s="43"/>
+      <c r="K263" s="43"/>
+      <c r="L263" s="43"/>
+      <c r="M263" s="43"/>
+      <c r="N263" s="43"/>
+      <c r="O263" s="43"/>
+      <c r="P263" s="43"/>
+      <c r="Q263" s="43"/>
+      <c r="R263" s="43"/>
+      <c r="S263" s="43"/>
+      <c r="T263" s="43"/>
+      <c r="U263" s="44"/>
     </row>
     <row r="264" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A264" s="27"/>
@@ -31662,20 +31676,20 @@
       <c r="E264" s="28"/>
       <c r="F264" s="28"/>
       <c r="G264" s="28"/>
-      <c r="H264" s="54"/>
-      <c r="I264" s="62"/>
-      <c r="J264" s="62"/>
-      <c r="K264" s="62"/>
-      <c r="L264" s="62"/>
-      <c r="M264" s="62"/>
-      <c r="N264" s="62"/>
-      <c r="O264" s="62"/>
-      <c r="P264" s="62"/>
-      <c r="Q264" s="62"/>
-      <c r="R264" s="62"/>
-      <c r="S264" s="62"/>
-      <c r="T264" s="62"/>
-      <c r="U264" s="55"/>
+      <c r="H264" s="42"/>
+      <c r="I264" s="43"/>
+      <c r="J264" s="43"/>
+      <c r="K264" s="43"/>
+      <c r="L264" s="43"/>
+      <c r="M264" s="43"/>
+      <c r="N264" s="43"/>
+      <c r="O264" s="43"/>
+      <c r="P264" s="43"/>
+      <c r="Q264" s="43"/>
+      <c r="R264" s="43"/>
+      <c r="S264" s="43"/>
+      <c r="T264" s="43"/>
+      <c r="U264" s="44"/>
     </row>
     <row r="265" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A265" s="27"/>
@@ -31691,20 +31705,20 @@
       <c r="E265" s="28"/>
       <c r="F265" s="28"/>
       <c r="G265" s="28"/>
-      <c r="H265" s="54"/>
-      <c r="I265" s="62"/>
-      <c r="J265" s="62"/>
-      <c r="K265" s="62"/>
-      <c r="L265" s="62"/>
-      <c r="M265" s="62"/>
-      <c r="N265" s="62"/>
-      <c r="O265" s="62"/>
-      <c r="P265" s="62"/>
-      <c r="Q265" s="62"/>
-      <c r="R265" s="62"/>
-      <c r="S265" s="62"/>
-      <c r="T265" s="62"/>
-      <c r="U265" s="55"/>
+      <c r="H265" s="42"/>
+      <c r="I265" s="43"/>
+      <c r="J265" s="43"/>
+      <c r="K265" s="43"/>
+      <c r="L265" s="43"/>
+      <c r="M265" s="43"/>
+      <c r="N265" s="43"/>
+      <c r="O265" s="43"/>
+      <c r="P265" s="43"/>
+      <c r="Q265" s="43"/>
+      <c r="R265" s="43"/>
+      <c r="S265" s="43"/>
+      <c r="T265" s="43"/>
+      <c r="U265" s="44"/>
     </row>
     <row r="266" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A266" s="27"/>
@@ -31720,20 +31734,20 @@
       <c r="E266" s="28"/>
       <c r="F266" s="28"/>
       <c r="G266" s="28"/>
-      <c r="H266" s="54"/>
-      <c r="I266" s="62"/>
-      <c r="J266" s="62"/>
-      <c r="K266" s="62"/>
-      <c r="L266" s="62"/>
-      <c r="M266" s="62"/>
-      <c r="N266" s="62"/>
-      <c r="O266" s="62"/>
-      <c r="P266" s="62"/>
-      <c r="Q266" s="62"/>
-      <c r="R266" s="62"/>
-      <c r="S266" s="62"/>
-      <c r="T266" s="62"/>
-      <c r="U266" s="55"/>
+      <c r="H266" s="42"/>
+      <c r="I266" s="43"/>
+      <c r="J266" s="43"/>
+      <c r="K266" s="43"/>
+      <c r="L266" s="43"/>
+      <c r="M266" s="43"/>
+      <c r="N266" s="43"/>
+      <c r="O266" s="43"/>
+      <c r="P266" s="43"/>
+      <c r="Q266" s="43"/>
+      <c r="R266" s="43"/>
+      <c r="S266" s="43"/>
+      <c r="T266" s="43"/>
+      <c r="U266" s="44"/>
     </row>
     <row r="267" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="27"/>
@@ -31749,20 +31763,20 @@
       <c r="E267" s="28"/>
       <c r="F267" s="28"/>
       <c r="G267" s="28"/>
-      <c r="H267" s="54"/>
-      <c r="I267" s="62"/>
-      <c r="J267" s="62"/>
-      <c r="K267" s="62"/>
-      <c r="L267" s="62"/>
-      <c r="M267" s="62"/>
-      <c r="N267" s="62"/>
-      <c r="O267" s="62"/>
-      <c r="P267" s="62"/>
-      <c r="Q267" s="62"/>
-      <c r="R267" s="62"/>
-      <c r="S267" s="62"/>
-      <c r="T267" s="62"/>
-      <c r="U267" s="55"/>
+      <c r="H267" s="42"/>
+      <c r="I267" s="43"/>
+      <c r="J267" s="43"/>
+      <c r="K267" s="43"/>
+      <c r="L267" s="43"/>
+      <c r="M267" s="43"/>
+      <c r="N267" s="43"/>
+      <c r="O267" s="43"/>
+      <c r="P267" s="43"/>
+      <c r="Q267" s="43"/>
+      <c r="R267" s="43"/>
+      <c r="S267" s="43"/>
+      <c r="T267" s="43"/>
+      <c r="U267" s="44"/>
     </row>
     <row r="268" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="27"/>
@@ -31778,22 +31792,22 @@
       <c r="E268" s="28"/>
       <c r="F268" s="28"/>
       <c r="G268" s="28"/>
-      <c r="H268" s="54" t="s">
+      <c r="H268" s="42" t="s">
         <v>1092</v>
       </c>
-      <c r="I268" s="62"/>
-      <c r="J268" s="62"/>
-      <c r="K268" s="62"/>
-      <c r="L268" s="62"/>
-      <c r="M268" s="62"/>
-      <c r="N268" s="62"/>
-      <c r="O268" s="62"/>
-      <c r="P268" s="62"/>
-      <c r="Q268" s="62"/>
-      <c r="R268" s="62"/>
-      <c r="S268" s="62"/>
-      <c r="T268" s="62"/>
-      <c r="U268" s="55"/>
+      <c r="I268" s="43"/>
+      <c r="J268" s="43"/>
+      <c r="K268" s="43"/>
+      <c r="L268" s="43"/>
+      <c r="M268" s="43"/>
+      <c r="N268" s="43"/>
+      <c r="O268" s="43"/>
+      <c r="P268" s="43"/>
+      <c r="Q268" s="43"/>
+      <c r="R268" s="43"/>
+      <c r="S268" s="43"/>
+      <c r="T268" s="43"/>
+      <c r="U268" s="44"/>
     </row>
     <row r="269" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="27"/>
@@ -31809,20 +31823,20 @@
       <c r="E269" s="28"/>
       <c r="F269" s="28"/>
       <c r="G269" s="28"/>
-      <c r="H269" s="54"/>
-      <c r="I269" s="62"/>
-      <c r="J269" s="62"/>
-      <c r="K269" s="62"/>
-      <c r="L269" s="62"/>
-      <c r="M269" s="62"/>
-      <c r="N269" s="62"/>
-      <c r="O269" s="62"/>
-      <c r="P269" s="62"/>
-      <c r="Q269" s="62"/>
-      <c r="R269" s="62"/>
-      <c r="S269" s="62"/>
-      <c r="T269" s="62"/>
-      <c r="U269" s="55"/>
+      <c r="H269" s="42"/>
+      <c r="I269" s="43"/>
+      <c r="J269" s="43"/>
+      <c r="K269" s="43"/>
+      <c r="L269" s="43"/>
+      <c r="M269" s="43"/>
+      <c r="N269" s="43"/>
+      <c r="O269" s="43"/>
+      <c r="P269" s="43"/>
+      <c r="Q269" s="43"/>
+      <c r="R269" s="43"/>
+      <c r="S269" s="43"/>
+      <c r="T269" s="43"/>
+      <c r="U269" s="44"/>
     </row>
     <row r="270" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A270" s="27"/>
@@ -31836,20 +31850,20 @@
       <c r="E270" s="28"/>
       <c r="F270" s="28"/>
       <c r="G270" s="28"/>
-      <c r="H270" s="54"/>
-      <c r="I270" s="62"/>
-      <c r="J270" s="62"/>
-      <c r="K270" s="62"/>
-      <c r="L270" s="62"/>
-      <c r="M270" s="62"/>
-      <c r="N270" s="62"/>
-      <c r="O270" s="62"/>
-      <c r="P270" s="62"/>
-      <c r="Q270" s="62"/>
-      <c r="R270" s="62"/>
-      <c r="S270" s="62"/>
-      <c r="T270" s="62"/>
-      <c r="U270" s="55"/>
+      <c r="H270" s="42"/>
+      <c r="I270" s="43"/>
+      <c r="J270" s="43"/>
+      <c r="K270" s="43"/>
+      <c r="L270" s="43"/>
+      <c r="M270" s="43"/>
+      <c r="N270" s="43"/>
+      <c r="O270" s="43"/>
+      <c r="P270" s="43"/>
+      <c r="Q270" s="43"/>
+      <c r="R270" s="43"/>
+      <c r="S270" s="43"/>
+      <c r="T270" s="43"/>
+      <c r="U270" s="44"/>
     </row>
     <row r="271" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="27"/>
@@ -31863,20 +31877,20 @@
       <c r="E271" s="28"/>
       <c r="F271" s="28"/>
       <c r="G271" s="28"/>
-      <c r="H271" s="54"/>
-      <c r="I271" s="62"/>
-      <c r="J271" s="62"/>
-      <c r="K271" s="62"/>
-      <c r="L271" s="62"/>
-      <c r="M271" s="62"/>
-      <c r="N271" s="62"/>
-      <c r="O271" s="62"/>
-      <c r="P271" s="62"/>
-      <c r="Q271" s="62"/>
-      <c r="R271" s="62"/>
-      <c r="S271" s="62"/>
-      <c r="T271" s="62"/>
-      <c r="U271" s="55"/>
+      <c r="H271" s="42"/>
+      <c r="I271" s="43"/>
+      <c r="J271" s="43"/>
+      <c r="K271" s="43"/>
+      <c r="L271" s="43"/>
+      <c r="M271" s="43"/>
+      <c r="N271" s="43"/>
+      <c r="O271" s="43"/>
+      <c r="P271" s="43"/>
+      <c r="Q271" s="43"/>
+      <c r="R271" s="43"/>
+      <c r="S271" s="43"/>
+      <c r="T271" s="43"/>
+      <c r="U271" s="44"/>
     </row>
     <row r="272" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="27"/>
@@ -31890,34 +31904,60 @@
       <c r="E272" s="28"/>
       <c r="F272" s="28"/>
       <c r="G272" s="28"/>
-      <c r="H272" s="54"/>
-      <c r="I272" s="62"/>
-      <c r="J272" s="62"/>
-      <c r="K272" s="62"/>
-      <c r="L272" s="62"/>
-      <c r="M272" s="62"/>
-      <c r="N272" s="62"/>
-      <c r="O272" s="62"/>
-      <c r="P272" s="62"/>
-      <c r="Q272" s="62"/>
-      <c r="R272" s="62"/>
-      <c r="S272" s="62"/>
-      <c r="T272" s="62"/>
-      <c r="U272" s="55"/>
+      <c r="H272" s="42"/>
+      <c r="I272" s="43"/>
+      <c r="J272" s="43"/>
+      <c r="K272" s="43"/>
+      <c r="L272" s="43"/>
+      <c r="M272" s="43"/>
+      <c r="N272" s="43"/>
+      <c r="O272" s="43"/>
+      <c r="P272" s="43"/>
+      <c r="Q272" s="43"/>
+      <c r="R272" s="43"/>
+      <c r="S272" s="43"/>
+      <c r="T272" s="43"/>
+      <c r="U272" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:U3"/>
-    <mergeCell ref="A4:U4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="H271:U271"/>
+    <mergeCell ref="H272:U272"/>
+    <mergeCell ref="H265:U265"/>
+    <mergeCell ref="H266:U266"/>
+    <mergeCell ref="H267:U267"/>
+    <mergeCell ref="H268:U268"/>
+    <mergeCell ref="H269:U269"/>
+    <mergeCell ref="H270:U270"/>
+    <mergeCell ref="H264:U264"/>
+    <mergeCell ref="C248:I248"/>
+    <mergeCell ref="A254:U254"/>
+    <mergeCell ref="H255:U255"/>
+    <mergeCell ref="H256:U256"/>
+    <mergeCell ref="H257:U257"/>
+    <mergeCell ref="H258:U258"/>
+    <mergeCell ref="H259:U259"/>
+    <mergeCell ref="H260:U260"/>
+    <mergeCell ref="H261:U261"/>
+    <mergeCell ref="H262:U262"/>
+    <mergeCell ref="H263:U263"/>
+    <mergeCell ref="C203:I203"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C119:I119"/>
+    <mergeCell ref="C122:I122"/>
+    <mergeCell ref="C123:I123"/>
+    <mergeCell ref="C163:I163"/>
+    <mergeCell ref="C164:I164"/>
+    <mergeCell ref="C184:I184"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C20:I20"/>
     <mergeCell ref="C21:I21"/>
     <mergeCell ref="R6:R7"/>
     <mergeCell ref="S6:T6"/>
@@ -31934,43 +31974,17 @@
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="O6:O7"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="C203:I203"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C119:I119"/>
-    <mergeCell ref="C122:I122"/>
-    <mergeCell ref="C123:I123"/>
-    <mergeCell ref="C163:I163"/>
-    <mergeCell ref="C164:I164"/>
-    <mergeCell ref="C184:I184"/>
-    <mergeCell ref="H264:U264"/>
-    <mergeCell ref="C248:I248"/>
-    <mergeCell ref="A254:U254"/>
-    <mergeCell ref="H255:U255"/>
-    <mergeCell ref="H256:U256"/>
-    <mergeCell ref="H257:U257"/>
-    <mergeCell ref="H258:U258"/>
-    <mergeCell ref="H259:U259"/>
-    <mergeCell ref="H260:U260"/>
-    <mergeCell ref="H261:U261"/>
-    <mergeCell ref="H262:U262"/>
-    <mergeCell ref="H263:U263"/>
-    <mergeCell ref="H271:U271"/>
-    <mergeCell ref="H272:U272"/>
-    <mergeCell ref="H265:U265"/>
-    <mergeCell ref="H266:U266"/>
-    <mergeCell ref="H267:U267"/>
-    <mergeCell ref="H268:U268"/>
-    <mergeCell ref="H269:U269"/>
-    <mergeCell ref="H270:U270"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A3:U3"/>
+    <mergeCell ref="A4:U4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="G5:G7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/school_lublino/lublino_KP.xlsx
+++ b/school_lublino/lublino_KP.xlsx
@@ -3714,7 +3714,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3827,37 +3827,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3890,7 +3866,40 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3902,13 +3911,13 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4299,217 +4308,217 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="54"/>
-      <c r="P3" s="54"/>
-      <c r="Q3" s="54"/>
-      <c r="R3" s="54"/>
-      <c r="S3" s="54"/>
-      <c r="T3" s="54"/>
-      <c r="U3" s="54"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="46"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="46"/>
+      <c r="T3" s="46"/>
+      <c r="U3" s="46"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="55"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="55"/>
-      <c r="U4" s="55"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="47"/>
+      <c r="T4" s="47"/>
+      <c r="U4" s="47"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="51" t="s">
+      <c r="D5" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="51" t="s">
+      <c r="F5" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="51" t="s">
+      <c r="G5" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="51" t="s">
+      <c r="H5" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="51" t="s">
+      <c r="I5" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="56" t="s">
+      <c r="J5" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="58"/>
-      <c r="P5" s="59" t="s">
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="50"/>
+      <c r="P5" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="60"/>
-      <c r="R5" s="61"/>
-      <c r="S5" s="59" t="s">
+      <c r="Q5" s="52"/>
+      <c r="R5" s="53"/>
+      <c r="S5" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="60"/>
-      <c r="U5" s="61"/>
+      <c r="T5" s="52"/>
+      <c r="U5" s="53"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="62"/>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="42" t="s">
+      <c r="A6" s="55"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="44"/>
-      <c r="L6" s="51" t="s">
+      <c r="K6" s="58"/>
+      <c r="L6" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="42" t="s">
+      <c r="M6" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="44"/>
-      <c r="O6" s="51" t="s">
+      <c r="N6" s="58"/>
+      <c r="O6" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="42" t="s">
+      <c r="P6" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="51" t="s">
+      <c r="Q6" s="58"/>
+      <c r="R6" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="S6" s="42" t="s">
+      <c r="S6" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="44"/>
-      <c r="U6" s="51" t="s">
+      <c r="T6" s="58"/>
+      <c r="U6" s="54" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="52"/>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="A7" s="56"/>
+      <c r="B7" s="56"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
       <c r="J7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="52"/>
+      <c r="L7" s="56"/>
       <c r="M7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="52"/>
+      <c r="O7" s="56"/>
       <c r="P7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="52"/>
+      <c r="R7" s="56"/>
       <c r="S7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="U7" s="52"/>
+      <c r="U7" s="56"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="50"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="61"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -4551,15 +4560,15 @@
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="47"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="64"/>
       <c r="M9" s="6">
         <f>SUM(M10,M20)</f>
         <v>18303819.899999999</v>
@@ -4595,15 +4604,15 @@
       <c r="B10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="47"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="64"/>
       <c r="M10" s="6">
         <f t="shared" ref="M10:O14" si="0">SUM(M11)</f>
         <v>126283.29</v>
@@ -4639,15 +4648,15 @@
       <c r="B11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C11" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="47"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="64"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4683,15 +4692,15 @@
       <c r="B12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="C12" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="47"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="64"/>
       <c r="M12" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4727,15 +4736,15 @@
       <c r="B13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="47"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="64"/>
       <c r="M13" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4771,15 +4780,15 @@
       <c r="B14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="47"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="64"/>
       <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -5070,15 +5079,15 @@
       <c r="B20" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="45" t="s">
+      <c r="C20" s="62" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="47"/>
+      <c r="D20" s="63"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="64"/>
       <c r="M20" s="6">
         <f t="shared" ref="M20:O21" si="1">SUM(M21)</f>
         <v>18177536.609999999</v>
@@ -5114,15 +5123,15 @@
       <c r="B21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="45" t="s">
+      <c r="C21" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="47"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="63"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="63"/>
+      <c r="I21" s="64"/>
       <c r="M21" s="6">
         <f t="shared" si="1"/>
         <v>18177536.609999999</v>
@@ -5158,15 +5167,15 @@
       <c r="B22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="45" t="s">
+      <c r="C22" s="62" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="47"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="64"/>
       <c r="M22" s="6">
         <f>SUM(M23,M122,M163,M203,M248)</f>
         <v>18177536.609999999</v>
@@ -5202,15 +5211,15 @@
       <c r="B23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="45" t="s">
+      <c r="C23" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="47"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="64"/>
       <c r="M23" s="6">
         <f>SUM(M24,M67,M76,M119)</f>
         <v>12831032.07</v>
@@ -5246,15 +5255,15 @@
       <c r="B24" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="45" t="s">
+      <c r="C24" s="62" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="47"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="64"/>
       <c r="M24" s="6">
         <f>SUM(M25,M29,M31,M34,M36,M41,M46,M51,M57,M62)</f>
         <v>7808423.3099999996</v>
@@ -7478,15 +7487,15 @@
       <c r="B67" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="45" t="s">
+      <c r="C67" s="62" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="46"/>
-      <c r="E67" s="46"/>
-      <c r="F67" s="46"/>
-      <c r="G67" s="46"/>
-      <c r="H67" s="46"/>
-      <c r="I67" s="47"/>
+      <c r="D67" s="63"/>
+      <c r="E67" s="63"/>
+      <c r="F67" s="63"/>
+      <c r="G67" s="63"/>
+      <c r="H67" s="63"/>
+      <c r="I67" s="64"/>
       <c r="M67" s="6">
         <f>SUM(M68,M72,M74)</f>
         <v>748533.11</v>
@@ -7984,15 +7993,15 @@
       <c r="B76" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C76" s="45" t="s">
+      <c r="C76" s="62" t="s">
         <v>325</v>
       </c>
-      <c r="D76" s="46"/>
-      <c r="E76" s="46"/>
-      <c r="F76" s="46"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="46"/>
-      <c r="I76" s="47"/>
+      <c r="D76" s="63"/>
+      <c r="E76" s="63"/>
+      <c r="F76" s="63"/>
+      <c r="G76" s="63"/>
+      <c r="H76" s="63"/>
+      <c r="I76" s="64"/>
       <c r="M76" s="6">
         <f>SUM(M77,M82,M87,M93,M96,M99,M104,M109,M114,M117)</f>
         <v>3831185.6499999994</v>
@@ -10242,15 +10251,15 @@
       <c r="B119" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C119" s="45" t="s">
+      <c r="C119" s="62" t="s">
         <v>526</v>
       </c>
-      <c r="D119" s="46"/>
-      <c r="E119" s="46"/>
-      <c r="F119" s="46"/>
-      <c r="G119" s="46"/>
-      <c r="H119" s="46"/>
-      <c r="I119" s="47"/>
+      <c r="D119" s="63"/>
+      <c r="E119" s="63"/>
+      <c r="F119" s="63"/>
+      <c r="G119" s="63"/>
+      <c r="H119" s="63"/>
+      <c r="I119" s="64"/>
       <c r="M119" s="6">
         <f>SUM(M120)</f>
         <v>442890</v>
@@ -10412,15 +10421,15 @@
       <c r="B122" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="C122" s="45" t="s">
+      <c r="C122" s="62" t="s">
         <v>541</v>
       </c>
-      <c r="D122" s="46"/>
-      <c r="E122" s="46"/>
-      <c r="F122" s="46"/>
-      <c r="G122" s="46"/>
-      <c r="H122" s="46"/>
-      <c r="I122" s="47"/>
+      <c r="D122" s="63"/>
+      <c r="E122" s="63"/>
+      <c r="F122" s="63"/>
+      <c r="G122" s="63"/>
+      <c r="H122" s="63"/>
+      <c r="I122" s="64"/>
       <c r="M122" s="6">
         <f>SUM(M123)</f>
         <v>4016037.31</v>
@@ -10456,15 +10465,15 @@
       <c r="B123" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="C123" s="45" t="s">
+      <c r="C123" s="62" t="s">
         <v>544</v>
       </c>
-      <c r="D123" s="46"/>
-      <c r="E123" s="46"/>
-      <c r="F123" s="46"/>
-      <c r="G123" s="46"/>
-      <c r="H123" s="46"/>
-      <c r="I123" s="47"/>
+      <c r="D123" s="63"/>
+      <c r="E123" s="63"/>
+      <c r="F123" s="63"/>
+      <c r="G123" s="63"/>
+      <c r="H123" s="63"/>
+      <c r="I123" s="64"/>
       <c r="M123" s="6">
         <f>SUM(M124,M127,M131,M136,M140,M143,M148,M153,M158)</f>
         <v>4016037.31</v>
@@ -12545,15 +12554,15 @@
       <c r="B163" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C163" s="45" t="s">
+      <c r="C163" s="62" t="s">
         <v>710</v>
       </c>
-      <c r="D163" s="46"/>
-      <c r="E163" s="46"/>
-      <c r="F163" s="46"/>
-      <c r="G163" s="46"/>
-      <c r="H163" s="46"/>
-      <c r="I163" s="47"/>
+      <c r="D163" s="63"/>
+      <c r="E163" s="63"/>
+      <c r="F163" s="63"/>
+      <c r="G163" s="63"/>
+      <c r="H163" s="63"/>
+      <c r="I163" s="64"/>
       <c r="M163" s="6">
         <f>SUM(M164,M184)</f>
         <v>611422.71999999997</v>
@@ -12589,15 +12598,15 @@
       <c r="B164" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="C164" s="45" t="s">
+      <c r="C164" s="62" t="s">
         <v>713</v>
       </c>
-      <c r="D164" s="46"/>
-      <c r="E164" s="46"/>
-      <c r="F164" s="46"/>
-      <c r="G164" s="46"/>
-      <c r="H164" s="46"/>
-      <c r="I164" s="47"/>
+      <c r="D164" s="63"/>
+      <c r="E164" s="63"/>
+      <c r="F164" s="63"/>
+      <c r="G164" s="63"/>
+      <c r="H164" s="63"/>
+      <c r="I164" s="64"/>
       <c r="M164" s="6">
         <f>SUM(M165,M171,M174,M178,M182)</f>
         <v>415021.23999999993</v>
@@ -13644,15 +13653,15 @@
       <c r="B184" s="9" t="s">
         <v>789</v>
       </c>
-      <c r="C184" s="45" t="s">
+      <c r="C184" s="62" t="s">
         <v>790</v>
       </c>
-      <c r="D184" s="46"/>
-      <c r="E184" s="46"/>
-      <c r="F184" s="46"/>
-      <c r="G184" s="46"/>
-      <c r="H184" s="46"/>
-      <c r="I184" s="47"/>
+      <c r="D184" s="63"/>
+      <c r="E184" s="63"/>
+      <c r="F184" s="63"/>
+      <c r="G184" s="63"/>
+      <c r="H184" s="63"/>
+      <c r="I184" s="64"/>
       <c r="M184" s="6">
         <f>SUM(M185,M188,M191,M194,M197,M200)</f>
         <v>196401.48</v>
@@ -14702,15 +14711,15 @@
       <c r="B203" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="C203" s="45" t="s">
+      <c r="C203" s="62" t="s">
         <v>856</v>
       </c>
-      <c r="D203" s="46"/>
-      <c r="E203" s="46"/>
-      <c r="F203" s="46"/>
-      <c r="G203" s="46"/>
-      <c r="H203" s="46"/>
-      <c r="I203" s="47"/>
+      <c r="D203" s="63"/>
+      <c r="E203" s="63"/>
+      <c r="F203" s="63"/>
+      <c r="G203" s="63"/>
+      <c r="H203" s="63"/>
+      <c r="I203" s="64"/>
       <c r="M203" s="6">
         <f>SUM(M204,M206,M221,M236,M238,M240,M242,M243,M244,M245,M246,M247)</f>
         <v>719044.50999999989</v>
@@ -16440,7 +16449,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="239" spans="1:35" ht="393.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:35" ht="375" x14ac:dyDescent="0.25">
       <c r="A239" s="9" t="s">
         <v>1004</v>
       </c>
@@ -17092,15 +17101,15 @@
       <c r="B248" s="9" t="s">
         <v>1031</v>
       </c>
-      <c r="C248" s="45" t="s">
+      <c r="C248" s="62" t="s">
         <v>1032</v>
       </c>
-      <c r="D248" s="46"/>
-      <c r="E248" s="46"/>
-      <c r="F248" s="46"/>
-      <c r="G248" s="46"/>
-      <c r="H248" s="46"/>
-      <c r="I248" s="47"/>
+      <c r="D248" s="63"/>
+      <c r="E248" s="63"/>
+      <c r="F248" s="63"/>
+      <c r="G248" s="63"/>
+      <c r="H248" s="63"/>
+      <c r="I248" s="64"/>
       <c r="M248" s="6">
         <f>SUM(M249,M250,M251,M252)</f>
         <v>0</v>
@@ -17487,29 +17496,29 @@
       </c>
     </row>
     <row r="254" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="48" t="s">
+      <c r="A254" s="59" t="s">
         <v>1050</v>
       </c>
-      <c r="B254" s="49"/>
-      <c r="C254" s="49"/>
-      <c r="D254" s="49"/>
-      <c r="E254" s="49"/>
-      <c r="F254" s="49"/>
-      <c r="G254" s="49"/>
-      <c r="H254" s="49"/>
-      <c r="I254" s="49"/>
-      <c r="J254" s="49"/>
-      <c r="K254" s="49"/>
-      <c r="L254" s="49"/>
-      <c r="M254" s="49"/>
-      <c r="N254" s="49"/>
-      <c r="O254" s="49"/>
-      <c r="P254" s="49"/>
-      <c r="Q254" s="49"/>
-      <c r="R254" s="49"/>
-      <c r="S254" s="49"/>
-      <c r="T254" s="49"/>
-      <c r="U254" s="50"/>
+      <c r="B254" s="60"/>
+      <c r="C254" s="60"/>
+      <c r="D254" s="60"/>
+      <c r="E254" s="60"/>
+      <c r="F254" s="60"/>
+      <c r="G254" s="60"/>
+      <c r="H254" s="60"/>
+      <c r="I254" s="60"/>
+      <c r="J254" s="60"/>
+      <c r="K254" s="60"/>
+      <c r="L254" s="60"/>
+      <c r="M254" s="60"/>
+      <c r="N254" s="60"/>
+      <c r="O254" s="60"/>
+      <c r="P254" s="60"/>
+      <c r="Q254" s="60"/>
+      <c r="R254" s="60"/>
+      <c r="S254" s="60"/>
+      <c r="T254" s="60"/>
+      <c r="U254" s="61"/>
     </row>
     <row r="255" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="27"/>
@@ -17525,20 +17534,20 @@
       <c r="E255" s="28"/>
       <c r="F255" s="28"/>
       <c r="G255" s="28"/>
-      <c r="H255" s="42"/>
-      <c r="I255" s="43"/>
-      <c r="J255" s="43"/>
-      <c r="K255" s="43"/>
-      <c r="L255" s="43"/>
-      <c r="M255" s="43"/>
-      <c r="N255" s="43"/>
-      <c r="O255" s="43"/>
-      <c r="P255" s="43"/>
-      <c r="Q255" s="43"/>
-      <c r="R255" s="43"/>
-      <c r="S255" s="43"/>
-      <c r="T255" s="43"/>
-      <c r="U255" s="44"/>
+      <c r="H255" s="57"/>
+      <c r="I255" s="65"/>
+      <c r="J255" s="65"/>
+      <c r="K255" s="65"/>
+      <c r="L255" s="65"/>
+      <c r="M255" s="65"/>
+      <c r="N255" s="65"/>
+      <c r="O255" s="65"/>
+      <c r="P255" s="65"/>
+      <c r="Q255" s="65"/>
+      <c r="R255" s="65"/>
+      <c r="S255" s="65"/>
+      <c r="T255" s="65"/>
+      <c r="U255" s="58"/>
     </row>
     <row r="256" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="27"/>
@@ -17554,20 +17563,20 @@
       <c r="E256" s="28"/>
       <c r="F256" s="28"/>
       <c r="G256" s="28"/>
-      <c r="H256" s="42"/>
-      <c r="I256" s="43"/>
-      <c r="J256" s="43"/>
-      <c r="K256" s="43"/>
-      <c r="L256" s="43"/>
-      <c r="M256" s="43"/>
-      <c r="N256" s="43"/>
-      <c r="O256" s="43"/>
-      <c r="P256" s="43"/>
-      <c r="Q256" s="43"/>
-      <c r="R256" s="43"/>
-      <c r="S256" s="43"/>
-      <c r="T256" s="43"/>
-      <c r="U256" s="44"/>
+      <c r="H256" s="57"/>
+      <c r="I256" s="65"/>
+      <c r="J256" s="65"/>
+      <c r="K256" s="65"/>
+      <c r="L256" s="65"/>
+      <c r="M256" s="65"/>
+      <c r="N256" s="65"/>
+      <c r="O256" s="65"/>
+      <c r="P256" s="65"/>
+      <c r="Q256" s="65"/>
+      <c r="R256" s="65"/>
+      <c r="S256" s="65"/>
+      <c r="T256" s="65"/>
+      <c r="U256" s="58"/>
     </row>
     <row r="257" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A257" s="27"/>
@@ -17583,20 +17592,20 @@
       <c r="E257" s="28"/>
       <c r="F257" s="28"/>
       <c r="G257" s="28"/>
-      <c r="H257" s="42"/>
-      <c r="I257" s="43"/>
-      <c r="J257" s="43"/>
-      <c r="K257" s="43"/>
-      <c r="L257" s="43"/>
-      <c r="M257" s="43"/>
-      <c r="N257" s="43"/>
-      <c r="O257" s="43"/>
-      <c r="P257" s="43"/>
-      <c r="Q257" s="43"/>
-      <c r="R257" s="43"/>
-      <c r="S257" s="43"/>
-      <c r="T257" s="43"/>
-      <c r="U257" s="44"/>
+      <c r="H257" s="57"/>
+      <c r="I257" s="65"/>
+      <c r="J257" s="65"/>
+      <c r="K257" s="65"/>
+      <c r="L257" s="65"/>
+      <c r="M257" s="65"/>
+      <c r="N257" s="65"/>
+      <c r="O257" s="65"/>
+      <c r="P257" s="65"/>
+      <c r="Q257" s="65"/>
+      <c r="R257" s="65"/>
+      <c r="S257" s="65"/>
+      <c r="T257" s="65"/>
+      <c r="U257" s="58"/>
     </row>
     <row r="258" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="27"/>
@@ -17612,20 +17621,20 @@
       <c r="E258" s="28"/>
       <c r="F258" s="28"/>
       <c r="G258" s="28"/>
-      <c r="H258" s="42"/>
-      <c r="I258" s="43"/>
-      <c r="J258" s="43"/>
-      <c r="K258" s="43"/>
-      <c r="L258" s="43"/>
-      <c r="M258" s="43"/>
-      <c r="N258" s="43"/>
-      <c r="O258" s="43"/>
-      <c r="P258" s="43"/>
-      <c r="Q258" s="43"/>
-      <c r="R258" s="43"/>
-      <c r="S258" s="43"/>
-      <c r="T258" s="43"/>
-      <c r="U258" s="44"/>
+      <c r="H258" s="57"/>
+      <c r="I258" s="65"/>
+      <c r="J258" s="65"/>
+      <c r="K258" s="65"/>
+      <c r="L258" s="65"/>
+      <c r="M258" s="65"/>
+      <c r="N258" s="65"/>
+      <c r="O258" s="65"/>
+      <c r="P258" s="65"/>
+      <c r="Q258" s="65"/>
+      <c r="R258" s="65"/>
+      <c r="S258" s="65"/>
+      <c r="T258" s="65"/>
+      <c r="U258" s="58"/>
     </row>
     <row r="259" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="27"/>
@@ -17641,20 +17650,20 @@
       <c r="E259" s="28"/>
       <c r="F259" s="28"/>
       <c r="G259" s="28"/>
-      <c r="H259" s="42"/>
-      <c r="I259" s="43"/>
-      <c r="J259" s="43"/>
-      <c r="K259" s="43"/>
-      <c r="L259" s="43"/>
-      <c r="M259" s="43"/>
-      <c r="N259" s="43"/>
-      <c r="O259" s="43"/>
-      <c r="P259" s="43"/>
-      <c r="Q259" s="43"/>
-      <c r="R259" s="43"/>
-      <c r="S259" s="43"/>
-      <c r="T259" s="43"/>
-      <c r="U259" s="44"/>
+      <c r="H259" s="57"/>
+      <c r="I259" s="65"/>
+      <c r="J259" s="65"/>
+      <c r="K259" s="65"/>
+      <c r="L259" s="65"/>
+      <c r="M259" s="65"/>
+      <c r="N259" s="65"/>
+      <c r="O259" s="65"/>
+      <c r="P259" s="65"/>
+      <c r="Q259" s="65"/>
+      <c r="R259" s="65"/>
+      <c r="S259" s="65"/>
+      <c r="T259" s="65"/>
+      <c r="U259" s="58"/>
     </row>
     <row r="260" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A260" s="27"/>
@@ -17670,20 +17679,20 @@
       <c r="E260" s="28"/>
       <c r="F260" s="28"/>
       <c r="G260" s="28"/>
-      <c r="H260" s="42"/>
-      <c r="I260" s="43"/>
-      <c r="J260" s="43"/>
-      <c r="K260" s="43"/>
-      <c r="L260" s="43"/>
-      <c r="M260" s="43"/>
-      <c r="N260" s="43"/>
-      <c r="O260" s="43"/>
-      <c r="P260" s="43"/>
-      <c r="Q260" s="43"/>
-      <c r="R260" s="43"/>
-      <c r="S260" s="43"/>
-      <c r="T260" s="43"/>
-      <c r="U260" s="44"/>
+      <c r="H260" s="57"/>
+      <c r="I260" s="65"/>
+      <c r="J260" s="65"/>
+      <c r="K260" s="65"/>
+      <c r="L260" s="65"/>
+      <c r="M260" s="65"/>
+      <c r="N260" s="65"/>
+      <c r="O260" s="65"/>
+      <c r="P260" s="65"/>
+      <c r="Q260" s="65"/>
+      <c r="R260" s="65"/>
+      <c r="S260" s="65"/>
+      <c r="T260" s="65"/>
+      <c r="U260" s="58"/>
     </row>
     <row r="261" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A261" s="27"/>
@@ -17699,20 +17708,20 @@
       <c r="E261" s="28"/>
       <c r="F261" s="28"/>
       <c r="G261" s="28"/>
-      <c r="H261" s="42"/>
-      <c r="I261" s="43"/>
-      <c r="J261" s="43"/>
-      <c r="K261" s="43"/>
-      <c r="L261" s="43"/>
-      <c r="M261" s="43"/>
-      <c r="N261" s="43"/>
-      <c r="O261" s="43"/>
-      <c r="P261" s="43"/>
-      <c r="Q261" s="43"/>
-      <c r="R261" s="43"/>
-      <c r="S261" s="43"/>
-      <c r="T261" s="43"/>
-      <c r="U261" s="44"/>
+      <c r="H261" s="57"/>
+      <c r="I261" s="65"/>
+      <c r="J261" s="65"/>
+      <c r="K261" s="65"/>
+      <c r="L261" s="65"/>
+      <c r="M261" s="65"/>
+      <c r="N261" s="65"/>
+      <c r="O261" s="65"/>
+      <c r="P261" s="65"/>
+      <c r="Q261" s="65"/>
+      <c r="R261" s="65"/>
+      <c r="S261" s="65"/>
+      <c r="T261" s="65"/>
+      <c r="U261" s="58"/>
     </row>
     <row r="262" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="27"/>
@@ -17728,20 +17737,20 @@
       <c r="E262" s="28"/>
       <c r="F262" s="28"/>
       <c r="G262" s="28"/>
-      <c r="H262" s="42"/>
-      <c r="I262" s="43"/>
-      <c r="J262" s="43"/>
-      <c r="K262" s="43"/>
-      <c r="L262" s="43"/>
-      <c r="M262" s="43"/>
-      <c r="N262" s="43"/>
-      <c r="O262" s="43"/>
-      <c r="P262" s="43"/>
-      <c r="Q262" s="43"/>
-      <c r="R262" s="43"/>
-      <c r="S262" s="43"/>
-      <c r="T262" s="43"/>
-      <c r="U262" s="44"/>
+      <c r="H262" s="57"/>
+      <c r="I262" s="65"/>
+      <c r="J262" s="65"/>
+      <c r="K262" s="65"/>
+      <c r="L262" s="65"/>
+      <c r="M262" s="65"/>
+      <c r="N262" s="65"/>
+      <c r="O262" s="65"/>
+      <c r="P262" s="65"/>
+      <c r="Q262" s="65"/>
+      <c r="R262" s="65"/>
+      <c r="S262" s="65"/>
+      <c r="T262" s="65"/>
+      <c r="U262" s="58"/>
     </row>
     <row r="263" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="27"/>
@@ -17757,20 +17766,20 @@
       <c r="E263" s="28"/>
       <c r="F263" s="28"/>
       <c r="G263" s="28"/>
-      <c r="H263" s="42"/>
-      <c r="I263" s="43"/>
-      <c r="J263" s="43"/>
-      <c r="K263" s="43"/>
-      <c r="L263" s="43"/>
-      <c r="M263" s="43"/>
-      <c r="N263" s="43"/>
-      <c r="O263" s="43"/>
-      <c r="P263" s="43"/>
-      <c r="Q263" s="43"/>
-      <c r="R263" s="43"/>
-      <c r="S263" s="43"/>
-      <c r="T263" s="43"/>
-      <c r="U263" s="44"/>
+      <c r="H263" s="57"/>
+      <c r="I263" s="65"/>
+      <c r="J263" s="65"/>
+      <c r="K263" s="65"/>
+      <c r="L263" s="65"/>
+      <c r="M263" s="65"/>
+      <c r="N263" s="65"/>
+      <c r="O263" s="65"/>
+      <c r="P263" s="65"/>
+      <c r="Q263" s="65"/>
+      <c r="R263" s="65"/>
+      <c r="S263" s="65"/>
+      <c r="T263" s="65"/>
+      <c r="U263" s="58"/>
     </row>
     <row r="264" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A264" s="27"/>
@@ -17786,20 +17795,20 @@
       <c r="E264" s="28"/>
       <c r="F264" s="28"/>
       <c r="G264" s="28"/>
-      <c r="H264" s="42"/>
-      <c r="I264" s="43"/>
-      <c r="J264" s="43"/>
-      <c r="K264" s="43"/>
-      <c r="L264" s="43"/>
-      <c r="M264" s="43"/>
-      <c r="N264" s="43"/>
-      <c r="O264" s="43"/>
-      <c r="P264" s="43"/>
-      <c r="Q264" s="43"/>
-      <c r="R264" s="43"/>
-      <c r="S264" s="43"/>
-      <c r="T264" s="43"/>
-      <c r="U264" s="44"/>
+      <c r="H264" s="57"/>
+      <c r="I264" s="65"/>
+      <c r="J264" s="65"/>
+      <c r="K264" s="65"/>
+      <c r="L264" s="65"/>
+      <c r="M264" s="65"/>
+      <c r="N264" s="65"/>
+      <c r="O264" s="65"/>
+      <c r="P264" s="65"/>
+      <c r="Q264" s="65"/>
+      <c r="R264" s="65"/>
+      <c r="S264" s="65"/>
+      <c r="T264" s="65"/>
+      <c r="U264" s="58"/>
     </row>
     <row r="265" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A265" s="27"/>
@@ -17815,20 +17824,20 @@
       <c r="E265" s="28"/>
       <c r="F265" s="28"/>
       <c r="G265" s="28"/>
-      <c r="H265" s="42"/>
-      <c r="I265" s="43"/>
-      <c r="J265" s="43"/>
-      <c r="K265" s="43"/>
-      <c r="L265" s="43"/>
-      <c r="M265" s="43"/>
-      <c r="N265" s="43"/>
-      <c r="O265" s="43"/>
-      <c r="P265" s="43"/>
-      <c r="Q265" s="43"/>
-      <c r="R265" s="43"/>
-      <c r="S265" s="43"/>
-      <c r="T265" s="43"/>
-      <c r="U265" s="44"/>
+      <c r="H265" s="57"/>
+      <c r="I265" s="65"/>
+      <c r="J265" s="65"/>
+      <c r="K265" s="65"/>
+      <c r="L265" s="65"/>
+      <c r="M265" s="65"/>
+      <c r="N265" s="65"/>
+      <c r="O265" s="65"/>
+      <c r="P265" s="65"/>
+      <c r="Q265" s="65"/>
+      <c r="R265" s="65"/>
+      <c r="S265" s="65"/>
+      <c r="T265" s="65"/>
+      <c r="U265" s="58"/>
     </row>
     <row r="266" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A266" s="27"/>
@@ -17844,20 +17853,20 @@
       <c r="E266" s="28"/>
       <c r="F266" s="28"/>
       <c r="G266" s="28"/>
-      <c r="H266" s="42"/>
-      <c r="I266" s="43"/>
-      <c r="J266" s="43"/>
-      <c r="K266" s="43"/>
-      <c r="L266" s="43"/>
-      <c r="M266" s="43"/>
-      <c r="N266" s="43"/>
-      <c r="O266" s="43"/>
-      <c r="P266" s="43"/>
-      <c r="Q266" s="43"/>
-      <c r="R266" s="43"/>
-      <c r="S266" s="43"/>
-      <c r="T266" s="43"/>
-      <c r="U266" s="44"/>
+      <c r="H266" s="57"/>
+      <c r="I266" s="65"/>
+      <c r="J266" s="65"/>
+      <c r="K266" s="65"/>
+      <c r="L266" s="65"/>
+      <c r="M266" s="65"/>
+      <c r="N266" s="65"/>
+      <c r="O266" s="65"/>
+      <c r="P266" s="65"/>
+      <c r="Q266" s="65"/>
+      <c r="R266" s="65"/>
+      <c r="S266" s="65"/>
+      <c r="T266" s="65"/>
+      <c r="U266" s="58"/>
     </row>
     <row r="267" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="27"/>
@@ -17873,20 +17882,20 @@
       <c r="E267" s="28"/>
       <c r="F267" s="28"/>
       <c r="G267" s="28"/>
-      <c r="H267" s="42"/>
-      <c r="I267" s="43"/>
-      <c r="J267" s="43"/>
-      <c r="K267" s="43"/>
-      <c r="L267" s="43"/>
-      <c r="M267" s="43"/>
-      <c r="N267" s="43"/>
-      <c r="O267" s="43"/>
-      <c r="P267" s="43"/>
-      <c r="Q267" s="43"/>
-      <c r="R267" s="43"/>
-      <c r="S267" s="43"/>
-      <c r="T267" s="43"/>
-      <c r="U267" s="44"/>
+      <c r="H267" s="57"/>
+      <c r="I267" s="65"/>
+      <c r="J267" s="65"/>
+      <c r="K267" s="65"/>
+      <c r="L267" s="65"/>
+      <c r="M267" s="65"/>
+      <c r="N267" s="65"/>
+      <c r="O267" s="65"/>
+      <c r="P267" s="65"/>
+      <c r="Q267" s="65"/>
+      <c r="R267" s="65"/>
+      <c r="S267" s="65"/>
+      <c r="T267" s="65"/>
+      <c r="U267" s="58"/>
     </row>
     <row r="268" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="27"/>
@@ -17902,22 +17911,22 @@
       <c r="E268" s="28"/>
       <c r="F268" s="28"/>
       <c r="G268" s="28"/>
-      <c r="H268" s="42" t="s">
+      <c r="H268" s="57" t="s">
         <v>1092</v>
       </c>
-      <c r="I268" s="43"/>
-      <c r="J268" s="43"/>
-      <c r="K268" s="43"/>
-      <c r="L268" s="43"/>
-      <c r="M268" s="43"/>
-      <c r="N268" s="43"/>
-      <c r="O268" s="43"/>
-      <c r="P268" s="43"/>
-      <c r="Q268" s="43"/>
-      <c r="R268" s="43"/>
-      <c r="S268" s="43"/>
-      <c r="T268" s="43"/>
-      <c r="U268" s="44"/>
+      <c r="I268" s="65"/>
+      <c r="J268" s="65"/>
+      <c r="K268" s="65"/>
+      <c r="L268" s="65"/>
+      <c r="M268" s="65"/>
+      <c r="N268" s="65"/>
+      <c r="O268" s="65"/>
+      <c r="P268" s="65"/>
+      <c r="Q268" s="65"/>
+      <c r="R268" s="65"/>
+      <c r="S268" s="65"/>
+      <c r="T268" s="65"/>
+      <c r="U268" s="58"/>
     </row>
     <row r="269" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="27"/>
@@ -17933,20 +17942,20 @@
       <c r="E269" s="28"/>
       <c r="F269" s="28"/>
       <c r="G269" s="28"/>
-      <c r="H269" s="42"/>
-      <c r="I269" s="43"/>
-      <c r="J269" s="43"/>
-      <c r="K269" s="43"/>
-      <c r="L269" s="43"/>
-      <c r="M269" s="43"/>
-      <c r="N269" s="43"/>
-      <c r="O269" s="43"/>
-      <c r="P269" s="43"/>
-      <c r="Q269" s="43"/>
-      <c r="R269" s="43"/>
-      <c r="S269" s="43"/>
-      <c r="T269" s="43"/>
-      <c r="U269" s="44"/>
+      <c r="H269" s="57"/>
+      <c r="I269" s="65"/>
+      <c r="J269" s="65"/>
+      <c r="K269" s="65"/>
+      <c r="L269" s="65"/>
+      <c r="M269" s="65"/>
+      <c r="N269" s="65"/>
+      <c r="O269" s="65"/>
+      <c r="P269" s="65"/>
+      <c r="Q269" s="65"/>
+      <c r="R269" s="65"/>
+      <c r="S269" s="65"/>
+      <c r="T269" s="65"/>
+      <c r="U269" s="58"/>
     </row>
     <row r="270" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A270" s="27"/>
@@ -17960,20 +17969,20 @@
       <c r="E270" s="28"/>
       <c r="F270" s="28"/>
       <c r="G270" s="28"/>
-      <c r="H270" s="42"/>
-      <c r="I270" s="43"/>
-      <c r="J270" s="43"/>
-      <c r="K270" s="43"/>
-      <c r="L270" s="43"/>
-      <c r="M270" s="43"/>
-      <c r="N270" s="43"/>
-      <c r="O270" s="43"/>
-      <c r="P270" s="43"/>
-      <c r="Q270" s="43"/>
-      <c r="R270" s="43"/>
-      <c r="S270" s="43"/>
-      <c r="T270" s="43"/>
-      <c r="U270" s="44"/>
+      <c r="H270" s="57"/>
+      <c r="I270" s="65"/>
+      <c r="J270" s="65"/>
+      <c r="K270" s="65"/>
+      <c r="L270" s="65"/>
+      <c r="M270" s="65"/>
+      <c r="N270" s="65"/>
+      <c r="O270" s="65"/>
+      <c r="P270" s="65"/>
+      <c r="Q270" s="65"/>
+      <c r="R270" s="65"/>
+      <c r="S270" s="65"/>
+      <c r="T270" s="65"/>
+      <c r="U270" s="58"/>
     </row>
     <row r="271" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="27"/>
@@ -17987,20 +17996,20 @@
       <c r="E271" s="28"/>
       <c r="F271" s="28"/>
       <c r="G271" s="28"/>
-      <c r="H271" s="42"/>
-      <c r="I271" s="43"/>
-      <c r="J271" s="43"/>
-      <c r="K271" s="43"/>
-      <c r="L271" s="43"/>
-      <c r="M271" s="43"/>
-      <c r="N271" s="43"/>
-      <c r="O271" s="43"/>
-      <c r="P271" s="43"/>
-      <c r="Q271" s="43"/>
-      <c r="R271" s="43"/>
-      <c r="S271" s="43"/>
-      <c r="T271" s="43"/>
-      <c r="U271" s="44"/>
+      <c r="H271" s="57"/>
+      <c r="I271" s="65"/>
+      <c r="J271" s="65"/>
+      <c r="K271" s="65"/>
+      <c r="L271" s="65"/>
+      <c r="M271" s="65"/>
+      <c r="N271" s="65"/>
+      <c r="O271" s="65"/>
+      <c r="P271" s="65"/>
+      <c r="Q271" s="65"/>
+      <c r="R271" s="65"/>
+      <c r="S271" s="65"/>
+      <c r="T271" s="65"/>
+      <c r="U271" s="58"/>
     </row>
     <row r="272" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="27"/>
@@ -18014,25 +18023,73 @@
       <c r="E272" s="28"/>
       <c r="F272" s="28"/>
       <c r="G272" s="28"/>
-      <c r="H272" s="42"/>
-      <c r="I272" s="43"/>
-      <c r="J272" s="43"/>
-      <c r="K272" s="43"/>
-      <c r="L272" s="43"/>
-      <c r="M272" s="43"/>
-      <c r="N272" s="43"/>
-      <c r="O272" s="43"/>
-      <c r="P272" s="43"/>
-      <c r="Q272" s="43"/>
-      <c r="R272" s="43"/>
-      <c r="S272" s="43"/>
-      <c r="T272" s="43"/>
-      <c r="U272" s="44"/>
+      <c r="H272" s="57"/>
+      <c r="I272" s="65"/>
+      <c r="J272" s="65"/>
+      <c r="K272" s="65"/>
+      <c r="L272" s="65"/>
+      <c r="M272" s="65"/>
+      <c r="N272" s="65"/>
+      <c r="O272" s="65"/>
+      <c r="P272" s="65"/>
+      <c r="Q272" s="65"/>
+      <c r="R272" s="65"/>
+      <c r="S272" s="65"/>
+      <c r="T272" s="65"/>
+      <c r="U272" s="58"/>
     </row>
   </sheetData>
   <sheetProtection password="C644" sheet="1" formatColumns="0" autoFilter="0"/>
   <autoFilter ref="A7:U7"/>
   <mergeCells count="64">
+    <mergeCell ref="H270:U270"/>
+    <mergeCell ref="H271:U271"/>
+    <mergeCell ref="H272:U272"/>
+    <mergeCell ref="H265:U265"/>
+    <mergeCell ref="H266:U266"/>
+    <mergeCell ref="H267:U267"/>
+    <mergeCell ref="H268:U268"/>
+    <mergeCell ref="H269:U269"/>
+    <mergeCell ref="H260:U260"/>
+    <mergeCell ref="H261:U261"/>
+    <mergeCell ref="H262:U262"/>
+    <mergeCell ref="H263:U263"/>
+    <mergeCell ref="H264:U264"/>
+    <mergeCell ref="H255:U255"/>
+    <mergeCell ref="H256:U256"/>
+    <mergeCell ref="H257:U257"/>
+    <mergeCell ref="H258:U258"/>
+    <mergeCell ref="H259:U259"/>
+    <mergeCell ref="C164:I164"/>
+    <mergeCell ref="C184:I184"/>
+    <mergeCell ref="C203:I203"/>
+    <mergeCell ref="C248:I248"/>
+    <mergeCell ref="A254:U254"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C119:I119"/>
+    <mergeCell ref="C122:I122"/>
+    <mergeCell ref="C123:I123"/>
+    <mergeCell ref="C163:I163"/>
+    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:R7"/>
     <mergeCell ref="A2:U2"/>
     <mergeCell ref="A3:U3"/>
     <mergeCell ref="A4:U4"/>
@@ -18049,54 +18106,6 @@
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="I5:I7"/>
     <mergeCell ref="J6:K6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:R7"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="C21:I21"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C119:I119"/>
-    <mergeCell ref="C122:I122"/>
-    <mergeCell ref="C123:I123"/>
-    <mergeCell ref="C163:I163"/>
-    <mergeCell ref="C164:I164"/>
-    <mergeCell ref="C184:I184"/>
-    <mergeCell ref="C203:I203"/>
-    <mergeCell ref="C248:I248"/>
-    <mergeCell ref="A254:U254"/>
-    <mergeCell ref="H255:U255"/>
-    <mergeCell ref="H256:U256"/>
-    <mergeCell ref="H257:U257"/>
-    <mergeCell ref="H258:U258"/>
-    <mergeCell ref="H259:U259"/>
-    <mergeCell ref="H260:U260"/>
-    <mergeCell ref="H261:U261"/>
-    <mergeCell ref="H262:U262"/>
-    <mergeCell ref="H263:U263"/>
-    <mergeCell ref="H264:U264"/>
-    <mergeCell ref="H270:U270"/>
-    <mergeCell ref="H271:U271"/>
-    <mergeCell ref="H272:U272"/>
-    <mergeCell ref="H265:U265"/>
-    <mergeCell ref="H266:U266"/>
-    <mergeCell ref="H267:U267"/>
-    <mergeCell ref="H268:U268"/>
-    <mergeCell ref="H269:U269"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18187,217 +18196,217 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="54"/>
-      <c r="P3" s="54"/>
-      <c r="Q3" s="54"/>
-      <c r="R3" s="54"/>
-      <c r="S3" s="54"/>
-      <c r="T3" s="54"/>
-      <c r="U3" s="54"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="46"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="46"/>
+      <c r="T3" s="46"/>
+      <c r="U3" s="46"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="55"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="55"/>
-      <c r="U4" s="55"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="47"/>
+      <c r="T4" s="47"/>
+      <c r="U4" s="47"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="51" t="s">
+      <c r="D5" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="51" t="s">
+      <c r="F5" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="51" t="s">
+      <c r="G5" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="51" t="s">
+      <c r="H5" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="51" t="s">
+      <c r="I5" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="56" t="s">
+      <c r="J5" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="58"/>
-      <c r="P5" s="59" t="s">
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="50"/>
+      <c r="P5" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="60"/>
-      <c r="R5" s="61"/>
-      <c r="S5" s="59" t="s">
+      <c r="Q5" s="52"/>
+      <c r="R5" s="53"/>
+      <c r="S5" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="60"/>
-      <c r="U5" s="61"/>
+      <c r="T5" s="52"/>
+      <c r="U5" s="53"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="62"/>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="42" t="s">
+      <c r="A6" s="55"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="44"/>
-      <c r="L6" s="51" t="s">
+      <c r="K6" s="58"/>
+      <c r="L6" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="42" t="s">
+      <c r="M6" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="44"/>
-      <c r="O6" s="51" t="s">
+      <c r="N6" s="58"/>
+      <c r="O6" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="42" t="s">
+      <c r="P6" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="51" t="s">
+      <c r="Q6" s="58"/>
+      <c r="R6" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="S6" s="42" t="s">
+      <c r="S6" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="44"/>
-      <c r="U6" s="51" t="s">
+      <c r="T6" s="58"/>
+      <c r="U6" s="54" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="52"/>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
+      <c r="A7" s="56"/>
+      <c r="B7" s="56"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
       <c r="J7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="52"/>
+      <c r="L7" s="56"/>
       <c r="M7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="52"/>
+      <c r="O7" s="56"/>
       <c r="P7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="52"/>
+      <c r="R7" s="56"/>
       <c r="S7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="U7" s="52"/>
+      <c r="U7" s="56"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="50"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="61"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -18439,15 +18448,15 @@
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="47"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="64"/>
       <c r="M9" s="6">
         <f>SUM(M10,M20)</f>
         <v>18303819.899999999</v>
@@ -18483,15 +18492,15 @@
       <c r="B10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="47"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="64"/>
       <c r="M10" s="6">
         <f t="shared" ref="M10:O14" si="0">SUM(M11)</f>
         <v>126283.29</v>
@@ -18527,15 +18536,15 @@
       <c r="B11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C11" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="47"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="64"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18571,15 +18580,15 @@
       <c r="B12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="C12" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="47"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="64"/>
       <c r="M12" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18615,15 +18624,15 @@
       <c r="B13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="47"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="64"/>
       <c r="M13" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18659,15 +18668,15 @@
       <c r="B14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="47"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="64"/>
       <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18958,15 +18967,15 @@
       <c r="B20" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="45" t="s">
+      <c r="C20" s="62" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="47"/>
+      <c r="D20" s="63"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="64"/>
       <c r="M20" s="6">
         <f t="shared" ref="M20:O21" si="1">SUM(M21)</f>
         <v>18177536.609999999</v>
@@ -19002,15 +19011,15 @@
       <c r="B21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="45" t="s">
+      <c r="C21" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="47"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="63"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="63"/>
+      <c r="I21" s="64"/>
       <c r="M21" s="6">
         <f t="shared" si="1"/>
         <v>18177536.609999999</v>
@@ -19046,15 +19055,15 @@
       <c r="B22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="45" t="s">
+      <c r="C22" s="62" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="47"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="64"/>
       <c r="M22" s="6">
         <f>SUM(M23,M122,M163,M203,M248)</f>
         <v>18177536.609999999</v>
@@ -19090,15 +19099,15 @@
       <c r="B23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="45" t="s">
+      <c r="C23" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="47"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="64"/>
       <c r="M23" s="6">
         <f>SUM(M24,M67,M76,M119)</f>
         <v>12831032.07</v>
@@ -19134,15 +19143,15 @@
       <c r="B24" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="45" t="s">
+      <c r="C24" s="62" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="47"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="64"/>
       <c r="M24" s="6">
         <f>SUM(M25,M29,M31,M34,M36,M41,M46,M51,M57,M62)</f>
         <v>7808423.3099999996</v>
@@ -21366,15 +21375,15 @@
       <c r="B67" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="45" t="s">
+      <c r="C67" s="62" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="46"/>
-      <c r="E67" s="46"/>
-      <c r="F67" s="46"/>
-      <c r="G67" s="46"/>
-      <c r="H67" s="46"/>
-      <c r="I67" s="47"/>
+      <c r="D67" s="63"/>
+      <c r="E67" s="63"/>
+      <c r="F67" s="63"/>
+      <c r="G67" s="63"/>
+      <c r="H67" s="63"/>
+      <c r="I67" s="64"/>
       <c r="M67" s="6">
         <f>SUM(M68,M72,M74)</f>
         <v>748533.11</v>
@@ -21872,15 +21881,15 @@
       <c r="B76" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C76" s="45" t="s">
+      <c r="C76" s="62" t="s">
         <v>325</v>
       </c>
-      <c r="D76" s="46"/>
-      <c r="E76" s="46"/>
-      <c r="F76" s="46"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="46"/>
-      <c r="I76" s="47"/>
+      <c r="D76" s="63"/>
+      <c r="E76" s="63"/>
+      <c r="F76" s="63"/>
+      <c r="G76" s="63"/>
+      <c r="H76" s="63"/>
+      <c r="I76" s="64"/>
       <c r="M76" s="6">
         <f>SUM(M77,M82,M87,M93,M96,M99,M104,M109,M114,M117)</f>
         <v>3831185.6499999994</v>
@@ -24130,15 +24139,15 @@
       <c r="B119" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C119" s="45" t="s">
+      <c r="C119" s="62" t="s">
         <v>526</v>
       </c>
-      <c r="D119" s="46"/>
-      <c r="E119" s="46"/>
-      <c r="F119" s="46"/>
-      <c r="G119" s="46"/>
-      <c r="H119" s="46"/>
-      <c r="I119" s="47"/>
+      <c r="D119" s="63"/>
+      <c r="E119" s="63"/>
+      <c r="F119" s="63"/>
+      <c r="G119" s="63"/>
+      <c r="H119" s="63"/>
+      <c r="I119" s="64"/>
       <c r="M119" s="6">
         <f>SUM(M120)</f>
         <v>442890</v>
@@ -24300,15 +24309,15 @@
       <c r="B122" s="29" t="s">
         <v>540</v>
       </c>
-      <c r="C122" s="63" t="s">
+      <c r="C122" s="66" t="s">
         <v>541</v>
       </c>
-      <c r="D122" s="64"/>
-      <c r="E122" s="64"/>
-      <c r="F122" s="64"/>
-      <c r="G122" s="64"/>
-      <c r="H122" s="64"/>
-      <c r="I122" s="65"/>
+      <c r="D122" s="67"/>
+      <c r="E122" s="67"/>
+      <c r="F122" s="67"/>
+      <c r="G122" s="67"/>
+      <c r="H122" s="67"/>
+      <c r="I122" s="68"/>
       <c r="J122" s="30"/>
       <c r="M122" s="6">
         <f>SUM(M123)</f>
@@ -24345,15 +24354,15 @@
       <c r="B123" s="29" t="s">
         <v>543</v>
       </c>
-      <c r="C123" s="63" t="s">
+      <c r="C123" s="66" t="s">
         <v>544</v>
       </c>
-      <c r="D123" s="64"/>
-      <c r="E123" s="64"/>
-      <c r="F123" s="64"/>
-      <c r="G123" s="64"/>
-      <c r="H123" s="64"/>
-      <c r="I123" s="65"/>
+      <c r="D123" s="67"/>
+      <c r="E123" s="67"/>
+      <c r="F123" s="67"/>
+      <c r="G123" s="67"/>
+      <c r="H123" s="67"/>
+      <c r="I123" s="68"/>
       <c r="J123" s="30"/>
       <c r="M123" s="6">
         <f>SUM(M124,M127,M131,M136,M140,M143,M148,M153,M158)</f>
@@ -24390,7 +24399,7 @@
       <c r="B124" s="9" t="s">
         <v>546</v>
       </c>
-      <c r="C124" s="10" t="s">
+      <c r="C124" s="39" t="s">
         <v>547</v>
       </c>
       <c r="D124" s="11"/>
@@ -24467,7 +24476,7 @@
         <v>550</v>
       </c>
       <c r="B125" s="9"/>
-      <c r="C125" s="20" t="s">
+      <c r="C125" s="40" t="s">
         <v>551</v>
       </c>
       <c r="D125" s="11"/>
@@ -25405,7 +25414,7 @@
       <c r="D143" s="33" t="s">
         <v>641</v>
       </c>
-      <c r="E143" s="33" t="s">
+      <c r="E143" s="70" t="s">
         <v>642</v>
       </c>
       <c r="F143" s="33" t="s">
@@ -25664,7 +25673,7 @@
       <c r="D148" s="11" t="s">
         <v>641</v>
       </c>
-      <c r="E148" s="11" t="s">
+      <c r="E148" s="71" t="s">
         <v>666</v>
       </c>
       <c r="F148" s="11" t="s">
@@ -25883,7 +25892,10 @@
       <c r="G152" s="17">
         <v>1.3</v>
       </c>
-      <c r="H152" s="22"/>
+      <c r="H152" s="22">
+        <f>I152/I148/G152</f>
+        <v>23.076916276191319</v>
+      </c>
       <c r="I152" s="22">
         <v>6786.598</v>
       </c>
@@ -25923,7 +25935,7 @@
       <c r="D153" s="11" t="s">
         <v>641</v>
       </c>
-      <c r="E153" s="11" t="s">
+      <c r="E153" s="71" t="s">
         <v>680</v>
       </c>
       <c r="F153" s="11" t="s">
@@ -26011,7 +26023,10 @@
       <c r="G154" s="17">
         <v>1.3</v>
       </c>
-      <c r="H154" s="22"/>
+      <c r="H154" s="22">
+        <f>I154/I153/G154</f>
+        <v>23.076921686311376</v>
+      </c>
       <c r="I154" s="22">
         <v>33189.597999999998</v>
       </c>
@@ -26182,7 +26197,7 @@
       <c r="D158" s="37" t="s">
         <v>641</v>
       </c>
-      <c r="E158" s="37" t="s">
+      <c r="E158" s="69" t="s">
         <v>694</v>
       </c>
       <c r="F158" s="37" t="s">
@@ -26401,7 +26416,10 @@
       <c r="G162" s="17">
         <v>1.3</v>
       </c>
-      <c r="H162" s="22"/>
+      <c r="H162" s="22">
+        <f>I162/I158/G162</f>
+        <v>23.076923554010534</v>
+      </c>
       <c r="I162" s="22">
         <v>193481.704</v>
       </c>
@@ -26435,15 +26453,15 @@
       <c r="B163" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C163" s="45" t="s">
+      <c r="C163" s="62" t="s">
         <v>710</v>
       </c>
-      <c r="D163" s="46"/>
-      <c r="E163" s="46"/>
-      <c r="F163" s="46"/>
-      <c r="G163" s="46"/>
-      <c r="H163" s="46"/>
-      <c r="I163" s="47"/>
+      <c r="D163" s="63"/>
+      <c r="E163" s="63"/>
+      <c r="F163" s="63"/>
+      <c r="G163" s="63"/>
+      <c r="H163" s="63"/>
+      <c r="I163" s="64"/>
       <c r="M163" s="6">
         <f>SUM(M164,M184)</f>
         <v>611422.71999999997</v>
@@ -26479,15 +26497,15 @@
       <c r="B164" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="C164" s="45" t="s">
+      <c r="C164" s="62" t="s">
         <v>713</v>
       </c>
-      <c r="D164" s="46"/>
-      <c r="E164" s="46"/>
-      <c r="F164" s="46"/>
-      <c r="G164" s="46"/>
-      <c r="H164" s="46"/>
-      <c r="I164" s="47"/>
+      <c r="D164" s="63"/>
+      <c r="E164" s="63"/>
+      <c r="F164" s="63"/>
+      <c r="G164" s="63"/>
+      <c r="H164" s="63"/>
+      <c r="I164" s="64"/>
       <c r="M164" s="6">
         <f>SUM(M165,M171,M174,M178,M182)</f>
         <v>415021.23999999993</v>
@@ -26823,21 +26841,21 @@
       <c r="B171" s="29" t="s">
         <v>744</v>
       </c>
-      <c r="C171" s="66" t="s">
+      <c r="C171" s="42" t="s">
         <v>745</v>
       </c>
-      <c r="D171" s="67"/>
-      <c r="E171" s="67" t="s">
+      <c r="D171" s="43"/>
+      <c r="E171" s="43" t="s">
         <v>746</v>
       </c>
-      <c r="F171" s="67" t="s">
+      <c r="F171" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="G171" s="68">
+      <c r="G171" s="44">
         <v>1</v>
       </c>
-      <c r="H171" s="68"/>
-      <c r="I171" s="68">
+      <c r="H171" s="44"/>
+      <c r="I171" s="44">
         <v>3246.61</v>
       </c>
       <c r="J171" s="13">
@@ -27534,15 +27552,15 @@
       <c r="B184" s="9" t="s">
         <v>789</v>
       </c>
-      <c r="C184" s="45" t="s">
+      <c r="C184" s="62" t="s">
         <v>790</v>
       </c>
-      <c r="D184" s="46"/>
-      <c r="E184" s="46"/>
-      <c r="F184" s="46"/>
-      <c r="G184" s="46"/>
-      <c r="H184" s="46"/>
-      <c r="I184" s="47"/>
+      <c r="D184" s="63"/>
+      <c r="E184" s="63"/>
+      <c r="F184" s="63"/>
+      <c r="G184" s="63"/>
+      <c r="H184" s="63"/>
+      <c r="I184" s="64"/>
       <c r="M184" s="6">
         <f>SUM(M185,M188,M191,M194,M197,M200)</f>
         <v>196401.48</v>
@@ -28592,15 +28610,15 @@
       <c r="B203" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="C203" s="45" t="s">
+      <c r="C203" s="62" t="s">
         <v>856</v>
       </c>
-      <c r="D203" s="46"/>
-      <c r="E203" s="46"/>
-      <c r="F203" s="46"/>
-      <c r="G203" s="46"/>
-      <c r="H203" s="46"/>
-      <c r="I203" s="47"/>
+      <c r="D203" s="63"/>
+      <c r="E203" s="63"/>
+      <c r="F203" s="63"/>
+      <c r="G203" s="63"/>
+      <c r="H203" s="63"/>
+      <c r="I203" s="64"/>
       <c r="M203" s="6">
         <f>SUM(M204,M206,M221,M236,M238,M240,M242,M243,M244,M245,M246,M247)</f>
         <v>719044.50999999989</v>
@@ -30982,15 +31000,15 @@
       <c r="B248" s="9" t="s">
         <v>1031</v>
       </c>
-      <c r="C248" s="45" t="s">
+      <c r="C248" s="62" t="s">
         <v>1032</v>
       </c>
-      <c r="D248" s="46"/>
-      <c r="E248" s="46"/>
-      <c r="F248" s="46"/>
-      <c r="G248" s="46"/>
-      <c r="H248" s="46"/>
-      <c r="I248" s="47"/>
+      <c r="D248" s="63"/>
+      <c r="E248" s="63"/>
+      <c r="F248" s="63"/>
+      <c r="G248" s="63"/>
+      <c r="H248" s="63"/>
+      <c r="I248" s="64"/>
       <c r="M248" s="6">
         <f>SUM(M249,M250,M251,M252)</f>
         <v>0</v>
@@ -31377,29 +31395,29 @@
       </c>
     </row>
     <row r="254" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="48" t="s">
+      <c r="A254" s="59" t="s">
         <v>1050</v>
       </c>
-      <c r="B254" s="49"/>
-      <c r="C254" s="49"/>
-      <c r="D254" s="49"/>
-      <c r="E254" s="49"/>
-      <c r="F254" s="49"/>
-      <c r="G254" s="49"/>
-      <c r="H254" s="49"/>
-      <c r="I254" s="49"/>
-      <c r="J254" s="49"/>
-      <c r="K254" s="49"/>
-      <c r="L254" s="49"/>
-      <c r="M254" s="49"/>
-      <c r="N254" s="49"/>
-      <c r="O254" s="49"/>
-      <c r="P254" s="49"/>
-      <c r="Q254" s="49"/>
-      <c r="R254" s="49"/>
-      <c r="S254" s="49"/>
-      <c r="T254" s="49"/>
-      <c r="U254" s="50"/>
+      <c r="B254" s="60"/>
+      <c r="C254" s="60"/>
+      <c r="D254" s="60"/>
+      <c r="E254" s="60"/>
+      <c r="F254" s="60"/>
+      <c r="G254" s="60"/>
+      <c r="H254" s="60"/>
+      <c r="I254" s="60"/>
+      <c r="J254" s="60"/>
+      <c r="K254" s="60"/>
+      <c r="L254" s="60"/>
+      <c r="M254" s="60"/>
+      <c r="N254" s="60"/>
+      <c r="O254" s="60"/>
+      <c r="P254" s="60"/>
+      <c r="Q254" s="60"/>
+      <c r="R254" s="60"/>
+      <c r="S254" s="60"/>
+      <c r="T254" s="60"/>
+      <c r="U254" s="61"/>
     </row>
     <row r="255" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="27"/>
@@ -31415,20 +31433,20 @@
       <c r="E255" s="28"/>
       <c r="F255" s="28"/>
       <c r="G255" s="28"/>
-      <c r="H255" s="42"/>
-      <c r="I255" s="43"/>
-      <c r="J255" s="43"/>
-      <c r="K255" s="43"/>
-      <c r="L255" s="43"/>
-      <c r="M255" s="43"/>
-      <c r="N255" s="43"/>
-      <c r="O255" s="43"/>
-      <c r="P255" s="43"/>
-      <c r="Q255" s="43"/>
-      <c r="R255" s="43"/>
-      <c r="S255" s="43"/>
-      <c r="T255" s="43"/>
-      <c r="U255" s="44"/>
+      <c r="H255" s="57"/>
+      <c r="I255" s="65"/>
+      <c r="J255" s="65"/>
+      <c r="K255" s="65"/>
+      <c r="L255" s="65"/>
+      <c r="M255" s="65"/>
+      <c r="N255" s="65"/>
+      <c r="O255" s="65"/>
+      <c r="P255" s="65"/>
+      <c r="Q255" s="65"/>
+      <c r="R255" s="65"/>
+      <c r="S255" s="65"/>
+      <c r="T255" s="65"/>
+      <c r="U255" s="58"/>
     </row>
     <row r="256" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="27"/>
@@ -31444,20 +31462,20 @@
       <c r="E256" s="28"/>
       <c r="F256" s="28"/>
       <c r="G256" s="28"/>
-      <c r="H256" s="42"/>
-      <c r="I256" s="43"/>
-      <c r="J256" s="43"/>
-      <c r="K256" s="43"/>
-      <c r="L256" s="43"/>
-      <c r="M256" s="43"/>
-      <c r="N256" s="43"/>
-      <c r="O256" s="43"/>
-      <c r="P256" s="43"/>
-      <c r="Q256" s="43"/>
-      <c r="R256" s="43"/>
-      <c r="S256" s="43"/>
-      <c r="T256" s="43"/>
-      <c r="U256" s="44"/>
+      <c r="H256" s="57"/>
+      <c r="I256" s="65"/>
+      <c r="J256" s="65"/>
+      <c r="K256" s="65"/>
+      <c r="L256" s="65"/>
+      <c r="M256" s="65"/>
+      <c r="N256" s="65"/>
+      <c r="O256" s="65"/>
+      <c r="P256" s="65"/>
+      <c r="Q256" s="65"/>
+      <c r="R256" s="65"/>
+      <c r="S256" s="65"/>
+      <c r="T256" s="65"/>
+      <c r="U256" s="58"/>
     </row>
     <row r="257" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A257" s="27"/>
@@ -31473,20 +31491,20 @@
       <c r="E257" s="28"/>
       <c r="F257" s="28"/>
       <c r="G257" s="28"/>
-      <c r="H257" s="42"/>
-      <c r="I257" s="43"/>
-      <c r="J257" s="43"/>
-      <c r="K257" s="43"/>
-      <c r="L257" s="43"/>
-      <c r="M257" s="43"/>
-      <c r="N257" s="43"/>
-      <c r="O257" s="43"/>
-      <c r="P257" s="43"/>
-      <c r="Q257" s="43"/>
-      <c r="R257" s="43"/>
-      <c r="S257" s="43"/>
-      <c r="T257" s="43"/>
-      <c r="U257" s="44"/>
+      <c r="H257" s="57"/>
+      <c r="I257" s="65"/>
+      <c r="J257" s="65"/>
+      <c r="K257" s="65"/>
+      <c r="L257" s="65"/>
+      <c r="M257" s="65"/>
+      <c r="N257" s="65"/>
+      <c r="O257" s="65"/>
+      <c r="P257" s="65"/>
+      <c r="Q257" s="65"/>
+      <c r="R257" s="65"/>
+      <c r="S257" s="65"/>
+      <c r="T257" s="65"/>
+      <c r="U257" s="58"/>
     </row>
     <row r="258" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="27"/>
@@ -31502,20 +31520,20 @@
       <c r="E258" s="28"/>
       <c r="F258" s="28"/>
       <c r="G258" s="28"/>
-      <c r="H258" s="42"/>
-      <c r="I258" s="43"/>
-      <c r="J258" s="43"/>
-      <c r="K258" s="43"/>
-      <c r="L258" s="43"/>
-      <c r="M258" s="43"/>
-      <c r="N258" s="43"/>
-      <c r="O258" s="43"/>
-      <c r="P258" s="43"/>
-      <c r="Q258" s="43"/>
-      <c r="R258" s="43"/>
-      <c r="S258" s="43"/>
-      <c r="T258" s="43"/>
-      <c r="U258" s="44"/>
+      <c r="H258" s="57"/>
+      <c r="I258" s="65"/>
+      <c r="J258" s="65"/>
+      <c r="K258" s="65"/>
+      <c r="L258" s="65"/>
+      <c r="M258" s="65"/>
+      <c r="N258" s="65"/>
+      <c r="O258" s="65"/>
+      <c r="P258" s="65"/>
+      <c r="Q258" s="65"/>
+      <c r="R258" s="65"/>
+      <c r="S258" s="65"/>
+      <c r="T258" s="65"/>
+      <c r="U258" s="58"/>
     </row>
     <row r="259" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="27"/>
@@ -31531,20 +31549,20 @@
       <c r="E259" s="28"/>
       <c r="F259" s="28"/>
       <c r="G259" s="28"/>
-      <c r="H259" s="42"/>
-      <c r="I259" s="43"/>
-      <c r="J259" s="43"/>
-      <c r="K259" s="43"/>
-      <c r="L259" s="43"/>
-      <c r="M259" s="43"/>
-      <c r="N259" s="43"/>
-      <c r="O259" s="43"/>
-      <c r="P259" s="43"/>
-      <c r="Q259" s="43"/>
-      <c r="R259" s="43"/>
-      <c r="S259" s="43"/>
-      <c r="T259" s="43"/>
-      <c r="U259" s="44"/>
+      <c r="H259" s="57"/>
+      <c r="I259" s="65"/>
+      <c r="J259" s="65"/>
+      <c r="K259" s="65"/>
+      <c r="L259" s="65"/>
+      <c r="M259" s="65"/>
+      <c r="N259" s="65"/>
+      <c r="O259" s="65"/>
+      <c r="P259" s="65"/>
+      <c r="Q259" s="65"/>
+      <c r="R259" s="65"/>
+      <c r="S259" s="65"/>
+      <c r="T259" s="65"/>
+      <c r="U259" s="58"/>
     </row>
     <row r="260" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A260" s="27"/>
@@ -31560,20 +31578,20 @@
       <c r="E260" s="28"/>
       <c r="F260" s="28"/>
       <c r="G260" s="28"/>
-      <c r="H260" s="42"/>
-      <c r="I260" s="43"/>
-      <c r="J260" s="43"/>
-      <c r="K260" s="43"/>
-      <c r="L260" s="43"/>
-      <c r="M260" s="43"/>
-      <c r="N260" s="43"/>
-      <c r="O260" s="43"/>
-      <c r="P260" s="43"/>
-      <c r="Q260" s="43"/>
-      <c r="R260" s="43"/>
-      <c r="S260" s="43"/>
-      <c r="T260" s="43"/>
-      <c r="U260" s="44"/>
+      <c r="H260" s="57"/>
+      <c r="I260" s="65"/>
+      <c r="J260" s="65"/>
+      <c r="K260" s="65"/>
+      <c r="L260" s="65"/>
+      <c r="M260" s="65"/>
+      <c r="N260" s="65"/>
+      <c r="O260" s="65"/>
+      <c r="P260" s="65"/>
+      <c r="Q260" s="65"/>
+      <c r="R260" s="65"/>
+      <c r="S260" s="65"/>
+      <c r="T260" s="65"/>
+      <c r="U260" s="58"/>
     </row>
     <row r="261" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A261" s="27"/>
@@ -31589,20 +31607,20 @@
       <c r="E261" s="28"/>
       <c r="F261" s="28"/>
       <c r="G261" s="28"/>
-      <c r="H261" s="42"/>
-      <c r="I261" s="43"/>
-      <c r="J261" s="43"/>
-      <c r="K261" s="43"/>
-      <c r="L261" s="43"/>
-      <c r="M261" s="43"/>
-      <c r="N261" s="43"/>
-      <c r="O261" s="43"/>
-      <c r="P261" s="43"/>
-      <c r="Q261" s="43"/>
-      <c r="R261" s="43"/>
-      <c r="S261" s="43"/>
-      <c r="T261" s="43"/>
-      <c r="U261" s="44"/>
+      <c r="H261" s="57"/>
+      <c r="I261" s="65"/>
+      <c r="J261" s="65"/>
+      <c r="K261" s="65"/>
+      <c r="L261" s="65"/>
+      <c r="M261" s="65"/>
+      <c r="N261" s="65"/>
+      <c r="O261" s="65"/>
+      <c r="P261" s="65"/>
+      <c r="Q261" s="65"/>
+      <c r="R261" s="65"/>
+      <c r="S261" s="65"/>
+      <c r="T261" s="65"/>
+      <c r="U261" s="58"/>
     </row>
     <row r="262" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="27"/>
@@ -31618,20 +31636,20 @@
       <c r="E262" s="28"/>
       <c r="F262" s="28"/>
       <c r="G262" s="28"/>
-      <c r="H262" s="42"/>
-      <c r="I262" s="43"/>
-      <c r="J262" s="43"/>
-      <c r="K262" s="43"/>
-      <c r="L262" s="43"/>
-      <c r="M262" s="43"/>
-      <c r="N262" s="43"/>
-      <c r="O262" s="43"/>
-      <c r="P262" s="43"/>
-      <c r="Q262" s="43"/>
-      <c r="R262" s="43"/>
-      <c r="S262" s="43"/>
-      <c r="T262" s="43"/>
-      <c r="U262" s="44"/>
+      <c r="H262" s="57"/>
+      <c r="I262" s="65"/>
+      <c r="J262" s="65"/>
+      <c r="K262" s="65"/>
+      <c r="L262" s="65"/>
+      <c r="M262" s="65"/>
+      <c r="N262" s="65"/>
+      <c r="O262" s="65"/>
+      <c r="P262" s="65"/>
+      <c r="Q262" s="65"/>
+      <c r="R262" s="65"/>
+      <c r="S262" s="65"/>
+      <c r="T262" s="65"/>
+      <c r="U262" s="58"/>
     </row>
     <row r="263" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="27"/>
@@ -31647,20 +31665,20 @@
       <c r="E263" s="28"/>
       <c r="F263" s="28"/>
       <c r="G263" s="28"/>
-      <c r="H263" s="42"/>
-      <c r="I263" s="43"/>
-      <c r="J263" s="43"/>
-      <c r="K263" s="43"/>
-      <c r="L263" s="43"/>
-      <c r="M263" s="43"/>
-      <c r="N263" s="43"/>
-      <c r="O263" s="43"/>
-      <c r="P263" s="43"/>
-      <c r="Q263" s="43"/>
-      <c r="R263" s="43"/>
-      <c r="S263" s="43"/>
-      <c r="T263" s="43"/>
-      <c r="U263" s="44"/>
+      <c r="H263" s="57"/>
+      <c r="I263" s="65"/>
+      <c r="J263" s="65"/>
+      <c r="K263" s="65"/>
+      <c r="L263" s="65"/>
+      <c r="M263" s="65"/>
+      <c r="N263" s="65"/>
+      <c r="O263" s="65"/>
+      <c r="P263" s="65"/>
+      <c r="Q263" s="65"/>
+      <c r="R263" s="65"/>
+      <c r="S263" s="65"/>
+      <c r="T263" s="65"/>
+      <c r="U263" s="58"/>
     </row>
     <row r="264" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A264" s="27"/>
@@ -31676,20 +31694,20 @@
       <c r="E264" s="28"/>
       <c r="F264" s="28"/>
       <c r="G264" s="28"/>
-      <c r="H264" s="42"/>
-      <c r="I264" s="43"/>
-      <c r="J264" s="43"/>
-      <c r="K264" s="43"/>
-      <c r="L264" s="43"/>
-      <c r="M264" s="43"/>
-      <c r="N264" s="43"/>
-      <c r="O264" s="43"/>
-      <c r="P264" s="43"/>
-      <c r="Q264" s="43"/>
-      <c r="R264" s="43"/>
-      <c r="S264" s="43"/>
-      <c r="T264" s="43"/>
-      <c r="U264" s="44"/>
+      <c r="H264" s="57"/>
+      <c r="I264" s="65"/>
+      <c r="J264" s="65"/>
+      <c r="K264" s="65"/>
+      <c r="L264" s="65"/>
+      <c r="M264" s="65"/>
+      <c r="N264" s="65"/>
+      <c r="O264" s="65"/>
+      <c r="P264" s="65"/>
+      <c r="Q264" s="65"/>
+      <c r="R264" s="65"/>
+      <c r="S264" s="65"/>
+      <c r="T264" s="65"/>
+      <c r="U264" s="58"/>
     </row>
     <row r="265" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A265" s="27"/>
@@ -31705,20 +31723,20 @@
       <c r="E265" s="28"/>
       <c r="F265" s="28"/>
       <c r="G265" s="28"/>
-      <c r="H265" s="42"/>
-      <c r="I265" s="43"/>
-      <c r="J265" s="43"/>
-      <c r="K265" s="43"/>
-      <c r="L265" s="43"/>
-      <c r="M265" s="43"/>
-      <c r="N265" s="43"/>
-      <c r="O265" s="43"/>
-      <c r="P265" s="43"/>
-      <c r="Q265" s="43"/>
-      <c r="R265" s="43"/>
-      <c r="S265" s="43"/>
-      <c r="T265" s="43"/>
-      <c r="U265" s="44"/>
+      <c r="H265" s="57"/>
+      <c r="I265" s="65"/>
+      <c r="J265" s="65"/>
+      <c r="K265" s="65"/>
+      <c r="L265" s="65"/>
+      <c r="M265" s="65"/>
+      <c r="N265" s="65"/>
+      <c r="O265" s="65"/>
+      <c r="P265" s="65"/>
+      <c r="Q265" s="65"/>
+      <c r="R265" s="65"/>
+      <c r="S265" s="65"/>
+      <c r="T265" s="65"/>
+      <c r="U265" s="58"/>
     </row>
     <row r="266" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A266" s="27"/>
@@ -31734,20 +31752,20 @@
       <c r="E266" s="28"/>
       <c r="F266" s="28"/>
       <c r="G266" s="28"/>
-      <c r="H266" s="42"/>
-      <c r="I266" s="43"/>
-      <c r="J266" s="43"/>
-      <c r="K266" s="43"/>
-      <c r="L266" s="43"/>
-      <c r="M266" s="43"/>
-      <c r="N266" s="43"/>
-      <c r="O266" s="43"/>
-      <c r="P266" s="43"/>
-      <c r="Q266" s="43"/>
-      <c r="R266" s="43"/>
-      <c r="S266" s="43"/>
-      <c r="T266" s="43"/>
-      <c r="U266" s="44"/>
+      <c r="H266" s="57"/>
+      <c r="I266" s="65"/>
+      <c r="J266" s="65"/>
+      <c r="K266" s="65"/>
+      <c r="L266" s="65"/>
+      <c r="M266" s="65"/>
+      <c r="N266" s="65"/>
+      <c r="O266" s="65"/>
+      <c r="P266" s="65"/>
+      <c r="Q266" s="65"/>
+      <c r="R266" s="65"/>
+      <c r="S266" s="65"/>
+      <c r="T266" s="65"/>
+      <c r="U266" s="58"/>
     </row>
     <row r="267" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="27"/>
@@ -31763,20 +31781,20 @@
       <c r="E267" s="28"/>
       <c r="F267" s="28"/>
       <c r="G267" s="28"/>
-      <c r="H267" s="42"/>
-      <c r="I267" s="43"/>
-      <c r="J267" s="43"/>
-      <c r="K267" s="43"/>
-      <c r="L267" s="43"/>
-      <c r="M267" s="43"/>
-      <c r="N267" s="43"/>
-      <c r="O267" s="43"/>
-      <c r="P267" s="43"/>
-      <c r="Q267" s="43"/>
-      <c r="R267" s="43"/>
-      <c r="S267" s="43"/>
-      <c r="T267" s="43"/>
-      <c r="U267" s="44"/>
+      <c r="H267" s="57"/>
+      <c r="I267" s="65"/>
+      <c r="J267" s="65"/>
+      <c r="K267" s="65"/>
+      <c r="L267" s="65"/>
+      <c r="M267" s="65"/>
+      <c r="N267" s="65"/>
+      <c r="O267" s="65"/>
+      <c r="P267" s="65"/>
+      <c r="Q267" s="65"/>
+      <c r="R267" s="65"/>
+      <c r="S267" s="65"/>
+      <c r="T267" s="65"/>
+      <c r="U267" s="58"/>
     </row>
     <row r="268" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="27"/>
@@ -31792,22 +31810,22 @@
       <c r="E268" s="28"/>
       <c r="F268" s="28"/>
       <c r="G268" s="28"/>
-      <c r="H268" s="42" t="s">
+      <c r="H268" s="57" t="s">
         <v>1092</v>
       </c>
-      <c r="I268" s="43"/>
-      <c r="J268" s="43"/>
-      <c r="K268" s="43"/>
-      <c r="L268" s="43"/>
-      <c r="M268" s="43"/>
-      <c r="N268" s="43"/>
-      <c r="O268" s="43"/>
-      <c r="P268" s="43"/>
-      <c r="Q268" s="43"/>
-      <c r="R268" s="43"/>
-      <c r="S268" s="43"/>
-      <c r="T268" s="43"/>
-      <c r="U268" s="44"/>
+      <c r="I268" s="65"/>
+      <c r="J268" s="65"/>
+      <c r="K268" s="65"/>
+      <c r="L268" s="65"/>
+      <c r="M268" s="65"/>
+      <c r="N268" s="65"/>
+      <c r="O268" s="65"/>
+      <c r="P268" s="65"/>
+      <c r="Q268" s="65"/>
+      <c r="R268" s="65"/>
+      <c r="S268" s="65"/>
+      <c r="T268" s="65"/>
+      <c r="U268" s="58"/>
     </row>
     <row r="269" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="27"/>
@@ -31823,20 +31841,20 @@
       <c r="E269" s="28"/>
       <c r="F269" s="28"/>
       <c r="G269" s="28"/>
-      <c r="H269" s="42"/>
-      <c r="I269" s="43"/>
-      <c r="J269" s="43"/>
-      <c r="K269" s="43"/>
-      <c r="L269" s="43"/>
-      <c r="M269" s="43"/>
-      <c r="N269" s="43"/>
-      <c r="O269" s="43"/>
-      <c r="P269" s="43"/>
-      <c r="Q269" s="43"/>
-      <c r="R269" s="43"/>
-      <c r="S269" s="43"/>
-      <c r="T269" s="43"/>
-      <c r="U269" s="44"/>
+      <c r="H269" s="57"/>
+      <c r="I269" s="65"/>
+      <c r="J269" s="65"/>
+      <c r="K269" s="65"/>
+      <c r="L269" s="65"/>
+      <c r="M269" s="65"/>
+      <c r="N269" s="65"/>
+      <c r="O269" s="65"/>
+      <c r="P269" s="65"/>
+      <c r="Q269" s="65"/>
+      <c r="R269" s="65"/>
+      <c r="S269" s="65"/>
+      <c r="T269" s="65"/>
+      <c r="U269" s="58"/>
     </row>
     <row r="270" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A270" s="27"/>
@@ -31850,20 +31868,20 @@
       <c r="E270" s="28"/>
       <c r="F270" s="28"/>
       <c r="G270" s="28"/>
-      <c r="H270" s="42"/>
-      <c r="I270" s="43"/>
-      <c r="J270" s="43"/>
-      <c r="K270" s="43"/>
-      <c r="L270" s="43"/>
-      <c r="M270" s="43"/>
-      <c r="N270" s="43"/>
-      <c r="O270" s="43"/>
-      <c r="P270" s="43"/>
-      <c r="Q270" s="43"/>
-      <c r="R270" s="43"/>
-      <c r="S270" s="43"/>
-      <c r="T270" s="43"/>
-      <c r="U270" s="44"/>
+      <c r="H270" s="57"/>
+      <c r="I270" s="65"/>
+      <c r="J270" s="65"/>
+      <c r="K270" s="65"/>
+      <c r="L270" s="65"/>
+      <c r="M270" s="65"/>
+      <c r="N270" s="65"/>
+      <c r="O270" s="65"/>
+      <c r="P270" s="65"/>
+      <c r="Q270" s="65"/>
+      <c r="R270" s="65"/>
+      <c r="S270" s="65"/>
+      <c r="T270" s="65"/>
+      <c r="U270" s="58"/>
     </row>
     <row r="271" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="27"/>
@@ -31877,20 +31895,20 @@
       <c r="E271" s="28"/>
       <c r="F271" s="28"/>
       <c r="G271" s="28"/>
-      <c r="H271" s="42"/>
-      <c r="I271" s="43"/>
-      <c r="J271" s="43"/>
-      <c r="K271" s="43"/>
-      <c r="L271" s="43"/>
-      <c r="M271" s="43"/>
-      <c r="N271" s="43"/>
-      <c r="O271" s="43"/>
-      <c r="P271" s="43"/>
-      <c r="Q271" s="43"/>
-      <c r="R271" s="43"/>
-      <c r="S271" s="43"/>
-      <c r="T271" s="43"/>
-      <c r="U271" s="44"/>
+      <c r="H271" s="57"/>
+      <c r="I271" s="65"/>
+      <c r="J271" s="65"/>
+      <c r="K271" s="65"/>
+      <c r="L271" s="65"/>
+      <c r="M271" s="65"/>
+      <c r="N271" s="65"/>
+      <c r="O271" s="65"/>
+      <c r="P271" s="65"/>
+      <c r="Q271" s="65"/>
+      <c r="R271" s="65"/>
+      <c r="S271" s="65"/>
+      <c r="T271" s="65"/>
+      <c r="U271" s="58"/>
     </row>
     <row r="272" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="27"/>
@@ -31904,60 +31922,34 @@
       <c r="E272" s="28"/>
       <c r="F272" s="28"/>
       <c r="G272" s="28"/>
-      <c r="H272" s="42"/>
-      <c r="I272" s="43"/>
-      <c r="J272" s="43"/>
-      <c r="K272" s="43"/>
-      <c r="L272" s="43"/>
-      <c r="M272" s="43"/>
-      <c r="N272" s="43"/>
-      <c r="O272" s="43"/>
-      <c r="P272" s="43"/>
-      <c r="Q272" s="43"/>
-      <c r="R272" s="43"/>
-      <c r="S272" s="43"/>
-      <c r="T272" s="43"/>
-      <c r="U272" s="44"/>
+      <c r="H272" s="57"/>
+      <c r="I272" s="65"/>
+      <c r="J272" s="65"/>
+      <c r="K272" s="65"/>
+      <c r="L272" s="65"/>
+      <c r="M272" s="65"/>
+      <c r="N272" s="65"/>
+      <c r="O272" s="65"/>
+      <c r="P272" s="65"/>
+      <c r="Q272" s="65"/>
+      <c r="R272" s="65"/>
+      <c r="S272" s="65"/>
+      <c r="T272" s="65"/>
+      <c r="U272" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="H271:U271"/>
-    <mergeCell ref="H272:U272"/>
-    <mergeCell ref="H265:U265"/>
-    <mergeCell ref="H266:U266"/>
-    <mergeCell ref="H267:U267"/>
-    <mergeCell ref="H268:U268"/>
-    <mergeCell ref="H269:U269"/>
-    <mergeCell ref="H270:U270"/>
-    <mergeCell ref="H264:U264"/>
-    <mergeCell ref="C248:I248"/>
-    <mergeCell ref="A254:U254"/>
-    <mergeCell ref="H255:U255"/>
-    <mergeCell ref="H256:U256"/>
-    <mergeCell ref="H257:U257"/>
-    <mergeCell ref="H258:U258"/>
-    <mergeCell ref="H259:U259"/>
-    <mergeCell ref="H260:U260"/>
-    <mergeCell ref="H261:U261"/>
-    <mergeCell ref="H262:U262"/>
-    <mergeCell ref="H263:U263"/>
-    <mergeCell ref="C203:I203"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C119:I119"/>
-    <mergeCell ref="C122:I122"/>
-    <mergeCell ref="C123:I123"/>
-    <mergeCell ref="C163:I163"/>
-    <mergeCell ref="C164:I164"/>
-    <mergeCell ref="C184:I184"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A3:U3"/>
+    <mergeCell ref="A4:U4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="G5:G7"/>
     <mergeCell ref="C21:I21"/>
     <mergeCell ref="R6:R7"/>
     <mergeCell ref="S6:T6"/>
@@ -31974,17 +31966,43 @@
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:U3"/>
-    <mergeCell ref="A4:U4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="C203:I203"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C119:I119"/>
+    <mergeCell ref="C122:I122"/>
+    <mergeCell ref="C123:I123"/>
+    <mergeCell ref="C163:I163"/>
+    <mergeCell ref="C164:I164"/>
+    <mergeCell ref="C184:I184"/>
+    <mergeCell ref="H264:U264"/>
+    <mergeCell ref="C248:I248"/>
+    <mergeCell ref="A254:U254"/>
+    <mergeCell ref="H255:U255"/>
+    <mergeCell ref="H256:U256"/>
+    <mergeCell ref="H257:U257"/>
+    <mergeCell ref="H258:U258"/>
+    <mergeCell ref="H259:U259"/>
+    <mergeCell ref="H260:U260"/>
+    <mergeCell ref="H261:U261"/>
+    <mergeCell ref="H262:U262"/>
+    <mergeCell ref="H263:U263"/>
+    <mergeCell ref="H271:U271"/>
+    <mergeCell ref="H272:U272"/>
+    <mergeCell ref="H265:U265"/>
+    <mergeCell ref="H266:U266"/>
+    <mergeCell ref="H267:U267"/>
+    <mergeCell ref="H268:U268"/>
+    <mergeCell ref="H269:U269"/>
+    <mergeCell ref="H270:U270"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/school_lublino/lublino_KP.xlsx
+++ b/school_lublino/lublino_KP.xlsx
@@ -3836,6 +3836,15 @@
     <xf numFmtId="164" fontId="9" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3910,15 +3919,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4308,217 +4308,217 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="46"/>
-      <c r="P3" s="46"/>
-      <c r="Q3" s="46"/>
-      <c r="R3" s="46"/>
-      <c r="S3" s="46"/>
-      <c r="T3" s="46"/>
-      <c r="U3" s="46"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="50"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="50"/>
+      <c r="R4" s="50"/>
+      <c r="S4" s="50"/>
+      <c r="T4" s="50"/>
+      <c r="U4" s="50"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="54" t="s">
+      <c r="E5" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="54" t="s">
+      <c r="F5" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="54" t="s">
+      <c r="G5" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="54" t="s">
+      <c r="H5" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="54" t="s">
+      <c r="I5" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="48" t="s">
+      <c r="J5" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="51" t="s">
+      <c r="K5" s="52"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="52"/>
+      <c r="O5" s="53"/>
+      <c r="P5" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="53"/>
-      <c r="S5" s="51" t="s">
+      <c r="Q5" s="55"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="52"/>
-      <c r="U5" s="53"/>
+      <c r="T5" s="55"/>
+      <c r="U5" s="56"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="55"/>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="57" t="s">
+      <c r="A6" s="58"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="58"/>
-      <c r="L6" s="54" t="s">
+      <c r="K6" s="61"/>
+      <c r="L6" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="57" t="s">
+      <c r="M6" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="58"/>
-      <c r="O6" s="54" t="s">
+      <c r="N6" s="61"/>
+      <c r="O6" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="57" t="s">
+      <c r="P6" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="58"/>
-      <c r="R6" s="54" t="s">
+      <c r="Q6" s="61"/>
+      <c r="R6" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="S6" s="57" t="s">
+      <c r="S6" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="58"/>
-      <c r="U6" s="54" t="s">
+      <c r="T6" s="61"/>
+      <c r="U6" s="57" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="56"/>
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
+      <c r="A7" s="59"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
       <c r="J7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="56"/>
+      <c r="L7" s="59"/>
       <c r="M7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="56"/>
+      <c r="O7" s="59"/>
       <c r="P7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="56"/>
+      <c r="R7" s="59"/>
       <c r="S7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="U7" s="56"/>
+      <c r="U7" s="59"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="61"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="64"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -4560,15 +4560,15 @@
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="62" t="s">
+      <c r="C9" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="64"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="67"/>
       <c r="M9" s="6">
         <f>SUM(M10,M20)</f>
         <v>18303819.899999999</v>
@@ -4604,15 +4604,15 @@
       <c r="B10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="62" t="s">
+      <c r="C10" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="64"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="67"/>
       <c r="M10" s="6">
         <f t="shared" ref="M10:O14" si="0">SUM(M11)</f>
         <v>126283.29</v>
@@ -4648,15 +4648,15 @@
       <c r="B11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="62" t="s">
+      <c r="C11" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="64"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="67"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4692,15 +4692,15 @@
       <c r="B12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="64"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="67"/>
       <c r="M12" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4736,15 +4736,15 @@
       <c r="B13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="62" t="s">
+      <c r="C13" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="64"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="67"/>
       <c r="M13" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4780,15 +4780,15 @@
       <c r="B14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="C14" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="63"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="64"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="67"/>
       <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -5079,15 +5079,15 @@
       <c r="B20" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="62" t="s">
+      <c r="C20" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="64"/>
+      <c r="D20" s="66"/>
+      <c r="E20" s="66"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="66"/>
+      <c r="H20" s="66"/>
+      <c r="I20" s="67"/>
       <c r="M20" s="6">
         <f t="shared" ref="M20:O21" si="1">SUM(M21)</f>
         <v>18177536.609999999</v>
@@ -5123,15 +5123,15 @@
       <c r="B21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="62" t="s">
+      <c r="C21" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="63"/>
-      <c r="E21" s="63"/>
-      <c r="F21" s="63"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="63"/>
-      <c r="I21" s="64"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="66"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="67"/>
       <c r="M21" s="6">
         <f t="shared" si="1"/>
         <v>18177536.609999999</v>
@@ -5167,15 +5167,15 @@
       <c r="B22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="62" t="s">
+      <c r="C22" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="63"/>
-      <c r="H22" s="63"/>
-      <c r="I22" s="64"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="67"/>
       <c r="M22" s="6">
         <f>SUM(M23,M122,M163,M203,M248)</f>
         <v>18177536.609999999</v>
@@ -5211,15 +5211,15 @@
       <c r="B23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="62" t="s">
+      <c r="C23" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="64"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="67"/>
       <c r="M23" s="6">
         <f>SUM(M24,M67,M76,M119)</f>
         <v>12831032.07</v>
@@ -5255,15 +5255,15 @@
       <c r="B24" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C24" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="64"/>
+      <c r="D24" s="66"/>
+      <c r="E24" s="66"/>
+      <c r="F24" s="66"/>
+      <c r="G24" s="66"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="67"/>
       <c r="M24" s="6">
         <f>SUM(M25,M29,M31,M34,M36,M41,M46,M51,M57,M62)</f>
         <v>7808423.3099999996</v>
@@ -7487,15 +7487,15 @@
       <c r="B67" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="62" t="s">
+      <c r="C67" s="65" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="63"/>
-      <c r="E67" s="63"/>
-      <c r="F67" s="63"/>
-      <c r="G67" s="63"/>
-      <c r="H67" s="63"/>
-      <c r="I67" s="64"/>
+      <c r="D67" s="66"/>
+      <c r="E67" s="66"/>
+      <c r="F67" s="66"/>
+      <c r="G67" s="66"/>
+      <c r="H67" s="66"/>
+      <c r="I67" s="67"/>
       <c r="M67" s="6">
         <f>SUM(M68,M72,M74)</f>
         <v>748533.11</v>
@@ -7993,15 +7993,15 @@
       <c r="B76" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C76" s="62" t="s">
+      <c r="C76" s="65" t="s">
         <v>325</v>
       </c>
-      <c r="D76" s="63"/>
-      <c r="E76" s="63"/>
-      <c r="F76" s="63"/>
-      <c r="G76" s="63"/>
-      <c r="H76" s="63"/>
-      <c r="I76" s="64"/>
+      <c r="D76" s="66"/>
+      <c r="E76" s="66"/>
+      <c r="F76" s="66"/>
+      <c r="G76" s="66"/>
+      <c r="H76" s="66"/>
+      <c r="I76" s="67"/>
       <c r="M76" s="6">
         <f>SUM(M77,M82,M87,M93,M96,M99,M104,M109,M114,M117)</f>
         <v>3831185.6499999994</v>
@@ -10251,15 +10251,15 @@
       <c r="B119" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C119" s="62" t="s">
+      <c r="C119" s="65" t="s">
         <v>526</v>
       </c>
-      <c r="D119" s="63"/>
-      <c r="E119" s="63"/>
-      <c r="F119" s="63"/>
-      <c r="G119" s="63"/>
-      <c r="H119" s="63"/>
-      <c r="I119" s="64"/>
+      <c r="D119" s="66"/>
+      <c r="E119" s="66"/>
+      <c r="F119" s="66"/>
+      <c r="G119" s="66"/>
+      <c r="H119" s="66"/>
+      <c r="I119" s="67"/>
       <c r="M119" s="6">
         <f>SUM(M120)</f>
         <v>442890</v>
@@ -10421,15 +10421,15 @@
       <c r="B122" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="C122" s="62" t="s">
+      <c r="C122" s="65" t="s">
         <v>541</v>
       </c>
-      <c r="D122" s="63"/>
-      <c r="E122" s="63"/>
-      <c r="F122" s="63"/>
-      <c r="G122" s="63"/>
-      <c r="H122" s="63"/>
-      <c r="I122" s="64"/>
+      <c r="D122" s="66"/>
+      <c r="E122" s="66"/>
+      <c r="F122" s="66"/>
+      <c r="G122" s="66"/>
+      <c r="H122" s="66"/>
+      <c r="I122" s="67"/>
       <c r="M122" s="6">
         <f>SUM(M123)</f>
         <v>4016037.31</v>
@@ -10465,15 +10465,15 @@
       <c r="B123" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="C123" s="62" t="s">
+      <c r="C123" s="65" t="s">
         <v>544</v>
       </c>
-      <c r="D123" s="63"/>
-      <c r="E123" s="63"/>
-      <c r="F123" s="63"/>
-      <c r="G123" s="63"/>
-      <c r="H123" s="63"/>
-      <c r="I123" s="64"/>
+      <c r="D123" s="66"/>
+      <c r="E123" s="66"/>
+      <c r="F123" s="66"/>
+      <c r="G123" s="66"/>
+      <c r="H123" s="66"/>
+      <c r="I123" s="67"/>
       <c r="M123" s="6">
         <f>SUM(M124,M127,M131,M136,M140,M143,M148,M153,M158)</f>
         <v>4016037.31</v>
@@ -12554,15 +12554,15 @@
       <c r="B163" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C163" s="62" t="s">
+      <c r="C163" s="65" t="s">
         <v>710</v>
       </c>
-      <c r="D163" s="63"/>
-      <c r="E163" s="63"/>
-      <c r="F163" s="63"/>
-      <c r="G163" s="63"/>
-      <c r="H163" s="63"/>
-      <c r="I163" s="64"/>
+      <c r="D163" s="66"/>
+      <c r="E163" s="66"/>
+      <c r="F163" s="66"/>
+      <c r="G163" s="66"/>
+      <c r="H163" s="66"/>
+      <c r="I163" s="67"/>
       <c r="M163" s="6">
         <f>SUM(M164,M184)</f>
         <v>611422.71999999997</v>
@@ -12598,15 +12598,15 @@
       <c r="B164" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="C164" s="62" t="s">
+      <c r="C164" s="65" t="s">
         <v>713</v>
       </c>
-      <c r="D164" s="63"/>
-      <c r="E164" s="63"/>
-      <c r="F164" s="63"/>
-      <c r="G164" s="63"/>
-      <c r="H164" s="63"/>
-      <c r="I164" s="64"/>
+      <c r="D164" s="66"/>
+      <c r="E164" s="66"/>
+      <c r="F164" s="66"/>
+      <c r="G164" s="66"/>
+      <c r="H164" s="66"/>
+      <c r="I164" s="67"/>
       <c r="M164" s="6">
         <f>SUM(M165,M171,M174,M178,M182)</f>
         <v>415021.23999999993</v>
@@ -13653,15 +13653,15 @@
       <c r="B184" s="9" t="s">
         <v>789</v>
       </c>
-      <c r="C184" s="62" t="s">
+      <c r="C184" s="65" t="s">
         <v>790</v>
       </c>
-      <c r="D184" s="63"/>
-      <c r="E184" s="63"/>
-      <c r="F184" s="63"/>
-      <c r="G184" s="63"/>
-      <c r="H184" s="63"/>
-      <c r="I184" s="64"/>
+      <c r="D184" s="66"/>
+      <c r="E184" s="66"/>
+      <c r="F184" s="66"/>
+      <c r="G184" s="66"/>
+      <c r="H184" s="66"/>
+      <c r="I184" s="67"/>
       <c r="M184" s="6">
         <f>SUM(M185,M188,M191,M194,M197,M200)</f>
         <v>196401.48</v>
@@ -14711,15 +14711,15 @@
       <c r="B203" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="C203" s="62" t="s">
+      <c r="C203" s="65" t="s">
         <v>856</v>
       </c>
-      <c r="D203" s="63"/>
-      <c r="E203" s="63"/>
-      <c r="F203" s="63"/>
-      <c r="G203" s="63"/>
-      <c r="H203" s="63"/>
-      <c r="I203" s="64"/>
+      <c r="D203" s="66"/>
+      <c r="E203" s="66"/>
+      <c r="F203" s="66"/>
+      <c r="G203" s="66"/>
+      <c r="H203" s="66"/>
+      <c r="I203" s="67"/>
       <c r="M203" s="6">
         <f>SUM(M204,M206,M221,M236,M238,M240,M242,M243,M244,M245,M246,M247)</f>
         <v>719044.50999999989</v>
@@ -16449,7 +16449,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="239" spans="1:35" ht="375" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:35" ht="393.75" x14ac:dyDescent="0.25">
       <c r="A239" s="9" t="s">
         <v>1004</v>
       </c>
@@ -17101,15 +17101,15 @@
       <c r="B248" s="9" t="s">
         <v>1031</v>
       </c>
-      <c r="C248" s="62" t="s">
+      <c r="C248" s="65" t="s">
         <v>1032</v>
       </c>
-      <c r="D248" s="63"/>
-      <c r="E248" s="63"/>
-      <c r="F248" s="63"/>
-      <c r="G248" s="63"/>
-      <c r="H248" s="63"/>
-      <c r="I248" s="64"/>
+      <c r="D248" s="66"/>
+      <c r="E248" s="66"/>
+      <c r="F248" s="66"/>
+      <c r="G248" s="66"/>
+      <c r="H248" s="66"/>
+      <c r="I248" s="67"/>
       <c r="M248" s="6">
         <f>SUM(M249,M250,M251,M252)</f>
         <v>0</v>
@@ -17496,29 +17496,29 @@
       </c>
     </row>
     <row r="254" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="59" t="s">
+      <c r="A254" s="62" t="s">
         <v>1050</v>
       </c>
-      <c r="B254" s="60"/>
-      <c r="C254" s="60"/>
-      <c r="D254" s="60"/>
-      <c r="E254" s="60"/>
-      <c r="F254" s="60"/>
-      <c r="G254" s="60"/>
-      <c r="H254" s="60"/>
-      <c r="I254" s="60"/>
-      <c r="J254" s="60"/>
-      <c r="K254" s="60"/>
-      <c r="L254" s="60"/>
-      <c r="M254" s="60"/>
-      <c r="N254" s="60"/>
-      <c r="O254" s="60"/>
-      <c r="P254" s="60"/>
-      <c r="Q254" s="60"/>
-      <c r="R254" s="60"/>
-      <c r="S254" s="60"/>
-      <c r="T254" s="60"/>
-      <c r="U254" s="61"/>
+      <c r="B254" s="63"/>
+      <c r="C254" s="63"/>
+      <c r="D254" s="63"/>
+      <c r="E254" s="63"/>
+      <c r="F254" s="63"/>
+      <c r="G254" s="63"/>
+      <c r="H254" s="63"/>
+      <c r="I254" s="63"/>
+      <c r="J254" s="63"/>
+      <c r="K254" s="63"/>
+      <c r="L254" s="63"/>
+      <c r="M254" s="63"/>
+      <c r="N254" s="63"/>
+      <c r="O254" s="63"/>
+      <c r="P254" s="63"/>
+      <c r="Q254" s="63"/>
+      <c r="R254" s="63"/>
+      <c r="S254" s="63"/>
+      <c r="T254" s="63"/>
+      <c r="U254" s="64"/>
     </row>
     <row r="255" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="27"/>
@@ -17534,20 +17534,20 @@
       <c r="E255" s="28"/>
       <c r="F255" s="28"/>
       <c r="G255" s="28"/>
-      <c r="H255" s="57"/>
-      <c r="I255" s="65"/>
-      <c r="J255" s="65"/>
-      <c r="K255" s="65"/>
-      <c r="L255" s="65"/>
-      <c r="M255" s="65"/>
-      <c r="N255" s="65"/>
-      <c r="O255" s="65"/>
-      <c r="P255" s="65"/>
-      <c r="Q255" s="65"/>
-      <c r="R255" s="65"/>
-      <c r="S255" s="65"/>
-      <c r="T255" s="65"/>
-      <c r="U255" s="58"/>
+      <c r="H255" s="60"/>
+      <c r="I255" s="68"/>
+      <c r="J255" s="68"/>
+      <c r="K255" s="68"/>
+      <c r="L255" s="68"/>
+      <c r="M255" s="68"/>
+      <c r="N255" s="68"/>
+      <c r="O255" s="68"/>
+      <c r="P255" s="68"/>
+      <c r="Q255" s="68"/>
+      <c r="R255" s="68"/>
+      <c r="S255" s="68"/>
+      <c r="T255" s="68"/>
+      <c r="U255" s="61"/>
     </row>
     <row r="256" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="27"/>
@@ -17563,20 +17563,20 @@
       <c r="E256" s="28"/>
       <c r="F256" s="28"/>
       <c r="G256" s="28"/>
-      <c r="H256" s="57"/>
-      <c r="I256" s="65"/>
-      <c r="J256" s="65"/>
-      <c r="K256" s="65"/>
-      <c r="L256" s="65"/>
-      <c r="M256" s="65"/>
-      <c r="N256" s="65"/>
-      <c r="O256" s="65"/>
-      <c r="P256" s="65"/>
-      <c r="Q256" s="65"/>
-      <c r="R256" s="65"/>
-      <c r="S256" s="65"/>
-      <c r="T256" s="65"/>
-      <c r="U256" s="58"/>
+      <c r="H256" s="60"/>
+      <c r="I256" s="68"/>
+      <c r="J256" s="68"/>
+      <c r="K256" s="68"/>
+      <c r="L256" s="68"/>
+      <c r="M256" s="68"/>
+      <c r="N256" s="68"/>
+      <c r="O256" s="68"/>
+      <c r="P256" s="68"/>
+      <c r="Q256" s="68"/>
+      <c r="R256" s="68"/>
+      <c r="S256" s="68"/>
+      <c r="T256" s="68"/>
+      <c r="U256" s="61"/>
     </row>
     <row r="257" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A257" s="27"/>
@@ -17592,20 +17592,20 @@
       <c r="E257" s="28"/>
       <c r="F257" s="28"/>
       <c r="G257" s="28"/>
-      <c r="H257" s="57"/>
-      <c r="I257" s="65"/>
-      <c r="J257" s="65"/>
-      <c r="K257" s="65"/>
-      <c r="L257" s="65"/>
-      <c r="M257" s="65"/>
-      <c r="N257" s="65"/>
-      <c r="O257" s="65"/>
-      <c r="P257" s="65"/>
-      <c r="Q257" s="65"/>
-      <c r="R257" s="65"/>
-      <c r="S257" s="65"/>
-      <c r="T257" s="65"/>
-      <c r="U257" s="58"/>
+      <c r="H257" s="60"/>
+      <c r="I257" s="68"/>
+      <c r="J257" s="68"/>
+      <c r="K257" s="68"/>
+      <c r="L257" s="68"/>
+      <c r="M257" s="68"/>
+      <c r="N257" s="68"/>
+      <c r="O257" s="68"/>
+      <c r="P257" s="68"/>
+      <c r="Q257" s="68"/>
+      <c r="R257" s="68"/>
+      <c r="S257" s="68"/>
+      <c r="T257" s="68"/>
+      <c r="U257" s="61"/>
     </row>
     <row r="258" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="27"/>
@@ -17621,20 +17621,20 @@
       <c r="E258" s="28"/>
       <c r="F258" s="28"/>
       <c r="G258" s="28"/>
-      <c r="H258" s="57"/>
-      <c r="I258" s="65"/>
-      <c r="J258" s="65"/>
-      <c r="K258" s="65"/>
-      <c r="L258" s="65"/>
-      <c r="M258" s="65"/>
-      <c r="N258" s="65"/>
-      <c r="O258" s="65"/>
-      <c r="P258" s="65"/>
-      <c r="Q258" s="65"/>
-      <c r="R258" s="65"/>
-      <c r="S258" s="65"/>
-      <c r="T258" s="65"/>
-      <c r="U258" s="58"/>
+      <c r="H258" s="60"/>
+      <c r="I258" s="68"/>
+      <c r="J258" s="68"/>
+      <c r="K258" s="68"/>
+      <c r="L258" s="68"/>
+      <c r="M258" s="68"/>
+      <c r="N258" s="68"/>
+      <c r="O258" s="68"/>
+      <c r="P258" s="68"/>
+      <c r="Q258" s="68"/>
+      <c r="R258" s="68"/>
+      <c r="S258" s="68"/>
+      <c r="T258" s="68"/>
+      <c r="U258" s="61"/>
     </row>
     <row r="259" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="27"/>
@@ -17650,20 +17650,20 @@
       <c r="E259" s="28"/>
       <c r="F259" s="28"/>
       <c r="G259" s="28"/>
-      <c r="H259" s="57"/>
-      <c r="I259" s="65"/>
-      <c r="J259" s="65"/>
-      <c r="K259" s="65"/>
-      <c r="L259" s="65"/>
-      <c r="M259" s="65"/>
-      <c r="N259" s="65"/>
-      <c r="O259" s="65"/>
-      <c r="P259" s="65"/>
-      <c r="Q259" s="65"/>
-      <c r="R259" s="65"/>
-      <c r="S259" s="65"/>
-      <c r="T259" s="65"/>
-      <c r="U259" s="58"/>
+      <c r="H259" s="60"/>
+      <c r="I259" s="68"/>
+      <c r="J259" s="68"/>
+      <c r="K259" s="68"/>
+      <c r="L259" s="68"/>
+      <c r="M259" s="68"/>
+      <c r="N259" s="68"/>
+      <c r="O259" s="68"/>
+      <c r="P259" s="68"/>
+      <c r="Q259" s="68"/>
+      <c r="R259" s="68"/>
+      <c r="S259" s="68"/>
+      <c r="T259" s="68"/>
+      <c r="U259" s="61"/>
     </row>
     <row r="260" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A260" s="27"/>
@@ -17679,20 +17679,20 @@
       <c r="E260" s="28"/>
       <c r="F260" s="28"/>
       <c r="G260" s="28"/>
-      <c r="H260" s="57"/>
-      <c r="I260" s="65"/>
-      <c r="J260" s="65"/>
-      <c r="K260" s="65"/>
-      <c r="L260" s="65"/>
-      <c r="M260" s="65"/>
-      <c r="N260" s="65"/>
-      <c r="O260" s="65"/>
-      <c r="P260" s="65"/>
-      <c r="Q260" s="65"/>
-      <c r="R260" s="65"/>
-      <c r="S260" s="65"/>
-      <c r="T260" s="65"/>
-      <c r="U260" s="58"/>
+      <c r="H260" s="60"/>
+      <c r="I260" s="68"/>
+      <c r="J260" s="68"/>
+      <c r="K260" s="68"/>
+      <c r="L260" s="68"/>
+      <c r="M260" s="68"/>
+      <c r="N260" s="68"/>
+      <c r="O260" s="68"/>
+      <c r="P260" s="68"/>
+      <c r="Q260" s="68"/>
+      <c r="R260" s="68"/>
+      <c r="S260" s="68"/>
+      <c r="T260" s="68"/>
+      <c r="U260" s="61"/>
     </row>
     <row r="261" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A261" s="27"/>
@@ -17708,20 +17708,20 @@
       <c r="E261" s="28"/>
       <c r="F261" s="28"/>
       <c r="G261" s="28"/>
-      <c r="H261" s="57"/>
-      <c r="I261" s="65"/>
-      <c r="J261" s="65"/>
-      <c r="K261" s="65"/>
-      <c r="L261" s="65"/>
-      <c r="M261" s="65"/>
-      <c r="N261" s="65"/>
-      <c r="O261" s="65"/>
-      <c r="P261" s="65"/>
-      <c r="Q261" s="65"/>
-      <c r="R261" s="65"/>
-      <c r="S261" s="65"/>
-      <c r="T261" s="65"/>
-      <c r="U261" s="58"/>
+      <c r="H261" s="60"/>
+      <c r="I261" s="68"/>
+      <c r="J261" s="68"/>
+      <c r="K261" s="68"/>
+      <c r="L261" s="68"/>
+      <c r="M261" s="68"/>
+      <c r="N261" s="68"/>
+      <c r="O261" s="68"/>
+      <c r="P261" s="68"/>
+      <c r="Q261" s="68"/>
+      <c r="R261" s="68"/>
+      <c r="S261" s="68"/>
+      <c r="T261" s="68"/>
+      <c r="U261" s="61"/>
     </row>
     <row r="262" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="27"/>
@@ -17737,20 +17737,20 @@
       <c r="E262" s="28"/>
       <c r="F262" s="28"/>
       <c r="G262" s="28"/>
-      <c r="H262" s="57"/>
-      <c r="I262" s="65"/>
-      <c r="J262" s="65"/>
-      <c r="K262" s="65"/>
-      <c r="L262" s="65"/>
-      <c r="M262" s="65"/>
-      <c r="N262" s="65"/>
-      <c r="O262" s="65"/>
-      <c r="P262" s="65"/>
-      <c r="Q262" s="65"/>
-      <c r="R262" s="65"/>
-      <c r="S262" s="65"/>
-      <c r="T262" s="65"/>
-      <c r="U262" s="58"/>
+      <c r="H262" s="60"/>
+      <c r="I262" s="68"/>
+      <c r="J262" s="68"/>
+      <c r="K262" s="68"/>
+      <c r="L262" s="68"/>
+      <c r="M262" s="68"/>
+      <c r="N262" s="68"/>
+      <c r="O262" s="68"/>
+      <c r="P262" s="68"/>
+      <c r="Q262" s="68"/>
+      <c r="R262" s="68"/>
+      <c r="S262" s="68"/>
+      <c r="T262" s="68"/>
+      <c r="U262" s="61"/>
     </row>
     <row r="263" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="27"/>
@@ -17766,20 +17766,20 @@
       <c r="E263" s="28"/>
       <c r="F263" s="28"/>
       <c r="G263" s="28"/>
-      <c r="H263" s="57"/>
-      <c r="I263" s="65"/>
-      <c r="J263" s="65"/>
-      <c r="K263" s="65"/>
-      <c r="L263" s="65"/>
-      <c r="M263" s="65"/>
-      <c r="N263" s="65"/>
-      <c r="O263" s="65"/>
-      <c r="P263" s="65"/>
-      <c r="Q263" s="65"/>
-      <c r="R263" s="65"/>
-      <c r="S263" s="65"/>
-      <c r="T263" s="65"/>
-      <c r="U263" s="58"/>
+      <c r="H263" s="60"/>
+      <c r="I263" s="68"/>
+      <c r="J263" s="68"/>
+      <c r="K263" s="68"/>
+      <c r="L263" s="68"/>
+      <c r="M263" s="68"/>
+      <c r="N263" s="68"/>
+      <c r="O263" s="68"/>
+      <c r="P263" s="68"/>
+      <c r="Q263" s="68"/>
+      <c r="R263" s="68"/>
+      <c r="S263" s="68"/>
+      <c r="T263" s="68"/>
+      <c r="U263" s="61"/>
     </row>
     <row r="264" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A264" s="27"/>
@@ -17795,20 +17795,20 @@
       <c r="E264" s="28"/>
       <c r="F264" s="28"/>
       <c r="G264" s="28"/>
-      <c r="H264" s="57"/>
-      <c r="I264" s="65"/>
-      <c r="J264" s="65"/>
-      <c r="K264" s="65"/>
-      <c r="L264" s="65"/>
-      <c r="M264" s="65"/>
-      <c r="N264" s="65"/>
-      <c r="O264" s="65"/>
-      <c r="P264" s="65"/>
-      <c r="Q264" s="65"/>
-      <c r="R264" s="65"/>
-      <c r="S264" s="65"/>
-      <c r="T264" s="65"/>
-      <c r="U264" s="58"/>
+      <c r="H264" s="60"/>
+      <c r="I264" s="68"/>
+      <c r="J264" s="68"/>
+      <c r="K264" s="68"/>
+      <c r="L264" s="68"/>
+      <c r="M264" s="68"/>
+      <c r="N264" s="68"/>
+      <c r="O264" s="68"/>
+      <c r="P264" s="68"/>
+      <c r="Q264" s="68"/>
+      <c r="R264" s="68"/>
+      <c r="S264" s="68"/>
+      <c r="T264" s="68"/>
+      <c r="U264" s="61"/>
     </row>
     <row r="265" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A265" s="27"/>
@@ -17824,20 +17824,20 @@
       <c r="E265" s="28"/>
       <c r="F265" s="28"/>
       <c r="G265" s="28"/>
-      <c r="H265" s="57"/>
-      <c r="I265" s="65"/>
-      <c r="J265" s="65"/>
-      <c r="K265" s="65"/>
-      <c r="L265" s="65"/>
-      <c r="M265" s="65"/>
-      <c r="N265" s="65"/>
-      <c r="O265" s="65"/>
-      <c r="P265" s="65"/>
-      <c r="Q265" s="65"/>
-      <c r="R265" s="65"/>
-      <c r="S265" s="65"/>
-      <c r="T265" s="65"/>
-      <c r="U265" s="58"/>
+      <c r="H265" s="60"/>
+      <c r="I265" s="68"/>
+      <c r="J265" s="68"/>
+      <c r="K265" s="68"/>
+      <c r="L265" s="68"/>
+      <c r="M265" s="68"/>
+      <c r="N265" s="68"/>
+      <c r="O265" s="68"/>
+      <c r="P265" s="68"/>
+      <c r="Q265" s="68"/>
+      <c r="R265" s="68"/>
+      <c r="S265" s="68"/>
+      <c r="T265" s="68"/>
+      <c r="U265" s="61"/>
     </row>
     <row r="266" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A266" s="27"/>
@@ -17853,20 +17853,20 @@
       <c r="E266" s="28"/>
       <c r="F266" s="28"/>
       <c r="G266" s="28"/>
-      <c r="H266" s="57"/>
-      <c r="I266" s="65"/>
-      <c r="J266" s="65"/>
-      <c r="K266" s="65"/>
-      <c r="L266" s="65"/>
-      <c r="M266" s="65"/>
-      <c r="N266" s="65"/>
-      <c r="O266" s="65"/>
-      <c r="P266" s="65"/>
-      <c r="Q266" s="65"/>
-      <c r="R266" s="65"/>
-      <c r="S266" s="65"/>
-      <c r="T266" s="65"/>
-      <c r="U266" s="58"/>
+      <c r="H266" s="60"/>
+      <c r="I266" s="68"/>
+      <c r="J266" s="68"/>
+      <c r="K266" s="68"/>
+      <c r="L266" s="68"/>
+      <c r="M266" s="68"/>
+      <c r="N266" s="68"/>
+      <c r="O266" s="68"/>
+      <c r="P266" s="68"/>
+      <c r="Q266" s="68"/>
+      <c r="R266" s="68"/>
+      <c r="S266" s="68"/>
+      <c r="T266" s="68"/>
+      <c r="U266" s="61"/>
     </row>
     <row r="267" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="27"/>
@@ -17882,20 +17882,20 @@
       <c r="E267" s="28"/>
       <c r="F267" s="28"/>
       <c r="G267" s="28"/>
-      <c r="H267" s="57"/>
-      <c r="I267" s="65"/>
-      <c r="J267" s="65"/>
-      <c r="K267" s="65"/>
-      <c r="L267" s="65"/>
-      <c r="M267" s="65"/>
-      <c r="N267" s="65"/>
-      <c r="O267" s="65"/>
-      <c r="P267" s="65"/>
-      <c r="Q267" s="65"/>
-      <c r="R267" s="65"/>
-      <c r="S267" s="65"/>
-      <c r="T267" s="65"/>
-      <c r="U267" s="58"/>
+      <c r="H267" s="60"/>
+      <c r="I267" s="68"/>
+      <c r="J267" s="68"/>
+      <c r="K267" s="68"/>
+      <c r="L267" s="68"/>
+      <c r="M267" s="68"/>
+      <c r="N267" s="68"/>
+      <c r="O267" s="68"/>
+      <c r="P267" s="68"/>
+      <c r="Q267" s="68"/>
+      <c r="R267" s="68"/>
+      <c r="S267" s="68"/>
+      <c r="T267" s="68"/>
+      <c r="U267" s="61"/>
     </row>
     <row r="268" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="27"/>
@@ -17911,22 +17911,22 @@
       <c r="E268" s="28"/>
       <c r="F268" s="28"/>
       <c r="G268" s="28"/>
-      <c r="H268" s="57" t="s">
+      <c r="H268" s="60" t="s">
         <v>1092</v>
       </c>
-      <c r="I268" s="65"/>
-      <c r="J268" s="65"/>
-      <c r="K268" s="65"/>
-      <c r="L268" s="65"/>
-      <c r="M268" s="65"/>
-      <c r="N268" s="65"/>
-      <c r="O268" s="65"/>
-      <c r="P268" s="65"/>
-      <c r="Q268" s="65"/>
-      <c r="R268" s="65"/>
-      <c r="S268" s="65"/>
-      <c r="T268" s="65"/>
-      <c r="U268" s="58"/>
+      <c r="I268" s="68"/>
+      <c r="J268" s="68"/>
+      <c r="K268" s="68"/>
+      <c r="L268" s="68"/>
+      <c r="M268" s="68"/>
+      <c r="N268" s="68"/>
+      <c r="O268" s="68"/>
+      <c r="P268" s="68"/>
+      <c r="Q268" s="68"/>
+      <c r="R268" s="68"/>
+      <c r="S268" s="68"/>
+      <c r="T268" s="68"/>
+      <c r="U268" s="61"/>
     </row>
     <row r="269" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="27"/>
@@ -17942,20 +17942,20 @@
       <c r="E269" s="28"/>
       <c r="F269" s="28"/>
       <c r="G269" s="28"/>
-      <c r="H269" s="57"/>
-      <c r="I269" s="65"/>
-      <c r="J269" s="65"/>
-      <c r="K269" s="65"/>
-      <c r="L269" s="65"/>
-      <c r="M269" s="65"/>
-      <c r="N269" s="65"/>
-      <c r="O269" s="65"/>
-      <c r="P269" s="65"/>
-      <c r="Q269" s="65"/>
-      <c r="R269" s="65"/>
-      <c r="S269" s="65"/>
-      <c r="T269" s="65"/>
-      <c r="U269" s="58"/>
+      <c r="H269" s="60"/>
+      <c r="I269" s="68"/>
+      <c r="J269" s="68"/>
+      <c r="K269" s="68"/>
+      <c r="L269" s="68"/>
+      <c r="M269" s="68"/>
+      <c r="N269" s="68"/>
+      <c r="O269" s="68"/>
+      <c r="P269" s="68"/>
+      <c r="Q269" s="68"/>
+      <c r="R269" s="68"/>
+      <c r="S269" s="68"/>
+      <c r="T269" s="68"/>
+      <c r="U269" s="61"/>
     </row>
     <row r="270" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A270" s="27"/>
@@ -17969,20 +17969,20 @@
       <c r="E270" s="28"/>
       <c r="F270" s="28"/>
       <c r="G270" s="28"/>
-      <c r="H270" s="57"/>
-      <c r="I270" s="65"/>
-      <c r="J270" s="65"/>
-      <c r="K270" s="65"/>
-      <c r="L270" s="65"/>
-      <c r="M270" s="65"/>
-      <c r="N270" s="65"/>
-      <c r="O270" s="65"/>
-      <c r="P270" s="65"/>
-      <c r="Q270" s="65"/>
-      <c r="R270" s="65"/>
-      <c r="S270" s="65"/>
-      <c r="T270" s="65"/>
-      <c r="U270" s="58"/>
+      <c r="H270" s="60"/>
+      <c r="I270" s="68"/>
+      <c r="J270" s="68"/>
+      <c r="K270" s="68"/>
+      <c r="L270" s="68"/>
+      <c r="M270" s="68"/>
+      <c r="N270" s="68"/>
+      <c r="O270" s="68"/>
+      <c r="P270" s="68"/>
+      <c r="Q270" s="68"/>
+      <c r="R270" s="68"/>
+      <c r="S270" s="68"/>
+      <c r="T270" s="68"/>
+      <c r="U270" s="61"/>
     </row>
     <row r="271" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="27"/>
@@ -17996,20 +17996,20 @@
       <c r="E271" s="28"/>
       <c r="F271" s="28"/>
       <c r="G271" s="28"/>
-      <c r="H271" s="57"/>
-      <c r="I271" s="65"/>
-      <c r="J271" s="65"/>
-      <c r="K271" s="65"/>
-      <c r="L271" s="65"/>
-      <c r="M271" s="65"/>
-      <c r="N271" s="65"/>
-      <c r="O271" s="65"/>
-      <c r="P271" s="65"/>
-      <c r="Q271" s="65"/>
-      <c r="R271" s="65"/>
-      <c r="S271" s="65"/>
-      <c r="T271" s="65"/>
-      <c r="U271" s="58"/>
+      <c r="H271" s="60"/>
+      <c r="I271" s="68"/>
+      <c r="J271" s="68"/>
+      <c r="K271" s="68"/>
+      <c r="L271" s="68"/>
+      <c r="M271" s="68"/>
+      <c r="N271" s="68"/>
+      <c r="O271" s="68"/>
+      <c r="P271" s="68"/>
+      <c r="Q271" s="68"/>
+      <c r="R271" s="68"/>
+      <c r="S271" s="68"/>
+      <c r="T271" s="68"/>
+      <c r="U271" s="61"/>
     </row>
     <row r="272" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="27"/>
@@ -18023,20 +18023,20 @@
       <c r="E272" s="28"/>
       <c r="F272" s="28"/>
       <c r="G272" s="28"/>
-      <c r="H272" s="57"/>
-      <c r="I272" s="65"/>
-      <c r="J272" s="65"/>
-      <c r="K272" s="65"/>
-      <c r="L272" s="65"/>
-      <c r="M272" s="65"/>
-      <c r="N272" s="65"/>
-      <c r="O272" s="65"/>
-      <c r="P272" s="65"/>
-      <c r="Q272" s="65"/>
-      <c r="R272" s="65"/>
-      <c r="S272" s="65"/>
-      <c r="T272" s="65"/>
-      <c r="U272" s="58"/>
+      <c r="H272" s="60"/>
+      <c r="I272" s="68"/>
+      <c r="J272" s="68"/>
+      <c r="K272" s="68"/>
+      <c r="L272" s="68"/>
+      <c r="M272" s="68"/>
+      <c r="N272" s="68"/>
+      <c r="O272" s="68"/>
+      <c r="P272" s="68"/>
+      <c r="Q272" s="68"/>
+      <c r="R272" s="68"/>
+      <c r="S272" s="68"/>
+      <c r="T272" s="68"/>
+      <c r="U272" s="61"/>
     </row>
   </sheetData>
   <sheetProtection password="C644" sheet="1" formatColumns="0" autoFilter="0"/>
@@ -18196,217 +18196,217 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="46"/>
-      <c r="P3" s="46"/>
-      <c r="Q3" s="46"/>
-      <c r="R3" s="46"/>
-      <c r="S3" s="46"/>
-      <c r="T3" s="46"/>
-      <c r="U3" s="46"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="47"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="50"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="50"/>
+      <c r="R4" s="50"/>
+      <c r="S4" s="50"/>
+      <c r="T4" s="50"/>
+      <c r="U4" s="50"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="54" t="s">
+      <c r="E5" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="54" t="s">
+      <c r="F5" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="54" t="s">
+      <c r="G5" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="54" t="s">
+      <c r="H5" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="54" t="s">
+      <c r="I5" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="48" t="s">
+      <c r="J5" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="51" t="s">
+      <c r="K5" s="52"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="52"/>
+      <c r="O5" s="53"/>
+      <c r="P5" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="53"/>
-      <c r="S5" s="51" t="s">
+      <c r="Q5" s="55"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="52"/>
-      <c r="U5" s="53"/>
+      <c r="T5" s="55"/>
+      <c r="U5" s="56"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="55"/>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="57" t="s">
+      <c r="A6" s="58"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="58"/>
-      <c r="L6" s="54" t="s">
+      <c r="K6" s="61"/>
+      <c r="L6" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="57" t="s">
+      <c r="M6" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="58"/>
-      <c r="O6" s="54" t="s">
+      <c r="N6" s="61"/>
+      <c r="O6" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="57" t="s">
+      <c r="P6" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="58"/>
-      <c r="R6" s="54" t="s">
+      <c r="Q6" s="61"/>
+      <c r="R6" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="S6" s="57" t="s">
+      <c r="S6" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="58"/>
-      <c r="U6" s="54" t="s">
+      <c r="T6" s="61"/>
+      <c r="U6" s="57" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="56"/>
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
+      <c r="A7" s="59"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
       <c r="J7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="56"/>
+      <c r="L7" s="59"/>
       <c r="M7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="56"/>
+      <c r="O7" s="59"/>
       <c r="P7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="56"/>
+      <c r="R7" s="59"/>
       <c r="S7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="U7" s="56"/>
+      <c r="U7" s="59"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="61"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="64"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -18448,15 +18448,15 @@
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="62" t="s">
+      <c r="C9" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="64"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="67"/>
       <c r="M9" s="6">
         <f>SUM(M10,M20)</f>
         <v>18303819.899999999</v>
@@ -18492,15 +18492,15 @@
       <c r="B10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="62" t="s">
+      <c r="C10" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="64"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="67"/>
       <c r="M10" s="6">
         <f t="shared" ref="M10:O14" si="0">SUM(M11)</f>
         <v>126283.29</v>
@@ -18536,15 +18536,15 @@
       <c r="B11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="62" t="s">
+      <c r="C11" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="64"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="67"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18580,15 +18580,15 @@
       <c r="B12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="64"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="67"/>
       <c r="M12" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18624,15 +18624,15 @@
       <c r="B13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="62" t="s">
+      <c r="C13" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="64"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="67"/>
       <c r="M13" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18668,15 +18668,15 @@
       <c r="B14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="C14" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="63"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="64"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="67"/>
       <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18967,15 +18967,15 @@
       <c r="B20" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="62" t="s">
+      <c r="C20" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="64"/>
+      <c r="D20" s="66"/>
+      <c r="E20" s="66"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="66"/>
+      <c r="H20" s="66"/>
+      <c r="I20" s="67"/>
       <c r="M20" s="6">
         <f t="shared" ref="M20:O21" si="1">SUM(M21)</f>
         <v>18177536.609999999</v>
@@ -19011,15 +19011,15 @@
       <c r="B21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="62" t="s">
+      <c r="C21" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="63"/>
-      <c r="E21" s="63"/>
-      <c r="F21" s="63"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="63"/>
-      <c r="I21" s="64"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="66"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="67"/>
       <c r="M21" s="6">
         <f t="shared" si="1"/>
         <v>18177536.609999999</v>
@@ -19055,15 +19055,15 @@
       <c r="B22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="62" t="s">
+      <c r="C22" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="63"/>
-      <c r="H22" s="63"/>
-      <c r="I22" s="64"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="67"/>
       <c r="M22" s="6">
         <f>SUM(M23,M122,M163,M203,M248)</f>
         <v>18177536.609999999</v>
@@ -19099,15 +19099,15 @@
       <c r="B23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="62" t="s">
+      <c r="C23" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="64"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="67"/>
       <c r="M23" s="6">
         <f>SUM(M24,M67,M76,M119)</f>
         <v>12831032.07</v>
@@ -19143,15 +19143,15 @@
       <c r="B24" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C24" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="64"/>
+      <c r="D24" s="66"/>
+      <c r="E24" s="66"/>
+      <c r="F24" s="66"/>
+      <c r="G24" s="66"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="67"/>
       <c r="M24" s="6">
         <f>SUM(M25,M29,M31,M34,M36,M41,M46,M51,M57,M62)</f>
         <v>7808423.3099999996</v>
@@ -21375,15 +21375,15 @@
       <c r="B67" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="62" t="s">
+      <c r="C67" s="65" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="63"/>
-      <c r="E67" s="63"/>
-      <c r="F67" s="63"/>
-      <c r="G67" s="63"/>
-      <c r="H67" s="63"/>
-      <c r="I67" s="64"/>
+      <c r="D67" s="66"/>
+      <c r="E67" s="66"/>
+      <c r="F67" s="66"/>
+      <c r="G67" s="66"/>
+      <c r="H67" s="66"/>
+      <c r="I67" s="67"/>
       <c r="M67" s="6">
         <f>SUM(M68,M72,M74)</f>
         <v>748533.11</v>
@@ -21881,15 +21881,15 @@
       <c r="B76" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C76" s="62" t="s">
+      <c r="C76" s="65" t="s">
         <v>325</v>
       </c>
-      <c r="D76" s="63"/>
-      <c r="E76" s="63"/>
-      <c r="F76" s="63"/>
-      <c r="G76" s="63"/>
-      <c r="H76" s="63"/>
-      <c r="I76" s="64"/>
+      <c r="D76" s="66"/>
+      <c r="E76" s="66"/>
+      <c r="F76" s="66"/>
+      <c r="G76" s="66"/>
+      <c r="H76" s="66"/>
+      <c r="I76" s="67"/>
       <c r="M76" s="6">
         <f>SUM(M77,M82,M87,M93,M96,M99,M104,M109,M114,M117)</f>
         <v>3831185.6499999994</v>
@@ -24139,15 +24139,15 @@
       <c r="B119" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C119" s="62" t="s">
+      <c r="C119" s="65" t="s">
         <v>526</v>
       </c>
-      <c r="D119" s="63"/>
-      <c r="E119" s="63"/>
-      <c r="F119" s="63"/>
-      <c r="G119" s="63"/>
-      <c r="H119" s="63"/>
-      <c r="I119" s="64"/>
+      <c r="D119" s="66"/>
+      <c r="E119" s="66"/>
+      <c r="F119" s="66"/>
+      <c r="G119" s="66"/>
+      <c r="H119" s="66"/>
+      <c r="I119" s="67"/>
       <c r="M119" s="6">
         <f>SUM(M120)</f>
         <v>442890</v>
@@ -24309,15 +24309,15 @@
       <c r="B122" s="29" t="s">
         <v>540</v>
       </c>
-      <c r="C122" s="66" t="s">
+      <c r="C122" s="69" t="s">
         <v>541</v>
       </c>
-      <c r="D122" s="67"/>
-      <c r="E122" s="67"/>
-      <c r="F122" s="67"/>
-      <c r="G122" s="67"/>
-      <c r="H122" s="67"/>
-      <c r="I122" s="68"/>
+      <c r="D122" s="70"/>
+      <c r="E122" s="70"/>
+      <c r="F122" s="70"/>
+      <c r="G122" s="70"/>
+      <c r="H122" s="70"/>
+      <c r="I122" s="71"/>
       <c r="J122" s="30"/>
       <c r="M122" s="6">
         <f>SUM(M123)</f>
@@ -24354,15 +24354,15 @@
       <c r="B123" s="29" t="s">
         <v>543</v>
       </c>
-      <c r="C123" s="66" t="s">
+      <c r="C123" s="69" t="s">
         <v>544</v>
       </c>
-      <c r="D123" s="67"/>
-      <c r="E123" s="67"/>
-      <c r="F123" s="67"/>
-      <c r="G123" s="67"/>
-      <c r="H123" s="67"/>
-      <c r="I123" s="68"/>
+      <c r="D123" s="70"/>
+      <c r="E123" s="70"/>
+      <c r="F123" s="70"/>
+      <c r="G123" s="70"/>
+      <c r="H123" s="70"/>
+      <c r="I123" s="71"/>
       <c r="J123" s="30"/>
       <c r="M123" s="6">
         <f>SUM(M124,M127,M131,M136,M140,M143,M148,M153,M158)</f>
@@ -25414,7 +25414,7 @@
       <c r="D143" s="33" t="s">
         <v>641</v>
       </c>
-      <c r="E143" s="70" t="s">
+      <c r="E143" s="46" t="s">
         <v>642</v>
       </c>
       <c r="F143" s="33" t="s">
@@ -25673,7 +25673,7 @@
       <c r="D148" s="11" t="s">
         <v>641</v>
       </c>
-      <c r="E148" s="71" t="s">
+      <c r="E148" s="47" t="s">
         <v>666</v>
       </c>
       <c r="F148" s="11" t="s">
@@ -25935,7 +25935,7 @@
       <c r="D153" s="11" t="s">
         <v>641</v>
       </c>
-      <c r="E153" s="71" t="s">
+      <c r="E153" s="47" t="s">
         <v>680</v>
       </c>
       <c r="F153" s="11" t="s">
@@ -26197,7 +26197,7 @@
       <c r="D158" s="37" t="s">
         <v>641</v>
       </c>
-      <c r="E158" s="69" t="s">
+      <c r="E158" s="45" t="s">
         <v>694</v>
       </c>
       <c r="F158" s="37" t="s">
@@ -26453,15 +26453,15 @@
       <c r="B163" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C163" s="62" t="s">
+      <c r="C163" s="65" t="s">
         <v>710</v>
       </c>
-      <c r="D163" s="63"/>
-      <c r="E163" s="63"/>
-      <c r="F163" s="63"/>
-      <c r="G163" s="63"/>
-      <c r="H163" s="63"/>
-      <c r="I163" s="64"/>
+      <c r="D163" s="66"/>
+      <c r="E163" s="66"/>
+      <c r="F163" s="66"/>
+      <c r="G163" s="66"/>
+      <c r="H163" s="66"/>
+      <c r="I163" s="67"/>
       <c r="M163" s="6">
         <f>SUM(M164,M184)</f>
         <v>611422.71999999997</v>
@@ -26497,15 +26497,15 @@
       <c r="B164" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="C164" s="62" t="s">
+      <c r="C164" s="65" t="s">
         <v>713</v>
       </c>
-      <c r="D164" s="63"/>
-      <c r="E164" s="63"/>
-      <c r="F164" s="63"/>
-      <c r="G164" s="63"/>
-      <c r="H164" s="63"/>
-      <c r="I164" s="64"/>
+      <c r="D164" s="66"/>
+      <c r="E164" s="66"/>
+      <c r="F164" s="66"/>
+      <c r="G164" s="66"/>
+      <c r="H164" s="66"/>
+      <c r="I164" s="67"/>
       <c r="M164" s="6">
         <f>SUM(M165,M171,M174,M178,M182)</f>
         <v>415021.23999999993</v>
@@ -27552,15 +27552,15 @@
       <c r="B184" s="9" t="s">
         <v>789</v>
       </c>
-      <c r="C184" s="62" t="s">
+      <c r="C184" s="65" t="s">
         <v>790</v>
       </c>
-      <c r="D184" s="63"/>
-      <c r="E184" s="63"/>
-      <c r="F184" s="63"/>
-      <c r="G184" s="63"/>
-      <c r="H184" s="63"/>
-      <c r="I184" s="64"/>
+      <c r="D184" s="66"/>
+      <c r="E184" s="66"/>
+      <c r="F184" s="66"/>
+      <c r="G184" s="66"/>
+      <c r="H184" s="66"/>
+      <c r="I184" s="67"/>
       <c r="M184" s="6">
         <f>SUM(M185,M188,M191,M194,M197,M200)</f>
         <v>196401.48</v>
@@ -28610,15 +28610,15 @@
       <c r="B203" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="C203" s="62" t="s">
+      <c r="C203" s="65" t="s">
         <v>856</v>
       </c>
-      <c r="D203" s="63"/>
-      <c r="E203" s="63"/>
-      <c r="F203" s="63"/>
-      <c r="G203" s="63"/>
-      <c r="H203" s="63"/>
-      <c r="I203" s="64"/>
+      <c r="D203" s="66"/>
+      <c r="E203" s="66"/>
+      <c r="F203" s="66"/>
+      <c r="G203" s="66"/>
+      <c r="H203" s="66"/>
+      <c r="I203" s="67"/>
       <c r="M203" s="6">
         <f>SUM(M204,M206,M221,M236,M238,M240,M242,M243,M244,M245,M246,M247)</f>
         <v>719044.50999999989</v>
@@ -31000,15 +31000,15 @@
       <c r="B248" s="9" t="s">
         <v>1031</v>
       </c>
-      <c r="C248" s="62" t="s">
+      <c r="C248" s="65" t="s">
         <v>1032</v>
       </c>
-      <c r="D248" s="63"/>
-      <c r="E248" s="63"/>
-      <c r="F248" s="63"/>
-      <c r="G248" s="63"/>
-      <c r="H248" s="63"/>
-      <c r="I248" s="64"/>
+      <c r="D248" s="66"/>
+      <c r="E248" s="66"/>
+      <c r="F248" s="66"/>
+      <c r="G248" s="66"/>
+      <c r="H248" s="66"/>
+      <c r="I248" s="67"/>
       <c r="M248" s="6">
         <f>SUM(M249,M250,M251,M252)</f>
         <v>0</v>
@@ -31395,29 +31395,29 @@
       </c>
     </row>
     <row r="254" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="59" t="s">
+      <c r="A254" s="62" t="s">
         <v>1050</v>
       </c>
-      <c r="B254" s="60"/>
-      <c r="C254" s="60"/>
-      <c r="D254" s="60"/>
-      <c r="E254" s="60"/>
-      <c r="F254" s="60"/>
-      <c r="G254" s="60"/>
-      <c r="H254" s="60"/>
-      <c r="I254" s="60"/>
-      <c r="J254" s="60"/>
-      <c r="K254" s="60"/>
-      <c r="L254" s="60"/>
-      <c r="M254" s="60"/>
-      <c r="N254" s="60"/>
-      <c r="O254" s="60"/>
-      <c r="P254" s="60"/>
-      <c r="Q254" s="60"/>
-      <c r="R254" s="60"/>
-      <c r="S254" s="60"/>
-      <c r="T254" s="60"/>
-      <c r="U254" s="61"/>
+      <c r="B254" s="63"/>
+      <c r="C254" s="63"/>
+      <c r="D254" s="63"/>
+      <c r="E254" s="63"/>
+      <c r="F254" s="63"/>
+      <c r="G254" s="63"/>
+      <c r="H254" s="63"/>
+      <c r="I254" s="63"/>
+      <c r="J254" s="63"/>
+      <c r="K254" s="63"/>
+      <c r="L254" s="63"/>
+      <c r="M254" s="63"/>
+      <c r="N254" s="63"/>
+      <c r="O254" s="63"/>
+      <c r="P254" s="63"/>
+      <c r="Q254" s="63"/>
+      <c r="R254" s="63"/>
+      <c r="S254" s="63"/>
+      <c r="T254" s="63"/>
+      <c r="U254" s="64"/>
     </row>
     <row r="255" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="27"/>
@@ -31433,20 +31433,20 @@
       <c r="E255" s="28"/>
       <c r="F255" s="28"/>
       <c r="G255" s="28"/>
-      <c r="H255" s="57"/>
-      <c r="I255" s="65"/>
-      <c r="J255" s="65"/>
-      <c r="K255" s="65"/>
-      <c r="L255" s="65"/>
-      <c r="M255" s="65"/>
-      <c r="N255" s="65"/>
-      <c r="O255" s="65"/>
-      <c r="P255" s="65"/>
-      <c r="Q255" s="65"/>
-      <c r="R255" s="65"/>
-      <c r="S255" s="65"/>
-      <c r="T255" s="65"/>
-      <c r="U255" s="58"/>
+      <c r="H255" s="60"/>
+      <c r="I255" s="68"/>
+      <c r="J255" s="68"/>
+      <c r="K255" s="68"/>
+      <c r="L255" s="68"/>
+      <c r="M255" s="68"/>
+      <c r="N255" s="68"/>
+      <c r="O255" s="68"/>
+      <c r="P255" s="68"/>
+      <c r="Q255" s="68"/>
+      <c r="R255" s="68"/>
+      <c r="S255" s="68"/>
+      <c r="T255" s="68"/>
+      <c r="U255" s="61"/>
     </row>
     <row r="256" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="27"/>
@@ -31462,20 +31462,20 @@
       <c r="E256" s="28"/>
       <c r="F256" s="28"/>
       <c r="G256" s="28"/>
-      <c r="H256" s="57"/>
-      <c r="I256" s="65"/>
-      <c r="J256" s="65"/>
-      <c r="K256" s="65"/>
-      <c r="L256" s="65"/>
-      <c r="M256" s="65"/>
-      <c r="N256" s="65"/>
-      <c r="O256" s="65"/>
-      <c r="P256" s="65"/>
-      <c r="Q256" s="65"/>
-      <c r="R256" s="65"/>
-      <c r="S256" s="65"/>
-      <c r="T256" s="65"/>
-      <c r="U256" s="58"/>
+      <c r="H256" s="60"/>
+      <c r="I256" s="68"/>
+      <c r="J256" s="68"/>
+      <c r="K256" s="68"/>
+      <c r="L256" s="68"/>
+      <c r="M256" s="68"/>
+      <c r="N256" s="68"/>
+      <c r="O256" s="68"/>
+      <c r="P256" s="68"/>
+      <c r="Q256" s="68"/>
+      <c r="R256" s="68"/>
+      <c r="S256" s="68"/>
+      <c r="T256" s="68"/>
+      <c r="U256" s="61"/>
     </row>
     <row r="257" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A257" s="27"/>
@@ -31491,20 +31491,20 @@
       <c r="E257" s="28"/>
       <c r="F257" s="28"/>
       <c r="G257" s="28"/>
-      <c r="H257" s="57"/>
-      <c r="I257" s="65"/>
-      <c r="J257" s="65"/>
-      <c r="K257" s="65"/>
-      <c r="L257" s="65"/>
-      <c r="M257" s="65"/>
-      <c r="N257" s="65"/>
-      <c r="O257" s="65"/>
-      <c r="P257" s="65"/>
-      <c r="Q257" s="65"/>
-      <c r="R257" s="65"/>
-      <c r="S257" s="65"/>
-      <c r="T257" s="65"/>
-      <c r="U257" s="58"/>
+      <c r="H257" s="60"/>
+      <c r="I257" s="68"/>
+      <c r="J257" s="68"/>
+      <c r="K257" s="68"/>
+      <c r="L257" s="68"/>
+      <c r="M257" s="68"/>
+      <c r="N257" s="68"/>
+      <c r="O257" s="68"/>
+      <c r="P257" s="68"/>
+      <c r="Q257" s="68"/>
+      <c r="R257" s="68"/>
+      <c r="S257" s="68"/>
+      <c r="T257" s="68"/>
+      <c r="U257" s="61"/>
     </row>
     <row r="258" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="27"/>
@@ -31520,20 +31520,20 @@
       <c r="E258" s="28"/>
       <c r="F258" s="28"/>
       <c r="G258" s="28"/>
-      <c r="H258" s="57"/>
-      <c r="I258" s="65"/>
-      <c r="J258" s="65"/>
-      <c r="K258" s="65"/>
-      <c r="L258" s="65"/>
-      <c r="M258" s="65"/>
-      <c r="N258" s="65"/>
-      <c r="O258" s="65"/>
-      <c r="P258" s="65"/>
-      <c r="Q258" s="65"/>
-      <c r="R258" s="65"/>
-      <c r="S258" s="65"/>
-      <c r="T258" s="65"/>
-      <c r="U258" s="58"/>
+      <c r="H258" s="60"/>
+      <c r="I258" s="68"/>
+      <c r="J258" s="68"/>
+      <c r="K258" s="68"/>
+      <c r="L258" s="68"/>
+      <c r="M258" s="68"/>
+      <c r="N258" s="68"/>
+      <c r="O258" s="68"/>
+      <c r="P258" s="68"/>
+      <c r="Q258" s="68"/>
+      <c r="R258" s="68"/>
+      <c r="S258" s="68"/>
+      <c r="T258" s="68"/>
+      <c r="U258" s="61"/>
     </row>
     <row r="259" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="27"/>
@@ -31549,20 +31549,20 @@
       <c r="E259" s="28"/>
       <c r="F259" s="28"/>
       <c r="G259" s="28"/>
-      <c r="H259" s="57"/>
-      <c r="I259" s="65"/>
-      <c r="J259" s="65"/>
-      <c r="K259" s="65"/>
-      <c r="L259" s="65"/>
-      <c r="M259" s="65"/>
-      <c r="N259" s="65"/>
-      <c r="O259" s="65"/>
-      <c r="P259" s="65"/>
-      <c r="Q259" s="65"/>
-      <c r="R259" s="65"/>
-      <c r="S259" s="65"/>
-      <c r="T259" s="65"/>
-      <c r="U259" s="58"/>
+      <c r="H259" s="60"/>
+      <c r="I259" s="68"/>
+      <c r="J259" s="68"/>
+      <c r="K259" s="68"/>
+      <c r="L259" s="68"/>
+      <c r="M259" s="68"/>
+      <c r="N259" s="68"/>
+      <c r="O259" s="68"/>
+      <c r="P259" s="68"/>
+      <c r="Q259" s="68"/>
+      <c r="R259" s="68"/>
+      <c r="S259" s="68"/>
+      <c r="T259" s="68"/>
+      <c r="U259" s="61"/>
     </row>
     <row r="260" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A260" s="27"/>
@@ -31578,20 +31578,20 @@
       <c r="E260" s="28"/>
       <c r="F260" s="28"/>
       <c r="G260" s="28"/>
-      <c r="H260" s="57"/>
-      <c r="I260" s="65"/>
-      <c r="J260" s="65"/>
-      <c r="K260" s="65"/>
-      <c r="L260" s="65"/>
-      <c r="M260" s="65"/>
-      <c r="N260" s="65"/>
-      <c r="O260" s="65"/>
-      <c r="P260" s="65"/>
-      <c r="Q260" s="65"/>
-      <c r="R260" s="65"/>
-      <c r="S260" s="65"/>
-      <c r="T260" s="65"/>
-      <c r="U260" s="58"/>
+      <c r="H260" s="60"/>
+      <c r="I260" s="68"/>
+      <c r="J260" s="68"/>
+      <c r="K260" s="68"/>
+      <c r="L260" s="68"/>
+      <c r="M260" s="68"/>
+      <c r="N260" s="68"/>
+      <c r="O260" s="68"/>
+      <c r="P260" s="68"/>
+      <c r="Q260" s="68"/>
+      <c r="R260" s="68"/>
+      <c r="S260" s="68"/>
+      <c r="T260" s="68"/>
+      <c r="U260" s="61"/>
     </row>
     <row r="261" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A261" s="27"/>
@@ -31607,20 +31607,20 @@
       <c r="E261" s="28"/>
       <c r="F261" s="28"/>
       <c r="G261" s="28"/>
-      <c r="H261" s="57"/>
-      <c r="I261" s="65"/>
-      <c r="J261" s="65"/>
-      <c r="K261" s="65"/>
-      <c r="L261" s="65"/>
-      <c r="M261" s="65"/>
-      <c r="N261" s="65"/>
-      <c r="O261" s="65"/>
-      <c r="P261" s="65"/>
-      <c r="Q261" s="65"/>
-      <c r="R261" s="65"/>
-      <c r="S261" s="65"/>
-      <c r="T261" s="65"/>
-      <c r="U261" s="58"/>
+      <c r="H261" s="60"/>
+      <c r="I261" s="68"/>
+      <c r="J261" s="68"/>
+      <c r="K261" s="68"/>
+      <c r="L261" s="68"/>
+      <c r="M261" s="68"/>
+      <c r="N261" s="68"/>
+      <c r="O261" s="68"/>
+      <c r="P261" s="68"/>
+      <c r="Q261" s="68"/>
+      <c r="R261" s="68"/>
+      <c r="S261" s="68"/>
+      <c r="T261" s="68"/>
+      <c r="U261" s="61"/>
     </row>
     <row r="262" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="27"/>
@@ -31636,20 +31636,20 @@
       <c r="E262" s="28"/>
       <c r="F262" s="28"/>
       <c r="G262" s="28"/>
-      <c r="H262" s="57"/>
-      <c r="I262" s="65"/>
-      <c r="J262" s="65"/>
-      <c r="K262" s="65"/>
-      <c r="L262" s="65"/>
-      <c r="M262" s="65"/>
-      <c r="N262" s="65"/>
-      <c r="O262" s="65"/>
-      <c r="P262" s="65"/>
-      <c r="Q262" s="65"/>
-      <c r="R262" s="65"/>
-      <c r="S262" s="65"/>
-      <c r="T262" s="65"/>
-      <c r="U262" s="58"/>
+      <c r="H262" s="60"/>
+      <c r="I262" s="68"/>
+      <c r="J262" s="68"/>
+      <c r="K262" s="68"/>
+      <c r="L262" s="68"/>
+      <c r="M262" s="68"/>
+      <c r="N262" s="68"/>
+      <c r="O262" s="68"/>
+      <c r="P262" s="68"/>
+      <c r="Q262" s="68"/>
+      <c r="R262" s="68"/>
+      <c r="S262" s="68"/>
+      <c r="T262" s="68"/>
+      <c r="U262" s="61"/>
     </row>
     <row r="263" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="27"/>
@@ -31665,20 +31665,20 @@
       <c r="E263" s="28"/>
       <c r="F263" s="28"/>
       <c r="G263" s="28"/>
-      <c r="H263" s="57"/>
-      <c r="I263" s="65"/>
-      <c r="J263" s="65"/>
-      <c r="K263" s="65"/>
-      <c r="L263" s="65"/>
-      <c r="M263" s="65"/>
-      <c r="N263" s="65"/>
-      <c r="O263" s="65"/>
-      <c r="P263" s="65"/>
-      <c r="Q263" s="65"/>
-      <c r="R263" s="65"/>
-      <c r="S263" s="65"/>
-      <c r="T263" s="65"/>
-      <c r="U263" s="58"/>
+      <c r="H263" s="60"/>
+      <c r="I263" s="68"/>
+      <c r="J263" s="68"/>
+      <c r="K263" s="68"/>
+      <c r="L263" s="68"/>
+      <c r="M263" s="68"/>
+      <c r="N263" s="68"/>
+      <c r="O263" s="68"/>
+      <c r="P263" s="68"/>
+      <c r="Q263" s="68"/>
+      <c r="R263" s="68"/>
+      <c r="S263" s="68"/>
+      <c r="T263" s="68"/>
+      <c r="U263" s="61"/>
     </row>
     <row r="264" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A264" s="27"/>
@@ -31694,20 +31694,20 @@
       <c r="E264" s="28"/>
       <c r="F264" s="28"/>
       <c r="G264" s="28"/>
-      <c r="H264" s="57"/>
-      <c r="I264" s="65"/>
-      <c r="J264" s="65"/>
-      <c r="K264" s="65"/>
-      <c r="L264" s="65"/>
-      <c r="M264" s="65"/>
-      <c r="N264" s="65"/>
-      <c r="O264" s="65"/>
-      <c r="P264" s="65"/>
-      <c r="Q264" s="65"/>
-      <c r="R264" s="65"/>
-      <c r="S264" s="65"/>
-      <c r="T264" s="65"/>
-      <c r="U264" s="58"/>
+      <c r="H264" s="60"/>
+      <c r="I264" s="68"/>
+      <c r="J264" s="68"/>
+      <c r="K264" s="68"/>
+      <c r="L264" s="68"/>
+      <c r="M264" s="68"/>
+      <c r="N264" s="68"/>
+      <c r="O264" s="68"/>
+      <c r="P264" s="68"/>
+      <c r="Q264" s="68"/>
+      <c r="R264" s="68"/>
+      <c r="S264" s="68"/>
+      <c r="T264" s="68"/>
+      <c r="U264" s="61"/>
     </row>
     <row r="265" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A265" s="27"/>
@@ -31723,20 +31723,20 @@
       <c r="E265" s="28"/>
       <c r="F265" s="28"/>
       <c r="G265" s="28"/>
-      <c r="H265" s="57"/>
-      <c r="I265" s="65"/>
-      <c r="J265" s="65"/>
-      <c r="K265" s="65"/>
-      <c r="L265" s="65"/>
-      <c r="M265" s="65"/>
-      <c r="N265" s="65"/>
-      <c r="O265" s="65"/>
-      <c r="P265" s="65"/>
-      <c r="Q265" s="65"/>
-      <c r="R265" s="65"/>
-      <c r="S265" s="65"/>
-      <c r="T265" s="65"/>
-      <c r="U265" s="58"/>
+      <c r="H265" s="60"/>
+      <c r="I265" s="68"/>
+      <c r="J265" s="68"/>
+      <c r="K265" s="68"/>
+      <c r="L265" s="68"/>
+      <c r="M265" s="68"/>
+      <c r="N265" s="68"/>
+      <c r="O265" s="68"/>
+      <c r="P265" s="68"/>
+      <c r="Q265" s="68"/>
+      <c r="R265" s="68"/>
+      <c r="S265" s="68"/>
+      <c r="T265" s="68"/>
+      <c r="U265" s="61"/>
     </row>
     <row r="266" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A266" s="27"/>
@@ -31752,20 +31752,20 @@
       <c r="E266" s="28"/>
       <c r="F266" s="28"/>
       <c r="G266" s="28"/>
-      <c r="H266" s="57"/>
-      <c r="I266" s="65"/>
-      <c r="J266" s="65"/>
-      <c r="K266" s="65"/>
-      <c r="L266" s="65"/>
-      <c r="M266" s="65"/>
-      <c r="N266" s="65"/>
-      <c r="O266" s="65"/>
-      <c r="P266" s="65"/>
-      <c r="Q266" s="65"/>
-      <c r="R266" s="65"/>
-      <c r="S266" s="65"/>
-      <c r="T266" s="65"/>
-      <c r="U266" s="58"/>
+      <c r="H266" s="60"/>
+      <c r="I266" s="68"/>
+      <c r="J266" s="68"/>
+      <c r="K266" s="68"/>
+      <c r="L266" s="68"/>
+      <c r="M266" s="68"/>
+      <c r="N266" s="68"/>
+      <c r="O266" s="68"/>
+      <c r="P266" s="68"/>
+      <c r="Q266" s="68"/>
+      <c r="R266" s="68"/>
+      <c r="S266" s="68"/>
+      <c r="T266" s="68"/>
+      <c r="U266" s="61"/>
     </row>
     <row r="267" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="27"/>
@@ -31781,20 +31781,20 @@
       <c r="E267" s="28"/>
       <c r="F267" s="28"/>
       <c r="G267" s="28"/>
-      <c r="H267" s="57"/>
-      <c r="I267" s="65"/>
-      <c r="J267" s="65"/>
-      <c r="K267" s="65"/>
-      <c r="L267" s="65"/>
-      <c r="M267" s="65"/>
-      <c r="N267" s="65"/>
-      <c r="O267" s="65"/>
-      <c r="P267" s="65"/>
-      <c r="Q267" s="65"/>
-      <c r="R267" s="65"/>
-      <c r="S267" s="65"/>
-      <c r="T267" s="65"/>
-      <c r="U267" s="58"/>
+      <c r="H267" s="60"/>
+      <c r="I267" s="68"/>
+      <c r="J267" s="68"/>
+      <c r="K267" s="68"/>
+      <c r="L267" s="68"/>
+      <c r="M267" s="68"/>
+      <c r="N267" s="68"/>
+      <c r="O267" s="68"/>
+      <c r="P267" s="68"/>
+      <c r="Q267" s="68"/>
+      <c r="R267" s="68"/>
+      <c r="S267" s="68"/>
+      <c r="T267" s="68"/>
+      <c r="U267" s="61"/>
     </row>
     <row r="268" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="27"/>
@@ -31810,22 +31810,22 @@
       <c r="E268" s="28"/>
       <c r="F268" s="28"/>
       <c r="G268" s="28"/>
-      <c r="H268" s="57" t="s">
+      <c r="H268" s="60" t="s">
         <v>1092</v>
       </c>
-      <c r="I268" s="65"/>
-      <c r="J268" s="65"/>
-      <c r="K268" s="65"/>
-      <c r="L268" s="65"/>
-      <c r="M268" s="65"/>
-      <c r="N268" s="65"/>
-      <c r="O268" s="65"/>
-      <c r="P268" s="65"/>
-      <c r="Q268" s="65"/>
-      <c r="R268" s="65"/>
-      <c r="S268" s="65"/>
-      <c r="T268" s="65"/>
-      <c r="U268" s="58"/>
+      <c r="I268" s="68"/>
+      <c r="J268" s="68"/>
+      <c r="K268" s="68"/>
+      <c r="L268" s="68"/>
+      <c r="M268" s="68"/>
+      <c r="N268" s="68"/>
+      <c r="O268" s="68"/>
+      <c r="P268" s="68"/>
+      <c r="Q268" s="68"/>
+      <c r="R268" s="68"/>
+      <c r="S268" s="68"/>
+      <c r="T268" s="68"/>
+      <c r="U268" s="61"/>
     </row>
     <row r="269" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="27"/>
@@ -31841,20 +31841,20 @@
       <c r="E269" s="28"/>
       <c r="F269" s="28"/>
       <c r="G269" s="28"/>
-      <c r="H269" s="57"/>
-      <c r="I269" s="65"/>
-      <c r="J269" s="65"/>
-      <c r="K269" s="65"/>
-      <c r="L269" s="65"/>
-      <c r="M269" s="65"/>
-      <c r="N269" s="65"/>
-      <c r="O269" s="65"/>
-      <c r="P269" s="65"/>
-      <c r="Q269" s="65"/>
-      <c r="R269" s="65"/>
-      <c r="S269" s="65"/>
-      <c r="T269" s="65"/>
-      <c r="U269" s="58"/>
+      <c r="H269" s="60"/>
+      <c r="I269" s="68"/>
+      <c r="J269" s="68"/>
+      <c r="K269" s="68"/>
+      <c r="L269" s="68"/>
+      <c r="M269" s="68"/>
+      <c r="N269" s="68"/>
+      <c r="O269" s="68"/>
+      <c r="P269" s="68"/>
+      <c r="Q269" s="68"/>
+      <c r="R269" s="68"/>
+      <c r="S269" s="68"/>
+      <c r="T269" s="68"/>
+      <c r="U269" s="61"/>
     </row>
     <row r="270" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A270" s="27"/>
@@ -31868,20 +31868,20 @@
       <c r="E270" s="28"/>
       <c r="F270" s="28"/>
       <c r="G270" s="28"/>
-      <c r="H270" s="57"/>
-      <c r="I270" s="65"/>
-      <c r="J270" s="65"/>
-      <c r="K270" s="65"/>
-      <c r="L270" s="65"/>
-      <c r="M270" s="65"/>
-      <c r="N270" s="65"/>
-      <c r="O270" s="65"/>
-      <c r="P270" s="65"/>
-      <c r="Q270" s="65"/>
-      <c r="R270" s="65"/>
-      <c r="S270" s="65"/>
-      <c r="T270" s="65"/>
-      <c r="U270" s="58"/>
+      <c r="H270" s="60"/>
+      <c r="I270" s="68"/>
+      <c r="J270" s="68"/>
+      <c r="K270" s="68"/>
+      <c r="L270" s="68"/>
+      <c r="M270" s="68"/>
+      <c r="N270" s="68"/>
+      <c r="O270" s="68"/>
+      <c r="P270" s="68"/>
+      <c r="Q270" s="68"/>
+      <c r="R270" s="68"/>
+      <c r="S270" s="68"/>
+      <c r="T270" s="68"/>
+      <c r="U270" s="61"/>
     </row>
     <row r="271" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="27"/>
@@ -31895,20 +31895,20 @@
       <c r="E271" s="28"/>
       <c r="F271" s="28"/>
       <c r="G271" s="28"/>
-      <c r="H271" s="57"/>
-      <c r="I271" s="65"/>
-      <c r="J271" s="65"/>
-      <c r="K271" s="65"/>
-      <c r="L271" s="65"/>
-      <c r="M271" s="65"/>
-      <c r="N271" s="65"/>
-      <c r="O271" s="65"/>
-      <c r="P271" s="65"/>
-      <c r="Q271" s="65"/>
-      <c r="R271" s="65"/>
-      <c r="S271" s="65"/>
-      <c r="T271" s="65"/>
-      <c r="U271" s="58"/>
+      <c r="H271" s="60"/>
+      <c r="I271" s="68"/>
+      <c r="J271" s="68"/>
+      <c r="K271" s="68"/>
+      <c r="L271" s="68"/>
+      <c r="M271" s="68"/>
+      <c r="N271" s="68"/>
+      <c r="O271" s="68"/>
+      <c r="P271" s="68"/>
+      <c r="Q271" s="68"/>
+      <c r="R271" s="68"/>
+      <c r="S271" s="68"/>
+      <c r="T271" s="68"/>
+      <c r="U271" s="61"/>
     </row>
     <row r="272" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="27"/>
@@ -31922,20 +31922,20 @@
       <c r="E272" s="28"/>
       <c r="F272" s="28"/>
       <c r="G272" s="28"/>
-      <c r="H272" s="57"/>
-      <c r="I272" s="65"/>
-      <c r="J272" s="65"/>
-      <c r="K272" s="65"/>
-      <c r="L272" s="65"/>
-      <c r="M272" s="65"/>
-      <c r="N272" s="65"/>
-      <c r="O272" s="65"/>
-      <c r="P272" s="65"/>
-      <c r="Q272" s="65"/>
-      <c r="R272" s="65"/>
-      <c r="S272" s="65"/>
-      <c r="T272" s="65"/>
-      <c r="U272" s="58"/>
+      <c r="H272" s="60"/>
+      <c r="I272" s="68"/>
+      <c r="J272" s="68"/>
+      <c r="K272" s="68"/>
+      <c r="L272" s="68"/>
+      <c r="M272" s="68"/>
+      <c r="N272" s="68"/>
+      <c r="O272" s="68"/>
+      <c r="P272" s="68"/>
+      <c r="Q272" s="68"/>
+      <c r="R272" s="68"/>
+      <c r="S272" s="68"/>
+      <c r="T272" s="68"/>
+      <c r="U272" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="64">

--- a/school_lublino/lublino_KP.xlsx
+++ b/school_lublino/lublino_KP.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" activeTab="1"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ТКП" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3336" uniqueCount="1103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3338" uniqueCount="1105">
   <si>
     <t>Указать название организации (на бланке организации)</t>
   </si>
@@ -3460,6 +3460,12 @@
 200 мм
 58,61кв.м* 0,2*1,03=12,07 куб.м</t>
   </si>
+  <si>
+    <t>Сделать</t>
+  </si>
+  <si>
+    <t>сделать</t>
+  </si>
 </sst>
 </file>
 
@@ -3479,73 +3485,99 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF2F5487"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <i/>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF800000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="14"/>
@@ -3563,7 +3595,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3609,6 +3641,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3714,7 +3758,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3845,6 +3889,27 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3918,6 +3983,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4308,217 +4376,217 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="55"/>
+      <c r="T2" s="55"/>
+      <c r="U2" s="55"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="49"/>
-      <c r="O3" s="49"/>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="49"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56"/>
+      <c r="N3" s="56"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="56"/>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="56"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="56"/>
+      <c r="U3" s="56"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
+      <c r="Q4" s="57"/>
+      <c r="R4" s="57"/>
+      <c r="S4" s="57"/>
+      <c r="T4" s="57"/>
+      <c r="U4" s="57"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="57" t="s">
+      <c r="B5" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="C5" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="57" t="s">
+      <c r="D5" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="57" t="s">
+      <c r="E5" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="57" t="s">
+      <c r="F5" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="57" t="s">
+      <c r="G5" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="57" t="s">
+      <c r="H5" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="57" t="s">
+      <c r="I5" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="51" t="s">
+      <c r="J5" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="53"/>
-      <c r="P5" s="54" t="s">
+      <c r="K5" s="59"/>
+      <c r="L5" s="59"/>
+      <c r="M5" s="59"/>
+      <c r="N5" s="59"/>
+      <c r="O5" s="60"/>
+      <c r="P5" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="56"/>
-      <c r="S5" s="54" t="s">
+      <c r="Q5" s="62"/>
+      <c r="R5" s="63"/>
+      <c r="S5" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="55"/>
-      <c r="U5" s="56"/>
+      <c r="T5" s="62"/>
+      <c r="U5" s="63"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="58"/>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="60" t="s">
+      <c r="A6" s="65"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="61"/>
-      <c r="L6" s="57" t="s">
+      <c r="K6" s="68"/>
+      <c r="L6" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="60" t="s">
+      <c r="M6" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="61"/>
-      <c r="O6" s="57" t="s">
+      <c r="N6" s="68"/>
+      <c r="O6" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="60" t="s">
+      <c r="P6" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="57" t="s">
+      <c r="Q6" s="68"/>
+      <c r="R6" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="S6" s="60" t="s">
+      <c r="S6" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="61"/>
-      <c r="U6" s="57" t="s">
+      <c r="T6" s="68"/>
+      <c r="U6" s="64" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="59"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
+      <c r="A7" s="66"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
       <c r="J7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="59"/>
+      <c r="L7" s="66"/>
       <c r="M7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="59"/>
+      <c r="O7" s="66"/>
       <c r="P7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="59"/>
+      <c r="R7" s="66"/>
       <c r="S7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="U7" s="59"/>
+      <c r="U7" s="66"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="64"/>
+      <c r="B8" s="70"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="71"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -4560,15 +4628,15 @@
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="65" t="s">
+      <c r="C9" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="67"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="74"/>
       <c r="M9" s="6">
         <f>SUM(M10,M20)</f>
         <v>18303819.899999999</v>
@@ -4604,15 +4672,15 @@
       <c r="B10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="65" t="s">
+      <c r="C10" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="67"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="74"/>
       <c r="M10" s="6">
         <f t="shared" ref="M10:O14" si="0">SUM(M11)</f>
         <v>126283.29</v>
@@ -4648,15 +4716,15 @@
       <c r="B11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="65" t="s">
+      <c r="C11" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="67"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="74"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4692,15 +4760,15 @@
       <c r="B12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="65" t="s">
+      <c r="C12" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
-      <c r="I12" s="67"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="74"/>
       <c r="M12" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4736,15 +4804,15 @@
       <c r="B13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="65" t="s">
+      <c r="C13" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="67"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="74"/>
       <c r="M13" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4780,15 +4848,15 @@
       <c r="B14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="67"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="74"/>
       <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -5079,15 +5147,15 @@
       <c r="B20" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="65" t="s">
+      <c r="C20" s="72" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="66"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="66"/>
-      <c r="G20" s="66"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="67"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="74"/>
       <c r="M20" s="6">
         <f t="shared" ref="M20:O21" si="1">SUM(M21)</f>
         <v>18177536.609999999</v>
@@ -5123,15 +5191,15 @@
       <c r="B21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="65" t="s">
+      <c r="C21" s="72" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="66"/>
-      <c r="E21" s="66"/>
-      <c r="F21" s="66"/>
-      <c r="G21" s="66"/>
-      <c r="H21" s="66"/>
-      <c r="I21" s="67"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="74"/>
       <c r="M21" s="6">
         <f t="shared" si="1"/>
         <v>18177536.609999999</v>
@@ -5167,15 +5235,15 @@
       <c r="B22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="65" t="s">
+      <c r="C22" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="67"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="74"/>
       <c r="M22" s="6">
         <f>SUM(M23,M122,M163,M203,M248)</f>
         <v>18177536.609999999</v>
@@ -5211,15 +5279,15 @@
       <c r="B23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="65" t="s">
+      <c r="C23" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="66"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="67"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="74"/>
       <c r="M23" s="6">
         <f>SUM(M24,M67,M76,M119)</f>
         <v>12831032.07</v>
@@ -5255,15 +5323,15 @@
       <c r="B24" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="65" t="s">
+      <c r="C24" s="72" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="66"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="66"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="67"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="74"/>
       <c r="M24" s="6">
         <f>SUM(M25,M29,M31,M34,M36,M41,M46,M51,M57,M62)</f>
         <v>7808423.3099999996</v>
@@ -7487,15 +7555,15 @@
       <c r="B67" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="65" t="s">
+      <c r="C67" s="72" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="66"/>
-      <c r="E67" s="66"/>
-      <c r="F67" s="66"/>
-      <c r="G67" s="66"/>
-      <c r="H67" s="66"/>
-      <c r="I67" s="67"/>
+      <c r="D67" s="73"/>
+      <c r="E67" s="73"/>
+      <c r="F67" s="73"/>
+      <c r="G67" s="73"/>
+      <c r="H67" s="73"/>
+      <c r="I67" s="74"/>
       <c r="M67" s="6">
         <f>SUM(M68,M72,M74)</f>
         <v>748533.11</v>
@@ -7993,15 +8061,15 @@
       <c r="B76" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C76" s="65" t="s">
+      <c r="C76" s="72" t="s">
         <v>325</v>
       </c>
-      <c r="D76" s="66"/>
-      <c r="E76" s="66"/>
-      <c r="F76" s="66"/>
-      <c r="G76" s="66"/>
-      <c r="H76" s="66"/>
-      <c r="I76" s="67"/>
+      <c r="D76" s="73"/>
+      <c r="E76" s="73"/>
+      <c r="F76" s="73"/>
+      <c r="G76" s="73"/>
+      <c r="H76" s="73"/>
+      <c r="I76" s="74"/>
       <c r="M76" s="6">
         <f>SUM(M77,M82,M87,M93,M96,M99,M104,M109,M114,M117)</f>
         <v>3831185.6499999994</v>
@@ -10251,15 +10319,15 @@
       <c r="B119" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C119" s="65" t="s">
+      <c r="C119" s="72" t="s">
         <v>526</v>
       </c>
-      <c r="D119" s="66"/>
-      <c r="E119" s="66"/>
-      <c r="F119" s="66"/>
-      <c r="G119" s="66"/>
-      <c r="H119" s="66"/>
-      <c r="I119" s="67"/>
+      <c r="D119" s="73"/>
+      <c r="E119" s="73"/>
+      <c r="F119" s="73"/>
+      <c r="G119" s="73"/>
+      <c r="H119" s="73"/>
+      <c r="I119" s="74"/>
       <c r="M119" s="6">
         <f>SUM(M120)</f>
         <v>442890</v>
@@ -10421,15 +10489,15 @@
       <c r="B122" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="C122" s="65" t="s">
+      <c r="C122" s="72" t="s">
         <v>541</v>
       </c>
-      <c r="D122" s="66"/>
-      <c r="E122" s="66"/>
-      <c r="F122" s="66"/>
-      <c r="G122" s="66"/>
-      <c r="H122" s="66"/>
-      <c r="I122" s="67"/>
+      <c r="D122" s="73"/>
+      <c r="E122" s="73"/>
+      <c r="F122" s="73"/>
+      <c r="G122" s="73"/>
+      <c r="H122" s="73"/>
+      <c r="I122" s="74"/>
       <c r="M122" s="6">
         <f>SUM(M123)</f>
         <v>4016037.31</v>
@@ -10465,15 +10533,15 @@
       <c r="B123" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="C123" s="65" t="s">
+      <c r="C123" s="72" t="s">
         <v>544</v>
       </c>
-      <c r="D123" s="66"/>
-      <c r="E123" s="66"/>
-      <c r="F123" s="66"/>
-      <c r="G123" s="66"/>
-      <c r="H123" s="66"/>
-      <c r="I123" s="67"/>
+      <c r="D123" s="73"/>
+      <c r="E123" s="73"/>
+      <c r="F123" s="73"/>
+      <c r="G123" s="73"/>
+      <c r="H123" s="73"/>
+      <c r="I123" s="74"/>
       <c r="M123" s="6">
         <f>SUM(M124,M127,M131,M136,M140,M143,M148,M153,M158)</f>
         <v>4016037.31</v>
@@ -12554,15 +12622,15 @@
       <c r="B163" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C163" s="65" t="s">
+      <c r="C163" s="72" t="s">
         <v>710</v>
       </c>
-      <c r="D163" s="66"/>
-      <c r="E163" s="66"/>
-      <c r="F163" s="66"/>
-      <c r="G163" s="66"/>
-      <c r="H163" s="66"/>
-      <c r="I163" s="67"/>
+      <c r="D163" s="73"/>
+      <c r="E163" s="73"/>
+      <c r="F163" s="73"/>
+      <c r="G163" s="73"/>
+      <c r="H163" s="73"/>
+      <c r="I163" s="74"/>
       <c r="M163" s="6">
         <f>SUM(M164,M184)</f>
         <v>611422.71999999997</v>
@@ -12598,15 +12666,15 @@
       <c r="B164" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="C164" s="65" t="s">
+      <c r="C164" s="72" t="s">
         <v>713</v>
       </c>
-      <c r="D164" s="66"/>
-      <c r="E164" s="66"/>
-      <c r="F164" s="66"/>
-      <c r="G164" s="66"/>
-      <c r="H164" s="66"/>
-      <c r="I164" s="67"/>
+      <c r="D164" s="73"/>
+      <c r="E164" s="73"/>
+      <c r="F164" s="73"/>
+      <c r="G164" s="73"/>
+      <c r="H164" s="73"/>
+      <c r="I164" s="74"/>
       <c r="M164" s="6">
         <f>SUM(M165,M171,M174,M178,M182)</f>
         <v>415021.23999999993</v>
@@ -13653,15 +13721,15 @@
       <c r="B184" s="9" t="s">
         <v>789</v>
       </c>
-      <c r="C184" s="65" t="s">
+      <c r="C184" s="72" t="s">
         <v>790</v>
       </c>
-      <c r="D184" s="66"/>
-      <c r="E184" s="66"/>
-      <c r="F184" s="66"/>
-      <c r="G184" s="66"/>
-      <c r="H184" s="66"/>
-      <c r="I184" s="67"/>
+      <c r="D184" s="73"/>
+      <c r="E184" s="73"/>
+      <c r="F184" s="73"/>
+      <c r="G184" s="73"/>
+      <c r="H184" s="73"/>
+      <c r="I184" s="74"/>
       <c r="M184" s="6">
         <f>SUM(M185,M188,M191,M194,M197,M200)</f>
         <v>196401.48</v>
@@ -14711,15 +14779,15 @@
       <c r="B203" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="C203" s="65" t="s">
+      <c r="C203" s="72" t="s">
         <v>856</v>
       </c>
-      <c r="D203" s="66"/>
-      <c r="E203" s="66"/>
-      <c r="F203" s="66"/>
-      <c r="G203" s="66"/>
-      <c r="H203" s="66"/>
-      <c r="I203" s="67"/>
+      <c r="D203" s="73"/>
+      <c r="E203" s="73"/>
+      <c r="F203" s="73"/>
+      <c r="G203" s="73"/>
+      <c r="H203" s="73"/>
+      <c r="I203" s="74"/>
       <c r="M203" s="6">
         <f>SUM(M204,M206,M221,M236,M238,M240,M242,M243,M244,M245,M246,M247)</f>
         <v>719044.50999999989</v>
@@ -17101,15 +17169,15 @@
       <c r="B248" s="9" t="s">
         <v>1031</v>
       </c>
-      <c r="C248" s="65" t="s">
+      <c r="C248" s="72" t="s">
         <v>1032</v>
       </c>
-      <c r="D248" s="66"/>
-      <c r="E248" s="66"/>
-      <c r="F248" s="66"/>
-      <c r="G248" s="66"/>
-      <c r="H248" s="66"/>
-      <c r="I248" s="67"/>
+      <c r="D248" s="73"/>
+      <c r="E248" s="73"/>
+      <c r="F248" s="73"/>
+      <c r="G248" s="73"/>
+      <c r="H248" s="73"/>
+      <c r="I248" s="74"/>
       <c r="M248" s="6">
         <f>SUM(M249,M250,M251,M252)</f>
         <v>0</v>
@@ -17496,29 +17564,29 @@
       </c>
     </row>
     <row r="254" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="62" t="s">
+      <c r="A254" s="69" t="s">
         <v>1050</v>
       </c>
-      <c r="B254" s="63"/>
-      <c r="C254" s="63"/>
-      <c r="D254" s="63"/>
-      <c r="E254" s="63"/>
-      <c r="F254" s="63"/>
-      <c r="G254" s="63"/>
-      <c r="H254" s="63"/>
-      <c r="I254" s="63"/>
-      <c r="J254" s="63"/>
-      <c r="K254" s="63"/>
-      <c r="L254" s="63"/>
-      <c r="M254" s="63"/>
-      <c r="N254" s="63"/>
-      <c r="O254" s="63"/>
-      <c r="P254" s="63"/>
-      <c r="Q254" s="63"/>
-      <c r="R254" s="63"/>
-      <c r="S254" s="63"/>
-      <c r="T254" s="63"/>
-      <c r="U254" s="64"/>
+      <c r="B254" s="70"/>
+      <c r="C254" s="70"/>
+      <c r="D254" s="70"/>
+      <c r="E254" s="70"/>
+      <c r="F254" s="70"/>
+      <c r="G254" s="70"/>
+      <c r="H254" s="70"/>
+      <c r="I254" s="70"/>
+      <c r="J254" s="70"/>
+      <c r="K254" s="70"/>
+      <c r="L254" s="70"/>
+      <c r="M254" s="70"/>
+      <c r="N254" s="70"/>
+      <c r="O254" s="70"/>
+      <c r="P254" s="70"/>
+      <c r="Q254" s="70"/>
+      <c r="R254" s="70"/>
+      <c r="S254" s="70"/>
+      <c r="T254" s="70"/>
+      <c r="U254" s="71"/>
     </row>
     <row r="255" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="27"/>
@@ -17534,20 +17602,20 @@
       <c r="E255" s="28"/>
       <c r="F255" s="28"/>
       <c r="G255" s="28"/>
-      <c r="H255" s="60"/>
-      <c r="I255" s="68"/>
-      <c r="J255" s="68"/>
-      <c r="K255" s="68"/>
-      <c r="L255" s="68"/>
-      <c r="M255" s="68"/>
-      <c r="N255" s="68"/>
-      <c r="O255" s="68"/>
-      <c r="P255" s="68"/>
-      <c r="Q255" s="68"/>
-      <c r="R255" s="68"/>
-      <c r="S255" s="68"/>
-      <c r="T255" s="68"/>
-      <c r="U255" s="61"/>
+      <c r="H255" s="67"/>
+      <c r="I255" s="75"/>
+      <c r="J255" s="75"/>
+      <c r="K255" s="75"/>
+      <c r="L255" s="75"/>
+      <c r="M255" s="75"/>
+      <c r="N255" s="75"/>
+      <c r="O255" s="75"/>
+      <c r="P255" s="75"/>
+      <c r="Q255" s="75"/>
+      <c r="R255" s="75"/>
+      <c r="S255" s="75"/>
+      <c r="T255" s="75"/>
+      <c r="U255" s="68"/>
     </row>
     <row r="256" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="27"/>
@@ -17563,20 +17631,20 @@
       <c r="E256" s="28"/>
       <c r="F256" s="28"/>
       <c r="G256" s="28"/>
-      <c r="H256" s="60"/>
-      <c r="I256" s="68"/>
-      <c r="J256" s="68"/>
-      <c r="K256" s="68"/>
-      <c r="L256" s="68"/>
-      <c r="M256" s="68"/>
-      <c r="N256" s="68"/>
-      <c r="O256" s="68"/>
-      <c r="P256" s="68"/>
-      <c r="Q256" s="68"/>
-      <c r="R256" s="68"/>
-      <c r="S256" s="68"/>
-      <c r="T256" s="68"/>
-      <c r="U256" s="61"/>
+      <c r="H256" s="67"/>
+      <c r="I256" s="75"/>
+      <c r="J256" s="75"/>
+      <c r="K256" s="75"/>
+      <c r="L256" s="75"/>
+      <c r="M256" s="75"/>
+      <c r="N256" s="75"/>
+      <c r="O256" s="75"/>
+      <c r="P256" s="75"/>
+      <c r="Q256" s="75"/>
+      <c r="R256" s="75"/>
+      <c r="S256" s="75"/>
+      <c r="T256" s="75"/>
+      <c r="U256" s="68"/>
     </row>
     <row r="257" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A257" s="27"/>
@@ -17592,20 +17660,20 @@
       <c r="E257" s="28"/>
       <c r="F257" s="28"/>
       <c r="G257" s="28"/>
-      <c r="H257" s="60"/>
-      <c r="I257" s="68"/>
-      <c r="J257" s="68"/>
-      <c r="K257" s="68"/>
-      <c r="L257" s="68"/>
-      <c r="M257" s="68"/>
-      <c r="N257" s="68"/>
-      <c r="O257" s="68"/>
-      <c r="P257" s="68"/>
-      <c r="Q257" s="68"/>
-      <c r="R257" s="68"/>
-      <c r="S257" s="68"/>
-      <c r="T257" s="68"/>
-      <c r="U257" s="61"/>
+      <c r="H257" s="67"/>
+      <c r="I257" s="75"/>
+      <c r="J257" s="75"/>
+      <c r="K257" s="75"/>
+      <c r="L257" s="75"/>
+      <c r="M257" s="75"/>
+      <c r="N257" s="75"/>
+      <c r="O257" s="75"/>
+      <c r="P257" s="75"/>
+      <c r="Q257" s="75"/>
+      <c r="R257" s="75"/>
+      <c r="S257" s="75"/>
+      <c r="T257" s="75"/>
+      <c r="U257" s="68"/>
     </row>
     <row r="258" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="27"/>
@@ -17621,20 +17689,20 @@
       <c r="E258" s="28"/>
       <c r="F258" s="28"/>
       <c r="G258" s="28"/>
-      <c r="H258" s="60"/>
-      <c r="I258" s="68"/>
-      <c r="J258" s="68"/>
-      <c r="K258" s="68"/>
-      <c r="L258" s="68"/>
-      <c r="M258" s="68"/>
-      <c r="N258" s="68"/>
-      <c r="O258" s="68"/>
-      <c r="P258" s="68"/>
-      <c r="Q258" s="68"/>
-      <c r="R258" s="68"/>
-      <c r="S258" s="68"/>
-      <c r="T258" s="68"/>
-      <c r="U258" s="61"/>
+      <c r="H258" s="67"/>
+      <c r="I258" s="75"/>
+      <c r="J258" s="75"/>
+      <c r="K258" s="75"/>
+      <c r="L258" s="75"/>
+      <c r="M258" s="75"/>
+      <c r="N258" s="75"/>
+      <c r="O258" s="75"/>
+      <c r="P258" s="75"/>
+      <c r="Q258" s="75"/>
+      <c r="R258" s="75"/>
+      <c r="S258" s="75"/>
+      <c r="T258" s="75"/>
+      <c r="U258" s="68"/>
     </row>
     <row r="259" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="27"/>
@@ -17650,20 +17718,20 @@
       <c r="E259" s="28"/>
       <c r="F259" s="28"/>
       <c r="G259" s="28"/>
-      <c r="H259" s="60"/>
-      <c r="I259" s="68"/>
-      <c r="J259" s="68"/>
-      <c r="K259" s="68"/>
-      <c r="L259" s="68"/>
-      <c r="M259" s="68"/>
-      <c r="N259" s="68"/>
-      <c r="O259" s="68"/>
-      <c r="P259" s="68"/>
-      <c r="Q259" s="68"/>
-      <c r="R259" s="68"/>
-      <c r="S259" s="68"/>
-      <c r="T259" s="68"/>
-      <c r="U259" s="61"/>
+      <c r="H259" s="67"/>
+      <c r="I259" s="75"/>
+      <c r="J259" s="75"/>
+      <c r="K259" s="75"/>
+      <c r="L259" s="75"/>
+      <c r="M259" s="75"/>
+      <c r="N259" s="75"/>
+      <c r="O259" s="75"/>
+      <c r="P259" s="75"/>
+      <c r="Q259" s="75"/>
+      <c r="R259" s="75"/>
+      <c r="S259" s="75"/>
+      <c r="T259" s="75"/>
+      <c r="U259" s="68"/>
     </row>
     <row r="260" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A260" s="27"/>
@@ -17679,20 +17747,20 @@
       <c r="E260" s="28"/>
       <c r="F260" s="28"/>
       <c r="G260" s="28"/>
-      <c r="H260" s="60"/>
-      <c r="I260" s="68"/>
-      <c r="J260" s="68"/>
-      <c r="K260" s="68"/>
-      <c r="L260" s="68"/>
-      <c r="M260" s="68"/>
-      <c r="N260" s="68"/>
-      <c r="O260" s="68"/>
-      <c r="P260" s="68"/>
-      <c r="Q260" s="68"/>
-      <c r="R260" s="68"/>
-      <c r="S260" s="68"/>
-      <c r="T260" s="68"/>
-      <c r="U260" s="61"/>
+      <c r="H260" s="67"/>
+      <c r="I260" s="75"/>
+      <c r="J260" s="75"/>
+      <c r="K260" s="75"/>
+      <c r="L260" s="75"/>
+      <c r="M260" s="75"/>
+      <c r="N260" s="75"/>
+      <c r="O260" s="75"/>
+      <c r="P260" s="75"/>
+      <c r="Q260" s="75"/>
+      <c r="R260" s="75"/>
+      <c r="S260" s="75"/>
+      <c r="T260" s="75"/>
+      <c r="U260" s="68"/>
     </row>
     <row r="261" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A261" s="27"/>
@@ -17708,20 +17776,20 @@
       <c r="E261" s="28"/>
       <c r="F261" s="28"/>
       <c r="G261" s="28"/>
-      <c r="H261" s="60"/>
-      <c r="I261" s="68"/>
-      <c r="J261" s="68"/>
-      <c r="K261" s="68"/>
-      <c r="L261" s="68"/>
-      <c r="M261" s="68"/>
-      <c r="N261" s="68"/>
-      <c r="O261" s="68"/>
-      <c r="P261" s="68"/>
-      <c r="Q261" s="68"/>
-      <c r="R261" s="68"/>
-      <c r="S261" s="68"/>
-      <c r="T261" s="68"/>
-      <c r="U261" s="61"/>
+      <c r="H261" s="67"/>
+      <c r="I261" s="75"/>
+      <c r="J261" s="75"/>
+      <c r="K261" s="75"/>
+      <c r="L261" s="75"/>
+      <c r="M261" s="75"/>
+      <c r="N261" s="75"/>
+      <c r="O261" s="75"/>
+      <c r="P261" s="75"/>
+      <c r="Q261" s="75"/>
+      <c r="R261" s="75"/>
+      <c r="S261" s="75"/>
+      <c r="T261" s="75"/>
+      <c r="U261" s="68"/>
     </row>
     <row r="262" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="27"/>
@@ -17737,20 +17805,20 @@
       <c r="E262" s="28"/>
       <c r="F262" s="28"/>
       <c r="G262" s="28"/>
-      <c r="H262" s="60"/>
-      <c r="I262" s="68"/>
-      <c r="J262" s="68"/>
-      <c r="K262" s="68"/>
-      <c r="L262" s="68"/>
-      <c r="M262" s="68"/>
-      <c r="N262" s="68"/>
-      <c r="O262" s="68"/>
-      <c r="P262" s="68"/>
-      <c r="Q262" s="68"/>
-      <c r="R262" s="68"/>
-      <c r="S262" s="68"/>
-      <c r="T262" s="68"/>
-      <c r="U262" s="61"/>
+      <c r="H262" s="67"/>
+      <c r="I262" s="75"/>
+      <c r="J262" s="75"/>
+      <c r="K262" s="75"/>
+      <c r="L262" s="75"/>
+      <c r="M262" s="75"/>
+      <c r="N262" s="75"/>
+      <c r="O262" s="75"/>
+      <c r="P262" s="75"/>
+      <c r="Q262" s="75"/>
+      <c r="R262" s="75"/>
+      <c r="S262" s="75"/>
+      <c r="T262" s="75"/>
+      <c r="U262" s="68"/>
     </row>
     <row r="263" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="27"/>
@@ -17766,20 +17834,20 @@
       <c r="E263" s="28"/>
       <c r="F263" s="28"/>
       <c r="G263" s="28"/>
-      <c r="H263" s="60"/>
-      <c r="I263" s="68"/>
-      <c r="J263" s="68"/>
-      <c r="K263" s="68"/>
-      <c r="L263" s="68"/>
-      <c r="M263" s="68"/>
-      <c r="N263" s="68"/>
-      <c r="O263" s="68"/>
-      <c r="P263" s="68"/>
-      <c r="Q263" s="68"/>
-      <c r="R263" s="68"/>
-      <c r="S263" s="68"/>
-      <c r="T263" s="68"/>
-      <c r="U263" s="61"/>
+      <c r="H263" s="67"/>
+      <c r="I263" s="75"/>
+      <c r="J263" s="75"/>
+      <c r="K263" s="75"/>
+      <c r="L263" s="75"/>
+      <c r="M263" s="75"/>
+      <c r="N263" s="75"/>
+      <c r="O263" s="75"/>
+      <c r="P263" s="75"/>
+      <c r="Q263" s="75"/>
+      <c r="R263" s="75"/>
+      <c r="S263" s="75"/>
+      <c r="T263" s="75"/>
+      <c r="U263" s="68"/>
     </row>
     <row r="264" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A264" s="27"/>
@@ -17795,20 +17863,20 @@
       <c r="E264" s="28"/>
       <c r="F264" s="28"/>
       <c r="G264" s="28"/>
-      <c r="H264" s="60"/>
-      <c r="I264" s="68"/>
-      <c r="J264" s="68"/>
-      <c r="K264" s="68"/>
-      <c r="L264" s="68"/>
-      <c r="M264" s="68"/>
-      <c r="N264" s="68"/>
-      <c r="O264" s="68"/>
-      <c r="P264" s="68"/>
-      <c r="Q264" s="68"/>
-      <c r="R264" s="68"/>
-      <c r="S264" s="68"/>
-      <c r="T264" s="68"/>
-      <c r="U264" s="61"/>
+      <c r="H264" s="67"/>
+      <c r="I264" s="75"/>
+      <c r="J264" s="75"/>
+      <c r="K264" s="75"/>
+      <c r="L264" s="75"/>
+      <c r="M264" s="75"/>
+      <c r="N264" s="75"/>
+      <c r="O264" s="75"/>
+      <c r="P264" s="75"/>
+      <c r="Q264" s="75"/>
+      <c r="R264" s="75"/>
+      <c r="S264" s="75"/>
+      <c r="T264" s="75"/>
+      <c r="U264" s="68"/>
     </row>
     <row r="265" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A265" s="27"/>
@@ -17824,20 +17892,20 @@
       <c r="E265" s="28"/>
       <c r="F265" s="28"/>
       <c r="G265" s="28"/>
-      <c r="H265" s="60"/>
-      <c r="I265" s="68"/>
-      <c r="J265" s="68"/>
-      <c r="K265" s="68"/>
-      <c r="L265" s="68"/>
-      <c r="M265" s="68"/>
-      <c r="N265" s="68"/>
-      <c r="O265" s="68"/>
-      <c r="P265" s="68"/>
-      <c r="Q265" s="68"/>
-      <c r="R265" s="68"/>
-      <c r="S265" s="68"/>
-      <c r="T265" s="68"/>
-      <c r="U265" s="61"/>
+      <c r="H265" s="67"/>
+      <c r="I265" s="75"/>
+      <c r="J265" s="75"/>
+      <c r="K265" s="75"/>
+      <c r="L265" s="75"/>
+      <c r="M265" s="75"/>
+      <c r="N265" s="75"/>
+      <c r="O265" s="75"/>
+      <c r="P265" s="75"/>
+      <c r="Q265" s="75"/>
+      <c r="R265" s="75"/>
+      <c r="S265" s="75"/>
+      <c r="T265" s="75"/>
+      <c r="U265" s="68"/>
     </row>
     <row r="266" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A266" s="27"/>
@@ -17853,20 +17921,20 @@
       <c r="E266" s="28"/>
       <c r="F266" s="28"/>
       <c r="G266" s="28"/>
-      <c r="H266" s="60"/>
-      <c r="I266" s="68"/>
-      <c r="J266" s="68"/>
-      <c r="K266" s="68"/>
-      <c r="L266" s="68"/>
-      <c r="M266" s="68"/>
-      <c r="N266" s="68"/>
-      <c r="O266" s="68"/>
-      <c r="P266" s="68"/>
-      <c r="Q266" s="68"/>
-      <c r="R266" s="68"/>
-      <c r="S266" s="68"/>
-      <c r="T266" s="68"/>
-      <c r="U266" s="61"/>
+      <c r="H266" s="67"/>
+      <c r="I266" s="75"/>
+      <c r="J266" s="75"/>
+      <c r="K266" s="75"/>
+      <c r="L266" s="75"/>
+      <c r="M266" s="75"/>
+      <c r="N266" s="75"/>
+      <c r="O266" s="75"/>
+      <c r="P266" s="75"/>
+      <c r="Q266" s="75"/>
+      <c r="R266" s="75"/>
+      <c r="S266" s="75"/>
+      <c r="T266" s="75"/>
+      <c r="U266" s="68"/>
     </row>
     <row r="267" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="27"/>
@@ -17882,20 +17950,20 @@
       <c r="E267" s="28"/>
       <c r="F267" s="28"/>
       <c r="G267" s="28"/>
-      <c r="H267" s="60"/>
-      <c r="I267" s="68"/>
-      <c r="J267" s="68"/>
-      <c r="K267" s="68"/>
-      <c r="L267" s="68"/>
-      <c r="M267" s="68"/>
-      <c r="N267" s="68"/>
-      <c r="O267" s="68"/>
-      <c r="P267" s="68"/>
-      <c r="Q267" s="68"/>
-      <c r="R267" s="68"/>
-      <c r="S267" s="68"/>
-      <c r="T267" s="68"/>
-      <c r="U267" s="61"/>
+      <c r="H267" s="67"/>
+      <c r="I267" s="75"/>
+      <c r="J267" s="75"/>
+      <c r="K267" s="75"/>
+      <c r="L267" s="75"/>
+      <c r="M267" s="75"/>
+      <c r="N267" s="75"/>
+      <c r="O267" s="75"/>
+      <c r="P267" s="75"/>
+      <c r="Q267" s="75"/>
+      <c r="R267" s="75"/>
+      <c r="S267" s="75"/>
+      <c r="T267" s="75"/>
+      <c r="U267" s="68"/>
     </row>
     <row r="268" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="27"/>
@@ -17911,22 +17979,22 @@
       <c r="E268" s="28"/>
       <c r="F268" s="28"/>
       <c r="G268" s="28"/>
-      <c r="H268" s="60" t="s">
+      <c r="H268" s="67" t="s">
         <v>1092</v>
       </c>
-      <c r="I268" s="68"/>
-      <c r="J268" s="68"/>
-      <c r="K268" s="68"/>
-      <c r="L268" s="68"/>
-      <c r="M268" s="68"/>
-      <c r="N268" s="68"/>
-      <c r="O268" s="68"/>
-      <c r="P268" s="68"/>
-      <c r="Q268" s="68"/>
-      <c r="R268" s="68"/>
-      <c r="S268" s="68"/>
-      <c r="T268" s="68"/>
-      <c r="U268" s="61"/>
+      <c r="I268" s="75"/>
+      <c r="J268" s="75"/>
+      <c r="K268" s="75"/>
+      <c r="L268" s="75"/>
+      <c r="M268" s="75"/>
+      <c r="N268" s="75"/>
+      <c r="O268" s="75"/>
+      <c r="P268" s="75"/>
+      <c r="Q268" s="75"/>
+      <c r="R268" s="75"/>
+      <c r="S268" s="75"/>
+      <c r="T268" s="75"/>
+      <c r="U268" s="68"/>
     </row>
     <row r="269" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="27"/>
@@ -17942,20 +18010,20 @@
       <c r="E269" s="28"/>
       <c r="F269" s="28"/>
       <c r="G269" s="28"/>
-      <c r="H269" s="60"/>
-      <c r="I269" s="68"/>
-      <c r="J269" s="68"/>
-      <c r="K269" s="68"/>
-      <c r="L269" s="68"/>
-      <c r="M269" s="68"/>
-      <c r="N269" s="68"/>
-      <c r="O269" s="68"/>
-      <c r="P269" s="68"/>
-      <c r="Q269" s="68"/>
-      <c r="R269" s="68"/>
-      <c r="S269" s="68"/>
-      <c r="T269" s="68"/>
-      <c r="U269" s="61"/>
+      <c r="H269" s="67"/>
+      <c r="I269" s="75"/>
+      <c r="J269" s="75"/>
+      <c r="K269" s="75"/>
+      <c r="L269" s="75"/>
+      <c r="M269" s="75"/>
+      <c r="N269" s="75"/>
+      <c r="O269" s="75"/>
+      <c r="P269" s="75"/>
+      <c r="Q269" s="75"/>
+      <c r="R269" s="75"/>
+      <c r="S269" s="75"/>
+      <c r="T269" s="75"/>
+      <c r="U269" s="68"/>
     </row>
     <row r="270" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A270" s="27"/>
@@ -17969,20 +18037,20 @@
       <c r="E270" s="28"/>
       <c r="F270" s="28"/>
       <c r="G270" s="28"/>
-      <c r="H270" s="60"/>
-      <c r="I270" s="68"/>
-      <c r="J270" s="68"/>
-      <c r="K270" s="68"/>
-      <c r="L270" s="68"/>
-      <c r="M270" s="68"/>
-      <c r="N270" s="68"/>
-      <c r="O270" s="68"/>
-      <c r="P270" s="68"/>
-      <c r="Q270" s="68"/>
-      <c r="R270" s="68"/>
-      <c r="S270" s="68"/>
-      <c r="T270" s="68"/>
-      <c r="U270" s="61"/>
+      <c r="H270" s="67"/>
+      <c r="I270" s="75"/>
+      <c r="J270" s="75"/>
+      <c r="K270" s="75"/>
+      <c r="L270" s="75"/>
+      <c r="M270" s="75"/>
+      <c r="N270" s="75"/>
+      <c r="O270" s="75"/>
+      <c r="P270" s="75"/>
+      <c r="Q270" s="75"/>
+      <c r="R270" s="75"/>
+      <c r="S270" s="75"/>
+      <c r="T270" s="75"/>
+      <c r="U270" s="68"/>
     </row>
     <row r="271" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="27"/>
@@ -17996,20 +18064,20 @@
       <c r="E271" s="28"/>
       <c r="F271" s="28"/>
       <c r="G271" s="28"/>
-      <c r="H271" s="60"/>
-      <c r="I271" s="68"/>
-      <c r="J271" s="68"/>
-      <c r="K271" s="68"/>
-      <c r="L271" s="68"/>
-      <c r="M271" s="68"/>
-      <c r="N271" s="68"/>
-      <c r="O271" s="68"/>
-      <c r="P271" s="68"/>
-      <c r="Q271" s="68"/>
-      <c r="R271" s="68"/>
-      <c r="S271" s="68"/>
-      <c r="T271" s="68"/>
-      <c r="U271" s="61"/>
+      <c r="H271" s="67"/>
+      <c r="I271" s="75"/>
+      <c r="J271" s="75"/>
+      <c r="K271" s="75"/>
+      <c r="L271" s="75"/>
+      <c r="M271" s="75"/>
+      <c r="N271" s="75"/>
+      <c r="O271" s="75"/>
+      <c r="P271" s="75"/>
+      <c r="Q271" s="75"/>
+      <c r="R271" s="75"/>
+      <c r="S271" s="75"/>
+      <c r="T271" s="75"/>
+      <c r="U271" s="68"/>
     </row>
     <row r="272" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="27"/>
@@ -18023,20 +18091,20 @@
       <c r="E272" s="28"/>
       <c r="F272" s="28"/>
       <c r="G272" s="28"/>
-      <c r="H272" s="60"/>
-      <c r="I272" s="68"/>
-      <c r="J272" s="68"/>
-      <c r="K272" s="68"/>
-      <c r="L272" s="68"/>
-      <c r="M272" s="68"/>
-      <c r="N272" s="68"/>
-      <c r="O272" s="68"/>
-      <c r="P272" s="68"/>
-      <c r="Q272" s="68"/>
-      <c r="R272" s="68"/>
-      <c r="S272" s="68"/>
-      <c r="T272" s="68"/>
-      <c r="U272" s="61"/>
+      <c r="H272" s="67"/>
+      <c r="I272" s="75"/>
+      <c r="J272" s="75"/>
+      <c r="K272" s="75"/>
+      <c r="L272" s="75"/>
+      <c r="M272" s="75"/>
+      <c r="N272" s="75"/>
+      <c r="O272" s="75"/>
+      <c r="P272" s="75"/>
+      <c r="Q272" s="75"/>
+      <c r="R272" s="75"/>
+      <c r="S272" s="75"/>
+      <c r="T272" s="75"/>
+      <c r="U272" s="68"/>
     </row>
   </sheetData>
   <sheetProtection password="C644" sheet="1" formatColumns="0" autoFilter="0"/>
@@ -18116,10 +18184,11 @@
   <dimension ref="A1:AI272"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
     <col min="3" max="3" width="55.5703125" customWidth="1"/>
-    <col min="4" max="5" width="38" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="5" max="5" width="34.140625" customWidth="1"/>
     <col min="6" max="7" width="16.42578125" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="16.85546875" customWidth="1"/>
@@ -18196,217 +18265,217 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="55"/>
+      <c r="T2" s="55"/>
+      <c r="U2" s="55"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="49"/>
-      <c r="O3" s="49"/>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="49"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56"/>
+      <c r="N3" s="56"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="56"/>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="56"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="56"/>
+      <c r="U3" s="56"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
+      <c r="Q4" s="57"/>
+      <c r="R4" s="57"/>
+      <c r="S4" s="57"/>
+      <c r="T4" s="57"/>
+      <c r="U4" s="57"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="57" t="s">
+      <c r="B5" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="C5" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="57" t="s">
+      <c r="D5" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="57" t="s">
+      <c r="E5" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="57" t="s">
+      <c r="F5" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="57" t="s">
+      <c r="G5" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="57" t="s">
+      <c r="H5" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="57" t="s">
+      <c r="I5" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="51" t="s">
+      <c r="J5" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="53"/>
-      <c r="P5" s="54" t="s">
+      <c r="K5" s="59"/>
+      <c r="L5" s="59"/>
+      <c r="M5" s="59"/>
+      <c r="N5" s="59"/>
+      <c r="O5" s="60"/>
+      <c r="P5" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="56"/>
-      <c r="S5" s="54" t="s">
+      <c r="Q5" s="62"/>
+      <c r="R5" s="63"/>
+      <c r="S5" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="55"/>
-      <c r="U5" s="56"/>
+      <c r="T5" s="62"/>
+      <c r="U5" s="63"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="58"/>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="60" t="s">
+      <c r="A6" s="65"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="61"/>
-      <c r="L6" s="57" t="s">
+      <c r="K6" s="68"/>
+      <c r="L6" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="60" t="s">
+      <c r="M6" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="61"/>
-      <c r="O6" s="57" t="s">
+      <c r="N6" s="68"/>
+      <c r="O6" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="60" t="s">
+      <c r="P6" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="57" t="s">
+      <c r="Q6" s="68"/>
+      <c r="R6" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="S6" s="60" t="s">
+      <c r="S6" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="61"/>
-      <c r="U6" s="57" t="s">
+      <c r="T6" s="68"/>
+      <c r="U6" s="64" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="59"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
+      <c r="A7" s="66"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
       <c r="J7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="59"/>
+      <c r="L7" s="66"/>
       <c r="M7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="59"/>
+      <c r="O7" s="66"/>
       <c r="P7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="59"/>
+      <c r="R7" s="66"/>
       <c r="S7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="U7" s="59"/>
+      <c r="U7" s="66"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="64"/>
+      <c r="B8" s="70"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="71"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -18448,15 +18517,15 @@
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="65" t="s">
+      <c r="C9" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="67"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="74"/>
       <c r="M9" s="6">
         <f>SUM(M10,M20)</f>
         <v>18303819.899999999</v>
@@ -18492,15 +18561,15 @@
       <c r="B10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="65" t="s">
+      <c r="C10" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="67"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="74"/>
       <c r="M10" s="6">
         <f t="shared" ref="M10:O14" si="0">SUM(M11)</f>
         <v>126283.29</v>
@@ -18536,15 +18605,15 @@
       <c r="B11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="65" t="s">
+      <c r="C11" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="67"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="74"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18580,15 +18649,15 @@
       <c r="B12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="65" t="s">
+      <c r="C12" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
-      <c r="I12" s="67"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="74"/>
       <c r="M12" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18624,15 +18693,15 @@
       <c r="B13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="65" t="s">
+      <c r="C13" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="67"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="74"/>
       <c r="M13" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18668,15 +18737,15 @@
       <c r="B14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="67"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="74"/>
       <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18967,15 +19036,15 @@
       <c r="B20" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="65" t="s">
+      <c r="C20" s="72" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="66"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="66"/>
-      <c r="G20" s="66"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="67"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="74"/>
       <c r="M20" s="6">
         <f t="shared" ref="M20:O21" si="1">SUM(M21)</f>
         <v>18177536.609999999</v>
@@ -19011,15 +19080,15 @@
       <c r="B21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="65" t="s">
+      <c r="C21" s="72" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="66"/>
-      <c r="E21" s="66"/>
-      <c r="F21" s="66"/>
-      <c r="G21" s="66"/>
-      <c r="H21" s="66"/>
-      <c r="I21" s="67"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="74"/>
       <c r="M21" s="6">
         <f t="shared" si="1"/>
         <v>18177536.609999999</v>
@@ -19055,15 +19124,15 @@
       <c r="B22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="65" t="s">
+      <c r="C22" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="67"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="74"/>
       <c r="M22" s="6">
         <f>SUM(M23,M122,M163,M203,M248)</f>
         <v>18177536.609999999</v>
@@ -19099,15 +19168,15 @@
       <c r="B23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="65" t="s">
+      <c r="C23" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="66"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="67"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="74"/>
       <c r="M23" s="6">
         <f>SUM(M24,M67,M76,M119)</f>
         <v>12831032.07</v>
@@ -19143,15 +19212,15 @@
       <c r="B24" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="65" t="s">
+      <c r="C24" s="72" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="66"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="66"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="67"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="74"/>
       <c r="M24" s="6">
         <f>SUM(M25,M29,M31,M34,M36,M41,M46,M51,M57,M62)</f>
         <v>7808423.3099999996</v>
@@ -19399,21 +19468,23 @@
       <c r="B29" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11" t="s">
+      <c r="D29" s="49" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E29" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="50">
         <v>1</v>
       </c>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12">
+      <c r="H29" s="50"/>
+      <c r="I29" s="50">
         <v>2785.09</v>
       </c>
       <c r="J29" s="13">
@@ -19811,24 +19882,24 @@
       <c r="A36" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="79" t="s">
         <v>163</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="52" t="s">
         <v>164</v>
       </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11" t="s">
+      <c r="D36" s="53"/>
+      <c r="E36" s="53" t="s">
         <v>165</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="G36" s="12">
+      <c r="G36" s="54">
         <v>1</v>
       </c>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12">
+      <c r="H36" s="54"/>
+      <c r="I36" s="54">
         <v>46.62</v>
       </c>
       <c r="J36" s="13">
@@ -20064,24 +20135,24 @@
       <c r="A41" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="79" t="s">
         <v>188</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="52" t="s">
         <v>189</v>
       </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11" t="s">
+      <c r="D41" s="53"/>
+      <c r="E41" s="53" t="s">
         <v>190</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="G41" s="12">
+      <c r="G41" s="54">
         <v>1</v>
       </c>
-      <c r="H41" s="12"/>
-      <c r="I41" s="12">
+      <c r="H41" s="54"/>
+      <c r="I41" s="54">
         <v>122.25</v>
       </c>
       <c r="J41" s="13">
@@ -20317,24 +20388,24 @@
       <c r="A46" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C46" s="52" t="s">
         <v>207</v>
       </c>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11" t="s">
+      <c r="D46" s="53"/>
+      <c r="E46" s="53" t="s">
         <v>208</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="G46" s="12">
+      <c r="G46" s="54">
         <v>1</v>
       </c>
-      <c r="H46" s="12"/>
-      <c r="I46" s="12">
+      <c r="H46" s="54"/>
+      <c r="I46" s="54">
         <v>5553.92</v>
       </c>
       <c r="J46" s="13">
@@ -20453,7 +20524,10 @@
       <c r="G48" s="17">
         <v>1.8</v>
       </c>
-      <c r="H48" s="22"/>
+      <c r="H48" s="22">
+        <f>I48/G48/I46</f>
+        <v>65</v>
+      </c>
       <c r="I48" s="22">
         <v>649808.64000000001</v>
       </c>
@@ -20570,24 +20644,24 @@
       <c r="A51" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C51" s="52" t="s">
         <v>207</v>
       </c>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11" t="s">
+      <c r="D51" s="53"/>
+      <c r="E51" s="53" t="s">
         <v>224</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F51" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="G51" s="12">
+      <c r="G51" s="54">
         <v>1</v>
       </c>
-      <c r="H51" s="12"/>
-      <c r="I51" s="12">
+      <c r="H51" s="54"/>
+      <c r="I51" s="54">
         <v>468.22</v>
       </c>
       <c r="J51" s="13">
@@ -20866,24 +20940,24 @@
       <c r="A57" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C57" s="52" t="s">
         <v>207</v>
       </c>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11" t="s">
+      <c r="D57" s="53"/>
+      <c r="E57" s="53" t="s">
         <v>243</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="G57" s="12">
+      <c r="G57" s="54">
         <v>1</v>
       </c>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12">
+      <c r="H57" s="54"/>
+      <c r="I57" s="54">
         <v>19.420000000000002</v>
       </c>
       <c r="J57" s="13">
@@ -21119,24 +21193,24 @@
       <c r="A62" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="79" t="s">
         <v>206</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="C62" s="52" t="s">
         <v>207</v>
       </c>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11" t="s">
+      <c r="D62" s="53"/>
+      <c r="E62" s="53" t="s">
         <v>261</v>
       </c>
-      <c r="F62" s="11" t="s">
+      <c r="F62" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="G62" s="12">
+      <c r="G62" s="54">
         <v>1</v>
       </c>
-      <c r="H62" s="12"/>
-      <c r="I62" s="12">
+      <c r="H62" s="54"/>
+      <c r="I62" s="54">
         <v>101.29</v>
       </c>
       <c r="J62" s="13">
@@ -21375,15 +21449,15 @@
       <c r="B67" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="65" t="s">
+      <c r="C67" s="72" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="66"/>
-      <c r="E67" s="66"/>
-      <c r="F67" s="66"/>
-      <c r="G67" s="66"/>
-      <c r="H67" s="66"/>
-      <c r="I67" s="67"/>
+      <c r="D67" s="73"/>
+      <c r="E67" s="73"/>
+      <c r="F67" s="73"/>
+      <c r="G67" s="73"/>
+      <c r="H67" s="73"/>
+      <c r="I67" s="74"/>
       <c r="M67" s="6">
         <f>SUM(M68,M72,M74)</f>
         <v>748533.11</v>
@@ -21628,24 +21702,26 @@
       <c r="A72" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="51" t="s">
         <v>300</v>
       </c>
-      <c r="C72" s="10" t="s">
+      <c r="C72" s="52" t="s">
         <v>301</v>
       </c>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11" t="s">
+      <c r="D72" s="53" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E72" s="53" t="s">
         <v>302</v>
       </c>
-      <c r="F72" s="11" t="s">
+      <c r="F72" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="G72" s="12">
+      <c r="G72" s="54">
         <v>1</v>
       </c>
-      <c r="H72" s="12"/>
-      <c r="I72" s="12">
+      <c r="H72" s="54"/>
+      <c r="I72" s="54">
         <v>2518.27</v>
       </c>
       <c r="J72" s="13">
@@ -21881,15 +21957,15 @@
       <c r="B76" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C76" s="65" t="s">
+      <c r="C76" s="72" t="s">
         <v>325</v>
       </c>
-      <c r="D76" s="66"/>
-      <c r="E76" s="66"/>
-      <c r="F76" s="66"/>
-      <c r="G76" s="66"/>
-      <c r="H76" s="66"/>
-      <c r="I76" s="67"/>
+      <c r="D76" s="73"/>
+      <c r="E76" s="73"/>
+      <c r="F76" s="73"/>
+      <c r="G76" s="73"/>
+      <c r="H76" s="73"/>
+      <c r="I76" s="74"/>
       <c r="M76" s="6">
         <f>SUM(M77,M82,M87,M93,M96,M99,M104,M109,M114,M117)</f>
         <v>3831185.6499999994</v>
@@ -24139,15 +24215,15 @@
       <c r="B119" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C119" s="65" t="s">
+      <c r="C119" s="72" t="s">
         <v>526</v>
       </c>
-      <c r="D119" s="66"/>
-      <c r="E119" s="66"/>
-      <c r="F119" s="66"/>
-      <c r="G119" s="66"/>
-      <c r="H119" s="66"/>
-      <c r="I119" s="67"/>
+      <c r="D119" s="73"/>
+      <c r="E119" s="73"/>
+      <c r="F119" s="73"/>
+      <c r="G119" s="73"/>
+      <c r="H119" s="73"/>
+      <c r="I119" s="74"/>
       <c r="M119" s="6">
         <f>SUM(M120)</f>
         <v>442890</v>
@@ -24309,15 +24385,15 @@
       <c r="B122" s="29" t="s">
         <v>540</v>
       </c>
-      <c r="C122" s="69" t="s">
+      <c r="C122" s="76" t="s">
         <v>541</v>
       </c>
-      <c r="D122" s="70"/>
-      <c r="E122" s="70"/>
-      <c r="F122" s="70"/>
-      <c r="G122" s="70"/>
-      <c r="H122" s="70"/>
-      <c r="I122" s="71"/>
+      <c r="D122" s="77"/>
+      <c r="E122" s="77"/>
+      <c r="F122" s="77"/>
+      <c r="G122" s="77"/>
+      <c r="H122" s="77"/>
+      <c r="I122" s="78"/>
       <c r="J122" s="30"/>
       <c r="M122" s="6">
         <f>SUM(M123)</f>
@@ -24354,15 +24430,15 @@
       <c r="B123" s="29" t="s">
         <v>543</v>
       </c>
-      <c r="C123" s="69" t="s">
+      <c r="C123" s="76" t="s">
         <v>544</v>
       </c>
-      <c r="D123" s="70"/>
-      <c r="E123" s="70"/>
-      <c r="F123" s="70"/>
-      <c r="G123" s="70"/>
-      <c r="H123" s="70"/>
-      <c r="I123" s="71"/>
+      <c r="D123" s="77"/>
+      <c r="E123" s="77"/>
+      <c r="F123" s="77"/>
+      <c r="G123" s="77"/>
+      <c r="H123" s="77"/>
+      <c r="I123" s="78"/>
       <c r="J123" s="30"/>
       <c r="M123" s="6">
         <f>SUM(M124,M127,M131,M136,M140,M143,M148,M153,M158)</f>
@@ -26453,15 +26529,15 @@
       <c r="B163" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C163" s="65" t="s">
+      <c r="C163" s="72" t="s">
         <v>710</v>
       </c>
-      <c r="D163" s="66"/>
-      <c r="E163" s="66"/>
-      <c r="F163" s="66"/>
-      <c r="G163" s="66"/>
-      <c r="H163" s="66"/>
-      <c r="I163" s="67"/>
+      <c r="D163" s="73"/>
+      <c r="E163" s="73"/>
+      <c r="F163" s="73"/>
+      <c r="G163" s="73"/>
+      <c r="H163" s="73"/>
+      <c r="I163" s="74"/>
       <c r="M163" s="6">
         <f>SUM(M164,M184)</f>
         <v>611422.71999999997</v>
@@ -26497,15 +26573,15 @@
       <c r="B164" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="C164" s="65" t="s">
+      <c r="C164" s="72" t="s">
         <v>713</v>
       </c>
-      <c r="D164" s="66"/>
-      <c r="E164" s="66"/>
-      <c r="F164" s="66"/>
-      <c r="G164" s="66"/>
-      <c r="H164" s="66"/>
-      <c r="I164" s="67"/>
+      <c r="D164" s="73"/>
+      <c r="E164" s="73"/>
+      <c r="F164" s="73"/>
+      <c r="G164" s="73"/>
+      <c r="H164" s="73"/>
+      <c r="I164" s="74"/>
       <c r="M164" s="6">
         <f>SUM(M165,M171,M174,M178,M182)</f>
         <v>415021.23999999993</v>
@@ -27552,15 +27628,15 @@
       <c r="B184" s="9" t="s">
         <v>789</v>
       </c>
-      <c r="C184" s="65" t="s">
+      <c r="C184" s="72" t="s">
         <v>790</v>
       </c>
-      <c r="D184" s="66"/>
-      <c r="E184" s="66"/>
-      <c r="F184" s="66"/>
-      <c r="G184" s="66"/>
-      <c r="H184" s="66"/>
-      <c r="I184" s="67"/>
+      <c r="D184" s="73"/>
+      <c r="E184" s="73"/>
+      <c r="F184" s="73"/>
+      <c r="G184" s="73"/>
+      <c r="H184" s="73"/>
+      <c r="I184" s="74"/>
       <c r="M184" s="6">
         <f>SUM(M185,M188,M191,M194,M197,M200)</f>
         <v>196401.48</v>
@@ -28610,15 +28686,15 @@
       <c r="B203" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="C203" s="65" t="s">
+      <c r="C203" s="72" t="s">
         <v>856</v>
       </c>
-      <c r="D203" s="66"/>
-      <c r="E203" s="66"/>
-      <c r="F203" s="66"/>
-      <c r="G203" s="66"/>
-      <c r="H203" s="66"/>
-      <c r="I203" s="67"/>
+      <c r="D203" s="73"/>
+      <c r="E203" s="73"/>
+      <c r="F203" s="73"/>
+      <c r="G203" s="73"/>
+      <c r="H203" s="73"/>
+      <c r="I203" s="74"/>
       <c r="M203" s="6">
         <f>SUM(M204,M206,M221,M236,M238,M240,M242,M243,M244,M245,M246,M247)</f>
         <v>719044.50999999989</v>
@@ -31000,15 +31076,15 @@
       <c r="B248" s="9" t="s">
         <v>1031</v>
       </c>
-      <c r="C248" s="65" t="s">
+      <c r="C248" s="72" t="s">
         <v>1032</v>
       </c>
-      <c r="D248" s="66"/>
-      <c r="E248" s="66"/>
-      <c r="F248" s="66"/>
-      <c r="G248" s="66"/>
-      <c r="H248" s="66"/>
-      <c r="I248" s="67"/>
+      <c r="D248" s="73"/>
+      <c r="E248" s="73"/>
+      <c r="F248" s="73"/>
+      <c r="G248" s="73"/>
+      <c r="H248" s="73"/>
+      <c r="I248" s="74"/>
       <c r="M248" s="6">
         <f>SUM(M249,M250,M251,M252)</f>
         <v>0</v>
@@ -31395,29 +31471,29 @@
       </c>
     </row>
     <row r="254" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="62" t="s">
+      <c r="A254" s="69" t="s">
         <v>1050</v>
       </c>
-      <c r="B254" s="63"/>
-      <c r="C254" s="63"/>
-      <c r="D254" s="63"/>
-      <c r="E254" s="63"/>
-      <c r="F254" s="63"/>
-      <c r="G254" s="63"/>
-      <c r="H254" s="63"/>
-      <c r="I254" s="63"/>
-      <c r="J254" s="63"/>
-      <c r="K254" s="63"/>
-      <c r="L254" s="63"/>
-      <c r="M254" s="63"/>
-      <c r="N254" s="63"/>
-      <c r="O254" s="63"/>
-      <c r="P254" s="63"/>
-      <c r="Q254" s="63"/>
-      <c r="R254" s="63"/>
-      <c r="S254" s="63"/>
-      <c r="T254" s="63"/>
-      <c r="U254" s="64"/>
+      <c r="B254" s="70"/>
+      <c r="C254" s="70"/>
+      <c r="D254" s="70"/>
+      <c r="E254" s="70"/>
+      <c r="F254" s="70"/>
+      <c r="G254" s="70"/>
+      <c r="H254" s="70"/>
+      <c r="I254" s="70"/>
+      <c r="J254" s="70"/>
+      <c r="K254" s="70"/>
+      <c r="L254" s="70"/>
+      <c r="M254" s="70"/>
+      <c r="N254" s="70"/>
+      <c r="O254" s="70"/>
+      <c r="P254" s="70"/>
+      <c r="Q254" s="70"/>
+      <c r="R254" s="70"/>
+      <c r="S254" s="70"/>
+      <c r="T254" s="70"/>
+      <c r="U254" s="71"/>
     </row>
     <row r="255" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="27"/>
@@ -31433,20 +31509,20 @@
       <c r="E255" s="28"/>
       <c r="F255" s="28"/>
       <c r="G255" s="28"/>
-      <c r="H255" s="60"/>
-      <c r="I255" s="68"/>
-      <c r="J255" s="68"/>
-      <c r="K255" s="68"/>
-      <c r="L255" s="68"/>
-      <c r="M255" s="68"/>
-      <c r="N255" s="68"/>
-      <c r="O255" s="68"/>
-      <c r="P255" s="68"/>
-      <c r="Q255" s="68"/>
-      <c r="R255" s="68"/>
-      <c r="S255" s="68"/>
-      <c r="T255" s="68"/>
-      <c r="U255" s="61"/>
+      <c r="H255" s="67"/>
+      <c r="I255" s="75"/>
+      <c r="J255" s="75"/>
+      <c r="K255" s="75"/>
+      <c r="L255" s="75"/>
+      <c r="M255" s="75"/>
+      <c r="N255" s="75"/>
+      <c r="O255" s="75"/>
+      <c r="P255" s="75"/>
+      <c r="Q255" s="75"/>
+      <c r="R255" s="75"/>
+      <c r="S255" s="75"/>
+      <c r="T255" s="75"/>
+      <c r="U255" s="68"/>
     </row>
     <row r="256" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="27"/>
@@ -31462,20 +31538,20 @@
       <c r="E256" s="28"/>
       <c r="F256" s="28"/>
       <c r="G256" s="28"/>
-      <c r="H256" s="60"/>
-      <c r="I256" s="68"/>
-      <c r="J256" s="68"/>
-      <c r="K256" s="68"/>
-      <c r="L256" s="68"/>
-      <c r="M256" s="68"/>
-      <c r="N256" s="68"/>
-      <c r="O256" s="68"/>
-      <c r="P256" s="68"/>
-      <c r="Q256" s="68"/>
-      <c r="R256" s="68"/>
-      <c r="S256" s="68"/>
-      <c r="T256" s="68"/>
-      <c r="U256" s="61"/>
+      <c r="H256" s="67"/>
+      <c r="I256" s="75"/>
+      <c r="J256" s="75"/>
+      <c r="K256" s="75"/>
+      <c r="L256" s="75"/>
+      <c r="M256" s="75"/>
+      <c r="N256" s="75"/>
+      <c r="O256" s="75"/>
+      <c r="P256" s="75"/>
+      <c r="Q256" s="75"/>
+      <c r="R256" s="75"/>
+      <c r="S256" s="75"/>
+      <c r="T256" s="75"/>
+      <c r="U256" s="68"/>
     </row>
     <row r="257" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A257" s="27"/>
@@ -31491,20 +31567,20 @@
       <c r="E257" s="28"/>
       <c r="F257" s="28"/>
       <c r="G257" s="28"/>
-      <c r="H257" s="60"/>
-      <c r="I257" s="68"/>
-      <c r="J257" s="68"/>
-      <c r="K257" s="68"/>
-      <c r="L257" s="68"/>
-      <c r="M257" s="68"/>
-      <c r="N257" s="68"/>
-      <c r="O257" s="68"/>
-      <c r="P257" s="68"/>
-      <c r="Q257" s="68"/>
-      <c r="R257" s="68"/>
-      <c r="S257" s="68"/>
-      <c r="T257" s="68"/>
-      <c r="U257" s="61"/>
+      <c r="H257" s="67"/>
+      <c r="I257" s="75"/>
+      <c r="J257" s="75"/>
+      <c r="K257" s="75"/>
+      <c r="L257" s="75"/>
+      <c r="M257" s="75"/>
+      <c r="N257" s="75"/>
+      <c r="O257" s="75"/>
+      <c r="P257" s="75"/>
+      <c r="Q257" s="75"/>
+      <c r="R257" s="75"/>
+      <c r="S257" s="75"/>
+      <c r="T257" s="75"/>
+      <c r="U257" s="68"/>
     </row>
     <row r="258" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="27"/>
@@ -31520,20 +31596,20 @@
       <c r="E258" s="28"/>
       <c r="F258" s="28"/>
       <c r="G258" s="28"/>
-      <c r="H258" s="60"/>
-      <c r="I258" s="68"/>
-      <c r="J258" s="68"/>
-      <c r="K258" s="68"/>
-      <c r="L258" s="68"/>
-      <c r="M258" s="68"/>
-      <c r="N258" s="68"/>
-      <c r="O258" s="68"/>
-      <c r="P258" s="68"/>
-      <c r="Q258" s="68"/>
-      <c r="R258" s="68"/>
-      <c r="S258" s="68"/>
-      <c r="T258" s="68"/>
-      <c r="U258" s="61"/>
+      <c r="H258" s="67"/>
+      <c r="I258" s="75"/>
+      <c r="J258" s="75"/>
+      <c r="K258" s="75"/>
+      <c r="L258" s="75"/>
+      <c r="M258" s="75"/>
+      <c r="N258" s="75"/>
+      <c r="O258" s="75"/>
+      <c r="P258" s="75"/>
+      <c r="Q258" s="75"/>
+      <c r="R258" s="75"/>
+      <c r="S258" s="75"/>
+      <c r="T258" s="75"/>
+      <c r="U258" s="68"/>
     </row>
     <row r="259" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="27"/>
@@ -31549,20 +31625,20 @@
       <c r="E259" s="28"/>
       <c r="F259" s="28"/>
       <c r="G259" s="28"/>
-      <c r="H259" s="60"/>
-      <c r="I259" s="68"/>
-      <c r="J259" s="68"/>
-      <c r="K259" s="68"/>
-      <c r="L259" s="68"/>
-      <c r="M259" s="68"/>
-      <c r="N259" s="68"/>
-      <c r="O259" s="68"/>
-      <c r="P259" s="68"/>
-      <c r="Q259" s="68"/>
-      <c r="R259" s="68"/>
-      <c r="S259" s="68"/>
-      <c r="T259" s="68"/>
-      <c r="U259" s="61"/>
+      <c r="H259" s="67"/>
+      <c r="I259" s="75"/>
+      <c r="J259" s="75"/>
+      <c r="K259" s="75"/>
+      <c r="L259" s="75"/>
+      <c r="M259" s="75"/>
+      <c r="N259" s="75"/>
+      <c r="O259" s="75"/>
+      <c r="P259" s="75"/>
+      <c r="Q259" s="75"/>
+      <c r="R259" s="75"/>
+      <c r="S259" s="75"/>
+      <c r="T259" s="75"/>
+      <c r="U259" s="68"/>
     </row>
     <row r="260" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A260" s="27"/>
@@ -31578,20 +31654,20 @@
       <c r="E260" s="28"/>
       <c r="F260" s="28"/>
       <c r="G260" s="28"/>
-      <c r="H260" s="60"/>
-      <c r="I260" s="68"/>
-      <c r="J260" s="68"/>
-      <c r="K260" s="68"/>
-      <c r="L260" s="68"/>
-      <c r="M260" s="68"/>
-      <c r="N260" s="68"/>
-      <c r="O260" s="68"/>
-      <c r="P260" s="68"/>
-      <c r="Q260" s="68"/>
-      <c r="R260" s="68"/>
-      <c r="S260" s="68"/>
-      <c r="T260" s="68"/>
-      <c r="U260" s="61"/>
+      <c r="H260" s="67"/>
+      <c r="I260" s="75"/>
+      <c r="J260" s="75"/>
+      <c r="K260" s="75"/>
+      <c r="L260" s="75"/>
+      <c r="M260" s="75"/>
+      <c r="N260" s="75"/>
+      <c r="O260" s="75"/>
+      <c r="P260" s="75"/>
+      <c r="Q260" s="75"/>
+      <c r="R260" s="75"/>
+      <c r="S260" s="75"/>
+      <c r="T260" s="75"/>
+      <c r="U260" s="68"/>
     </row>
     <row r="261" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A261" s="27"/>
@@ -31607,20 +31683,20 @@
       <c r="E261" s="28"/>
       <c r="F261" s="28"/>
       <c r="G261" s="28"/>
-      <c r="H261" s="60"/>
-      <c r="I261" s="68"/>
-      <c r="J261" s="68"/>
-      <c r="K261" s="68"/>
-      <c r="L261" s="68"/>
-      <c r="M261" s="68"/>
-      <c r="N261" s="68"/>
-      <c r="O261" s="68"/>
-      <c r="P261" s="68"/>
-      <c r="Q261" s="68"/>
-      <c r="R261" s="68"/>
-      <c r="S261" s="68"/>
-      <c r="T261" s="68"/>
-      <c r="U261" s="61"/>
+      <c r="H261" s="67"/>
+      <c r="I261" s="75"/>
+      <c r="J261" s="75"/>
+      <c r="K261" s="75"/>
+      <c r="L261" s="75"/>
+      <c r="M261" s="75"/>
+      <c r="N261" s="75"/>
+      <c r="O261" s="75"/>
+      <c r="P261" s="75"/>
+      <c r="Q261" s="75"/>
+      <c r="R261" s="75"/>
+      <c r="S261" s="75"/>
+      <c r="T261" s="75"/>
+      <c r="U261" s="68"/>
     </row>
     <row r="262" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="27"/>
@@ -31636,20 +31712,20 @@
       <c r="E262" s="28"/>
       <c r="F262" s="28"/>
       <c r="G262" s="28"/>
-      <c r="H262" s="60"/>
-      <c r="I262" s="68"/>
-      <c r="J262" s="68"/>
-      <c r="K262" s="68"/>
-      <c r="L262" s="68"/>
-      <c r="M262" s="68"/>
-      <c r="N262" s="68"/>
-      <c r="O262" s="68"/>
-      <c r="P262" s="68"/>
-      <c r="Q262" s="68"/>
-      <c r="R262" s="68"/>
-      <c r="S262" s="68"/>
-      <c r="T262" s="68"/>
-      <c r="U262" s="61"/>
+      <c r="H262" s="67"/>
+      <c r="I262" s="75"/>
+      <c r="J262" s="75"/>
+      <c r="K262" s="75"/>
+      <c r="L262" s="75"/>
+      <c r="M262" s="75"/>
+      <c r="N262" s="75"/>
+      <c r="O262" s="75"/>
+      <c r="P262" s="75"/>
+      <c r="Q262" s="75"/>
+      <c r="R262" s="75"/>
+      <c r="S262" s="75"/>
+      <c r="T262" s="75"/>
+      <c r="U262" s="68"/>
     </row>
     <row r="263" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="27"/>
@@ -31665,20 +31741,20 @@
       <c r="E263" s="28"/>
       <c r="F263" s="28"/>
       <c r="G263" s="28"/>
-      <c r="H263" s="60"/>
-      <c r="I263" s="68"/>
-      <c r="J263" s="68"/>
-      <c r="K263" s="68"/>
-      <c r="L263" s="68"/>
-      <c r="M263" s="68"/>
-      <c r="N263" s="68"/>
-      <c r="O263" s="68"/>
-      <c r="P263" s="68"/>
-      <c r="Q263" s="68"/>
-      <c r="R263" s="68"/>
-      <c r="S263" s="68"/>
-      <c r="T263" s="68"/>
-      <c r="U263" s="61"/>
+      <c r="H263" s="67"/>
+      <c r="I263" s="75"/>
+      <c r="J263" s="75"/>
+      <c r="K263" s="75"/>
+      <c r="L263" s="75"/>
+      <c r="M263" s="75"/>
+      <c r="N263" s="75"/>
+      <c r="O263" s="75"/>
+      <c r="P263" s="75"/>
+      <c r="Q263" s="75"/>
+      <c r="R263" s="75"/>
+      <c r="S263" s="75"/>
+      <c r="T263" s="75"/>
+      <c r="U263" s="68"/>
     </row>
     <row r="264" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A264" s="27"/>
@@ -31694,20 +31770,20 @@
       <c r="E264" s="28"/>
       <c r="F264" s="28"/>
       <c r="G264" s="28"/>
-      <c r="H264" s="60"/>
-      <c r="I264" s="68"/>
-      <c r="J264" s="68"/>
-      <c r="K264" s="68"/>
-      <c r="L264" s="68"/>
-      <c r="M264" s="68"/>
-      <c r="N264" s="68"/>
-      <c r="O264" s="68"/>
-      <c r="P264" s="68"/>
-      <c r="Q264" s="68"/>
-      <c r="R264" s="68"/>
-      <c r="S264" s="68"/>
-      <c r="T264" s="68"/>
-      <c r="U264" s="61"/>
+      <c r="H264" s="67"/>
+      <c r="I264" s="75"/>
+      <c r="J264" s="75"/>
+      <c r="K264" s="75"/>
+      <c r="L264" s="75"/>
+      <c r="M264" s="75"/>
+      <c r="N264" s="75"/>
+      <c r="O264" s="75"/>
+      <c r="P264" s="75"/>
+      <c r="Q264" s="75"/>
+      <c r="R264" s="75"/>
+      <c r="S264" s="75"/>
+      <c r="T264" s="75"/>
+      <c r="U264" s="68"/>
     </row>
     <row r="265" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A265" s="27"/>
@@ -31723,20 +31799,20 @@
       <c r="E265" s="28"/>
       <c r="F265" s="28"/>
       <c r="G265" s="28"/>
-      <c r="H265" s="60"/>
-      <c r="I265" s="68"/>
-      <c r="J265" s="68"/>
-      <c r="K265" s="68"/>
-      <c r="L265" s="68"/>
-      <c r="M265" s="68"/>
-      <c r="N265" s="68"/>
-      <c r="O265" s="68"/>
-      <c r="P265" s="68"/>
-      <c r="Q265" s="68"/>
-      <c r="R265" s="68"/>
-      <c r="S265" s="68"/>
-      <c r="T265" s="68"/>
-      <c r="U265" s="61"/>
+      <c r="H265" s="67"/>
+      <c r="I265" s="75"/>
+      <c r="J265" s="75"/>
+      <c r="K265" s="75"/>
+      <c r="L265" s="75"/>
+      <c r="M265" s="75"/>
+      <c r="N265" s="75"/>
+      <c r="O265" s="75"/>
+      <c r="P265" s="75"/>
+      <c r="Q265" s="75"/>
+      <c r="R265" s="75"/>
+      <c r="S265" s="75"/>
+      <c r="T265" s="75"/>
+      <c r="U265" s="68"/>
     </row>
     <row r="266" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A266" s="27"/>
@@ -31752,20 +31828,20 @@
       <c r="E266" s="28"/>
       <c r="F266" s="28"/>
       <c r="G266" s="28"/>
-      <c r="H266" s="60"/>
-      <c r="I266" s="68"/>
-      <c r="J266" s="68"/>
-      <c r="K266" s="68"/>
-      <c r="L266" s="68"/>
-      <c r="M266" s="68"/>
-      <c r="N266" s="68"/>
-      <c r="O266" s="68"/>
-      <c r="P266" s="68"/>
-      <c r="Q266" s="68"/>
-      <c r="R266" s="68"/>
-      <c r="S266" s="68"/>
-      <c r="T266" s="68"/>
-      <c r="U266" s="61"/>
+      <c r="H266" s="67"/>
+      <c r="I266" s="75"/>
+      <c r="J266" s="75"/>
+      <c r="K266" s="75"/>
+      <c r="L266" s="75"/>
+      <c r="M266" s="75"/>
+      <c r="N266" s="75"/>
+      <c r="O266" s="75"/>
+      <c r="P266" s="75"/>
+      <c r="Q266" s="75"/>
+      <c r="R266" s="75"/>
+      <c r="S266" s="75"/>
+      <c r="T266" s="75"/>
+      <c r="U266" s="68"/>
     </row>
     <row r="267" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="27"/>
@@ -31781,20 +31857,20 @@
       <c r="E267" s="28"/>
       <c r="F267" s="28"/>
       <c r="G267" s="28"/>
-      <c r="H267" s="60"/>
-      <c r="I267" s="68"/>
-      <c r="J267" s="68"/>
-      <c r="K267" s="68"/>
-      <c r="L267" s="68"/>
-      <c r="M267" s="68"/>
-      <c r="N267" s="68"/>
-      <c r="O267" s="68"/>
-      <c r="P267" s="68"/>
-      <c r="Q267" s="68"/>
-      <c r="R267" s="68"/>
-      <c r="S267" s="68"/>
-      <c r="T267" s="68"/>
-      <c r="U267" s="61"/>
+      <c r="H267" s="67"/>
+      <c r="I267" s="75"/>
+      <c r="J267" s="75"/>
+      <c r="K267" s="75"/>
+      <c r="L267" s="75"/>
+      <c r="M267" s="75"/>
+      <c r="N267" s="75"/>
+      <c r="O267" s="75"/>
+      <c r="P267" s="75"/>
+      <c r="Q267" s="75"/>
+      <c r="R267" s="75"/>
+      <c r="S267" s="75"/>
+      <c r="T267" s="75"/>
+      <c r="U267" s="68"/>
     </row>
     <row r="268" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="27"/>
@@ -31810,22 +31886,22 @@
       <c r="E268" s="28"/>
       <c r="F268" s="28"/>
       <c r="G268" s="28"/>
-      <c r="H268" s="60" t="s">
+      <c r="H268" s="67" t="s">
         <v>1092</v>
       </c>
-      <c r="I268" s="68"/>
-      <c r="J268" s="68"/>
-      <c r="K268" s="68"/>
-      <c r="L268" s="68"/>
-      <c r="M268" s="68"/>
-      <c r="N268" s="68"/>
-      <c r="O268" s="68"/>
-      <c r="P268" s="68"/>
-      <c r="Q268" s="68"/>
-      <c r="R268" s="68"/>
-      <c r="S268" s="68"/>
-      <c r="T268" s="68"/>
-      <c r="U268" s="61"/>
+      <c r="I268" s="75"/>
+      <c r="J268" s="75"/>
+      <c r="K268" s="75"/>
+      <c r="L268" s="75"/>
+      <c r="M268" s="75"/>
+      <c r="N268" s="75"/>
+      <c r="O268" s="75"/>
+      <c r="P268" s="75"/>
+      <c r="Q268" s="75"/>
+      <c r="R268" s="75"/>
+      <c r="S268" s="75"/>
+      <c r="T268" s="75"/>
+      <c r="U268" s="68"/>
     </row>
     <row r="269" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="27"/>
@@ -31841,20 +31917,20 @@
       <c r="E269" s="28"/>
       <c r="F269" s="28"/>
       <c r="G269" s="28"/>
-      <c r="H269" s="60"/>
-      <c r="I269" s="68"/>
-      <c r="J269" s="68"/>
-      <c r="K269" s="68"/>
-      <c r="L269" s="68"/>
-      <c r="M269" s="68"/>
-      <c r="N269" s="68"/>
-      <c r="O269" s="68"/>
-      <c r="P269" s="68"/>
-      <c r="Q269" s="68"/>
-      <c r="R269" s="68"/>
-      <c r="S269" s="68"/>
-      <c r="T269" s="68"/>
-      <c r="U269" s="61"/>
+      <c r="H269" s="67"/>
+      <c r="I269" s="75"/>
+      <c r="J269" s="75"/>
+      <c r="K269" s="75"/>
+      <c r="L269" s="75"/>
+      <c r="M269" s="75"/>
+      <c r="N269" s="75"/>
+      <c r="O269" s="75"/>
+      <c r="P269" s="75"/>
+      <c r="Q269" s="75"/>
+      <c r="R269" s="75"/>
+      <c r="S269" s="75"/>
+      <c r="T269" s="75"/>
+      <c r="U269" s="68"/>
     </row>
     <row r="270" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A270" s="27"/>
@@ -31868,20 +31944,20 @@
       <c r="E270" s="28"/>
       <c r="F270" s="28"/>
       <c r="G270" s="28"/>
-      <c r="H270" s="60"/>
-      <c r="I270" s="68"/>
-      <c r="J270" s="68"/>
-      <c r="K270" s="68"/>
-      <c r="L270" s="68"/>
-      <c r="M270" s="68"/>
-      <c r="N270" s="68"/>
-      <c r="O270" s="68"/>
-      <c r="P270" s="68"/>
-      <c r="Q270" s="68"/>
-      <c r="R270" s="68"/>
-      <c r="S270" s="68"/>
-      <c r="T270" s="68"/>
-      <c r="U270" s="61"/>
+      <c r="H270" s="67"/>
+      <c r="I270" s="75"/>
+      <c r="J270" s="75"/>
+      <c r="K270" s="75"/>
+      <c r="L270" s="75"/>
+      <c r="M270" s="75"/>
+      <c r="N270" s="75"/>
+      <c r="O270" s="75"/>
+      <c r="P270" s="75"/>
+      <c r="Q270" s="75"/>
+      <c r="R270" s="75"/>
+      <c r="S270" s="75"/>
+      <c r="T270" s="75"/>
+      <c r="U270" s="68"/>
     </row>
     <row r="271" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="27"/>
@@ -31895,20 +31971,20 @@
       <c r="E271" s="28"/>
       <c r="F271" s="28"/>
       <c r="G271" s="28"/>
-      <c r="H271" s="60"/>
-      <c r="I271" s="68"/>
-      <c r="J271" s="68"/>
-      <c r="K271" s="68"/>
-      <c r="L271" s="68"/>
-      <c r="M271" s="68"/>
-      <c r="N271" s="68"/>
-      <c r="O271" s="68"/>
-      <c r="P271" s="68"/>
-      <c r="Q271" s="68"/>
-      <c r="R271" s="68"/>
-      <c r="S271" s="68"/>
-      <c r="T271" s="68"/>
-      <c r="U271" s="61"/>
+      <c r="H271" s="67"/>
+      <c r="I271" s="75"/>
+      <c r="J271" s="75"/>
+      <c r="K271" s="75"/>
+      <c r="L271" s="75"/>
+      <c r="M271" s="75"/>
+      <c r="N271" s="75"/>
+      <c r="O271" s="75"/>
+      <c r="P271" s="75"/>
+      <c r="Q271" s="75"/>
+      <c r="R271" s="75"/>
+      <c r="S271" s="75"/>
+      <c r="T271" s="75"/>
+      <c r="U271" s="68"/>
     </row>
     <row r="272" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="27"/>
@@ -31922,20 +31998,20 @@
       <c r="E272" s="28"/>
       <c r="F272" s="28"/>
       <c r="G272" s="28"/>
-      <c r="H272" s="60"/>
-      <c r="I272" s="68"/>
-      <c r="J272" s="68"/>
-      <c r="K272" s="68"/>
-      <c r="L272" s="68"/>
-      <c r="M272" s="68"/>
-      <c r="N272" s="68"/>
-      <c r="O272" s="68"/>
-      <c r="P272" s="68"/>
-      <c r="Q272" s="68"/>
-      <c r="R272" s="68"/>
-      <c r="S272" s="68"/>
-      <c r="T272" s="68"/>
-      <c r="U272" s="61"/>
+      <c r="H272" s="67"/>
+      <c r="I272" s="75"/>
+      <c r="J272" s="75"/>
+      <c r="K272" s="75"/>
+      <c r="L272" s="75"/>
+      <c r="M272" s="75"/>
+      <c r="N272" s="75"/>
+      <c r="O272" s="75"/>
+      <c r="P272" s="75"/>
+      <c r="Q272" s="75"/>
+      <c r="R272" s="75"/>
+      <c r="S272" s="75"/>
+      <c r="T272" s="75"/>
+      <c r="U272" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="64">

--- a/school_lublino/lublino_KP.xlsx
+++ b/school_lublino/lublino_KP.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ТКП" sheetId="1" r:id="rId1"/>
@@ -3910,6 +3910,42 @@
     <xf numFmtId="164" fontId="9" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3940,40 +3976,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3983,9 +3986,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4376,163 +4376,163 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="55"/>
-      <c r="T2" s="55"/>
-      <c r="U2" s="55"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
+      <c r="P3" s="68"/>
+      <c r="Q3" s="68"/>
+      <c r="R3" s="68"/>
+      <c r="S3" s="68"/>
+      <c r="T3" s="68"/>
+      <c r="U3" s="68"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="57"/>
-      <c r="O4" s="57"/>
-      <c r="P4" s="57"/>
-      <c r="Q4" s="57"/>
-      <c r="R4" s="57"/>
-      <c r="S4" s="57"/>
-      <c r="T4" s="57"/>
-      <c r="U4" s="57"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="69"/>
+      <c r="Q4" s="69"/>
+      <c r="R4" s="69"/>
+      <c r="S4" s="69"/>
+      <c r="T4" s="69"/>
+      <c r="U4" s="69"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="64" t="s">
+      <c r="A5" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="64" t="s">
+      <c r="C5" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="64" t="s">
+      <c r="D5" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="64" t="s">
+      <c r="E5" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="64" t="s">
+      <c r="F5" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="64" t="s">
+      <c r="H5" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="64" t="s">
+      <c r="I5" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="58" t="s">
+      <c r="J5" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="59"/>
-      <c r="L5" s="59"/>
-      <c r="M5" s="59"/>
-      <c r="N5" s="59"/>
-      <c r="O5" s="60"/>
-      <c r="P5" s="61" t="s">
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="72"/>
+      <c r="P5" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="62"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="61" t="s">
+      <c r="Q5" s="74"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="62"/>
-      <c r="U5" s="63"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="75"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="65"/>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="67" t="s">
+      <c r="A6" s="76"/>
+      <c r="B6" s="76"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="68"/>
-      <c r="L6" s="64" t="s">
+      <c r="K6" s="58"/>
+      <c r="L6" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="67" t="s">
+      <c r="M6" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="68"/>
-      <c r="O6" s="64" t="s">
+      <c r="N6" s="58"/>
+      <c r="O6" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="67" t="s">
+      <c r="P6" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="68"/>
-      <c r="R6" s="64" t="s">
+      <c r="Q6" s="58"/>
+      <c r="R6" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="S6" s="67" t="s">
+      <c r="S6" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="68"/>
-      <c r="U6" s="64" t="s">
+      <c r="T6" s="58"/>
+      <c r="U6" s="65" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4576,17 +4576,17 @@
       <c r="U7" s="66"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="69" t="s">
+      <c r="A8" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="70"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="71"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="64"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -4628,15 +4628,15 @@
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="72" t="s">
+      <c r="C9" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="74"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="61"/>
       <c r="M9" s="6">
         <f>SUM(M10,M20)</f>
         <v>18303819.899999999</v>
@@ -4672,15 +4672,15 @@
       <c r="B10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="72" t="s">
+      <c r="C10" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="73"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="74"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="61"/>
       <c r="M10" s="6">
         <f t="shared" ref="M10:O14" si="0">SUM(M11)</f>
         <v>126283.29</v>
@@ -4716,15 +4716,15 @@
       <c r="B11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="72" t="s">
+      <c r="C11" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="74"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="61"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4760,15 +4760,15 @@
       <c r="B12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="72" t="s">
+      <c r="C12" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="74"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="61"/>
       <c r="M12" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4804,15 +4804,15 @@
       <c r="B13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="72" t="s">
+      <c r="C13" s="59" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="74"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="61"/>
       <c r="M13" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4848,15 +4848,15 @@
       <c r="B14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="72" t="s">
+      <c r="C14" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="74"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="61"/>
       <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -5147,15 +5147,15 @@
       <c r="B20" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="72" t="s">
+      <c r="C20" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="74"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="61"/>
       <c r="M20" s="6">
         <f t="shared" ref="M20:O21" si="1">SUM(M21)</f>
         <v>18177536.609999999</v>
@@ -5191,15 +5191,15 @@
       <c r="B21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="72" t="s">
+      <c r="C21" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="73"/>
-      <c r="G21" s="73"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="74"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="61"/>
       <c r="M21" s="6">
         <f t="shared" si="1"/>
         <v>18177536.609999999</v>
@@ -5235,15 +5235,15 @@
       <c r="B22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="72" t="s">
+      <c r="C22" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="74"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="61"/>
       <c r="M22" s="6">
         <f>SUM(M23,M122,M163,M203,M248)</f>
         <v>18177536.609999999</v>
@@ -5279,15 +5279,15 @@
       <c r="B23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="72" t="s">
+      <c r="C23" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="74"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="61"/>
       <c r="M23" s="6">
         <f>SUM(M24,M67,M76,M119)</f>
         <v>12831032.07</v>
@@ -5323,15 +5323,15 @@
       <c r="B24" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="72" t="s">
+      <c r="C24" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="73"/>
-      <c r="H24" s="73"/>
-      <c r="I24" s="74"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="61"/>
       <c r="M24" s="6">
         <f>SUM(M25,M29,M31,M34,M36,M41,M46,M51,M57,M62)</f>
         <v>7808423.3099999996</v>
@@ -7555,15 +7555,15 @@
       <c r="B67" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="72" t="s">
+      <c r="C67" s="59" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="73"/>
-      <c r="E67" s="73"/>
-      <c r="F67" s="73"/>
-      <c r="G67" s="73"/>
-      <c r="H67" s="73"/>
-      <c r="I67" s="74"/>
+      <c r="D67" s="60"/>
+      <c r="E67" s="60"/>
+      <c r="F67" s="60"/>
+      <c r="G67" s="60"/>
+      <c r="H67" s="60"/>
+      <c r="I67" s="61"/>
       <c r="M67" s="6">
         <f>SUM(M68,M72,M74)</f>
         <v>748533.11</v>
@@ -8061,15 +8061,15 @@
       <c r="B76" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C76" s="72" t="s">
+      <c r="C76" s="59" t="s">
         <v>325</v>
       </c>
-      <c r="D76" s="73"/>
-      <c r="E76" s="73"/>
-      <c r="F76" s="73"/>
-      <c r="G76" s="73"/>
-      <c r="H76" s="73"/>
-      <c r="I76" s="74"/>
+      <c r="D76" s="60"/>
+      <c r="E76" s="60"/>
+      <c r="F76" s="60"/>
+      <c r="G76" s="60"/>
+      <c r="H76" s="60"/>
+      <c r="I76" s="61"/>
       <c r="M76" s="6">
         <f>SUM(M77,M82,M87,M93,M96,M99,M104,M109,M114,M117)</f>
         <v>3831185.6499999994</v>
@@ -10319,15 +10319,15 @@
       <c r="B119" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C119" s="72" t="s">
+      <c r="C119" s="59" t="s">
         <v>526</v>
       </c>
-      <c r="D119" s="73"/>
-      <c r="E119" s="73"/>
-      <c r="F119" s="73"/>
-      <c r="G119" s="73"/>
-      <c r="H119" s="73"/>
-      <c r="I119" s="74"/>
+      <c r="D119" s="60"/>
+      <c r="E119" s="60"/>
+      <c r="F119" s="60"/>
+      <c r="G119" s="60"/>
+      <c r="H119" s="60"/>
+      <c r="I119" s="61"/>
       <c r="M119" s="6">
         <f>SUM(M120)</f>
         <v>442890</v>
@@ -10489,15 +10489,15 @@
       <c r="B122" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="C122" s="72" t="s">
+      <c r="C122" s="59" t="s">
         <v>541</v>
       </c>
-      <c r="D122" s="73"/>
-      <c r="E122" s="73"/>
-      <c r="F122" s="73"/>
-      <c r="G122" s="73"/>
-      <c r="H122" s="73"/>
-      <c r="I122" s="74"/>
+      <c r="D122" s="60"/>
+      <c r="E122" s="60"/>
+      <c r="F122" s="60"/>
+      <c r="G122" s="60"/>
+      <c r="H122" s="60"/>
+      <c r="I122" s="61"/>
       <c r="M122" s="6">
         <f>SUM(M123)</f>
         <v>4016037.31</v>
@@ -10533,15 +10533,15 @@
       <c r="B123" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="C123" s="72" t="s">
+      <c r="C123" s="59" t="s">
         <v>544</v>
       </c>
-      <c r="D123" s="73"/>
-      <c r="E123" s="73"/>
-      <c r="F123" s="73"/>
-      <c r="G123" s="73"/>
-      <c r="H123" s="73"/>
-      <c r="I123" s="74"/>
+      <c r="D123" s="60"/>
+      <c r="E123" s="60"/>
+      <c r="F123" s="60"/>
+      <c r="G123" s="60"/>
+      <c r="H123" s="60"/>
+      <c r="I123" s="61"/>
       <c r="M123" s="6">
         <f>SUM(M124,M127,M131,M136,M140,M143,M148,M153,M158)</f>
         <v>4016037.31</v>
@@ -12622,15 +12622,15 @@
       <c r="B163" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C163" s="72" t="s">
+      <c r="C163" s="59" t="s">
         <v>710</v>
       </c>
-      <c r="D163" s="73"/>
-      <c r="E163" s="73"/>
-      <c r="F163" s="73"/>
-      <c r="G163" s="73"/>
-      <c r="H163" s="73"/>
-      <c r="I163" s="74"/>
+      <c r="D163" s="60"/>
+      <c r="E163" s="60"/>
+      <c r="F163" s="60"/>
+      <c r="G163" s="60"/>
+      <c r="H163" s="60"/>
+      <c r="I163" s="61"/>
       <c r="M163" s="6">
         <f>SUM(M164,M184)</f>
         <v>611422.71999999997</v>
@@ -12666,15 +12666,15 @@
       <c r="B164" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="C164" s="72" t="s">
+      <c r="C164" s="59" t="s">
         <v>713</v>
       </c>
-      <c r="D164" s="73"/>
-      <c r="E164" s="73"/>
-      <c r="F164" s="73"/>
-      <c r="G164" s="73"/>
-      <c r="H164" s="73"/>
-      <c r="I164" s="74"/>
+      <c r="D164" s="60"/>
+      <c r="E164" s="60"/>
+      <c r="F164" s="60"/>
+      <c r="G164" s="60"/>
+      <c r="H164" s="60"/>
+      <c r="I164" s="61"/>
       <c r="M164" s="6">
         <f>SUM(M165,M171,M174,M178,M182)</f>
         <v>415021.23999999993</v>
@@ -13721,15 +13721,15 @@
       <c r="B184" s="9" t="s">
         <v>789</v>
       </c>
-      <c r="C184" s="72" t="s">
+      <c r="C184" s="59" t="s">
         <v>790</v>
       </c>
-      <c r="D184" s="73"/>
-      <c r="E184" s="73"/>
-      <c r="F184" s="73"/>
-      <c r="G184" s="73"/>
-      <c r="H184" s="73"/>
-      <c r="I184" s="74"/>
+      <c r="D184" s="60"/>
+      <c r="E184" s="60"/>
+      <c r="F184" s="60"/>
+      <c r="G184" s="60"/>
+      <c r="H184" s="60"/>
+      <c r="I184" s="61"/>
       <c r="M184" s="6">
         <f>SUM(M185,M188,M191,M194,M197,M200)</f>
         <v>196401.48</v>
@@ -14389,7 +14389,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="196" spans="1:35" ht="206.25" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:35" ht="225" x14ac:dyDescent="0.25">
       <c r="A196" s="9" t="s">
         <v>833</v>
       </c>
@@ -14779,15 +14779,15 @@
       <c r="B203" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="C203" s="72" t="s">
+      <c r="C203" s="59" t="s">
         <v>856</v>
       </c>
-      <c r="D203" s="73"/>
-      <c r="E203" s="73"/>
-      <c r="F203" s="73"/>
-      <c r="G203" s="73"/>
-      <c r="H203" s="73"/>
-      <c r="I203" s="74"/>
+      <c r="D203" s="60"/>
+      <c r="E203" s="60"/>
+      <c r="F203" s="60"/>
+      <c r="G203" s="60"/>
+      <c r="H203" s="60"/>
+      <c r="I203" s="61"/>
       <c r="M203" s="6">
         <f>SUM(M204,M206,M221,M236,M238,M240,M242,M243,M244,M245,M246,M247)</f>
         <v>719044.50999999989</v>
@@ -15195,7 +15195,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="211" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A211" s="9" t="s">
         <v>893</v>
       </c>
@@ -16138,7 +16138,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="232" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A232" s="9" t="s">
         <v>978</v>
       </c>
@@ -16517,7 +16517,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="239" spans="1:35" ht="393.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A239" s="9" t="s">
         <v>1004</v>
       </c>
@@ -17169,15 +17169,15 @@
       <c r="B248" s="9" t="s">
         <v>1031</v>
       </c>
-      <c r="C248" s="72" t="s">
+      <c r="C248" s="59" t="s">
         <v>1032</v>
       </c>
-      <c r="D248" s="73"/>
-      <c r="E248" s="73"/>
-      <c r="F248" s="73"/>
-      <c r="G248" s="73"/>
-      <c r="H248" s="73"/>
-      <c r="I248" s="74"/>
+      <c r="D248" s="60"/>
+      <c r="E248" s="60"/>
+      <c r="F248" s="60"/>
+      <c r="G248" s="60"/>
+      <c r="H248" s="60"/>
+      <c r="I248" s="61"/>
       <c r="M248" s="6">
         <f>SUM(M249,M250,M251,M252)</f>
         <v>0</v>
@@ -17564,29 +17564,29 @@
       </c>
     </row>
     <row r="254" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="69" t="s">
+      <c r="A254" s="62" t="s">
         <v>1050</v>
       </c>
-      <c r="B254" s="70"/>
-      <c r="C254" s="70"/>
-      <c r="D254" s="70"/>
-      <c r="E254" s="70"/>
-      <c r="F254" s="70"/>
-      <c r="G254" s="70"/>
-      <c r="H254" s="70"/>
-      <c r="I254" s="70"/>
-      <c r="J254" s="70"/>
-      <c r="K254" s="70"/>
-      <c r="L254" s="70"/>
-      <c r="M254" s="70"/>
-      <c r="N254" s="70"/>
-      <c r="O254" s="70"/>
-      <c r="P254" s="70"/>
-      <c r="Q254" s="70"/>
-      <c r="R254" s="70"/>
-      <c r="S254" s="70"/>
-      <c r="T254" s="70"/>
-      <c r="U254" s="71"/>
+      <c r="B254" s="63"/>
+      <c r="C254" s="63"/>
+      <c r="D254" s="63"/>
+      <c r="E254" s="63"/>
+      <c r="F254" s="63"/>
+      <c r="G254" s="63"/>
+      <c r="H254" s="63"/>
+      <c r="I254" s="63"/>
+      <c r="J254" s="63"/>
+      <c r="K254" s="63"/>
+      <c r="L254" s="63"/>
+      <c r="M254" s="63"/>
+      <c r="N254" s="63"/>
+      <c r="O254" s="63"/>
+      <c r="P254" s="63"/>
+      <c r="Q254" s="63"/>
+      <c r="R254" s="63"/>
+      <c r="S254" s="63"/>
+      <c r="T254" s="63"/>
+      <c r="U254" s="64"/>
     </row>
     <row r="255" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="27"/>
@@ -17602,20 +17602,20 @@
       <c r="E255" s="28"/>
       <c r="F255" s="28"/>
       <c r="G255" s="28"/>
-      <c r="H255" s="67"/>
-      <c r="I255" s="75"/>
-      <c r="J255" s="75"/>
-      <c r="K255" s="75"/>
-      <c r="L255" s="75"/>
-      <c r="M255" s="75"/>
-      <c r="N255" s="75"/>
-      <c r="O255" s="75"/>
-      <c r="P255" s="75"/>
-      <c r="Q255" s="75"/>
-      <c r="R255" s="75"/>
-      <c r="S255" s="75"/>
-      <c r="T255" s="75"/>
-      <c r="U255" s="68"/>
+      <c r="H255" s="56"/>
+      <c r="I255" s="57"/>
+      <c r="J255" s="57"/>
+      <c r="K255" s="57"/>
+      <c r="L255" s="57"/>
+      <c r="M255" s="57"/>
+      <c r="N255" s="57"/>
+      <c r="O255" s="57"/>
+      <c r="P255" s="57"/>
+      <c r="Q255" s="57"/>
+      <c r="R255" s="57"/>
+      <c r="S255" s="57"/>
+      <c r="T255" s="57"/>
+      <c r="U255" s="58"/>
     </row>
     <row r="256" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="27"/>
@@ -17631,20 +17631,20 @@
       <c r="E256" s="28"/>
       <c r="F256" s="28"/>
       <c r="G256" s="28"/>
-      <c r="H256" s="67"/>
-      <c r="I256" s="75"/>
-      <c r="J256" s="75"/>
-      <c r="K256" s="75"/>
-      <c r="L256" s="75"/>
-      <c r="M256" s="75"/>
-      <c r="N256" s="75"/>
-      <c r="O256" s="75"/>
-      <c r="P256" s="75"/>
-      <c r="Q256" s="75"/>
-      <c r="R256" s="75"/>
-      <c r="S256" s="75"/>
-      <c r="T256" s="75"/>
-      <c r="U256" s="68"/>
+      <c r="H256" s="56"/>
+      <c r="I256" s="57"/>
+      <c r="J256" s="57"/>
+      <c r="K256" s="57"/>
+      <c r="L256" s="57"/>
+      <c r="M256" s="57"/>
+      <c r="N256" s="57"/>
+      <c r="O256" s="57"/>
+      <c r="P256" s="57"/>
+      <c r="Q256" s="57"/>
+      <c r="R256" s="57"/>
+      <c r="S256" s="57"/>
+      <c r="T256" s="57"/>
+      <c r="U256" s="58"/>
     </row>
     <row r="257" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A257" s="27"/>
@@ -17660,20 +17660,20 @@
       <c r="E257" s="28"/>
       <c r="F257" s="28"/>
       <c r="G257" s="28"/>
-      <c r="H257" s="67"/>
-      <c r="I257" s="75"/>
-      <c r="J257" s="75"/>
-      <c r="K257" s="75"/>
-      <c r="L257" s="75"/>
-      <c r="M257" s="75"/>
-      <c r="N257" s="75"/>
-      <c r="O257" s="75"/>
-      <c r="P257" s="75"/>
-      <c r="Q257" s="75"/>
-      <c r="R257" s="75"/>
-      <c r="S257" s="75"/>
-      <c r="T257" s="75"/>
-      <c r="U257" s="68"/>
+      <c r="H257" s="56"/>
+      <c r="I257" s="57"/>
+      <c r="J257" s="57"/>
+      <c r="K257" s="57"/>
+      <c r="L257" s="57"/>
+      <c r="M257" s="57"/>
+      <c r="N257" s="57"/>
+      <c r="O257" s="57"/>
+      <c r="P257" s="57"/>
+      <c r="Q257" s="57"/>
+      <c r="R257" s="57"/>
+      <c r="S257" s="57"/>
+      <c r="T257" s="57"/>
+      <c r="U257" s="58"/>
     </row>
     <row r="258" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="27"/>
@@ -17689,20 +17689,20 @@
       <c r="E258" s="28"/>
       <c r="F258" s="28"/>
       <c r="G258" s="28"/>
-      <c r="H258" s="67"/>
-      <c r="I258" s="75"/>
-      <c r="J258" s="75"/>
-      <c r="K258" s="75"/>
-      <c r="L258" s="75"/>
-      <c r="M258" s="75"/>
-      <c r="N258" s="75"/>
-      <c r="O258" s="75"/>
-      <c r="P258" s="75"/>
-      <c r="Q258" s="75"/>
-      <c r="R258" s="75"/>
-      <c r="S258" s="75"/>
-      <c r="T258" s="75"/>
-      <c r="U258" s="68"/>
+      <c r="H258" s="56"/>
+      <c r="I258" s="57"/>
+      <c r="J258" s="57"/>
+      <c r="K258" s="57"/>
+      <c r="L258" s="57"/>
+      <c r="M258" s="57"/>
+      <c r="N258" s="57"/>
+      <c r="O258" s="57"/>
+      <c r="P258" s="57"/>
+      <c r="Q258" s="57"/>
+      <c r="R258" s="57"/>
+      <c r="S258" s="57"/>
+      <c r="T258" s="57"/>
+      <c r="U258" s="58"/>
     </row>
     <row r="259" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="27"/>
@@ -17718,20 +17718,20 @@
       <c r="E259" s="28"/>
       <c r="F259" s="28"/>
       <c r="G259" s="28"/>
-      <c r="H259" s="67"/>
-      <c r="I259" s="75"/>
-      <c r="J259" s="75"/>
-      <c r="K259" s="75"/>
-      <c r="L259" s="75"/>
-      <c r="M259" s="75"/>
-      <c r="N259" s="75"/>
-      <c r="O259" s="75"/>
-      <c r="P259" s="75"/>
-      <c r="Q259" s="75"/>
-      <c r="R259" s="75"/>
-      <c r="S259" s="75"/>
-      <c r="T259" s="75"/>
-      <c r="U259" s="68"/>
+      <c r="H259" s="56"/>
+      <c r="I259" s="57"/>
+      <c r="J259" s="57"/>
+      <c r="K259" s="57"/>
+      <c r="L259" s="57"/>
+      <c r="M259" s="57"/>
+      <c r="N259" s="57"/>
+      <c r="O259" s="57"/>
+      <c r="P259" s="57"/>
+      <c r="Q259" s="57"/>
+      <c r="R259" s="57"/>
+      <c r="S259" s="57"/>
+      <c r="T259" s="57"/>
+      <c r="U259" s="58"/>
     </row>
     <row r="260" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A260" s="27"/>
@@ -17747,20 +17747,20 @@
       <c r="E260" s="28"/>
       <c r="F260" s="28"/>
       <c r="G260" s="28"/>
-      <c r="H260" s="67"/>
-      <c r="I260" s="75"/>
-      <c r="J260" s="75"/>
-      <c r="K260" s="75"/>
-      <c r="L260" s="75"/>
-      <c r="M260" s="75"/>
-      <c r="N260" s="75"/>
-      <c r="O260" s="75"/>
-      <c r="P260" s="75"/>
-      <c r="Q260" s="75"/>
-      <c r="R260" s="75"/>
-      <c r="S260" s="75"/>
-      <c r="T260" s="75"/>
-      <c r="U260" s="68"/>
+      <c r="H260" s="56"/>
+      <c r="I260" s="57"/>
+      <c r="J260" s="57"/>
+      <c r="K260" s="57"/>
+      <c r="L260" s="57"/>
+      <c r="M260" s="57"/>
+      <c r="N260" s="57"/>
+      <c r="O260" s="57"/>
+      <c r="P260" s="57"/>
+      <c r="Q260" s="57"/>
+      <c r="R260" s="57"/>
+      <c r="S260" s="57"/>
+      <c r="T260" s="57"/>
+      <c r="U260" s="58"/>
     </row>
     <row r="261" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A261" s="27"/>
@@ -17776,22 +17776,22 @@
       <c r="E261" s="28"/>
       <c r="F261" s="28"/>
       <c r="G261" s="28"/>
-      <c r="H261" s="67"/>
-      <c r="I261" s="75"/>
-      <c r="J261" s="75"/>
-      <c r="K261" s="75"/>
-      <c r="L261" s="75"/>
-      <c r="M261" s="75"/>
-      <c r="N261" s="75"/>
-      <c r="O261" s="75"/>
-      <c r="P261" s="75"/>
-      <c r="Q261" s="75"/>
-      <c r="R261" s="75"/>
-      <c r="S261" s="75"/>
-      <c r="T261" s="75"/>
-      <c r="U261" s="68"/>
-    </row>
-    <row r="262" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H261" s="56"/>
+      <c r="I261" s="57"/>
+      <c r="J261" s="57"/>
+      <c r="K261" s="57"/>
+      <c r="L261" s="57"/>
+      <c r="M261" s="57"/>
+      <c r="N261" s="57"/>
+      <c r="O261" s="57"/>
+      <c r="P261" s="57"/>
+      <c r="Q261" s="57"/>
+      <c r="R261" s="57"/>
+      <c r="S261" s="57"/>
+      <c r="T261" s="57"/>
+      <c r="U261" s="58"/>
+    </row>
+    <row r="262" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A262" s="27"/>
       <c r="B262" s="5" t="s">
         <v>1071</v>
@@ -17805,20 +17805,20 @@
       <c r="E262" s="28"/>
       <c r="F262" s="28"/>
       <c r="G262" s="28"/>
-      <c r="H262" s="67"/>
-      <c r="I262" s="75"/>
-      <c r="J262" s="75"/>
-      <c r="K262" s="75"/>
-      <c r="L262" s="75"/>
-      <c r="M262" s="75"/>
-      <c r="N262" s="75"/>
-      <c r="O262" s="75"/>
-      <c r="P262" s="75"/>
-      <c r="Q262" s="75"/>
-      <c r="R262" s="75"/>
-      <c r="S262" s="75"/>
-      <c r="T262" s="75"/>
-      <c r="U262" s="68"/>
+      <c r="H262" s="56"/>
+      <c r="I262" s="57"/>
+      <c r="J262" s="57"/>
+      <c r="K262" s="57"/>
+      <c r="L262" s="57"/>
+      <c r="M262" s="57"/>
+      <c r="N262" s="57"/>
+      <c r="O262" s="57"/>
+      <c r="P262" s="57"/>
+      <c r="Q262" s="57"/>
+      <c r="R262" s="57"/>
+      <c r="S262" s="57"/>
+      <c r="T262" s="57"/>
+      <c r="U262" s="58"/>
     </row>
     <row r="263" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="27"/>
@@ -17834,20 +17834,20 @@
       <c r="E263" s="28"/>
       <c r="F263" s="28"/>
       <c r="G263" s="28"/>
-      <c r="H263" s="67"/>
-      <c r="I263" s="75"/>
-      <c r="J263" s="75"/>
-      <c r="K263" s="75"/>
-      <c r="L263" s="75"/>
-      <c r="M263" s="75"/>
-      <c r="N263" s="75"/>
-      <c r="O263" s="75"/>
-      <c r="P263" s="75"/>
-      <c r="Q263" s="75"/>
-      <c r="R263" s="75"/>
-      <c r="S263" s="75"/>
-      <c r="T263" s="75"/>
-      <c r="U263" s="68"/>
+      <c r="H263" s="56"/>
+      <c r="I263" s="57"/>
+      <c r="J263" s="57"/>
+      <c r="K263" s="57"/>
+      <c r="L263" s="57"/>
+      <c r="M263" s="57"/>
+      <c r="N263" s="57"/>
+      <c r="O263" s="57"/>
+      <c r="P263" s="57"/>
+      <c r="Q263" s="57"/>
+      <c r="R263" s="57"/>
+      <c r="S263" s="57"/>
+      <c r="T263" s="57"/>
+      <c r="U263" s="58"/>
     </row>
     <row r="264" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A264" s="27"/>
@@ -17863,20 +17863,20 @@
       <c r="E264" s="28"/>
       <c r="F264" s="28"/>
       <c r="G264" s="28"/>
-      <c r="H264" s="67"/>
-      <c r="I264" s="75"/>
-      <c r="J264" s="75"/>
-      <c r="K264" s="75"/>
-      <c r="L264" s="75"/>
-      <c r="M264" s="75"/>
-      <c r="N264" s="75"/>
-      <c r="O264" s="75"/>
-      <c r="P264" s="75"/>
-      <c r="Q264" s="75"/>
-      <c r="R264" s="75"/>
-      <c r="S264" s="75"/>
-      <c r="T264" s="75"/>
-      <c r="U264" s="68"/>
+      <c r="H264" s="56"/>
+      <c r="I264" s="57"/>
+      <c r="J264" s="57"/>
+      <c r="K264" s="57"/>
+      <c r="L264" s="57"/>
+      <c r="M264" s="57"/>
+      <c r="N264" s="57"/>
+      <c r="O264" s="57"/>
+      <c r="P264" s="57"/>
+      <c r="Q264" s="57"/>
+      <c r="R264" s="57"/>
+      <c r="S264" s="57"/>
+      <c r="T264" s="57"/>
+      <c r="U264" s="58"/>
     </row>
     <row r="265" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A265" s="27"/>
@@ -17892,20 +17892,20 @@
       <c r="E265" s="28"/>
       <c r="F265" s="28"/>
       <c r="G265" s="28"/>
-      <c r="H265" s="67"/>
-      <c r="I265" s="75"/>
-      <c r="J265" s="75"/>
-      <c r="K265" s="75"/>
-      <c r="L265" s="75"/>
-      <c r="M265" s="75"/>
-      <c r="N265" s="75"/>
-      <c r="O265" s="75"/>
-      <c r="P265" s="75"/>
-      <c r="Q265" s="75"/>
-      <c r="R265" s="75"/>
-      <c r="S265" s="75"/>
-      <c r="T265" s="75"/>
-      <c r="U265" s="68"/>
+      <c r="H265" s="56"/>
+      <c r="I265" s="57"/>
+      <c r="J265" s="57"/>
+      <c r="K265" s="57"/>
+      <c r="L265" s="57"/>
+      <c r="M265" s="57"/>
+      <c r="N265" s="57"/>
+      <c r="O265" s="57"/>
+      <c r="P265" s="57"/>
+      <c r="Q265" s="57"/>
+      <c r="R265" s="57"/>
+      <c r="S265" s="57"/>
+      <c r="T265" s="57"/>
+      <c r="U265" s="58"/>
     </row>
     <row r="266" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A266" s="27"/>
@@ -17921,20 +17921,20 @@
       <c r="E266" s="28"/>
       <c r="F266" s="28"/>
       <c r="G266" s="28"/>
-      <c r="H266" s="67"/>
-      <c r="I266" s="75"/>
-      <c r="J266" s="75"/>
-      <c r="K266" s="75"/>
-      <c r="L266" s="75"/>
-      <c r="M266" s="75"/>
-      <c r="N266" s="75"/>
-      <c r="O266" s="75"/>
-      <c r="P266" s="75"/>
-      <c r="Q266" s="75"/>
-      <c r="R266" s="75"/>
-      <c r="S266" s="75"/>
-      <c r="T266" s="75"/>
-      <c r="U266" s="68"/>
+      <c r="H266" s="56"/>
+      <c r="I266" s="57"/>
+      <c r="J266" s="57"/>
+      <c r="K266" s="57"/>
+      <c r="L266" s="57"/>
+      <c r="M266" s="57"/>
+      <c r="N266" s="57"/>
+      <c r="O266" s="57"/>
+      <c r="P266" s="57"/>
+      <c r="Q266" s="57"/>
+      <c r="R266" s="57"/>
+      <c r="S266" s="57"/>
+      <c r="T266" s="57"/>
+      <c r="U266" s="58"/>
     </row>
     <row r="267" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="27"/>
@@ -17950,20 +17950,20 @@
       <c r="E267" s="28"/>
       <c r="F267" s="28"/>
       <c r="G267" s="28"/>
-      <c r="H267" s="67"/>
-      <c r="I267" s="75"/>
-      <c r="J267" s="75"/>
-      <c r="K267" s="75"/>
-      <c r="L267" s="75"/>
-      <c r="M267" s="75"/>
-      <c r="N267" s="75"/>
-      <c r="O267" s="75"/>
-      <c r="P267" s="75"/>
-      <c r="Q267" s="75"/>
-      <c r="R267" s="75"/>
-      <c r="S267" s="75"/>
-      <c r="T267" s="75"/>
-      <c r="U267" s="68"/>
+      <c r="H267" s="56"/>
+      <c r="I267" s="57"/>
+      <c r="J267" s="57"/>
+      <c r="K267" s="57"/>
+      <c r="L267" s="57"/>
+      <c r="M267" s="57"/>
+      <c r="N267" s="57"/>
+      <c r="O267" s="57"/>
+      <c r="P267" s="57"/>
+      <c r="Q267" s="57"/>
+      <c r="R267" s="57"/>
+      <c r="S267" s="57"/>
+      <c r="T267" s="57"/>
+      <c r="U267" s="58"/>
     </row>
     <row r="268" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="27"/>
@@ -17979,22 +17979,22 @@
       <c r="E268" s="28"/>
       <c r="F268" s="28"/>
       <c r="G268" s="28"/>
-      <c r="H268" s="67" t="s">
+      <c r="H268" s="56" t="s">
         <v>1092</v>
       </c>
-      <c r="I268" s="75"/>
-      <c r="J268" s="75"/>
-      <c r="K268" s="75"/>
-      <c r="L268" s="75"/>
-      <c r="M268" s="75"/>
-      <c r="N268" s="75"/>
-      <c r="O268" s="75"/>
-      <c r="P268" s="75"/>
-      <c r="Q268" s="75"/>
-      <c r="R268" s="75"/>
-      <c r="S268" s="75"/>
-      <c r="T268" s="75"/>
-      <c r="U268" s="68"/>
+      <c r="I268" s="57"/>
+      <c r="J268" s="57"/>
+      <c r="K268" s="57"/>
+      <c r="L268" s="57"/>
+      <c r="M268" s="57"/>
+      <c r="N268" s="57"/>
+      <c r="O268" s="57"/>
+      <c r="P268" s="57"/>
+      <c r="Q268" s="57"/>
+      <c r="R268" s="57"/>
+      <c r="S268" s="57"/>
+      <c r="T268" s="57"/>
+      <c r="U268" s="58"/>
     </row>
     <row r="269" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="27"/>
@@ -18010,20 +18010,20 @@
       <c r="E269" s="28"/>
       <c r="F269" s="28"/>
       <c r="G269" s="28"/>
-      <c r="H269" s="67"/>
-      <c r="I269" s="75"/>
-      <c r="J269" s="75"/>
-      <c r="K269" s="75"/>
-      <c r="L269" s="75"/>
-      <c r="M269" s="75"/>
-      <c r="N269" s="75"/>
-      <c r="O269" s="75"/>
-      <c r="P269" s="75"/>
-      <c r="Q269" s="75"/>
-      <c r="R269" s="75"/>
-      <c r="S269" s="75"/>
-      <c r="T269" s="75"/>
-      <c r="U269" s="68"/>
+      <c r="H269" s="56"/>
+      <c r="I269" s="57"/>
+      <c r="J269" s="57"/>
+      <c r="K269" s="57"/>
+      <c r="L269" s="57"/>
+      <c r="M269" s="57"/>
+      <c r="N269" s="57"/>
+      <c r="O269" s="57"/>
+      <c r="P269" s="57"/>
+      <c r="Q269" s="57"/>
+      <c r="R269" s="57"/>
+      <c r="S269" s="57"/>
+      <c r="T269" s="57"/>
+      <c r="U269" s="58"/>
     </row>
     <row r="270" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A270" s="27"/>
@@ -18037,20 +18037,20 @@
       <c r="E270" s="28"/>
       <c r="F270" s="28"/>
       <c r="G270" s="28"/>
-      <c r="H270" s="67"/>
-      <c r="I270" s="75"/>
-      <c r="J270" s="75"/>
-      <c r="K270" s="75"/>
-      <c r="L270" s="75"/>
-      <c r="M270" s="75"/>
-      <c r="N270" s="75"/>
-      <c r="O270" s="75"/>
-      <c r="P270" s="75"/>
-      <c r="Q270" s="75"/>
-      <c r="R270" s="75"/>
-      <c r="S270" s="75"/>
-      <c r="T270" s="75"/>
-      <c r="U270" s="68"/>
+      <c r="H270" s="56"/>
+      <c r="I270" s="57"/>
+      <c r="J270" s="57"/>
+      <c r="K270" s="57"/>
+      <c r="L270" s="57"/>
+      <c r="M270" s="57"/>
+      <c r="N270" s="57"/>
+      <c r="O270" s="57"/>
+      <c r="P270" s="57"/>
+      <c r="Q270" s="57"/>
+      <c r="R270" s="57"/>
+      <c r="S270" s="57"/>
+      <c r="T270" s="57"/>
+      <c r="U270" s="58"/>
     </row>
     <row r="271" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="27"/>
@@ -18064,20 +18064,20 @@
       <c r="E271" s="28"/>
       <c r="F271" s="28"/>
       <c r="G271" s="28"/>
-      <c r="H271" s="67"/>
-      <c r="I271" s="75"/>
-      <c r="J271" s="75"/>
-      <c r="K271" s="75"/>
-      <c r="L271" s="75"/>
-      <c r="M271" s="75"/>
-      <c r="N271" s="75"/>
-      <c r="O271" s="75"/>
-      <c r="P271" s="75"/>
-      <c r="Q271" s="75"/>
-      <c r="R271" s="75"/>
-      <c r="S271" s="75"/>
-      <c r="T271" s="75"/>
-      <c r="U271" s="68"/>
+      <c r="H271" s="56"/>
+      <c r="I271" s="57"/>
+      <c r="J271" s="57"/>
+      <c r="K271" s="57"/>
+      <c r="L271" s="57"/>
+      <c r="M271" s="57"/>
+      <c r="N271" s="57"/>
+      <c r="O271" s="57"/>
+      <c r="P271" s="57"/>
+      <c r="Q271" s="57"/>
+      <c r="R271" s="57"/>
+      <c r="S271" s="57"/>
+      <c r="T271" s="57"/>
+      <c r="U271" s="58"/>
     </row>
     <row r="272" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="27"/>
@@ -18091,73 +18091,25 @@
       <c r="E272" s="28"/>
       <c r="F272" s="28"/>
       <c r="G272" s="28"/>
-      <c r="H272" s="67"/>
-      <c r="I272" s="75"/>
-      <c r="J272" s="75"/>
-      <c r="K272" s="75"/>
-      <c r="L272" s="75"/>
-      <c r="M272" s="75"/>
-      <c r="N272" s="75"/>
-      <c r="O272" s="75"/>
-      <c r="P272" s="75"/>
-      <c r="Q272" s="75"/>
-      <c r="R272" s="75"/>
-      <c r="S272" s="75"/>
-      <c r="T272" s="75"/>
-      <c r="U272" s="68"/>
+      <c r="H272" s="56"/>
+      <c r="I272" s="57"/>
+      <c r="J272" s="57"/>
+      <c r="K272" s="57"/>
+      <c r="L272" s="57"/>
+      <c r="M272" s="57"/>
+      <c r="N272" s="57"/>
+      <c r="O272" s="57"/>
+      <c r="P272" s="57"/>
+      <c r="Q272" s="57"/>
+      <c r="R272" s="57"/>
+      <c r="S272" s="57"/>
+      <c r="T272" s="57"/>
+      <c r="U272" s="58"/>
     </row>
   </sheetData>
   <sheetProtection password="C644" sheet="1" formatColumns="0" autoFilter="0"/>
   <autoFilter ref="A7:U7"/>
   <mergeCells count="64">
-    <mergeCell ref="H270:U270"/>
-    <mergeCell ref="H271:U271"/>
-    <mergeCell ref="H272:U272"/>
-    <mergeCell ref="H265:U265"/>
-    <mergeCell ref="H266:U266"/>
-    <mergeCell ref="H267:U267"/>
-    <mergeCell ref="H268:U268"/>
-    <mergeCell ref="H269:U269"/>
-    <mergeCell ref="H260:U260"/>
-    <mergeCell ref="H261:U261"/>
-    <mergeCell ref="H262:U262"/>
-    <mergeCell ref="H263:U263"/>
-    <mergeCell ref="H264:U264"/>
-    <mergeCell ref="H255:U255"/>
-    <mergeCell ref="H256:U256"/>
-    <mergeCell ref="H257:U257"/>
-    <mergeCell ref="H258:U258"/>
-    <mergeCell ref="H259:U259"/>
-    <mergeCell ref="C164:I164"/>
-    <mergeCell ref="C184:I184"/>
-    <mergeCell ref="C203:I203"/>
-    <mergeCell ref="C248:I248"/>
-    <mergeCell ref="A254:U254"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C119:I119"/>
-    <mergeCell ref="C122:I122"/>
-    <mergeCell ref="C123:I123"/>
-    <mergeCell ref="C163:I163"/>
-    <mergeCell ref="C21:I21"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:R7"/>
     <mergeCell ref="A2:U2"/>
     <mergeCell ref="A3:U3"/>
     <mergeCell ref="A4:U4"/>
@@ -18174,6 +18126,54 @@
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="I5:I7"/>
     <mergeCell ref="J6:K6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C119:I119"/>
+    <mergeCell ref="C122:I122"/>
+    <mergeCell ref="C123:I123"/>
+    <mergeCell ref="C163:I163"/>
+    <mergeCell ref="C164:I164"/>
+    <mergeCell ref="C184:I184"/>
+    <mergeCell ref="C203:I203"/>
+    <mergeCell ref="C248:I248"/>
+    <mergeCell ref="A254:U254"/>
+    <mergeCell ref="H255:U255"/>
+    <mergeCell ref="H256:U256"/>
+    <mergeCell ref="H257:U257"/>
+    <mergeCell ref="H258:U258"/>
+    <mergeCell ref="H259:U259"/>
+    <mergeCell ref="H260:U260"/>
+    <mergeCell ref="H261:U261"/>
+    <mergeCell ref="H262:U262"/>
+    <mergeCell ref="H263:U263"/>
+    <mergeCell ref="H264:U264"/>
+    <mergeCell ref="H270:U270"/>
+    <mergeCell ref="H271:U271"/>
+    <mergeCell ref="H272:U272"/>
+    <mergeCell ref="H265:U265"/>
+    <mergeCell ref="H266:U266"/>
+    <mergeCell ref="H267:U267"/>
+    <mergeCell ref="H268:U268"/>
+    <mergeCell ref="H269:U269"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18265,163 +18265,163 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="55"/>
-      <c r="T2" s="55"/>
-      <c r="U2" s="55"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
+      <c r="P3" s="68"/>
+      <c r="Q3" s="68"/>
+      <c r="R3" s="68"/>
+      <c r="S3" s="68"/>
+      <c r="T3" s="68"/>
+      <c r="U3" s="68"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="57"/>
-      <c r="O4" s="57"/>
-      <c r="P4" s="57"/>
-      <c r="Q4" s="57"/>
-      <c r="R4" s="57"/>
-      <c r="S4" s="57"/>
-      <c r="T4" s="57"/>
-      <c r="U4" s="57"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="69"/>
+      <c r="Q4" s="69"/>
+      <c r="R4" s="69"/>
+      <c r="S4" s="69"/>
+      <c r="T4" s="69"/>
+      <c r="U4" s="69"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="64" t="s">
+      <c r="A5" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="64" t="s">
+      <c r="C5" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="64" t="s">
+      <c r="D5" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="64" t="s">
+      <c r="E5" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="64" t="s">
+      <c r="F5" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="64" t="s">
+      <c r="H5" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="64" t="s">
+      <c r="I5" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="58" t="s">
+      <c r="J5" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="59"/>
-      <c r="L5" s="59"/>
-      <c r="M5" s="59"/>
-      <c r="N5" s="59"/>
-      <c r="O5" s="60"/>
-      <c r="P5" s="61" t="s">
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="72"/>
+      <c r="P5" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="62"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="61" t="s">
+      <c r="Q5" s="74"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="62"/>
-      <c r="U5" s="63"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="75"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="65"/>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="67" t="s">
+      <c r="A6" s="76"/>
+      <c r="B6" s="76"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="68"/>
-      <c r="L6" s="64" t="s">
+      <c r="K6" s="58"/>
+      <c r="L6" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="67" t="s">
+      <c r="M6" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="68"/>
-      <c r="O6" s="64" t="s">
+      <c r="N6" s="58"/>
+      <c r="O6" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="67" t="s">
+      <c r="P6" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="68"/>
-      <c r="R6" s="64" t="s">
+      <c r="Q6" s="58"/>
+      <c r="R6" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="S6" s="67" t="s">
+      <c r="S6" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="68"/>
-      <c r="U6" s="64" t="s">
+      <c r="T6" s="58"/>
+      <c r="U6" s="65" t="s">
         <v>33</v>
       </c>
     </row>
@@ -18465,17 +18465,17 @@
       <c r="U7" s="66"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="69" t="s">
+      <c r="A8" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="70"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="71"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="64"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -18510,22 +18510,22 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>36</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="72" t="s">
+      <c r="C9" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="74"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="61"/>
       <c r="M9" s="6">
         <f>SUM(M10,M20)</f>
         <v>18303819.899999999</v>
@@ -18554,22 +18554,22 @@
         <v>16969334</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>39</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="72" t="s">
+      <c r="C10" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="73"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="74"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="61"/>
       <c r="M10" s="6">
         <f t="shared" ref="M10:O14" si="0">SUM(M11)</f>
         <v>126283.29</v>
@@ -18598,22 +18598,22 @@
         <v>16969572</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="72" t="s">
+      <c r="C11" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="74"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="61"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18642,22 +18642,22 @@
         <v>16969570</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>45</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="72" t="s">
+      <c r="C12" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="74"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="61"/>
       <c r="M12" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18686,22 +18686,22 @@
         <v>16969567</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>48</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="72" t="s">
+      <c r="C13" s="59" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="74"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="61"/>
       <c r="M13" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18730,22 +18730,22 @@
         <v>17858933</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>51</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="72" t="s">
+      <c r="C14" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="74"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="61"/>
       <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18774,7 +18774,7 @@
         <v>17858928</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>54</v>
       </c>
@@ -18857,7 +18857,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>63</v>
       </c>
@@ -18900,7 +18900,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>69</v>
       </c>
@@ -18943,7 +18943,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>75</v>
       </c>
@@ -18986,7 +18986,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>80</v>
       </c>
@@ -19029,22 +19029,22 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>85</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="72" t="s">
+      <c r="C20" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="74"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="61"/>
       <c r="M20" s="6">
         <f t="shared" ref="M20:O21" si="1">SUM(M21)</f>
         <v>18177536.609999999</v>
@@ -19073,22 +19073,22 @@
         <v>16969335</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>88</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="72" t="s">
+      <c r="C21" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="73"/>
-      <c r="G21" s="73"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="74"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="61"/>
       <c r="M21" s="6">
         <f t="shared" si="1"/>
         <v>18177536.609999999</v>
@@ -19117,22 +19117,22 @@
         <v>16969337</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>91</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="72" t="s">
+      <c r="C22" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="74"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="61"/>
       <c r="M22" s="6">
         <f>SUM(M23,M122,M163,M203,M248)</f>
         <v>18177536.609999999</v>
@@ -19161,22 +19161,22 @@
         <v>16969339</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>94</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="72" t="s">
+      <c r="C23" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="74"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="61"/>
       <c r="M23" s="6">
         <f>SUM(M24,M67,M76,M119)</f>
         <v>12831032.07</v>
@@ -19205,22 +19205,22 @@
         <v>16983853</v>
       </c>
     </row>
-    <row r="24" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>97</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="72" t="s">
+      <c r="C24" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="73"/>
-      <c r="H24" s="73"/>
-      <c r="I24" s="74"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="61"/>
       <c r="M24" s="6">
         <f>SUM(M25,M29,M31,M34,M36,M41,M46,M51,M57,M62)</f>
         <v>7808423.3099999996</v>
@@ -19249,7 +19249,7 @@
         <v>16983851</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" ht="93.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>100</v>
       </c>
@@ -19332,7 +19332,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>108</v>
       </c>
@@ -19375,7 +19375,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>114</v>
       </c>
@@ -19418,7 +19418,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>119</v>
       </c>
@@ -19461,7 +19461,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="29" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>124</v>
       </c>
@@ -19544,7 +19544,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>130</v>
       </c>
@@ -19587,7 +19587,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="31" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>135</v>
       </c>
@@ -19668,7 +19668,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>141</v>
       </c>
@@ -19711,7 +19711,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="33" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>146</v>
       </c>
@@ -19754,7 +19754,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>151</v>
       </c>
@@ -19835,7 +19835,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="35" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>157</v>
       </c>
@@ -19878,11 +19878,11 @@
         <v>161</v>
       </c>
     </row>
-    <row r="36" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B36" s="79" t="s">
+      <c r="B36" s="55" t="s">
         <v>163</v>
       </c>
       <c r="C36" s="52" t="s">
@@ -19959,7 +19959,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="37" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
         <v>168</v>
       </c>
@@ -20002,7 +20002,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="38" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>174</v>
       </c>
@@ -20045,7 +20045,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="39" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>179</v>
       </c>
@@ -20088,7 +20088,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="40" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
         <v>184</v>
       </c>
@@ -20131,11 +20131,11 @@
         <v>118</v>
       </c>
     </row>
-    <row r="41" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="B41" s="79" t="s">
+      <c r="B41" s="55" t="s">
         <v>188</v>
       </c>
       <c r="C41" s="52" t="s">
@@ -20212,7 +20212,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
         <v>193</v>
       </c>
@@ -20255,7 +20255,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
         <v>196</v>
       </c>
@@ -20298,7 +20298,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>199</v>
       </c>
@@ -20341,7 +20341,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="45" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
         <v>202</v>
       </c>
@@ -20384,11 +20384,11 @@
         <v>118</v>
       </c>
     </row>
-    <row r="46" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="B46" s="79" t="s">
+      <c r="B46" s="55" t="s">
         <v>206</v>
       </c>
       <c r="C46" s="52" t="s">
@@ -20465,7 +20465,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>211</v>
       </c>
@@ -20508,7 +20508,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="48" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>214</v>
       </c>
@@ -20554,7 +20554,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="49" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
         <v>217</v>
       </c>
@@ -20597,7 +20597,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="50" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>220</v>
       </c>
@@ -20640,11 +20640,11 @@
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="B51" s="79" t="s">
+      <c r="B51" s="55" t="s">
         <v>206</v>
       </c>
       <c r="C51" s="52" t="s">
@@ -20721,7 +20721,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="52" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>225</v>
       </c>
@@ -20764,7 +20764,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="53" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
         <v>230</v>
       </c>
@@ -20807,7 +20807,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>233</v>
       </c>
@@ -20850,7 +20850,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="55" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
         <v>236</v>
       </c>
@@ -20893,7 +20893,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="56" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
         <v>239</v>
       </c>
@@ -20936,11 +20936,11 @@
         <v>173</v>
       </c>
     </row>
-    <row r="57" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="B57" s="79" t="s">
+      <c r="B57" s="55" t="s">
         <v>206</v>
       </c>
       <c r="C57" s="52" t="s">
@@ -21017,7 +21017,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="58" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
         <v>244</v>
       </c>
@@ -21060,7 +21060,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="59" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
         <v>247</v>
       </c>
@@ -21103,7 +21103,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="60" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="9" t="s">
         <v>252</v>
       </c>
@@ -21146,7 +21146,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="61" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
         <v>257</v>
       </c>
@@ -21189,11 +21189,11 @@
         <v>118</v>
       </c>
     </row>
-    <row r="62" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="B62" s="79" t="s">
+      <c r="B62" s="55" t="s">
         <v>206</v>
       </c>
       <c r="C62" s="52" t="s">
@@ -21270,7 +21270,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="63" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="s">
         <v>262</v>
       </c>
@@ -21313,7 +21313,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="64" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
         <v>265</v>
       </c>
@@ -21356,7 +21356,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="s">
         <v>268</v>
       </c>
@@ -21399,7 +21399,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="66" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
         <v>271</v>
       </c>
@@ -21442,22 +21442,22 @@
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="s">
         <v>274</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="72" t="s">
+      <c r="C67" s="59" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="73"/>
-      <c r="E67" s="73"/>
-      <c r="F67" s="73"/>
-      <c r="G67" s="73"/>
-      <c r="H67" s="73"/>
-      <c r="I67" s="74"/>
+      <c r="D67" s="60"/>
+      <c r="E67" s="60"/>
+      <c r="F67" s="60"/>
+      <c r="G67" s="60"/>
+      <c r="H67" s="60"/>
+      <c r="I67" s="61"/>
       <c r="M67" s="6">
         <f>SUM(M68,M72,M74)</f>
         <v>748533.11</v>
@@ -21486,7 +21486,7 @@
         <v>16996733</v>
       </c>
     </row>
-    <row r="68" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
         <v>277</v>
       </c>
@@ -21567,7 +21567,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="69" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="s">
         <v>283</v>
       </c>
@@ -21610,7 +21610,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="70" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
         <v>288</v>
       </c>
@@ -21655,7 +21655,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="71" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
         <v>294</v>
       </c>
@@ -21698,7 +21698,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="72" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="s">
         <v>299</v>
       </c>
@@ -21781,7 +21781,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="73" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" ht="93.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="9" t="s">
         <v>305</v>
       </c>
@@ -21826,7 +21826,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="74" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="s">
         <v>312</v>
       </c>
@@ -21907,7 +21907,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="s">
         <v>318</v>
       </c>
@@ -21950,22 +21950,22 @@
         <v>322</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="s">
         <v>323</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C76" s="72" t="s">
+      <c r="C76" s="59" t="s">
         <v>325</v>
       </c>
-      <c r="D76" s="73"/>
-      <c r="E76" s="73"/>
-      <c r="F76" s="73"/>
-      <c r="G76" s="73"/>
-      <c r="H76" s="73"/>
-      <c r="I76" s="74"/>
+      <c r="D76" s="60"/>
+      <c r="E76" s="60"/>
+      <c r="F76" s="60"/>
+      <c r="G76" s="60"/>
+      <c r="H76" s="60"/>
+      <c r="I76" s="61"/>
       <c r="M76" s="6">
         <f>SUM(M77,M82,M87,M93,M96,M99,M104,M109,M114,M117)</f>
         <v>3831185.6499999994</v>
@@ -21994,7 +21994,7 @@
         <v>17000002</v>
       </c>
     </row>
-    <row r="77" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="s">
         <v>326</v>
       </c>
@@ -22075,7 +22075,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="78" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" ht="112.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="9" t="s">
         <v>332</v>
       </c>
@@ -22120,7 +22120,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="9" t="s">
         <v>338</v>
       </c>
@@ -22163,7 +22163,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="80" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="9" t="s">
         <v>343</v>
       </c>
@@ -22206,7 +22206,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="81" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="9" t="s">
         <v>348</v>
       </c>
@@ -22249,7 +22249,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="82" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="9" t="s">
         <v>353</v>
       </c>
@@ -22330,7 +22330,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="83" spans="1:35" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" ht="112.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="9" t="s">
         <v>359</v>
       </c>
@@ -22375,7 +22375,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="84" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="9" t="s">
         <v>365</v>
       </c>
@@ -22420,7 +22420,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="85" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="9" t="s">
         <v>371</v>
       </c>
@@ -22463,7 +22463,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="86" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="9" t="s">
         <v>376</v>
       </c>
@@ -22506,7 +22506,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="87" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="9" t="s">
         <v>379</v>
       </c>
@@ -22589,7 +22589,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="88" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="9" t="s">
         <v>386</v>
       </c>
@@ -22632,7 +22632,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="89" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="9" t="s">
         <v>391</v>
       </c>
@@ -22675,7 +22675,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="90" spans="1:35" ht="131.25" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" ht="131.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="9" t="s">
         <v>396</v>
       </c>
@@ -22720,7 +22720,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="91" spans="1:35" ht="131.25" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" ht="131.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="9" t="s">
         <v>402</v>
       </c>
@@ -22765,7 +22765,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="92" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="9" t="s">
         <v>407</v>
       </c>
@@ -22808,7 +22808,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="93" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="9" t="s">
         <v>412</v>
       </c>
@@ -22889,7 +22889,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="94" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="9" t="s">
         <v>418</v>
       </c>
@@ -22932,7 +22932,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="95" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="9" t="s">
         <v>423</v>
       </c>
@@ -22975,7 +22975,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="96" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="9" t="s">
         <v>428</v>
       </c>
@@ -23056,7 +23056,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="97" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="9" t="s">
         <v>430</v>
       </c>
@@ -23099,7 +23099,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="98" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="9" t="s">
         <v>435</v>
       </c>
@@ -23144,7 +23144,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="99" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="9" t="s">
         <v>441</v>
       </c>
@@ -23225,7 +23225,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="100" spans="1:35" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" ht="112.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="9" t="s">
         <v>447</v>
       </c>
@@ -23270,7 +23270,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="101" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="9" t="s">
         <v>453</v>
       </c>
@@ -23315,7 +23315,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="102" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="9" t="s">
         <v>459</v>
       </c>
@@ -23358,7 +23358,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="103" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9" t="s">
         <v>462</v>
       </c>
@@ -23401,7 +23401,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="104" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="9" t="s">
         <v>465</v>
       </c>
@@ -23482,7 +23482,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="105" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="9" t="s">
         <v>467</v>
       </c>
@@ -23525,7 +23525,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="106" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="9" t="s">
         <v>470</v>
       </c>
@@ -23568,7 +23568,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="107" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="9" t="s">
         <v>473</v>
       </c>
@@ -23611,7 +23611,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="108" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="9" t="s">
         <v>478</v>
       </c>
@@ -23656,7 +23656,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="109" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="9" t="s">
         <v>481</v>
       </c>
@@ -23737,7 +23737,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="110" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="9" t="s">
         <v>482</v>
       </c>
@@ -23782,7 +23782,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="111" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="9" t="s">
         <v>485</v>
       </c>
@@ -23825,7 +23825,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="112" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="9" t="s">
         <v>488</v>
       </c>
@@ -23868,7 +23868,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="113" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="9" t="s">
         <v>491</v>
       </c>
@@ -23911,7 +23911,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="114" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="9" t="s">
         <v>494</v>
       </c>
@@ -23992,7 +23992,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="115" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" ht="93.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="9" t="s">
         <v>500</v>
       </c>
@@ -24037,7 +24037,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="116" spans="1:35" ht="168.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:35" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="9" t="s">
         <v>506</v>
       </c>
@@ -24082,7 +24082,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="117" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="9" t="s">
         <v>512</v>
       </c>
@@ -24163,7 +24163,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="118" spans="1:35" ht="131.25" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" ht="131.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="9" t="s">
         <v>518</v>
       </c>
@@ -24208,22 +24208,22 @@
         <v>523</v>
       </c>
     </row>
-    <row r="119" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="9" t="s">
         <v>524</v>
       </c>
       <c r="B119" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C119" s="72" t="s">
+      <c r="C119" s="59" t="s">
         <v>526</v>
       </c>
-      <c r="D119" s="73"/>
-      <c r="E119" s="73"/>
-      <c r="F119" s="73"/>
-      <c r="G119" s="73"/>
-      <c r="H119" s="73"/>
-      <c r="I119" s="74"/>
+      <c r="D119" s="60"/>
+      <c r="E119" s="60"/>
+      <c r="F119" s="60"/>
+      <c r="G119" s="60"/>
+      <c r="H119" s="60"/>
+      <c r="I119" s="61"/>
       <c r="M119" s="6">
         <f>SUM(M120)</f>
         <v>442890</v>
@@ -24252,7 +24252,7 @@
         <v>16997453</v>
       </c>
     </row>
-    <row r="120" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="9" t="s">
         <v>527</v>
       </c>
@@ -24333,7 +24333,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="121" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" ht="93.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="9" t="s">
         <v>533</v>
       </c>
@@ -24378,22 +24378,22 @@
         <v>538</v>
       </c>
     </row>
-    <row r="122" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="29" t="s">
         <v>539</v>
       </c>
       <c r="B122" s="29" t="s">
         <v>540</v>
       </c>
-      <c r="C122" s="76" t="s">
+      <c r="C122" s="77" t="s">
         <v>541</v>
       </c>
-      <c r="D122" s="77"/>
-      <c r="E122" s="77"/>
-      <c r="F122" s="77"/>
-      <c r="G122" s="77"/>
-      <c r="H122" s="77"/>
-      <c r="I122" s="78"/>
+      <c r="D122" s="78"/>
+      <c r="E122" s="78"/>
+      <c r="F122" s="78"/>
+      <c r="G122" s="78"/>
+      <c r="H122" s="78"/>
+      <c r="I122" s="79"/>
       <c r="J122" s="30"/>
       <c r="M122" s="6">
         <f>SUM(M123)</f>
@@ -24423,22 +24423,22 @@
         <v>16969333</v>
       </c>
     </row>
-    <row r="123" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="29" t="s">
         <v>542</v>
       </c>
       <c r="B123" s="29" t="s">
         <v>543</v>
       </c>
-      <c r="C123" s="76" t="s">
+      <c r="C123" s="77" t="s">
         <v>544</v>
       </c>
-      <c r="D123" s="77"/>
-      <c r="E123" s="77"/>
-      <c r="F123" s="77"/>
-      <c r="G123" s="77"/>
-      <c r="H123" s="77"/>
-      <c r="I123" s="78"/>
+      <c r="D123" s="78"/>
+      <c r="E123" s="78"/>
+      <c r="F123" s="78"/>
+      <c r="G123" s="78"/>
+      <c r="H123" s="78"/>
+      <c r="I123" s="79"/>
       <c r="J123" s="30"/>
       <c r="M123" s="6">
         <f>SUM(M124,M127,M131,M136,M140,M143,M148,M153,M158)</f>
@@ -24468,7 +24468,7 @@
         <v>16969336</v>
       </c>
     </row>
-    <row r="124" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="9" t="s">
         <v>545</v>
       </c>
@@ -24547,7 +24547,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="125" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="9" t="s">
         <v>550</v>
       </c>
@@ -24590,7 +24590,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="126" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="9" t="s">
         <v>555</v>
       </c>
@@ -24633,7 +24633,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="127" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="9" t="s">
         <v>560</v>
       </c>
@@ -24712,7 +24712,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="128" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="9" t="s">
         <v>565</v>
       </c>
@@ -24757,7 +24757,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="129" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="9" t="s">
         <v>571</v>
       </c>
@@ -24800,7 +24800,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="130" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="9" t="s">
         <v>576</v>
       </c>
@@ -24843,7 +24843,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="131" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="9" t="s">
         <v>581</v>
       </c>
@@ -24924,7 +24924,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="132" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="9" t="s">
         <v>587</v>
       </c>
@@ -24967,7 +24967,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="133" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="9" t="s">
         <v>592</v>
       </c>
@@ -25012,7 +25012,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="134" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="9" t="s">
         <v>596</v>
       </c>
@@ -25057,7 +25057,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="135" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="9" t="s">
         <v>602</v>
       </c>
@@ -25100,7 +25100,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="136" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="9" t="s">
         <v>607</v>
       </c>
@@ -25181,7 +25181,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="137" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="9" t="s">
         <v>613</v>
       </c>
@@ -25224,7 +25224,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="138" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="9" t="s">
         <v>616</v>
       </c>
@@ -25267,7 +25267,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="139" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="9" t="s">
         <v>621</v>
       </c>
@@ -25310,7 +25310,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="140" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="9" t="s">
         <v>624</v>
       </c>
@@ -25391,7 +25391,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="141" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="9" t="s">
         <v>630</v>
       </c>
@@ -25434,7 +25434,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="142" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="9" t="s">
         <v>635</v>
       </c>
@@ -25477,7 +25477,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="143" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="31" t="s">
         <v>638</v>
       </c>
@@ -25560,7 +25560,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="144" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="9" t="s">
         <v>645</v>
       </c>
@@ -25605,7 +25605,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="145" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="9" t="s">
         <v>651</v>
       </c>
@@ -25650,7 +25650,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="146" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="9" t="s">
         <v>657</v>
       </c>
@@ -25693,7 +25693,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="147" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="9" t="s">
         <v>662</v>
       </c>
@@ -25736,7 +25736,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="148" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="9" t="s">
         <v>665</v>
       </c>
@@ -25819,7 +25819,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="149" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="9" t="s">
         <v>667</v>
       </c>
@@ -25862,7 +25862,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="150" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="9" t="s">
         <v>670</v>
       </c>
@@ -25905,7 +25905,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="151" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="9" t="s">
         <v>673</v>
       </c>
@@ -25950,7 +25950,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="152" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="9" t="s">
         <v>676</v>
       </c>
@@ -25998,7 +25998,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="153" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="9" t="s">
         <v>679</v>
       </c>
@@ -26081,7 +26081,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="154" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="9" t="s">
         <v>681</v>
       </c>
@@ -26129,7 +26129,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="155" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="9" t="s">
         <v>684</v>
       </c>
@@ -26174,7 +26174,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="156" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="9" t="s">
         <v>687</v>
       </c>
@@ -26217,7 +26217,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="157" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="9" t="s">
         <v>690</v>
       </c>
@@ -26260,7 +26260,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="158" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="35" t="s">
         <v>693</v>
       </c>
@@ -26343,7 +26343,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="159" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="9" t="s">
         <v>695</v>
       </c>
@@ -26386,7 +26386,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="160" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="9" t="s">
         <v>698</v>
       </c>
@@ -26429,7 +26429,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="161" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="9" t="s">
         <v>701</v>
       </c>
@@ -26474,7 +26474,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="162" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="9" t="s">
         <v>704</v>
       </c>
@@ -26529,15 +26529,15 @@
       <c r="B163" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C163" s="72" t="s">
+      <c r="C163" s="59" t="s">
         <v>710</v>
       </c>
-      <c r="D163" s="73"/>
-      <c r="E163" s="73"/>
-      <c r="F163" s="73"/>
-      <c r="G163" s="73"/>
-      <c r="H163" s="73"/>
-      <c r="I163" s="74"/>
+      <c r="D163" s="60"/>
+      <c r="E163" s="60"/>
+      <c r="F163" s="60"/>
+      <c r="G163" s="60"/>
+      <c r="H163" s="60"/>
+      <c r="I163" s="61"/>
       <c r="M163" s="6">
         <f>SUM(M164,M184)</f>
         <v>611422.71999999997</v>
@@ -26566,22 +26566,22 @@
         <v>17024105</v>
       </c>
     </row>
-    <row r="164" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="9" t="s">
         <v>711</v>
       </c>
       <c r="B164" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="C164" s="72" t="s">
+      <c r="C164" s="59" t="s">
         <v>713</v>
       </c>
-      <c r="D164" s="73"/>
-      <c r="E164" s="73"/>
-      <c r="F164" s="73"/>
-      <c r="G164" s="73"/>
-      <c r="H164" s="73"/>
-      <c r="I164" s="74"/>
+      <c r="D164" s="60"/>
+      <c r="E164" s="60"/>
+      <c r="F164" s="60"/>
+      <c r="G164" s="60"/>
+      <c r="H164" s="60"/>
+      <c r="I164" s="61"/>
       <c r="M164" s="6">
         <f>SUM(M165,M171,M174,M178,M182)</f>
         <v>415021.23999999993</v>
@@ -26610,7 +26610,7 @@
         <v>17035965</v>
       </c>
     </row>
-    <row r="165" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="9" t="s">
         <v>714</v>
       </c>
@@ -26691,7 +26691,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="166" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="9" t="s">
         <v>720</v>
       </c>
@@ -26736,7 +26736,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="167" spans="1:35" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:35" ht="98.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="9" t="s">
         <v>724</v>
       </c>
@@ -26781,7 +26781,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="168" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="9" t="s">
         <v>730</v>
       </c>
@@ -26824,7 +26824,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="169" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="9" t="s">
         <v>735</v>
       </c>
@@ -26867,7 +26867,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="170" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="9" t="s">
         <v>740</v>
       </c>
@@ -26910,7 +26910,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="171" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="9" t="s">
         <v>743</v>
       </c>
@@ -26991,7 +26991,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="172" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="9" t="s">
         <v>749</v>
       </c>
@@ -27034,7 +27034,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="173" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="9" t="s">
         <v>752</v>
       </c>
@@ -27077,7 +27077,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="174" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="9" t="s">
         <v>755</v>
       </c>
@@ -27158,7 +27158,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="175" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="9" t="s">
         <v>759</v>
       </c>
@@ -27201,7 +27201,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="176" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="9" t="s">
         <v>762</v>
       </c>
@@ -27244,7 +27244,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="177" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="9" t="s">
         <v>765</v>
       </c>
@@ -27287,7 +27287,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="178" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="9" t="s">
         <v>768</v>
       </c>
@@ -27368,7 +27368,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="179" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="9" t="s">
         <v>770</v>
       </c>
@@ -27411,7 +27411,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="180" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="9" t="s">
         <v>773</v>
       </c>
@@ -27454,7 +27454,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="181" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
         <v>776</v>
       </c>
@@ -27497,7 +27497,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="182" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="9" t="s">
         <v>779</v>
       </c>
@@ -27578,7 +27578,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="183" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="9" t="s">
         <v>785</v>
       </c>
@@ -27628,15 +27628,15 @@
       <c r="B184" s="9" t="s">
         <v>789</v>
       </c>
-      <c r="C184" s="72" t="s">
+      <c r="C184" s="59" t="s">
         <v>790</v>
       </c>
-      <c r="D184" s="73"/>
-      <c r="E184" s="73"/>
-      <c r="F184" s="73"/>
-      <c r="G184" s="73"/>
-      <c r="H184" s="73"/>
-      <c r="I184" s="74"/>
+      <c r="D184" s="60"/>
+      <c r="E184" s="60"/>
+      <c r="F184" s="60"/>
+      <c r="G184" s="60"/>
+      <c r="H184" s="60"/>
+      <c r="I184" s="61"/>
       <c r="M184" s="6">
         <f>SUM(M185,M188,M191,M194,M197,M200)</f>
         <v>196401.48</v>
@@ -27958,7 +27958,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="190" spans="1:35" ht="150" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:35" ht="168.75" x14ac:dyDescent="0.25">
       <c r="A190" s="9" t="s">
         <v>811</v>
       </c>
@@ -28084,7 +28084,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="192" spans="1:35" ht="187.5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:35" ht="225" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
         <v>819</v>
       </c>
@@ -28296,7 +28296,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="196" spans="1:35" ht="206.25" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:35" ht="281.25" x14ac:dyDescent="0.25">
       <c r="A196" s="9" t="s">
         <v>833</v>
       </c>
@@ -28422,7 +28422,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="198" spans="1:35" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:35" ht="131.25" x14ac:dyDescent="0.25">
       <c r="A198" s="9" t="s">
         <v>839</v>
       </c>
@@ -28686,15 +28686,15 @@
       <c r="B203" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="C203" s="72" t="s">
+      <c r="C203" s="59" t="s">
         <v>856</v>
       </c>
-      <c r="D203" s="73"/>
-      <c r="E203" s="73"/>
-      <c r="F203" s="73"/>
-      <c r="G203" s="73"/>
-      <c r="H203" s="73"/>
-      <c r="I203" s="74"/>
+      <c r="D203" s="60"/>
+      <c r="E203" s="60"/>
+      <c r="F203" s="60"/>
+      <c r="G203" s="60"/>
+      <c r="H203" s="60"/>
+      <c r="I203" s="61"/>
       <c r="M203" s="6">
         <f>SUM(M204,M206,M221,M236,M238,M240,M242,M243,M244,M245,M246,M247)</f>
         <v>719044.50999999989</v>
@@ -30424,7 +30424,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="239" spans="1:35" ht="375" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A239" s="9" t="s">
         <v>1004</v>
       </c>
@@ -30550,7 +30550,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="241" spans="1:35" ht="262.5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:35" ht="300" x14ac:dyDescent="0.25">
       <c r="A241" s="9" t="s">
         <v>1014</v>
       </c>
@@ -31076,15 +31076,15 @@
       <c r="B248" s="9" t="s">
         <v>1031</v>
       </c>
-      <c r="C248" s="72" t="s">
+      <c r="C248" s="59" t="s">
         <v>1032</v>
       </c>
-      <c r="D248" s="73"/>
-      <c r="E248" s="73"/>
-      <c r="F248" s="73"/>
-      <c r="G248" s="73"/>
-      <c r="H248" s="73"/>
-      <c r="I248" s="74"/>
+      <c r="D248" s="60"/>
+      <c r="E248" s="60"/>
+      <c r="F248" s="60"/>
+      <c r="G248" s="60"/>
+      <c r="H248" s="60"/>
+      <c r="I248" s="61"/>
       <c r="M248" s="6">
         <f>SUM(M249,M250,M251,M252)</f>
         <v>0</v>
@@ -31346,7 +31346,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="252" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A252" s="9" t="s">
         <v>1041</v>
       </c>
@@ -31471,29 +31471,29 @@
       </c>
     </row>
     <row r="254" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="69" t="s">
+      <c r="A254" s="62" t="s">
         <v>1050</v>
       </c>
-      <c r="B254" s="70"/>
-      <c r="C254" s="70"/>
-      <c r="D254" s="70"/>
-      <c r="E254" s="70"/>
-      <c r="F254" s="70"/>
-      <c r="G254" s="70"/>
-      <c r="H254" s="70"/>
-      <c r="I254" s="70"/>
-      <c r="J254" s="70"/>
-      <c r="K254" s="70"/>
-      <c r="L254" s="70"/>
-      <c r="M254" s="70"/>
-      <c r="N254" s="70"/>
-      <c r="O254" s="70"/>
-      <c r="P254" s="70"/>
-      <c r="Q254" s="70"/>
-      <c r="R254" s="70"/>
-      <c r="S254" s="70"/>
-      <c r="T254" s="70"/>
-      <c r="U254" s="71"/>
+      <c r="B254" s="63"/>
+      <c r="C254" s="63"/>
+      <c r="D254" s="63"/>
+      <c r="E254" s="63"/>
+      <c r="F254" s="63"/>
+      <c r="G254" s="63"/>
+      <c r="H254" s="63"/>
+      <c r="I254" s="63"/>
+      <c r="J254" s="63"/>
+      <c r="K254" s="63"/>
+      <c r="L254" s="63"/>
+      <c r="M254" s="63"/>
+      <c r="N254" s="63"/>
+      <c r="O254" s="63"/>
+      <c r="P254" s="63"/>
+      <c r="Q254" s="63"/>
+      <c r="R254" s="63"/>
+      <c r="S254" s="63"/>
+      <c r="T254" s="63"/>
+      <c r="U254" s="64"/>
     </row>
     <row r="255" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="27"/>
@@ -31509,20 +31509,20 @@
       <c r="E255" s="28"/>
       <c r="F255" s="28"/>
       <c r="G255" s="28"/>
-      <c r="H255" s="67"/>
-      <c r="I255" s="75"/>
-      <c r="J255" s="75"/>
-      <c r="K255" s="75"/>
-      <c r="L255" s="75"/>
-      <c r="M255" s="75"/>
-      <c r="N255" s="75"/>
-      <c r="O255" s="75"/>
-      <c r="P255" s="75"/>
-      <c r="Q255" s="75"/>
-      <c r="R255" s="75"/>
-      <c r="S255" s="75"/>
-      <c r="T255" s="75"/>
-      <c r="U255" s="68"/>
+      <c r="H255" s="56"/>
+      <c r="I255" s="57"/>
+      <c r="J255" s="57"/>
+      <c r="K255" s="57"/>
+      <c r="L255" s="57"/>
+      <c r="M255" s="57"/>
+      <c r="N255" s="57"/>
+      <c r="O255" s="57"/>
+      <c r="P255" s="57"/>
+      <c r="Q255" s="57"/>
+      <c r="R255" s="57"/>
+      <c r="S255" s="57"/>
+      <c r="T255" s="57"/>
+      <c r="U255" s="58"/>
     </row>
     <row r="256" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="27"/>
@@ -31538,20 +31538,20 @@
       <c r="E256" s="28"/>
       <c r="F256" s="28"/>
       <c r="G256" s="28"/>
-      <c r="H256" s="67"/>
-      <c r="I256" s="75"/>
-      <c r="J256" s="75"/>
-      <c r="K256" s="75"/>
-      <c r="L256" s="75"/>
-      <c r="M256" s="75"/>
-      <c r="N256" s="75"/>
-      <c r="O256" s="75"/>
-      <c r="P256" s="75"/>
-      <c r="Q256" s="75"/>
-      <c r="R256" s="75"/>
-      <c r="S256" s="75"/>
-      <c r="T256" s="75"/>
-      <c r="U256" s="68"/>
+      <c r="H256" s="56"/>
+      <c r="I256" s="57"/>
+      <c r="J256" s="57"/>
+      <c r="K256" s="57"/>
+      <c r="L256" s="57"/>
+      <c r="M256" s="57"/>
+      <c r="N256" s="57"/>
+      <c r="O256" s="57"/>
+      <c r="P256" s="57"/>
+      <c r="Q256" s="57"/>
+      <c r="R256" s="57"/>
+      <c r="S256" s="57"/>
+      <c r="T256" s="57"/>
+      <c r="U256" s="58"/>
     </row>
     <row r="257" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A257" s="27"/>
@@ -31567,20 +31567,20 @@
       <c r="E257" s="28"/>
       <c r="F257" s="28"/>
       <c r="G257" s="28"/>
-      <c r="H257" s="67"/>
-      <c r="I257" s="75"/>
-      <c r="J257" s="75"/>
-      <c r="K257" s="75"/>
-      <c r="L257" s="75"/>
-      <c r="M257" s="75"/>
-      <c r="N257" s="75"/>
-      <c r="O257" s="75"/>
-      <c r="P257" s="75"/>
-      <c r="Q257" s="75"/>
-      <c r="R257" s="75"/>
-      <c r="S257" s="75"/>
-      <c r="T257" s="75"/>
-      <c r="U257" s="68"/>
+      <c r="H257" s="56"/>
+      <c r="I257" s="57"/>
+      <c r="J257" s="57"/>
+      <c r="K257" s="57"/>
+      <c r="L257" s="57"/>
+      <c r="M257" s="57"/>
+      <c r="N257" s="57"/>
+      <c r="O257" s="57"/>
+      <c r="P257" s="57"/>
+      <c r="Q257" s="57"/>
+      <c r="R257" s="57"/>
+      <c r="S257" s="57"/>
+      <c r="T257" s="57"/>
+      <c r="U257" s="58"/>
     </row>
     <row r="258" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="27"/>
@@ -31596,20 +31596,20 @@
       <c r="E258" s="28"/>
       <c r="F258" s="28"/>
       <c r="G258" s="28"/>
-      <c r="H258" s="67"/>
-      <c r="I258" s="75"/>
-      <c r="J258" s="75"/>
-      <c r="K258" s="75"/>
-      <c r="L258" s="75"/>
-      <c r="M258" s="75"/>
-      <c r="N258" s="75"/>
-      <c r="O258" s="75"/>
-      <c r="P258" s="75"/>
-      <c r="Q258" s="75"/>
-      <c r="R258" s="75"/>
-      <c r="S258" s="75"/>
-      <c r="T258" s="75"/>
-      <c r="U258" s="68"/>
+      <c r="H258" s="56"/>
+      <c r="I258" s="57"/>
+      <c r="J258" s="57"/>
+      <c r="K258" s="57"/>
+      <c r="L258" s="57"/>
+      <c r="M258" s="57"/>
+      <c r="N258" s="57"/>
+      <c r="O258" s="57"/>
+      <c r="P258" s="57"/>
+      <c r="Q258" s="57"/>
+      <c r="R258" s="57"/>
+      <c r="S258" s="57"/>
+      <c r="T258" s="57"/>
+      <c r="U258" s="58"/>
     </row>
     <row r="259" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="27"/>
@@ -31625,20 +31625,20 @@
       <c r="E259" s="28"/>
       <c r="F259" s="28"/>
       <c r="G259" s="28"/>
-      <c r="H259" s="67"/>
-      <c r="I259" s="75"/>
-      <c r="J259" s="75"/>
-      <c r="K259" s="75"/>
-      <c r="L259" s="75"/>
-      <c r="M259" s="75"/>
-      <c r="N259" s="75"/>
-      <c r="O259" s="75"/>
-      <c r="P259" s="75"/>
-      <c r="Q259" s="75"/>
-      <c r="R259" s="75"/>
-      <c r="S259" s="75"/>
-      <c r="T259" s="75"/>
-      <c r="U259" s="68"/>
+      <c r="H259" s="56"/>
+      <c r="I259" s="57"/>
+      <c r="J259" s="57"/>
+      <c r="K259" s="57"/>
+      <c r="L259" s="57"/>
+      <c r="M259" s="57"/>
+      <c r="N259" s="57"/>
+      <c r="O259" s="57"/>
+      <c r="P259" s="57"/>
+      <c r="Q259" s="57"/>
+      <c r="R259" s="57"/>
+      <c r="S259" s="57"/>
+      <c r="T259" s="57"/>
+      <c r="U259" s="58"/>
     </row>
     <row r="260" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A260" s="27"/>
@@ -31654,20 +31654,20 @@
       <c r="E260" s="28"/>
       <c r="F260" s="28"/>
       <c r="G260" s="28"/>
-      <c r="H260" s="67"/>
-      <c r="I260" s="75"/>
-      <c r="J260" s="75"/>
-      <c r="K260" s="75"/>
-      <c r="L260" s="75"/>
-      <c r="M260" s="75"/>
-      <c r="N260" s="75"/>
-      <c r="O260" s="75"/>
-      <c r="P260" s="75"/>
-      <c r="Q260" s="75"/>
-      <c r="R260" s="75"/>
-      <c r="S260" s="75"/>
-      <c r="T260" s="75"/>
-      <c r="U260" s="68"/>
+      <c r="H260" s="56"/>
+      <c r="I260" s="57"/>
+      <c r="J260" s="57"/>
+      <c r="K260" s="57"/>
+      <c r="L260" s="57"/>
+      <c r="M260" s="57"/>
+      <c r="N260" s="57"/>
+      <c r="O260" s="57"/>
+      <c r="P260" s="57"/>
+      <c r="Q260" s="57"/>
+      <c r="R260" s="57"/>
+      <c r="S260" s="57"/>
+      <c r="T260" s="57"/>
+      <c r="U260" s="58"/>
     </row>
     <row r="261" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A261" s="27"/>
@@ -31683,20 +31683,20 @@
       <c r="E261" s="28"/>
       <c r="F261" s="28"/>
       <c r="G261" s="28"/>
-      <c r="H261" s="67"/>
-      <c r="I261" s="75"/>
-      <c r="J261" s="75"/>
-      <c r="K261" s="75"/>
-      <c r="L261" s="75"/>
-      <c r="M261" s="75"/>
-      <c r="N261" s="75"/>
-      <c r="O261" s="75"/>
-      <c r="P261" s="75"/>
-      <c r="Q261" s="75"/>
-      <c r="R261" s="75"/>
-      <c r="S261" s="75"/>
-      <c r="T261" s="75"/>
-      <c r="U261" s="68"/>
+      <c r="H261" s="56"/>
+      <c r="I261" s="57"/>
+      <c r="J261" s="57"/>
+      <c r="K261" s="57"/>
+      <c r="L261" s="57"/>
+      <c r="M261" s="57"/>
+      <c r="N261" s="57"/>
+      <c r="O261" s="57"/>
+      <c r="P261" s="57"/>
+      <c r="Q261" s="57"/>
+      <c r="R261" s="57"/>
+      <c r="S261" s="57"/>
+      <c r="T261" s="57"/>
+      <c r="U261" s="58"/>
     </row>
     <row r="262" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="27"/>
@@ -31712,20 +31712,20 @@
       <c r="E262" s="28"/>
       <c r="F262" s="28"/>
       <c r="G262" s="28"/>
-      <c r="H262" s="67"/>
-      <c r="I262" s="75"/>
-      <c r="J262" s="75"/>
-      <c r="K262" s="75"/>
-      <c r="L262" s="75"/>
-      <c r="M262" s="75"/>
-      <c r="N262" s="75"/>
-      <c r="O262" s="75"/>
-      <c r="P262" s="75"/>
-      <c r="Q262" s="75"/>
-      <c r="R262" s="75"/>
-      <c r="S262" s="75"/>
-      <c r="T262" s="75"/>
-      <c r="U262" s="68"/>
+      <c r="H262" s="56"/>
+      <c r="I262" s="57"/>
+      <c r="J262" s="57"/>
+      <c r="K262" s="57"/>
+      <c r="L262" s="57"/>
+      <c r="M262" s="57"/>
+      <c r="N262" s="57"/>
+      <c r="O262" s="57"/>
+      <c r="P262" s="57"/>
+      <c r="Q262" s="57"/>
+      <c r="R262" s="57"/>
+      <c r="S262" s="57"/>
+      <c r="T262" s="57"/>
+      <c r="U262" s="58"/>
     </row>
     <row r="263" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="27"/>
@@ -31741,20 +31741,20 @@
       <c r="E263" s="28"/>
       <c r="F263" s="28"/>
       <c r="G263" s="28"/>
-      <c r="H263" s="67"/>
-      <c r="I263" s="75"/>
-      <c r="J263" s="75"/>
-      <c r="K263" s="75"/>
-      <c r="L263" s="75"/>
-      <c r="M263" s="75"/>
-      <c r="N263" s="75"/>
-      <c r="O263" s="75"/>
-      <c r="P263" s="75"/>
-      <c r="Q263" s="75"/>
-      <c r="R263" s="75"/>
-      <c r="S263" s="75"/>
-      <c r="T263" s="75"/>
-      <c r="U263" s="68"/>
+      <c r="H263" s="56"/>
+      <c r="I263" s="57"/>
+      <c r="J263" s="57"/>
+      <c r="K263" s="57"/>
+      <c r="L263" s="57"/>
+      <c r="M263" s="57"/>
+      <c r="N263" s="57"/>
+      <c r="O263" s="57"/>
+      <c r="P263" s="57"/>
+      <c r="Q263" s="57"/>
+      <c r="R263" s="57"/>
+      <c r="S263" s="57"/>
+      <c r="T263" s="57"/>
+      <c r="U263" s="58"/>
     </row>
     <row r="264" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A264" s="27"/>
@@ -31770,20 +31770,20 @@
       <c r="E264" s="28"/>
       <c r="F264" s="28"/>
       <c r="G264" s="28"/>
-      <c r="H264" s="67"/>
-      <c r="I264" s="75"/>
-      <c r="J264" s="75"/>
-      <c r="K264" s="75"/>
-      <c r="L264" s="75"/>
-      <c r="M264" s="75"/>
-      <c r="N264" s="75"/>
-      <c r="O264" s="75"/>
-      <c r="P264" s="75"/>
-      <c r="Q264" s="75"/>
-      <c r="R264" s="75"/>
-      <c r="S264" s="75"/>
-      <c r="T264" s="75"/>
-      <c r="U264" s="68"/>
+      <c r="H264" s="56"/>
+      <c r="I264" s="57"/>
+      <c r="J264" s="57"/>
+      <c r="K264" s="57"/>
+      <c r="L264" s="57"/>
+      <c r="M264" s="57"/>
+      <c r="N264" s="57"/>
+      <c r="O264" s="57"/>
+      <c r="P264" s="57"/>
+      <c r="Q264" s="57"/>
+      <c r="R264" s="57"/>
+      <c r="S264" s="57"/>
+      <c r="T264" s="57"/>
+      <c r="U264" s="58"/>
     </row>
     <row r="265" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A265" s="27"/>
@@ -31799,20 +31799,20 @@
       <c r="E265" s="28"/>
       <c r="F265" s="28"/>
       <c r="G265" s="28"/>
-      <c r="H265" s="67"/>
-      <c r="I265" s="75"/>
-      <c r="J265" s="75"/>
-      <c r="K265" s="75"/>
-      <c r="L265" s="75"/>
-      <c r="M265" s="75"/>
-      <c r="N265" s="75"/>
-      <c r="O265" s="75"/>
-      <c r="P265" s="75"/>
-      <c r="Q265" s="75"/>
-      <c r="R265" s="75"/>
-      <c r="S265" s="75"/>
-      <c r="T265" s="75"/>
-      <c r="U265" s="68"/>
+      <c r="H265" s="56"/>
+      <c r="I265" s="57"/>
+      <c r="J265" s="57"/>
+      <c r="K265" s="57"/>
+      <c r="L265" s="57"/>
+      <c r="M265" s="57"/>
+      <c r="N265" s="57"/>
+      <c r="O265" s="57"/>
+      <c r="P265" s="57"/>
+      <c r="Q265" s="57"/>
+      <c r="R265" s="57"/>
+      <c r="S265" s="57"/>
+      <c r="T265" s="57"/>
+      <c r="U265" s="58"/>
     </row>
     <row r="266" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A266" s="27"/>
@@ -31828,20 +31828,20 @@
       <c r="E266" s="28"/>
       <c r="F266" s="28"/>
       <c r="G266" s="28"/>
-      <c r="H266" s="67"/>
-      <c r="I266" s="75"/>
-      <c r="J266" s="75"/>
-      <c r="K266" s="75"/>
-      <c r="L266" s="75"/>
-      <c r="M266" s="75"/>
-      <c r="N266" s="75"/>
-      <c r="O266" s="75"/>
-      <c r="P266" s="75"/>
-      <c r="Q266" s="75"/>
-      <c r="R266" s="75"/>
-      <c r="S266" s="75"/>
-      <c r="T266" s="75"/>
-      <c r="U266" s="68"/>
+      <c r="H266" s="56"/>
+      <c r="I266" s="57"/>
+      <c r="J266" s="57"/>
+      <c r="K266" s="57"/>
+      <c r="L266" s="57"/>
+      <c r="M266" s="57"/>
+      <c r="N266" s="57"/>
+      <c r="O266" s="57"/>
+      <c r="P266" s="57"/>
+      <c r="Q266" s="57"/>
+      <c r="R266" s="57"/>
+      <c r="S266" s="57"/>
+      <c r="T266" s="57"/>
+      <c r="U266" s="58"/>
     </row>
     <row r="267" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="27"/>
@@ -31857,20 +31857,20 @@
       <c r="E267" s="28"/>
       <c r="F267" s="28"/>
       <c r="G267" s="28"/>
-      <c r="H267" s="67"/>
-      <c r="I267" s="75"/>
-      <c r="J267" s="75"/>
-      <c r="K267" s="75"/>
-      <c r="L267" s="75"/>
-      <c r="M267" s="75"/>
-      <c r="N267" s="75"/>
-      <c r="O267" s="75"/>
-      <c r="P267" s="75"/>
-      <c r="Q267" s="75"/>
-      <c r="R267" s="75"/>
-      <c r="S267" s="75"/>
-      <c r="T267" s="75"/>
-      <c r="U267" s="68"/>
+      <c r="H267" s="56"/>
+      <c r="I267" s="57"/>
+      <c r="J267" s="57"/>
+      <c r="K267" s="57"/>
+      <c r="L267" s="57"/>
+      <c r="M267" s="57"/>
+      <c r="N267" s="57"/>
+      <c r="O267" s="57"/>
+      <c r="P267" s="57"/>
+      <c r="Q267" s="57"/>
+      <c r="R267" s="57"/>
+      <c r="S267" s="57"/>
+      <c r="T267" s="57"/>
+      <c r="U267" s="58"/>
     </row>
     <row r="268" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="27"/>
@@ -31886,22 +31886,22 @@
       <c r="E268" s="28"/>
       <c r="F268" s="28"/>
       <c r="G268" s="28"/>
-      <c r="H268" s="67" t="s">
+      <c r="H268" s="56" t="s">
         <v>1092</v>
       </c>
-      <c r="I268" s="75"/>
-      <c r="J268" s="75"/>
-      <c r="K268" s="75"/>
-      <c r="L268" s="75"/>
-      <c r="M268" s="75"/>
-      <c r="N268" s="75"/>
-      <c r="O268" s="75"/>
-      <c r="P268" s="75"/>
-      <c r="Q268" s="75"/>
-      <c r="R268" s="75"/>
-      <c r="S268" s="75"/>
-      <c r="T268" s="75"/>
-      <c r="U268" s="68"/>
+      <c r="I268" s="57"/>
+      <c r="J268" s="57"/>
+      <c r="K268" s="57"/>
+      <c r="L268" s="57"/>
+      <c r="M268" s="57"/>
+      <c r="N268" s="57"/>
+      <c r="O268" s="57"/>
+      <c r="P268" s="57"/>
+      <c r="Q268" s="57"/>
+      <c r="R268" s="57"/>
+      <c r="S268" s="57"/>
+      <c r="T268" s="57"/>
+      <c r="U268" s="58"/>
     </row>
     <row r="269" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="27"/>
@@ -31917,20 +31917,20 @@
       <c r="E269" s="28"/>
       <c r="F269" s="28"/>
       <c r="G269" s="28"/>
-      <c r="H269" s="67"/>
-      <c r="I269" s="75"/>
-      <c r="J269" s="75"/>
-      <c r="K269" s="75"/>
-      <c r="L269" s="75"/>
-      <c r="M269" s="75"/>
-      <c r="N269" s="75"/>
-      <c r="O269" s="75"/>
-      <c r="P269" s="75"/>
-      <c r="Q269" s="75"/>
-      <c r="R269" s="75"/>
-      <c r="S269" s="75"/>
-      <c r="T269" s="75"/>
-      <c r="U269" s="68"/>
+      <c r="H269" s="56"/>
+      <c r="I269" s="57"/>
+      <c r="J269" s="57"/>
+      <c r="K269" s="57"/>
+      <c r="L269" s="57"/>
+      <c r="M269" s="57"/>
+      <c r="N269" s="57"/>
+      <c r="O269" s="57"/>
+      <c r="P269" s="57"/>
+      <c r="Q269" s="57"/>
+      <c r="R269" s="57"/>
+      <c r="S269" s="57"/>
+      <c r="T269" s="57"/>
+      <c r="U269" s="58"/>
     </row>
     <row r="270" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A270" s="27"/>
@@ -31944,20 +31944,20 @@
       <c r="E270" s="28"/>
       <c r="F270" s="28"/>
       <c r="G270" s="28"/>
-      <c r="H270" s="67"/>
-      <c r="I270" s="75"/>
-      <c r="J270" s="75"/>
-      <c r="K270" s="75"/>
-      <c r="L270" s="75"/>
-      <c r="M270" s="75"/>
-      <c r="N270" s="75"/>
-      <c r="O270" s="75"/>
-      <c r="P270" s="75"/>
-      <c r="Q270" s="75"/>
-      <c r="R270" s="75"/>
-      <c r="S270" s="75"/>
-      <c r="T270" s="75"/>
-      <c r="U270" s="68"/>
+      <c r="H270" s="56"/>
+      <c r="I270" s="57"/>
+      <c r="J270" s="57"/>
+      <c r="K270" s="57"/>
+      <c r="L270" s="57"/>
+      <c r="M270" s="57"/>
+      <c r="N270" s="57"/>
+      <c r="O270" s="57"/>
+      <c r="P270" s="57"/>
+      <c r="Q270" s="57"/>
+      <c r="R270" s="57"/>
+      <c r="S270" s="57"/>
+      <c r="T270" s="57"/>
+      <c r="U270" s="58"/>
     </row>
     <row r="271" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="27"/>
@@ -31971,20 +31971,20 @@
       <c r="E271" s="28"/>
       <c r="F271" s="28"/>
       <c r="G271" s="28"/>
-      <c r="H271" s="67"/>
-      <c r="I271" s="75"/>
-      <c r="J271" s="75"/>
-      <c r="K271" s="75"/>
-      <c r="L271" s="75"/>
-      <c r="M271" s="75"/>
-      <c r="N271" s="75"/>
-      <c r="O271" s="75"/>
-      <c r="P271" s="75"/>
-      <c r="Q271" s="75"/>
-      <c r="R271" s="75"/>
-      <c r="S271" s="75"/>
-      <c r="T271" s="75"/>
-      <c r="U271" s="68"/>
+      <c r="H271" s="56"/>
+      <c r="I271" s="57"/>
+      <c r="J271" s="57"/>
+      <c r="K271" s="57"/>
+      <c r="L271" s="57"/>
+      <c r="M271" s="57"/>
+      <c r="N271" s="57"/>
+      <c r="O271" s="57"/>
+      <c r="P271" s="57"/>
+      <c r="Q271" s="57"/>
+      <c r="R271" s="57"/>
+      <c r="S271" s="57"/>
+      <c r="T271" s="57"/>
+      <c r="U271" s="58"/>
     </row>
     <row r="272" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="27"/>
@@ -31998,34 +31998,60 @@
       <c r="E272" s="28"/>
       <c r="F272" s="28"/>
       <c r="G272" s="28"/>
-      <c r="H272" s="67"/>
-      <c r="I272" s="75"/>
-      <c r="J272" s="75"/>
-      <c r="K272" s="75"/>
-      <c r="L272" s="75"/>
-      <c r="M272" s="75"/>
-      <c r="N272" s="75"/>
-      <c r="O272" s="75"/>
-      <c r="P272" s="75"/>
-      <c r="Q272" s="75"/>
-      <c r="R272" s="75"/>
-      <c r="S272" s="75"/>
-      <c r="T272" s="75"/>
-      <c r="U272" s="68"/>
+      <c r="H272" s="56"/>
+      <c r="I272" s="57"/>
+      <c r="J272" s="57"/>
+      <c r="K272" s="57"/>
+      <c r="L272" s="57"/>
+      <c r="M272" s="57"/>
+      <c r="N272" s="57"/>
+      <c r="O272" s="57"/>
+      <c r="P272" s="57"/>
+      <c r="Q272" s="57"/>
+      <c r="R272" s="57"/>
+      <c r="S272" s="57"/>
+      <c r="T272" s="57"/>
+      <c r="U272" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:U3"/>
-    <mergeCell ref="A4:U4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="H271:U271"/>
+    <mergeCell ref="H272:U272"/>
+    <mergeCell ref="H265:U265"/>
+    <mergeCell ref="H266:U266"/>
+    <mergeCell ref="H267:U267"/>
+    <mergeCell ref="H268:U268"/>
+    <mergeCell ref="H269:U269"/>
+    <mergeCell ref="H270:U270"/>
+    <mergeCell ref="H264:U264"/>
+    <mergeCell ref="C248:I248"/>
+    <mergeCell ref="A254:U254"/>
+    <mergeCell ref="H255:U255"/>
+    <mergeCell ref="H256:U256"/>
+    <mergeCell ref="H257:U257"/>
+    <mergeCell ref="H258:U258"/>
+    <mergeCell ref="H259:U259"/>
+    <mergeCell ref="H260:U260"/>
+    <mergeCell ref="H261:U261"/>
+    <mergeCell ref="H262:U262"/>
+    <mergeCell ref="H263:U263"/>
+    <mergeCell ref="C203:I203"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C119:I119"/>
+    <mergeCell ref="C122:I122"/>
+    <mergeCell ref="C123:I123"/>
+    <mergeCell ref="C163:I163"/>
+    <mergeCell ref="C164:I164"/>
+    <mergeCell ref="C184:I184"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C20:I20"/>
     <mergeCell ref="C21:I21"/>
     <mergeCell ref="R6:R7"/>
     <mergeCell ref="S6:T6"/>
@@ -32042,43 +32068,17 @@
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="O6:O7"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="C203:I203"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C119:I119"/>
-    <mergeCell ref="C122:I122"/>
-    <mergeCell ref="C123:I123"/>
-    <mergeCell ref="C163:I163"/>
-    <mergeCell ref="C164:I164"/>
-    <mergeCell ref="C184:I184"/>
-    <mergeCell ref="H264:U264"/>
-    <mergeCell ref="C248:I248"/>
-    <mergeCell ref="A254:U254"/>
-    <mergeCell ref="H255:U255"/>
-    <mergeCell ref="H256:U256"/>
-    <mergeCell ref="H257:U257"/>
-    <mergeCell ref="H258:U258"/>
-    <mergeCell ref="H259:U259"/>
-    <mergeCell ref="H260:U260"/>
-    <mergeCell ref="H261:U261"/>
-    <mergeCell ref="H262:U262"/>
-    <mergeCell ref="H263:U263"/>
-    <mergeCell ref="H271:U271"/>
-    <mergeCell ref="H272:U272"/>
-    <mergeCell ref="H265:U265"/>
-    <mergeCell ref="H266:U266"/>
-    <mergeCell ref="H267:U267"/>
-    <mergeCell ref="H268:U268"/>
-    <mergeCell ref="H269:U269"/>
-    <mergeCell ref="H270:U270"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A3:U3"/>
+    <mergeCell ref="A4:U4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="G5:G7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/school_lublino/lublino_KP.xlsx
+++ b/school_lublino/lublino_KP.xlsx
@@ -3913,39 +3913,6 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3976,7 +3943,40 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4376,79 +4376,79 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
-      <c r="U3" s="68"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
-      <c r="P4" s="69"/>
-      <c r="Q4" s="69"/>
-      <c r="R4" s="69"/>
-      <c r="S4" s="69"/>
-      <c r="T4" s="69"/>
-      <c r="U4" s="69"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
+      <c r="U4" s="58"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="65" t="s">
@@ -4478,115 +4478,115 @@
       <c r="I5" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="70" t="s">
+      <c r="J5" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="72"/>
-      <c r="P5" s="73" t="s">
+      <c r="K5" s="60"/>
+      <c r="L5" s="60"/>
+      <c r="M5" s="60"/>
+      <c r="N5" s="60"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="75"/>
-      <c r="S5" s="73" t="s">
+      <c r="Q5" s="63"/>
+      <c r="R5" s="64"/>
+      <c r="S5" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="74"/>
-      <c r="U5" s="75"/>
+      <c r="T5" s="63"/>
+      <c r="U5" s="64"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="76"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="56" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="58"/>
+      <c r="K6" s="69"/>
       <c r="L6" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="56" t="s">
+      <c r="M6" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="58"/>
+      <c r="N6" s="69"/>
       <c r="O6" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="56" t="s">
+      <c r="P6" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="58"/>
+      <c r="Q6" s="69"/>
       <c r="R6" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="S6" s="56" t="s">
+      <c r="S6" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="58"/>
+      <c r="T6" s="69"/>
       <c r="U6" s="65" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="66"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
+      <c r="A7" s="67"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="67"/>
       <c r="J7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="66"/>
+      <c r="L7" s="67"/>
       <c r="M7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="66"/>
+      <c r="O7" s="67"/>
       <c r="P7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="66"/>
+      <c r="R7" s="67"/>
       <c r="S7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="U7" s="66"/>
+      <c r="U7" s="67"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="64"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="72"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -4628,15 +4628,15 @@
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="61"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="74"/>
+      <c r="H9" s="74"/>
+      <c r="I9" s="75"/>
       <c r="M9" s="6">
         <f>SUM(M10,M20)</f>
         <v>18303819.899999999</v>
@@ -4672,15 +4672,15 @@
       <c r="B10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="61"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="75"/>
       <c r="M10" s="6">
         <f t="shared" ref="M10:O14" si="0">SUM(M11)</f>
         <v>126283.29</v>
@@ -4716,15 +4716,15 @@
       <c r="B11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="61"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="74"/>
+      <c r="I11" s="75"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4760,15 +4760,15 @@
       <c r="B12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="61"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="75"/>
       <c r="M12" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4804,15 +4804,15 @@
       <c r="B13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="61"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="75"/>
       <c r="M13" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4848,15 +4848,15 @@
       <c r="B14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="61"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="75"/>
       <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -5147,15 +5147,15 @@
       <c r="B20" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="59" t="s">
+      <c r="C20" s="73" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="61"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="75"/>
       <c r="M20" s="6">
         <f t="shared" ref="M20:O21" si="1">SUM(M21)</f>
         <v>18177536.609999999</v>
@@ -5191,15 +5191,15 @@
       <c r="B21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="59" t="s">
+      <c r="C21" s="73" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="61"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="75"/>
       <c r="M21" s="6">
         <f t="shared" si="1"/>
         <v>18177536.609999999</v>
@@ -5235,15 +5235,15 @@
       <c r="B22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="59" t="s">
+      <c r="C22" s="73" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="61"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="75"/>
       <c r="M22" s="6">
         <f>SUM(M23,M122,M163,M203,M248)</f>
         <v>18177536.609999999</v>
@@ -5279,15 +5279,15 @@
       <c r="B23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="73" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="61"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="74"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="74"/>
+      <c r="I23" s="75"/>
       <c r="M23" s="6">
         <f>SUM(M24,M67,M76,M119)</f>
         <v>12831032.07</v>
@@ -5323,15 +5323,15 @@
       <c r="B24" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="73" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="60"/>
-      <c r="E24" s="60"/>
-      <c r="F24" s="60"/>
-      <c r="G24" s="60"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="61"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="74"/>
+      <c r="I24" s="75"/>
       <c r="M24" s="6">
         <f>SUM(M25,M29,M31,M34,M36,M41,M46,M51,M57,M62)</f>
         <v>7808423.3099999996</v>
@@ -7555,15 +7555,15 @@
       <c r="B67" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="59" t="s">
+      <c r="C67" s="73" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="60"/>
-      <c r="E67" s="60"/>
-      <c r="F67" s="60"/>
-      <c r="G67" s="60"/>
-      <c r="H67" s="60"/>
-      <c r="I67" s="61"/>
+      <c r="D67" s="74"/>
+      <c r="E67" s="74"/>
+      <c r="F67" s="74"/>
+      <c r="G67" s="74"/>
+      <c r="H67" s="74"/>
+      <c r="I67" s="75"/>
       <c r="M67" s="6">
         <f>SUM(M68,M72,M74)</f>
         <v>748533.11</v>
@@ -8061,15 +8061,15 @@
       <c r="B76" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C76" s="59" t="s">
+      <c r="C76" s="73" t="s">
         <v>325</v>
       </c>
-      <c r="D76" s="60"/>
-      <c r="E76" s="60"/>
-      <c r="F76" s="60"/>
-      <c r="G76" s="60"/>
-      <c r="H76" s="60"/>
-      <c r="I76" s="61"/>
+      <c r="D76" s="74"/>
+      <c r="E76" s="74"/>
+      <c r="F76" s="74"/>
+      <c r="G76" s="74"/>
+      <c r="H76" s="74"/>
+      <c r="I76" s="75"/>
       <c r="M76" s="6">
         <f>SUM(M77,M82,M87,M93,M96,M99,M104,M109,M114,M117)</f>
         <v>3831185.6499999994</v>
@@ -10319,15 +10319,15 @@
       <c r="B119" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C119" s="59" t="s">
+      <c r="C119" s="73" t="s">
         <v>526</v>
       </c>
-      <c r="D119" s="60"/>
-      <c r="E119" s="60"/>
-      <c r="F119" s="60"/>
-      <c r="G119" s="60"/>
-      <c r="H119" s="60"/>
-      <c r="I119" s="61"/>
+      <c r="D119" s="74"/>
+      <c r="E119" s="74"/>
+      <c r="F119" s="74"/>
+      <c r="G119" s="74"/>
+      <c r="H119" s="74"/>
+      <c r="I119" s="75"/>
       <c r="M119" s="6">
         <f>SUM(M120)</f>
         <v>442890</v>
@@ -10489,15 +10489,15 @@
       <c r="B122" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="C122" s="59" t="s">
+      <c r="C122" s="73" t="s">
         <v>541</v>
       </c>
-      <c r="D122" s="60"/>
-      <c r="E122" s="60"/>
-      <c r="F122" s="60"/>
-      <c r="G122" s="60"/>
-      <c r="H122" s="60"/>
-      <c r="I122" s="61"/>
+      <c r="D122" s="74"/>
+      <c r="E122" s="74"/>
+      <c r="F122" s="74"/>
+      <c r="G122" s="74"/>
+      <c r="H122" s="74"/>
+      <c r="I122" s="75"/>
       <c r="M122" s="6">
         <f>SUM(M123)</f>
         <v>4016037.31</v>
@@ -10533,15 +10533,15 @@
       <c r="B123" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="C123" s="59" t="s">
+      <c r="C123" s="73" t="s">
         <v>544</v>
       </c>
-      <c r="D123" s="60"/>
-      <c r="E123" s="60"/>
-      <c r="F123" s="60"/>
-      <c r="G123" s="60"/>
-      <c r="H123" s="60"/>
-      <c r="I123" s="61"/>
+      <c r="D123" s="74"/>
+      <c r="E123" s="74"/>
+      <c r="F123" s="74"/>
+      <c r="G123" s="74"/>
+      <c r="H123" s="74"/>
+      <c r="I123" s="75"/>
       <c r="M123" s="6">
         <f>SUM(M124,M127,M131,M136,M140,M143,M148,M153,M158)</f>
         <v>4016037.31</v>
@@ -12622,15 +12622,15 @@
       <c r="B163" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C163" s="59" t="s">
+      <c r="C163" s="73" t="s">
         <v>710</v>
       </c>
-      <c r="D163" s="60"/>
-      <c r="E163" s="60"/>
-      <c r="F163" s="60"/>
-      <c r="G163" s="60"/>
-      <c r="H163" s="60"/>
-      <c r="I163" s="61"/>
+      <c r="D163" s="74"/>
+      <c r="E163" s="74"/>
+      <c r="F163" s="74"/>
+      <c r="G163" s="74"/>
+      <c r="H163" s="74"/>
+      <c r="I163" s="75"/>
       <c r="M163" s="6">
         <f>SUM(M164,M184)</f>
         <v>611422.71999999997</v>
@@ -12666,15 +12666,15 @@
       <c r="B164" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="C164" s="59" t="s">
+      <c r="C164" s="73" t="s">
         <v>713</v>
       </c>
-      <c r="D164" s="60"/>
-      <c r="E164" s="60"/>
-      <c r="F164" s="60"/>
-      <c r="G164" s="60"/>
-      <c r="H164" s="60"/>
-      <c r="I164" s="61"/>
+      <c r="D164" s="74"/>
+      <c r="E164" s="74"/>
+      <c r="F164" s="74"/>
+      <c r="G164" s="74"/>
+      <c r="H164" s="74"/>
+      <c r="I164" s="75"/>
       <c r="M164" s="6">
         <f>SUM(M165,M171,M174,M178,M182)</f>
         <v>415021.23999999993</v>
@@ -13721,15 +13721,15 @@
       <c r="B184" s="9" t="s">
         <v>789</v>
       </c>
-      <c r="C184" s="59" t="s">
+      <c r="C184" s="73" t="s">
         <v>790</v>
       </c>
-      <c r="D184" s="60"/>
-      <c r="E184" s="60"/>
-      <c r="F184" s="60"/>
-      <c r="G184" s="60"/>
-      <c r="H184" s="60"/>
-      <c r="I184" s="61"/>
+      <c r="D184" s="74"/>
+      <c r="E184" s="74"/>
+      <c r="F184" s="74"/>
+      <c r="G184" s="74"/>
+      <c r="H184" s="74"/>
+      <c r="I184" s="75"/>
       <c r="M184" s="6">
         <f>SUM(M185,M188,M191,M194,M197,M200)</f>
         <v>196401.48</v>
@@ -14177,7 +14177,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="192" spans="1:35" ht="206.25" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:35" ht="187.5" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
         <v>819</v>
       </c>
@@ -14389,7 +14389,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="196" spans="1:35" ht="225" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:35" ht="206.25" x14ac:dyDescent="0.25">
       <c r="A196" s="9" t="s">
         <v>833</v>
       </c>
@@ -14779,15 +14779,15 @@
       <c r="B203" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="C203" s="59" t="s">
+      <c r="C203" s="73" t="s">
         <v>856</v>
       </c>
-      <c r="D203" s="60"/>
-      <c r="E203" s="60"/>
-      <c r="F203" s="60"/>
-      <c r="G203" s="60"/>
-      <c r="H203" s="60"/>
-      <c r="I203" s="61"/>
+      <c r="D203" s="74"/>
+      <c r="E203" s="74"/>
+      <c r="F203" s="74"/>
+      <c r="G203" s="74"/>
+      <c r="H203" s="74"/>
+      <c r="I203" s="75"/>
       <c r="M203" s="6">
         <f>SUM(M204,M206,M221,M236,M238,M240,M242,M243,M244,M245,M246,M247)</f>
         <v>719044.50999999989</v>
@@ -15195,7 +15195,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="211" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A211" s="9" t="s">
         <v>893</v>
       </c>
@@ -16138,7 +16138,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="232" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A232" s="9" t="s">
         <v>978</v>
       </c>
@@ -16517,7 +16517,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="239" spans="1:35" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:35" ht="375" x14ac:dyDescent="0.25">
       <c r="A239" s="9" t="s">
         <v>1004</v>
       </c>
@@ -17169,15 +17169,15 @@
       <c r="B248" s="9" t="s">
         <v>1031</v>
       </c>
-      <c r="C248" s="59" t="s">
+      <c r="C248" s="73" t="s">
         <v>1032</v>
       </c>
-      <c r="D248" s="60"/>
-      <c r="E248" s="60"/>
-      <c r="F248" s="60"/>
-      <c r="G248" s="60"/>
-      <c r="H248" s="60"/>
-      <c r="I248" s="61"/>
+      <c r="D248" s="74"/>
+      <c r="E248" s="74"/>
+      <c r="F248" s="74"/>
+      <c r="G248" s="74"/>
+      <c r="H248" s="74"/>
+      <c r="I248" s="75"/>
       <c r="M248" s="6">
         <f>SUM(M249,M250,M251,M252)</f>
         <v>0</v>
@@ -17564,29 +17564,29 @@
       </c>
     </row>
     <row r="254" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="62" t="s">
+      <c r="A254" s="70" t="s">
         <v>1050</v>
       </c>
-      <c r="B254" s="63"/>
-      <c r="C254" s="63"/>
-      <c r="D254" s="63"/>
-      <c r="E254" s="63"/>
-      <c r="F254" s="63"/>
-      <c r="G254" s="63"/>
-      <c r="H254" s="63"/>
-      <c r="I254" s="63"/>
-      <c r="J254" s="63"/>
-      <c r="K254" s="63"/>
-      <c r="L254" s="63"/>
-      <c r="M254" s="63"/>
-      <c r="N254" s="63"/>
-      <c r="O254" s="63"/>
-      <c r="P254" s="63"/>
-      <c r="Q254" s="63"/>
-      <c r="R254" s="63"/>
-      <c r="S254" s="63"/>
-      <c r="T254" s="63"/>
-      <c r="U254" s="64"/>
+      <c r="B254" s="71"/>
+      <c r="C254" s="71"/>
+      <c r="D254" s="71"/>
+      <c r="E254" s="71"/>
+      <c r="F254" s="71"/>
+      <c r="G254" s="71"/>
+      <c r="H254" s="71"/>
+      <c r="I254" s="71"/>
+      <c r="J254" s="71"/>
+      <c r="K254" s="71"/>
+      <c r="L254" s="71"/>
+      <c r="M254" s="71"/>
+      <c r="N254" s="71"/>
+      <c r="O254" s="71"/>
+      <c r="P254" s="71"/>
+      <c r="Q254" s="71"/>
+      <c r="R254" s="71"/>
+      <c r="S254" s="71"/>
+      <c r="T254" s="71"/>
+      <c r="U254" s="72"/>
     </row>
     <row r="255" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="27"/>
@@ -17602,20 +17602,20 @@
       <c r="E255" s="28"/>
       <c r="F255" s="28"/>
       <c r="G255" s="28"/>
-      <c r="H255" s="56"/>
-      <c r="I255" s="57"/>
-      <c r="J255" s="57"/>
-      <c r="K255" s="57"/>
-      <c r="L255" s="57"/>
-      <c r="M255" s="57"/>
-      <c r="N255" s="57"/>
-      <c r="O255" s="57"/>
-      <c r="P255" s="57"/>
-      <c r="Q255" s="57"/>
-      <c r="R255" s="57"/>
-      <c r="S255" s="57"/>
-      <c r="T255" s="57"/>
-      <c r="U255" s="58"/>
+      <c r="H255" s="68"/>
+      <c r="I255" s="76"/>
+      <c r="J255" s="76"/>
+      <c r="K255" s="76"/>
+      <c r="L255" s="76"/>
+      <c r="M255" s="76"/>
+      <c r="N255" s="76"/>
+      <c r="O255" s="76"/>
+      <c r="P255" s="76"/>
+      <c r="Q255" s="76"/>
+      <c r="R255" s="76"/>
+      <c r="S255" s="76"/>
+      <c r="T255" s="76"/>
+      <c r="U255" s="69"/>
     </row>
     <row r="256" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="27"/>
@@ -17631,20 +17631,20 @@
       <c r="E256" s="28"/>
       <c r="F256" s="28"/>
       <c r="G256" s="28"/>
-      <c r="H256" s="56"/>
-      <c r="I256" s="57"/>
-      <c r="J256" s="57"/>
-      <c r="K256" s="57"/>
-      <c r="L256" s="57"/>
-      <c r="M256" s="57"/>
-      <c r="N256" s="57"/>
-      <c r="O256" s="57"/>
-      <c r="P256" s="57"/>
-      <c r="Q256" s="57"/>
-      <c r="R256" s="57"/>
-      <c r="S256" s="57"/>
-      <c r="T256" s="57"/>
-      <c r="U256" s="58"/>
+      <c r="H256" s="68"/>
+      <c r="I256" s="76"/>
+      <c r="J256" s="76"/>
+      <c r="K256" s="76"/>
+      <c r="L256" s="76"/>
+      <c r="M256" s="76"/>
+      <c r="N256" s="76"/>
+      <c r="O256" s="76"/>
+      <c r="P256" s="76"/>
+      <c r="Q256" s="76"/>
+      <c r="R256" s="76"/>
+      <c r="S256" s="76"/>
+      <c r="T256" s="76"/>
+      <c r="U256" s="69"/>
     </row>
     <row r="257" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A257" s="27"/>
@@ -17660,20 +17660,20 @@
       <c r="E257" s="28"/>
       <c r="F257" s="28"/>
       <c r="G257" s="28"/>
-      <c r="H257" s="56"/>
-      <c r="I257" s="57"/>
-      <c r="J257" s="57"/>
-      <c r="K257" s="57"/>
-      <c r="L257" s="57"/>
-      <c r="M257" s="57"/>
-      <c r="N257" s="57"/>
-      <c r="O257" s="57"/>
-      <c r="P257" s="57"/>
-      <c r="Q257" s="57"/>
-      <c r="R257" s="57"/>
-      <c r="S257" s="57"/>
-      <c r="T257" s="57"/>
-      <c r="U257" s="58"/>
+      <c r="H257" s="68"/>
+      <c r="I257" s="76"/>
+      <c r="J257" s="76"/>
+      <c r="K257" s="76"/>
+      <c r="L257" s="76"/>
+      <c r="M257" s="76"/>
+      <c r="N257" s="76"/>
+      <c r="O257" s="76"/>
+      <c r="P257" s="76"/>
+      <c r="Q257" s="76"/>
+      <c r="R257" s="76"/>
+      <c r="S257" s="76"/>
+      <c r="T257" s="76"/>
+      <c r="U257" s="69"/>
     </row>
     <row r="258" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="27"/>
@@ -17689,20 +17689,20 @@
       <c r="E258" s="28"/>
       <c r="F258" s="28"/>
       <c r="G258" s="28"/>
-      <c r="H258" s="56"/>
-      <c r="I258" s="57"/>
-      <c r="J258" s="57"/>
-      <c r="K258" s="57"/>
-      <c r="L258" s="57"/>
-      <c r="M258" s="57"/>
-      <c r="N258" s="57"/>
-      <c r="O258" s="57"/>
-      <c r="P258" s="57"/>
-      <c r="Q258" s="57"/>
-      <c r="R258" s="57"/>
-      <c r="S258" s="57"/>
-      <c r="T258" s="57"/>
-      <c r="U258" s="58"/>
+      <c r="H258" s="68"/>
+      <c r="I258" s="76"/>
+      <c r="J258" s="76"/>
+      <c r="K258" s="76"/>
+      <c r="L258" s="76"/>
+      <c r="M258" s="76"/>
+      <c r="N258" s="76"/>
+      <c r="O258" s="76"/>
+      <c r="P258" s="76"/>
+      <c r="Q258" s="76"/>
+      <c r="R258" s="76"/>
+      <c r="S258" s="76"/>
+      <c r="T258" s="76"/>
+      <c r="U258" s="69"/>
     </row>
     <row r="259" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="27"/>
@@ -17718,20 +17718,20 @@
       <c r="E259" s="28"/>
       <c r="F259" s="28"/>
       <c r="G259" s="28"/>
-      <c r="H259" s="56"/>
-      <c r="I259" s="57"/>
-      <c r="J259" s="57"/>
-      <c r="K259" s="57"/>
-      <c r="L259" s="57"/>
-      <c r="M259" s="57"/>
-      <c r="N259" s="57"/>
-      <c r="O259" s="57"/>
-      <c r="P259" s="57"/>
-      <c r="Q259" s="57"/>
-      <c r="R259" s="57"/>
-      <c r="S259" s="57"/>
-      <c r="T259" s="57"/>
-      <c r="U259" s="58"/>
+      <c r="H259" s="68"/>
+      <c r="I259" s="76"/>
+      <c r="J259" s="76"/>
+      <c r="K259" s="76"/>
+      <c r="L259" s="76"/>
+      <c r="M259" s="76"/>
+      <c r="N259" s="76"/>
+      <c r="O259" s="76"/>
+      <c r="P259" s="76"/>
+      <c r="Q259" s="76"/>
+      <c r="R259" s="76"/>
+      <c r="S259" s="76"/>
+      <c r="T259" s="76"/>
+      <c r="U259" s="69"/>
     </row>
     <row r="260" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A260" s="27"/>
@@ -17747,20 +17747,20 @@
       <c r="E260" s="28"/>
       <c r="F260" s="28"/>
       <c r="G260" s="28"/>
-      <c r="H260" s="56"/>
-      <c r="I260" s="57"/>
-      <c r="J260" s="57"/>
-      <c r="K260" s="57"/>
-      <c r="L260" s="57"/>
-      <c r="M260" s="57"/>
-      <c r="N260" s="57"/>
-      <c r="O260" s="57"/>
-      <c r="P260" s="57"/>
-      <c r="Q260" s="57"/>
-      <c r="R260" s="57"/>
-      <c r="S260" s="57"/>
-      <c r="T260" s="57"/>
-      <c r="U260" s="58"/>
+      <c r="H260" s="68"/>
+      <c r="I260" s="76"/>
+      <c r="J260" s="76"/>
+      <c r="K260" s="76"/>
+      <c r="L260" s="76"/>
+      <c r="M260" s="76"/>
+      <c r="N260" s="76"/>
+      <c r="O260" s="76"/>
+      <c r="P260" s="76"/>
+      <c r="Q260" s="76"/>
+      <c r="R260" s="76"/>
+      <c r="S260" s="76"/>
+      <c r="T260" s="76"/>
+      <c r="U260" s="69"/>
     </row>
     <row r="261" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A261" s="27"/>
@@ -17776,22 +17776,22 @@
       <c r="E261" s="28"/>
       <c r="F261" s="28"/>
       <c r="G261" s="28"/>
-      <c r="H261" s="56"/>
-      <c r="I261" s="57"/>
-      <c r="J261" s="57"/>
-      <c r="K261" s="57"/>
-      <c r="L261" s="57"/>
-      <c r="M261" s="57"/>
-      <c r="N261" s="57"/>
-      <c r="O261" s="57"/>
-      <c r="P261" s="57"/>
-      <c r="Q261" s="57"/>
-      <c r="R261" s="57"/>
-      <c r="S261" s="57"/>
-      <c r="T261" s="57"/>
-      <c r="U261" s="58"/>
-    </row>
-    <row r="262" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="H261" s="68"/>
+      <c r="I261" s="76"/>
+      <c r="J261" s="76"/>
+      <c r="K261" s="76"/>
+      <c r="L261" s="76"/>
+      <c r="M261" s="76"/>
+      <c r="N261" s="76"/>
+      <c r="O261" s="76"/>
+      <c r="P261" s="76"/>
+      <c r="Q261" s="76"/>
+      <c r="R261" s="76"/>
+      <c r="S261" s="76"/>
+      <c r="T261" s="76"/>
+      <c r="U261" s="69"/>
+    </row>
+    <row r="262" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="27"/>
       <c r="B262" s="5" t="s">
         <v>1071</v>
@@ -17805,20 +17805,20 @@
       <c r="E262" s="28"/>
       <c r="F262" s="28"/>
       <c r="G262" s="28"/>
-      <c r="H262" s="56"/>
-      <c r="I262" s="57"/>
-      <c r="J262" s="57"/>
-      <c r="K262" s="57"/>
-      <c r="L262" s="57"/>
-      <c r="M262" s="57"/>
-      <c r="N262" s="57"/>
-      <c r="O262" s="57"/>
-      <c r="P262" s="57"/>
-      <c r="Q262" s="57"/>
-      <c r="R262" s="57"/>
-      <c r="S262" s="57"/>
-      <c r="T262" s="57"/>
-      <c r="U262" s="58"/>
+      <c r="H262" s="68"/>
+      <c r="I262" s="76"/>
+      <c r="J262" s="76"/>
+      <c r="K262" s="76"/>
+      <c r="L262" s="76"/>
+      <c r="M262" s="76"/>
+      <c r="N262" s="76"/>
+      <c r="O262" s="76"/>
+      <c r="P262" s="76"/>
+      <c r="Q262" s="76"/>
+      <c r="R262" s="76"/>
+      <c r="S262" s="76"/>
+      <c r="T262" s="76"/>
+      <c r="U262" s="69"/>
     </row>
     <row r="263" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="27"/>
@@ -17834,20 +17834,20 @@
       <c r="E263" s="28"/>
       <c r="F263" s="28"/>
       <c r="G263" s="28"/>
-      <c r="H263" s="56"/>
-      <c r="I263" s="57"/>
-      <c r="J263" s="57"/>
-      <c r="K263" s="57"/>
-      <c r="L263" s="57"/>
-      <c r="M263" s="57"/>
-      <c r="N263" s="57"/>
-      <c r="O263" s="57"/>
-      <c r="P263" s="57"/>
-      <c r="Q263" s="57"/>
-      <c r="R263" s="57"/>
-      <c r="S263" s="57"/>
-      <c r="T263" s="57"/>
-      <c r="U263" s="58"/>
+      <c r="H263" s="68"/>
+      <c r="I263" s="76"/>
+      <c r="J263" s="76"/>
+      <c r="K263" s="76"/>
+      <c r="L263" s="76"/>
+      <c r="M263" s="76"/>
+      <c r="N263" s="76"/>
+      <c r="O263" s="76"/>
+      <c r="P263" s="76"/>
+      <c r="Q263" s="76"/>
+      <c r="R263" s="76"/>
+      <c r="S263" s="76"/>
+      <c r="T263" s="76"/>
+      <c r="U263" s="69"/>
     </row>
     <row r="264" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A264" s="27"/>
@@ -17863,20 +17863,20 @@
       <c r="E264" s="28"/>
       <c r="F264" s="28"/>
       <c r="G264" s="28"/>
-      <c r="H264" s="56"/>
-      <c r="I264" s="57"/>
-      <c r="J264" s="57"/>
-      <c r="K264" s="57"/>
-      <c r="L264" s="57"/>
-      <c r="M264" s="57"/>
-      <c r="N264" s="57"/>
-      <c r="O264" s="57"/>
-      <c r="P264" s="57"/>
-      <c r="Q264" s="57"/>
-      <c r="R264" s="57"/>
-      <c r="S264" s="57"/>
-      <c r="T264" s="57"/>
-      <c r="U264" s="58"/>
+      <c r="H264" s="68"/>
+      <c r="I264" s="76"/>
+      <c r="J264" s="76"/>
+      <c r="K264" s="76"/>
+      <c r="L264" s="76"/>
+      <c r="M264" s="76"/>
+      <c r="N264" s="76"/>
+      <c r="O264" s="76"/>
+      <c r="P264" s="76"/>
+      <c r="Q264" s="76"/>
+      <c r="R264" s="76"/>
+      <c r="S264" s="76"/>
+      <c r="T264" s="76"/>
+      <c r="U264" s="69"/>
     </row>
     <row r="265" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A265" s="27"/>
@@ -17892,20 +17892,20 @@
       <c r="E265" s="28"/>
       <c r="F265" s="28"/>
       <c r="G265" s="28"/>
-      <c r="H265" s="56"/>
-      <c r="I265" s="57"/>
-      <c r="J265" s="57"/>
-      <c r="K265" s="57"/>
-      <c r="L265" s="57"/>
-      <c r="M265" s="57"/>
-      <c r="N265" s="57"/>
-      <c r="O265" s="57"/>
-      <c r="P265" s="57"/>
-      <c r="Q265" s="57"/>
-      <c r="R265" s="57"/>
-      <c r="S265" s="57"/>
-      <c r="T265" s="57"/>
-      <c r="U265" s="58"/>
+      <c r="H265" s="68"/>
+      <c r="I265" s="76"/>
+      <c r="J265" s="76"/>
+      <c r="K265" s="76"/>
+      <c r="L265" s="76"/>
+      <c r="M265" s="76"/>
+      <c r="N265" s="76"/>
+      <c r="O265" s="76"/>
+      <c r="P265" s="76"/>
+      <c r="Q265" s="76"/>
+      <c r="R265" s="76"/>
+      <c r="S265" s="76"/>
+      <c r="T265" s="76"/>
+      <c r="U265" s="69"/>
     </row>
     <row r="266" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A266" s="27"/>
@@ -17921,20 +17921,20 @@
       <c r="E266" s="28"/>
       <c r="F266" s="28"/>
       <c r="G266" s="28"/>
-      <c r="H266" s="56"/>
-      <c r="I266" s="57"/>
-      <c r="J266" s="57"/>
-      <c r="K266" s="57"/>
-      <c r="L266" s="57"/>
-      <c r="M266" s="57"/>
-      <c r="N266" s="57"/>
-      <c r="O266" s="57"/>
-      <c r="P266" s="57"/>
-      <c r="Q266" s="57"/>
-      <c r="R266" s="57"/>
-      <c r="S266" s="57"/>
-      <c r="T266" s="57"/>
-      <c r="U266" s="58"/>
+      <c r="H266" s="68"/>
+      <c r="I266" s="76"/>
+      <c r="J266" s="76"/>
+      <c r="K266" s="76"/>
+      <c r="L266" s="76"/>
+      <c r="M266" s="76"/>
+      <c r="N266" s="76"/>
+      <c r="O266" s="76"/>
+      <c r="P266" s="76"/>
+      <c r="Q266" s="76"/>
+      <c r="R266" s="76"/>
+      <c r="S266" s="76"/>
+      <c r="T266" s="76"/>
+      <c r="U266" s="69"/>
     </row>
     <row r="267" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="27"/>
@@ -17950,20 +17950,20 @@
       <c r="E267" s="28"/>
       <c r="F267" s="28"/>
       <c r="G267" s="28"/>
-      <c r="H267" s="56"/>
-      <c r="I267" s="57"/>
-      <c r="J267" s="57"/>
-      <c r="K267" s="57"/>
-      <c r="L267" s="57"/>
-      <c r="M267" s="57"/>
-      <c r="N267" s="57"/>
-      <c r="O267" s="57"/>
-      <c r="P267" s="57"/>
-      <c r="Q267" s="57"/>
-      <c r="R267" s="57"/>
-      <c r="S267" s="57"/>
-      <c r="T267" s="57"/>
-      <c r="U267" s="58"/>
+      <c r="H267" s="68"/>
+      <c r="I267" s="76"/>
+      <c r="J267" s="76"/>
+      <c r="K267" s="76"/>
+      <c r="L267" s="76"/>
+      <c r="M267" s="76"/>
+      <c r="N267" s="76"/>
+      <c r="O267" s="76"/>
+      <c r="P267" s="76"/>
+      <c r="Q267" s="76"/>
+      <c r="R267" s="76"/>
+      <c r="S267" s="76"/>
+      <c r="T267" s="76"/>
+      <c r="U267" s="69"/>
     </row>
     <row r="268" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="27"/>
@@ -17979,22 +17979,22 @@
       <c r="E268" s="28"/>
       <c r="F268" s="28"/>
       <c r="G268" s="28"/>
-      <c r="H268" s="56" t="s">
+      <c r="H268" s="68" t="s">
         <v>1092</v>
       </c>
-      <c r="I268" s="57"/>
-      <c r="J268" s="57"/>
-      <c r="K268" s="57"/>
-      <c r="L268" s="57"/>
-      <c r="M268" s="57"/>
-      <c r="N268" s="57"/>
-      <c r="O268" s="57"/>
-      <c r="P268" s="57"/>
-      <c r="Q268" s="57"/>
-      <c r="R268" s="57"/>
-      <c r="S268" s="57"/>
-      <c r="T268" s="57"/>
-      <c r="U268" s="58"/>
+      <c r="I268" s="76"/>
+      <c r="J268" s="76"/>
+      <c r="K268" s="76"/>
+      <c r="L268" s="76"/>
+      <c r="M268" s="76"/>
+      <c r="N268" s="76"/>
+      <c r="O268" s="76"/>
+      <c r="P268" s="76"/>
+      <c r="Q268" s="76"/>
+      <c r="R268" s="76"/>
+      <c r="S268" s="76"/>
+      <c r="T268" s="76"/>
+      <c r="U268" s="69"/>
     </row>
     <row r="269" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="27"/>
@@ -18010,20 +18010,20 @@
       <c r="E269" s="28"/>
       <c r="F269" s="28"/>
       <c r="G269" s="28"/>
-      <c r="H269" s="56"/>
-      <c r="I269" s="57"/>
-      <c r="J269" s="57"/>
-      <c r="K269" s="57"/>
-      <c r="L269" s="57"/>
-      <c r="M269" s="57"/>
-      <c r="N269" s="57"/>
-      <c r="O269" s="57"/>
-      <c r="P269" s="57"/>
-      <c r="Q269" s="57"/>
-      <c r="R269" s="57"/>
-      <c r="S269" s="57"/>
-      <c r="T269" s="57"/>
-      <c r="U269" s="58"/>
+      <c r="H269" s="68"/>
+      <c r="I269" s="76"/>
+      <c r="J269" s="76"/>
+      <c r="K269" s="76"/>
+      <c r="L269" s="76"/>
+      <c r="M269" s="76"/>
+      <c r="N269" s="76"/>
+      <c r="O269" s="76"/>
+      <c r="P269" s="76"/>
+      <c r="Q269" s="76"/>
+      <c r="R269" s="76"/>
+      <c r="S269" s="76"/>
+      <c r="T269" s="76"/>
+      <c r="U269" s="69"/>
     </row>
     <row r="270" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A270" s="27"/>
@@ -18037,20 +18037,20 @@
       <c r="E270" s="28"/>
       <c r="F270" s="28"/>
       <c r="G270" s="28"/>
-      <c r="H270" s="56"/>
-      <c r="I270" s="57"/>
-      <c r="J270" s="57"/>
-      <c r="K270" s="57"/>
-      <c r="L270" s="57"/>
-      <c r="M270" s="57"/>
-      <c r="N270" s="57"/>
-      <c r="O270" s="57"/>
-      <c r="P270" s="57"/>
-      <c r="Q270" s="57"/>
-      <c r="R270" s="57"/>
-      <c r="S270" s="57"/>
-      <c r="T270" s="57"/>
-      <c r="U270" s="58"/>
+      <c r="H270" s="68"/>
+      <c r="I270" s="76"/>
+      <c r="J270" s="76"/>
+      <c r="K270" s="76"/>
+      <c r="L270" s="76"/>
+      <c r="M270" s="76"/>
+      <c r="N270" s="76"/>
+      <c r="O270" s="76"/>
+      <c r="P270" s="76"/>
+      <c r="Q270" s="76"/>
+      <c r="R270" s="76"/>
+      <c r="S270" s="76"/>
+      <c r="T270" s="76"/>
+      <c r="U270" s="69"/>
     </row>
     <row r="271" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="27"/>
@@ -18064,20 +18064,20 @@
       <c r="E271" s="28"/>
       <c r="F271" s="28"/>
       <c r="G271" s="28"/>
-      <c r="H271" s="56"/>
-      <c r="I271" s="57"/>
-      <c r="J271" s="57"/>
-      <c r="K271" s="57"/>
-      <c r="L271" s="57"/>
-      <c r="M271" s="57"/>
-      <c r="N271" s="57"/>
-      <c r="O271" s="57"/>
-      <c r="P271" s="57"/>
-      <c r="Q271" s="57"/>
-      <c r="R271" s="57"/>
-      <c r="S271" s="57"/>
-      <c r="T271" s="57"/>
-      <c r="U271" s="58"/>
+      <c r="H271" s="68"/>
+      <c r="I271" s="76"/>
+      <c r="J271" s="76"/>
+      <c r="K271" s="76"/>
+      <c r="L271" s="76"/>
+      <c r="M271" s="76"/>
+      <c r="N271" s="76"/>
+      <c r="O271" s="76"/>
+      <c r="P271" s="76"/>
+      <c r="Q271" s="76"/>
+      <c r="R271" s="76"/>
+      <c r="S271" s="76"/>
+      <c r="T271" s="76"/>
+      <c r="U271" s="69"/>
     </row>
     <row r="272" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="27"/>
@@ -18091,25 +18091,73 @@
       <c r="E272" s="28"/>
       <c r="F272" s="28"/>
       <c r="G272" s="28"/>
-      <c r="H272" s="56"/>
-      <c r="I272" s="57"/>
-      <c r="J272" s="57"/>
-      <c r="K272" s="57"/>
-      <c r="L272" s="57"/>
-      <c r="M272" s="57"/>
-      <c r="N272" s="57"/>
-      <c r="O272" s="57"/>
-      <c r="P272" s="57"/>
-      <c r="Q272" s="57"/>
-      <c r="R272" s="57"/>
-      <c r="S272" s="57"/>
-      <c r="T272" s="57"/>
-      <c r="U272" s="58"/>
+      <c r="H272" s="68"/>
+      <c r="I272" s="76"/>
+      <c r="J272" s="76"/>
+      <c r="K272" s="76"/>
+      <c r="L272" s="76"/>
+      <c r="M272" s="76"/>
+      <c r="N272" s="76"/>
+      <c r="O272" s="76"/>
+      <c r="P272" s="76"/>
+      <c r="Q272" s="76"/>
+      <c r="R272" s="76"/>
+      <c r="S272" s="76"/>
+      <c r="T272" s="76"/>
+      <c r="U272" s="69"/>
     </row>
   </sheetData>
   <sheetProtection password="C644" sheet="1" formatColumns="0" autoFilter="0"/>
   <autoFilter ref="A7:U7"/>
   <mergeCells count="64">
+    <mergeCell ref="H270:U270"/>
+    <mergeCell ref="H271:U271"/>
+    <mergeCell ref="H272:U272"/>
+    <mergeCell ref="H265:U265"/>
+    <mergeCell ref="H266:U266"/>
+    <mergeCell ref="H267:U267"/>
+    <mergeCell ref="H268:U268"/>
+    <mergeCell ref="H269:U269"/>
+    <mergeCell ref="H260:U260"/>
+    <mergeCell ref="H261:U261"/>
+    <mergeCell ref="H262:U262"/>
+    <mergeCell ref="H263:U263"/>
+    <mergeCell ref="H264:U264"/>
+    <mergeCell ref="H255:U255"/>
+    <mergeCell ref="H256:U256"/>
+    <mergeCell ref="H257:U257"/>
+    <mergeCell ref="H258:U258"/>
+    <mergeCell ref="H259:U259"/>
+    <mergeCell ref="C164:I164"/>
+    <mergeCell ref="C184:I184"/>
+    <mergeCell ref="C203:I203"/>
+    <mergeCell ref="C248:I248"/>
+    <mergeCell ref="A254:U254"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C119:I119"/>
+    <mergeCell ref="C122:I122"/>
+    <mergeCell ref="C123:I123"/>
+    <mergeCell ref="C163:I163"/>
+    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:R7"/>
     <mergeCell ref="A2:U2"/>
     <mergeCell ref="A3:U3"/>
     <mergeCell ref="A4:U4"/>
@@ -18126,54 +18174,6 @@
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="I5:I7"/>
     <mergeCell ref="J6:K6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:R7"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="C21:I21"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C119:I119"/>
-    <mergeCell ref="C122:I122"/>
-    <mergeCell ref="C123:I123"/>
-    <mergeCell ref="C163:I163"/>
-    <mergeCell ref="C164:I164"/>
-    <mergeCell ref="C184:I184"/>
-    <mergeCell ref="C203:I203"/>
-    <mergeCell ref="C248:I248"/>
-    <mergeCell ref="A254:U254"/>
-    <mergeCell ref="H255:U255"/>
-    <mergeCell ref="H256:U256"/>
-    <mergeCell ref="H257:U257"/>
-    <mergeCell ref="H258:U258"/>
-    <mergeCell ref="H259:U259"/>
-    <mergeCell ref="H260:U260"/>
-    <mergeCell ref="H261:U261"/>
-    <mergeCell ref="H262:U262"/>
-    <mergeCell ref="H263:U263"/>
-    <mergeCell ref="H264:U264"/>
-    <mergeCell ref="H270:U270"/>
-    <mergeCell ref="H271:U271"/>
-    <mergeCell ref="H272:U272"/>
-    <mergeCell ref="H265:U265"/>
-    <mergeCell ref="H266:U266"/>
-    <mergeCell ref="H267:U267"/>
-    <mergeCell ref="H268:U268"/>
-    <mergeCell ref="H269:U269"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18265,79 +18265,79 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
-      <c r="U3" s="68"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
-      <c r="P4" s="69"/>
-      <c r="Q4" s="69"/>
-      <c r="R4" s="69"/>
-      <c r="S4" s="69"/>
-      <c r="T4" s="69"/>
-      <c r="U4" s="69"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
+      <c r="U4" s="58"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="65" t="s">
@@ -18367,115 +18367,115 @@
       <c r="I5" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="70" t="s">
+      <c r="J5" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="72"/>
-      <c r="P5" s="73" t="s">
+      <c r="K5" s="60"/>
+      <c r="L5" s="60"/>
+      <c r="M5" s="60"/>
+      <c r="N5" s="60"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="75"/>
-      <c r="S5" s="73" t="s">
+      <c r="Q5" s="63"/>
+      <c r="R5" s="64"/>
+      <c r="S5" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="74"/>
-      <c r="U5" s="75"/>
+      <c r="T5" s="63"/>
+      <c r="U5" s="64"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="76"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="56" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="58"/>
+      <c r="K6" s="69"/>
       <c r="L6" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="56" t="s">
+      <c r="M6" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="58"/>
+      <c r="N6" s="69"/>
       <c r="O6" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="56" t="s">
+      <c r="P6" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="58"/>
+      <c r="Q6" s="69"/>
       <c r="R6" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="S6" s="56" t="s">
+      <c r="S6" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="58"/>
+      <c r="T6" s="69"/>
       <c r="U6" s="65" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="66"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
+      <c r="A7" s="67"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="67"/>
       <c r="J7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="66"/>
+      <c r="L7" s="67"/>
       <c r="M7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="66"/>
+      <c r="O7" s="67"/>
       <c r="P7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="66"/>
+      <c r="R7" s="67"/>
       <c r="S7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="U7" s="66"/>
+      <c r="U7" s="67"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="64"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="72"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -18510,22 +18510,22 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>36</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="61"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="74"/>
+      <c r="H9" s="74"/>
+      <c r="I9" s="75"/>
       <c r="M9" s="6">
         <f>SUM(M10,M20)</f>
         <v>18303819.899999999</v>
@@ -18554,22 +18554,22 @@
         <v>16969334</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>39</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="61"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="75"/>
       <c r="M10" s="6">
         <f t="shared" ref="M10:O14" si="0">SUM(M11)</f>
         <v>126283.29</v>
@@ -18598,22 +18598,22 @@
         <v>16969572</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="61"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="74"/>
+      <c r="I11" s="75"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18642,22 +18642,22 @@
         <v>16969570</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>45</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="61"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="75"/>
       <c r="M12" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18686,22 +18686,22 @@
         <v>16969567</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>48</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="61"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="75"/>
       <c r="M13" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18730,22 +18730,22 @@
         <v>17858933</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>51</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="61"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="75"/>
       <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18774,7 +18774,7 @@
         <v>17858928</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>54</v>
       </c>
@@ -18857,7 +18857,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>63</v>
       </c>
@@ -18900,7 +18900,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>69</v>
       </c>
@@ -18943,7 +18943,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>75</v>
       </c>
@@ -18986,7 +18986,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>80</v>
       </c>
@@ -19029,22 +19029,22 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>85</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="59" t="s">
+      <c r="C20" s="73" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="61"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="75"/>
       <c r="M20" s="6">
         <f t="shared" ref="M20:O21" si="1">SUM(M21)</f>
         <v>18177536.609999999</v>
@@ -19073,22 +19073,22 @@
         <v>16969335</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>88</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="59" t="s">
+      <c r="C21" s="73" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="61"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="75"/>
       <c r="M21" s="6">
         <f t="shared" si="1"/>
         <v>18177536.609999999</v>
@@ -19117,22 +19117,22 @@
         <v>16969337</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>91</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="59" t="s">
+      <c r="C22" s="73" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="61"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="75"/>
       <c r="M22" s="6">
         <f>SUM(M23,M122,M163,M203,M248)</f>
         <v>18177536.609999999</v>
@@ -19161,22 +19161,22 @@
         <v>16969339</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>94</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="73" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="61"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="74"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="74"/>
+      <c r="I23" s="75"/>
       <c r="M23" s="6">
         <f>SUM(M24,M67,M76,M119)</f>
         <v>12831032.07</v>
@@ -19205,22 +19205,22 @@
         <v>16983853</v>
       </c>
     </row>
-    <row r="24" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>97</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="73" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="60"/>
-      <c r="E24" s="60"/>
-      <c r="F24" s="60"/>
-      <c r="G24" s="60"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="61"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="74"/>
+      <c r="I24" s="75"/>
       <c r="M24" s="6">
         <f>SUM(M25,M29,M31,M34,M36,M41,M46,M51,M57,M62)</f>
         <v>7808423.3099999996</v>
@@ -19249,7 +19249,7 @@
         <v>16983851</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="93.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>100</v>
       </c>
@@ -19332,7 +19332,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>108</v>
       </c>
@@ -19375,7 +19375,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>114</v>
       </c>
@@ -19418,7 +19418,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>119</v>
       </c>
@@ -19461,7 +19461,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="29" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>124</v>
       </c>
@@ -19544,7 +19544,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>130</v>
       </c>
@@ -19587,7 +19587,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="31" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>135</v>
       </c>
@@ -19668,7 +19668,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>141</v>
       </c>
@@ -19711,7 +19711,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="33" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>146</v>
       </c>
@@ -19754,7 +19754,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>151</v>
       </c>
@@ -19835,7 +19835,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="35" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>157</v>
       </c>
@@ -19878,7 +19878,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="36" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>162</v>
       </c>
@@ -19959,7 +19959,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="37" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
         <v>168</v>
       </c>
@@ -20002,7 +20002,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="38" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>174</v>
       </c>
@@ -20045,7 +20045,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="39" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>179</v>
       </c>
@@ -20088,7 +20088,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="40" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
         <v>184</v>
       </c>
@@ -20131,7 +20131,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="41" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
         <v>187</v>
       </c>
@@ -20212,7 +20212,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
         <v>193</v>
       </c>
@@ -20255,7 +20255,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
         <v>196</v>
       </c>
@@ -20298,7 +20298,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>199</v>
       </c>
@@ -20341,7 +20341,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="45" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
         <v>202</v>
       </c>
@@ -20384,7 +20384,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="46" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>205</v>
       </c>
@@ -20465,7 +20465,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>211</v>
       </c>
@@ -20508,7 +20508,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="48" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>214</v>
       </c>
@@ -20554,7 +20554,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="49" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
         <v>217</v>
       </c>
@@ -20597,7 +20597,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="50" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>220</v>
       </c>
@@ -20640,7 +20640,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
         <v>223</v>
       </c>
@@ -20721,7 +20721,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="52" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>225</v>
       </c>
@@ -20764,7 +20764,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="53" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
         <v>230</v>
       </c>
@@ -20807,7 +20807,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>233</v>
       </c>
@@ -20850,7 +20850,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="55" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
         <v>236</v>
       </c>
@@ -20893,7 +20893,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="56" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
         <v>239</v>
       </c>
@@ -20936,7 +20936,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="57" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
         <v>242</v>
       </c>
@@ -21017,7 +21017,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="58" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
         <v>244</v>
       </c>
@@ -21060,7 +21060,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="59" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
         <v>247</v>
       </c>
@@ -21103,7 +21103,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="60" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A60" s="9" t="s">
         <v>252</v>
       </c>
@@ -21146,7 +21146,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="61" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
         <v>257</v>
       </c>
@@ -21189,7 +21189,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="62" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
         <v>260</v>
       </c>
@@ -21270,7 +21270,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="63" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="s">
         <v>262</v>
       </c>
@@ -21313,7 +21313,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="64" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
         <v>265</v>
       </c>
@@ -21356,7 +21356,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="s">
         <v>268</v>
       </c>
@@ -21399,7 +21399,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="66" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
         <v>271</v>
       </c>
@@ -21442,22 +21442,22 @@
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="s">
         <v>274</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="59" t="s">
+      <c r="C67" s="73" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="60"/>
-      <c r="E67" s="60"/>
-      <c r="F67" s="60"/>
-      <c r="G67" s="60"/>
-      <c r="H67" s="60"/>
-      <c r="I67" s="61"/>
+      <c r="D67" s="74"/>
+      <c r="E67" s="74"/>
+      <c r="F67" s="74"/>
+      <c r="G67" s="74"/>
+      <c r="H67" s="74"/>
+      <c r="I67" s="75"/>
       <c r="M67" s="6">
         <f>SUM(M68,M72,M74)</f>
         <v>748533.11</v>
@@ -21486,7 +21486,7 @@
         <v>16996733</v>
       </c>
     </row>
-    <row r="68" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
         <v>277</v>
       </c>
@@ -21567,7 +21567,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="69" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="s">
         <v>283</v>
       </c>
@@ -21610,7 +21610,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="70" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
         <v>288</v>
       </c>
@@ -21655,7 +21655,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="71" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
         <v>294</v>
       </c>
@@ -21698,7 +21698,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="72" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="s">
         <v>299</v>
       </c>
@@ -21781,7 +21781,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="73" spans="1:35" ht="93.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A73" s="9" t="s">
         <v>305</v>
       </c>
@@ -21826,7 +21826,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="74" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="s">
         <v>312</v>
       </c>
@@ -21907,7 +21907,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="s">
         <v>318</v>
       </c>
@@ -21950,22 +21950,22 @@
         <v>322</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="s">
         <v>323</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C76" s="59" t="s">
+      <c r="C76" s="73" t="s">
         <v>325</v>
       </c>
-      <c r="D76" s="60"/>
-      <c r="E76" s="60"/>
-      <c r="F76" s="60"/>
-      <c r="G76" s="60"/>
-      <c r="H76" s="60"/>
-      <c r="I76" s="61"/>
+      <c r="D76" s="74"/>
+      <c r="E76" s="74"/>
+      <c r="F76" s="74"/>
+      <c r="G76" s="74"/>
+      <c r="H76" s="74"/>
+      <c r="I76" s="75"/>
       <c r="M76" s="6">
         <f>SUM(M77,M82,M87,M93,M96,M99,M104,M109,M114,M117)</f>
         <v>3831185.6499999994</v>
@@ -21994,7 +21994,7 @@
         <v>17000002</v>
       </c>
     </row>
-    <row r="77" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="s">
         <v>326</v>
       </c>
@@ -22075,7 +22075,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="78" spans="1:35" ht="112.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A78" s="9" t="s">
         <v>332</v>
       </c>
@@ -22120,7 +22120,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A79" s="9" t="s">
         <v>338</v>
       </c>
@@ -22163,7 +22163,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="80" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A80" s="9" t="s">
         <v>343</v>
       </c>
@@ -22206,7 +22206,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="81" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A81" s="9" t="s">
         <v>348</v>
       </c>
@@ -22249,7 +22249,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="82" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A82" s="9" t="s">
         <v>353</v>
       </c>
@@ -22330,7 +22330,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="83" spans="1:35" ht="112.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A83" s="9" t="s">
         <v>359</v>
       </c>
@@ -22375,7 +22375,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="84" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A84" s="9" t="s">
         <v>365</v>
       </c>
@@ -22420,7 +22420,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="85" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A85" s="9" t="s">
         <v>371</v>
       </c>
@@ -22463,7 +22463,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="86" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A86" s="9" t="s">
         <v>376</v>
       </c>
@@ -22506,7 +22506,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="87" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A87" s="9" t="s">
         <v>379</v>
       </c>
@@ -22589,7 +22589,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="88" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A88" s="9" t="s">
         <v>386</v>
       </c>
@@ -22632,7 +22632,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="89" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A89" s="9" t="s">
         <v>391</v>
       </c>
@@ -22675,7 +22675,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="90" spans="1:35" ht="131.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" ht="150" x14ac:dyDescent="0.25">
       <c r="A90" s="9" t="s">
         <v>396</v>
       </c>
@@ -22720,7 +22720,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="91" spans="1:35" ht="131.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" ht="150" x14ac:dyDescent="0.25">
       <c r="A91" s="9" t="s">
         <v>402</v>
       </c>
@@ -22765,7 +22765,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="92" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A92" s="9" t="s">
         <v>407</v>
       </c>
@@ -22808,7 +22808,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="93" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A93" s="9" t="s">
         <v>412</v>
       </c>
@@ -22889,7 +22889,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="94" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A94" s="9" t="s">
         <v>418</v>
       </c>
@@ -22932,7 +22932,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="95" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A95" s="9" t="s">
         <v>423</v>
       </c>
@@ -22975,7 +22975,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="96" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A96" s="9" t="s">
         <v>428</v>
       </c>
@@ -23056,7 +23056,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="97" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A97" s="9" t="s">
         <v>430</v>
       </c>
@@ -23099,7 +23099,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="98" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A98" s="9" t="s">
         <v>435</v>
       </c>
@@ -23144,7 +23144,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="99" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A99" s="9" t="s">
         <v>441</v>
       </c>
@@ -23225,7 +23225,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="100" spans="1:35" ht="112.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" ht="131.25" x14ac:dyDescent="0.25">
       <c r="A100" s="9" t="s">
         <v>447</v>
       </c>
@@ -23270,7 +23270,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="101" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A101" s="9" t="s">
         <v>453</v>
       </c>
@@ -23315,7 +23315,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="102" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A102" s="9" t="s">
         <v>459</v>
       </c>
@@ -23358,7 +23358,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="103" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A103" s="9" t="s">
         <v>462</v>
       </c>
@@ -23401,7 +23401,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="104" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A104" s="9" t="s">
         <v>465</v>
       </c>
@@ -23482,7 +23482,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="105" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A105" s="9" t="s">
         <v>467</v>
       </c>
@@ -23525,7 +23525,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="106" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A106" s="9" t="s">
         <v>470</v>
       </c>
@@ -23568,7 +23568,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="107" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A107" s="9" t="s">
         <v>473</v>
       </c>
@@ -23611,7 +23611,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="108" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A108" s="9" t="s">
         <v>478</v>
       </c>
@@ -23656,7 +23656,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="109" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A109" s="9" t="s">
         <v>481</v>
       </c>
@@ -23737,7 +23737,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="110" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A110" s="9" t="s">
         <v>482</v>
       </c>
@@ -23782,7 +23782,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="111" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A111" s="9" t="s">
         <v>485</v>
       </c>
@@ -23825,7 +23825,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="112" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A112" s="9" t="s">
         <v>488</v>
       </c>
@@ -23868,7 +23868,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="113" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A113" s="9" t="s">
         <v>491</v>
       </c>
@@ -23911,7 +23911,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="114" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A114" s="9" t="s">
         <v>494</v>
       </c>
@@ -23992,7 +23992,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="115" spans="1:35" ht="93.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A115" s="9" t="s">
         <v>500</v>
       </c>
@@ -24037,7 +24037,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="116" spans="1:35" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:35" ht="225" x14ac:dyDescent="0.25">
       <c r="A116" s="9" t="s">
         <v>506</v>
       </c>
@@ -24082,7 +24082,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="117" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A117" s="9" t="s">
         <v>512</v>
       </c>
@@ -24163,7 +24163,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="118" spans="1:35" ht="131.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" ht="150" x14ac:dyDescent="0.25">
       <c r="A118" s="9" t="s">
         <v>518</v>
       </c>
@@ -24208,22 +24208,22 @@
         <v>523</v>
       </c>
     </row>
-    <row r="119" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="9" t="s">
         <v>524</v>
       </c>
       <c r="B119" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C119" s="59" t="s">
+      <c r="C119" s="73" t="s">
         <v>526</v>
       </c>
-      <c r="D119" s="60"/>
-      <c r="E119" s="60"/>
-      <c r="F119" s="60"/>
-      <c r="G119" s="60"/>
-      <c r="H119" s="60"/>
-      <c r="I119" s="61"/>
+      <c r="D119" s="74"/>
+      <c r="E119" s="74"/>
+      <c r="F119" s="74"/>
+      <c r="G119" s="74"/>
+      <c r="H119" s="74"/>
+      <c r="I119" s="75"/>
       <c r="M119" s="6">
         <f>SUM(M120)</f>
         <v>442890</v>
@@ -24252,7 +24252,7 @@
         <v>16997453</v>
       </c>
     </row>
-    <row r="120" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A120" s="9" t="s">
         <v>527</v>
       </c>
@@ -24333,7 +24333,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="121" spans="1:35" ht="93.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A121" s="9" t="s">
         <v>533</v>
       </c>
@@ -24378,7 +24378,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="122" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="29" t="s">
         <v>539</v>
       </c>
@@ -24423,7 +24423,7 @@
         <v>16969333</v>
       </c>
     </row>
-    <row r="123" spans="1:35" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="29" t="s">
         <v>542</v>
       </c>
@@ -24468,7 +24468,7 @@
         <v>16969336</v>
       </c>
     </row>
-    <row r="124" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A124" s="9" t="s">
         <v>545</v>
       </c>
@@ -24547,7 +24547,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="125" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A125" s="9" t="s">
         <v>550</v>
       </c>
@@ -24590,7 +24590,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="126" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A126" s="9" t="s">
         <v>555</v>
       </c>
@@ -24633,7 +24633,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="127" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A127" s="9" t="s">
         <v>560</v>
       </c>
@@ -24712,7 +24712,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="128" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A128" s="9" t="s">
         <v>565</v>
       </c>
@@ -24757,7 +24757,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="129" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A129" s="9" t="s">
         <v>571</v>
       </c>
@@ -24800,7 +24800,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="130" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A130" s="9" t="s">
         <v>576</v>
       </c>
@@ -24843,7 +24843,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="131" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A131" s="9" t="s">
         <v>581</v>
       </c>
@@ -24924,7 +24924,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="132" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A132" s="9" t="s">
         <v>587</v>
       </c>
@@ -24967,7 +24967,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="133" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A133" s="9" t="s">
         <v>592</v>
       </c>
@@ -25012,7 +25012,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="134" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A134" s="9" t="s">
         <v>596</v>
       </c>
@@ -25057,7 +25057,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="135" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A135" s="9" t="s">
         <v>602</v>
       </c>
@@ -25100,7 +25100,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="136" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A136" s="9" t="s">
         <v>607</v>
       </c>
@@ -25181,7 +25181,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="137" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A137" s="9" t="s">
         <v>613</v>
       </c>
@@ -25224,7 +25224,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="138" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A138" s="9" t="s">
         <v>616</v>
       </c>
@@ -25267,7 +25267,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="139" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A139" s="9" t="s">
         <v>621</v>
       </c>
@@ -25310,7 +25310,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="140" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A140" s="9" t="s">
         <v>624</v>
       </c>
@@ -25391,7 +25391,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="141" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A141" s="9" t="s">
         <v>630</v>
       </c>
@@ -25434,7 +25434,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="142" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A142" s="9" t="s">
         <v>635</v>
       </c>
@@ -25477,7 +25477,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="143" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A143" s="31" t="s">
         <v>638</v>
       </c>
@@ -25560,7 +25560,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="144" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A144" s="9" t="s">
         <v>645</v>
       </c>
@@ -25605,7 +25605,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="145" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A145" s="9" t="s">
         <v>651</v>
       </c>
@@ -25650,7 +25650,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="146" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A146" s="9" t="s">
         <v>657</v>
       </c>
@@ -25693,7 +25693,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="147" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A147" s="9" t="s">
         <v>662</v>
       </c>
@@ -25736,7 +25736,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="148" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A148" s="9" t="s">
         <v>665</v>
       </c>
@@ -25819,7 +25819,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="149" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A149" s="9" t="s">
         <v>667</v>
       </c>
@@ -25862,7 +25862,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="150" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A150" s="9" t="s">
         <v>670</v>
       </c>
@@ -25905,7 +25905,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="151" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A151" s="9" t="s">
         <v>673</v>
       </c>
@@ -25950,7 +25950,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="152" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A152" s="9" t="s">
         <v>676</v>
       </c>
@@ -25998,7 +25998,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="153" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A153" s="9" t="s">
         <v>679</v>
       </c>
@@ -26081,7 +26081,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="154" spans="1:35" ht="56.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A154" s="9" t="s">
         <v>681</v>
       </c>
@@ -26129,7 +26129,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="155" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A155" s="9" t="s">
         <v>684</v>
       </c>
@@ -26174,7 +26174,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="156" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A156" s="9" t="s">
         <v>687</v>
       </c>
@@ -26217,7 +26217,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="157" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A157" s="9" t="s">
         <v>690</v>
       </c>
@@ -26260,7 +26260,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="158" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A158" s="35" t="s">
         <v>693</v>
       </c>
@@ -26343,7 +26343,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="159" spans="1:35" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A159" s="9" t="s">
         <v>695</v>
       </c>
@@ -26386,7 +26386,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="160" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A160" s="9" t="s">
         <v>698</v>
       </c>
@@ -26429,7 +26429,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="161" spans="1:35" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A161" s="9" t="s">
         <v>701</v>
       </c>
@@ -26474,7 +26474,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="162" spans="1:35" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A162" s="9" t="s">
         <v>704</v>
       </c>
@@ -26529,15 +26529,15 @@
       <c r="B163" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C163" s="59" t="s">
+      <c r="C163" s="73" t="s">
         <v>710</v>
       </c>
-      <c r="D163" s="60"/>
-      <c r="E163" s="60"/>
-      <c r="F163" s="60"/>
-      <c r="G163" s="60"/>
-      <c r="H163" s="60"/>
-      <c r="I163" s="61"/>
+      <c r="D163" s="74"/>
+      <c r="E163" s="74"/>
+      <c r="F163" s="74"/>
+      <c r="G163" s="74"/>
+      <c r="H163" s="74"/>
+      <c r="I163" s="75"/>
       <c r="M163" s="6">
         <f>SUM(M164,M184)</f>
         <v>611422.71999999997</v>
@@ -26573,15 +26573,15 @@
       <c r="B164" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="C164" s="59" t="s">
+      <c r="C164" s="73" t="s">
         <v>713</v>
       </c>
-      <c r="D164" s="60"/>
-      <c r="E164" s="60"/>
-      <c r="F164" s="60"/>
-      <c r="G164" s="60"/>
-      <c r="H164" s="60"/>
-      <c r="I164" s="61"/>
+      <c r="D164" s="74"/>
+      <c r="E164" s="74"/>
+      <c r="F164" s="74"/>
+      <c r="G164" s="74"/>
+      <c r="H164" s="74"/>
+      <c r="I164" s="75"/>
       <c r="M164" s="6">
         <f>SUM(M165,M171,M174,M178,M182)</f>
         <v>415021.23999999993</v>
@@ -27628,15 +27628,15 @@
       <c r="B184" s="9" t="s">
         <v>789</v>
       </c>
-      <c r="C184" s="59" t="s">
+      <c r="C184" s="73" t="s">
         <v>790</v>
       </c>
-      <c r="D184" s="60"/>
-      <c r="E184" s="60"/>
-      <c r="F184" s="60"/>
-      <c r="G184" s="60"/>
-      <c r="H184" s="60"/>
-      <c r="I184" s="61"/>
+      <c r="D184" s="74"/>
+      <c r="E184" s="74"/>
+      <c r="F184" s="74"/>
+      <c r="G184" s="74"/>
+      <c r="H184" s="74"/>
+      <c r="I184" s="75"/>
       <c r="M184" s="6">
         <f>SUM(M185,M188,M191,M194,M197,M200)</f>
         <v>196401.48</v>
@@ -28686,15 +28686,15 @@
       <c r="B203" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="C203" s="59" t="s">
+      <c r="C203" s="73" t="s">
         <v>856</v>
       </c>
-      <c r="D203" s="60"/>
-      <c r="E203" s="60"/>
-      <c r="F203" s="60"/>
-      <c r="G203" s="60"/>
-      <c r="H203" s="60"/>
-      <c r="I203" s="61"/>
+      <c r="D203" s="74"/>
+      <c r="E203" s="74"/>
+      <c r="F203" s="74"/>
+      <c r="G203" s="74"/>
+      <c r="H203" s="74"/>
+      <c r="I203" s="75"/>
       <c r="M203" s="6">
         <f>SUM(M204,M206,M221,M236,M238,M240,M242,M243,M244,M245,M246,M247)</f>
         <v>719044.50999999989</v>
@@ -29102,7 +29102,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="211" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A211" s="9" t="s">
         <v>893</v>
       </c>
@@ -30045,7 +30045,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="232" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A232" s="9" t="s">
         <v>978</v>
       </c>
@@ -31076,15 +31076,15 @@
       <c r="B248" s="9" t="s">
         <v>1031</v>
       </c>
-      <c r="C248" s="59" t="s">
+      <c r="C248" s="73" t="s">
         <v>1032</v>
       </c>
-      <c r="D248" s="60"/>
-      <c r="E248" s="60"/>
-      <c r="F248" s="60"/>
-      <c r="G248" s="60"/>
-      <c r="H248" s="60"/>
-      <c r="I248" s="61"/>
+      <c r="D248" s="74"/>
+      <c r="E248" s="74"/>
+      <c r="F248" s="74"/>
+      <c r="G248" s="74"/>
+      <c r="H248" s="74"/>
+      <c r="I248" s="75"/>
       <c r="M248" s="6">
         <f>SUM(M249,M250,M251,M252)</f>
         <v>0</v>
@@ -31346,7 +31346,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="252" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A252" s="9" t="s">
         <v>1041</v>
       </c>
@@ -31471,29 +31471,29 @@
       </c>
     </row>
     <row r="254" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="62" t="s">
+      <c r="A254" s="70" t="s">
         <v>1050</v>
       </c>
-      <c r="B254" s="63"/>
-      <c r="C254" s="63"/>
-      <c r="D254" s="63"/>
-      <c r="E254" s="63"/>
-      <c r="F254" s="63"/>
-      <c r="G254" s="63"/>
-      <c r="H254" s="63"/>
-      <c r="I254" s="63"/>
-      <c r="J254" s="63"/>
-      <c r="K254" s="63"/>
-      <c r="L254" s="63"/>
-      <c r="M254" s="63"/>
-      <c r="N254" s="63"/>
-      <c r="O254" s="63"/>
-      <c r="P254" s="63"/>
-      <c r="Q254" s="63"/>
-      <c r="R254" s="63"/>
-      <c r="S254" s="63"/>
-      <c r="T254" s="63"/>
-      <c r="U254" s="64"/>
+      <c r="B254" s="71"/>
+      <c r="C254" s="71"/>
+      <c r="D254" s="71"/>
+      <c r="E254" s="71"/>
+      <c r="F254" s="71"/>
+      <c r="G254" s="71"/>
+      <c r="H254" s="71"/>
+      <c r="I254" s="71"/>
+      <c r="J254" s="71"/>
+      <c r="K254" s="71"/>
+      <c r="L254" s="71"/>
+      <c r="M254" s="71"/>
+      <c r="N254" s="71"/>
+      <c r="O254" s="71"/>
+      <c r="P254" s="71"/>
+      <c r="Q254" s="71"/>
+      <c r="R254" s="71"/>
+      <c r="S254" s="71"/>
+      <c r="T254" s="71"/>
+      <c r="U254" s="72"/>
     </row>
     <row r="255" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="27"/>
@@ -31509,20 +31509,20 @@
       <c r="E255" s="28"/>
       <c r="F255" s="28"/>
       <c r="G255" s="28"/>
-      <c r="H255" s="56"/>
-      <c r="I255" s="57"/>
-      <c r="J255" s="57"/>
-      <c r="K255" s="57"/>
-      <c r="L255" s="57"/>
-      <c r="M255" s="57"/>
-      <c r="N255" s="57"/>
-      <c r="O255" s="57"/>
-      <c r="P255" s="57"/>
-      <c r="Q255" s="57"/>
-      <c r="R255" s="57"/>
-      <c r="S255" s="57"/>
-      <c r="T255" s="57"/>
-      <c r="U255" s="58"/>
+      <c r="H255" s="68"/>
+      <c r="I255" s="76"/>
+      <c r="J255" s="76"/>
+      <c r="K255" s="76"/>
+      <c r="L255" s="76"/>
+      <c r="M255" s="76"/>
+      <c r="N255" s="76"/>
+      <c r="O255" s="76"/>
+      <c r="P255" s="76"/>
+      <c r="Q255" s="76"/>
+      <c r="R255" s="76"/>
+      <c r="S255" s="76"/>
+      <c r="T255" s="76"/>
+      <c r="U255" s="69"/>
     </row>
     <row r="256" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="27"/>
@@ -31538,20 +31538,20 @@
       <c r="E256" s="28"/>
       <c r="F256" s="28"/>
       <c r="G256" s="28"/>
-      <c r="H256" s="56"/>
-      <c r="I256" s="57"/>
-      <c r="J256" s="57"/>
-      <c r="K256" s="57"/>
-      <c r="L256" s="57"/>
-      <c r="M256" s="57"/>
-      <c r="N256" s="57"/>
-      <c r="O256" s="57"/>
-      <c r="P256" s="57"/>
-      <c r="Q256" s="57"/>
-      <c r="R256" s="57"/>
-      <c r="S256" s="57"/>
-      <c r="T256" s="57"/>
-      <c r="U256" s="58"/>
+      <c r="H256" s="68"/>
+      <c r="I256" s="76"/>
+      <c r="J256" s="76"/>
+      <c r="K256" s="76"/>
+      <c r="L256" s="76"/>
+      <c r="M256" s="76"/>
+      <c r="N256" s="76"/>
+      <c r="O256" s="76"/>
+      <c r="P256" s="76"/>
+      <c r="Q256" s="76"/>
+      <c r="R256" s="76"/>
+      <c r="S256" s="76"/>
+      <c r="T256" s="76"/>
+      <c r="U256" s="69"/>
     </row>
     <row r="257" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A257" s="27"/>
@@ -31567,20 +31567,20 @@
       <c r="E257" s="28"/>
       <c r="F257" s="28"/>
       <c r="G257" s="28"/>
-      <c r="H257" s="56"/>
-      <c r="I257" s="57"/>
-      <c r="J257" s="57"/>
-      <c r="K257" s="57"/>
-      <c r="L257" s="57"/>
-      <c r="M257" s="57"/>
-      <c r="N257" s="57"/>
-      <c r="O257" s="57"/>
-      <c r="P257" s="57"/>
-      <c r="Q257" s="57"/>
-      <c r="R257" s="57"/>
-      <c r="S257" s="57"/>
-      <c r="T257" s="57"/>
-      <c r="U257" s="58"/>
+      <c r="H257" s="68"/>
+      <c r="I257" s="76"/>
+      <c r="J257" s="76"/>
+      <c r="K257" s="76"/>
+      <c r="L257" s="76"/>
+      <c r="M257" s="76"/>
+      <c r="N257" s="76"/>
+      <c r="O257" s="76"/>
+      <c r="P257" s="76"/>
+      <c r="Q257" s="76"/>
+      <c r="R257" s="76"/>
+      <c r="S257" s="76"/>
+      <c r="T257" s="76"/>
+      <c r="U257" s="69"/>
     </row>
     <row r="258" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="27"/>
@@ -31596,20 +31596,20 @@
       <c r="E258" s="28"/>
       <c r="F258" s="28"/>
       <c r="G258" s="28"/>
-      <c r="H258" s="56"/>
-      <c r="I258" s="57"/>
-      <c r="J258" s="57"/>
-      <c r="K258" s="57"/>
-      <c r="L258" s="57"/>
-      <c r="M258" s="57"/>
-      <c r="N258" s="57"/>
-      <c r="O258" s="57"/>
-      <c r="P258" s="57"/>
-      <c r="Q258" s="57"/>
-      <c r="R258" s="57"/>
-      <c r="S258" s="57"/>
-      <c r="T258" s="57"/>
-      <c r="U258" s="58"/>
+      <c r="H258" s="68"/>
+      <c r="I258" s="76"/>
+      <c r="J258" s="76"/>
+      <c r="K258" s="76"/>
+      <c r="L258" s="76"/>
+      <c r="M258" s="76"/>
+      <c r="N258" s="76"/>
+      <c r="O258" s="76"/>
+      <c r="P258" s="76"/>
+      <c r="Q258" s="76"/>
+      <c r="R258" s="76"/>
+      <c r="S258" s="76"/>
+      <c r="T258" s="76"/>
+      <c r="U258" s="69"/>
     </row>
     <row r="259" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="27"/>
@@ -31625,20 +31625,20 @@
       <c r="E259" s="28"/>
       <c r="F259" s="28"/>
       <c r="G259" s="28"/>
-      <c r="H259" s="56"/>
-      <c r="I259" s="57"/>
-      <c r="J259" s="57"/>
-      <c r="K259" s="57"/>
-      <c r="L259" s="57"/>
-      <c r="M259" s="57"/>
-      <c r="N259" s="57"/>
-      <c r="O259" s="57"/>
-      <c r="P259" s="57"/>
-      <c r="Q259" s="57"/>
-      <c r="R259" s="57"/>
-      <c r="S259" s="57"/>
-      <c r="T259" s="57"/>
-      <c r="U259" s="58"/>
+      <c r="H259" s="68"/>
+      <c r="I259" s="76"/>
+      <c r="J259" s="76"/>
+      <c r="K259" s="76"/>
+      <c r="L259" s="76"/>
+      <c r="M259" s="76"/>
+      <c r="N259" s="76"/>
+      <c r="O259" s="76"/>
+      <c r="P259" s="76"/>
+      <c r="Q259" s="76"/>
+      <c r="R259" s="76"/>
+      <c r="S259" s="76"/>
+      <c r="T259" s="76"/>
+      <c r="U259" s="69"/>
     </row>
     <row r="260" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A260" s="27"/>
@@ -31654,20 +31654,20 @@
       <c r="E260" s="28"/>
       <c r="F260" s="28"/>
       <c r="G260" s="28"/>
-      <c r="H260" s="56"/>
-      <c r="I260" s="57"/>
-      <c r="J260" s="57"/>
-      <c r="K260" s="57"/>
-      <c r="L260" s="57"/>
-      <c r="M260" s="57"/>
-      <c r="N260" s="57"/>
-      <c r="O260" s="57"/>
-      <c r="P260" s="57"/>
-      <c r="Q260" s="57"/>
-      <c r="R260" s="57"/>
-      <c r="S260" s="57"/>
-      <c r="T260" s="57"/>
-      <c r="U260" s="58"/>
+      <c r="H260" s="68"/>
+      <c r="I260" s="76"/>
+      <c r="J260" s="76"/>
+      <c r="K260" s="76"/>
+      <c r="L260" s="76"/>
+      <c r="M260" s="76"/>
+      <c r="N260" s="76"/>
+      <c r="O260" s="76"/>
+      <c r="P260" s="76"/>
+      <c r="Q260" s="76"/>
+      <c r="R260" s="76"/>
+      <c r="S260" s="76"/>
+      <c r="T260" s="76"/>
+      <c r="U260" s="69"/>
     </row>
     <row r="261" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A261" s="27"/>
@@ -31683,22 +31683,22 @@
       <c r="E261" s="28"/>
       <c r="F261" s="28"/>
       <c r="G261" s="28"/>
-      <c r="H261" s="56"/>
-      <c r="I261" s="57"/>
-      <c r="J261" s="57"/>
-      <c r="K261" s="57"/>
-      <c r="L261" s="57"/>
-      <c r="M261" s="57"/>
-      <c r="N261" s="57"/>
-      <c r="O261" s="57"/>
-      <c r="P261" s="57"/>
-      <c r="Q261" s="57"/>
-      <c r="R261" s="57"/>
-      <c r="S261" s="57"/>
-      <c r="T261" s="57"/>
-      <c r="U261" s="58"/>
-    </row>
-    <row r="262" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H261" s="68"/>
+      <c r="I261" s="76"/>
+      <c r="J261" s="76"/>
+      <c r="K261" s="76"/>
+      <c r="L261" s="76"/>
+      <c r="M261" s="76"/>
+      <c r="N261" s="76"/>
+      <c r="O261" s="76"/>
+      <c r="P261" s="76"/>
+      <c r="Q261" s="76"/>
+      <c r="R261" s="76"/>
+      <c r="S261" s="76"/>
+      <c r="T261" s="76"/>
+      <c r="U261" s="69"/>
+    </row>
+    <row r="262" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A262" s="27"/>
       <c r="B262" s="5" t="s">
         <v>1071</v>
@@ -31712,20 +31712,20 @@
       <c r="E262" s="28"/>
       <c r="F262" s="28"/>
       <c r="G262" s="28"/>
-      <c r="H262" s="56"/>
-      <c r="I262" s="57"/>
-      <c r="J262" s="57"/>
-      <c r="K262" s="57"/>
-      <c r="L262" s="57"/>
-      <c r="M262" s="57"/>
-      <c r="N262" s="57"/>
-      <c r="O262" s="57"/>
-      <c r="P262" s="57"/>
-      <c r="Q262" s="57"/>
-      <c r="R262" s="57"/>
-      <c r="S262" s="57"/>
-      <c r="T262" s="57"/>
-      <c r="U262" s="58"/>
+      <c r="H262" s="68"/>
+      <c r="I262" s="76"/>
+      <c r="J262" s="76"/>
+      <c r="K262" s="76"/>
+      <c r="L262" s="76"/>
+      <c r="M262" s="76"/>
+      <c r="N262" s="76"/>
+      <c r="O262" s="76"/>
+      <c r="P262" s="76"/>
+      <c r="Q262" s="76"/>
+      <c r="R262" s="76"/>
+      <c r="S262" s="76"/>
+      <c r="T262" s="76"/>
+      <c r="U262" s="69"/>
     </row>
     <row r="263" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="27"/>
@@ -31741,20 +31741,20 @@
       <c r="E263" s="28"/>
       <c r="F263" s="28"/>
       <c r="G263" s="28"/>
-      <c r="H263" s="56"/>
-      <c r="I263" s="57"/>
-      <c r="J263" s="57"/>
-      <c r="K263" s="57"/>
-      <c r="L263" s="57"/>
-      <c r="M263" s="57"/>
-      <c r="N263" s="57"/>
-      <c r="O263" s="57"/>
-      <c r="P263" s="57"/>
-      <c r="Q263" s="57"/>
-      <c r="R263" s="57"/>
-      <c r="S263" s="57"/>
-      <c r="T263" s="57"/>
-      <c r="U263" s="58"/>
+      <c r="H263" s="68"/>
+      <c r="I263" s="76"/>
+      <c r="J263" s="76"/>
+      <c r="K263" s="76"/>
+      <c r="L263" s="76"/>
+      <c r="M263" s="76"/>
+      <c r="N263" s="76"/>
+      <c r="O263" s="76"/>
+      <c r="P263" s="76"/>
+      <c r="Q263" s="76"/>
+      <c r="R263" s="76"/>
+      <c r="S263" s="76"/>
+      <c r="T263" s="76"/>
+      <c r="U263" s="69"/>
     </row>
     <row r="264" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A264" s="27"/>
@@ -31770,20 +31770,20 @@
       <c r="E264" s="28"/>
       <c r="F264" s="28"/>
       <c r="G264" s="28"/>
-      <c r="H264" s="56"/>
-      <c r="I264" s="57"/>
-      <c r="J264" s="57"/>
-      <c r="K264" s="57"/>
-      <c r="L264" s="57"/>
-      <c r="M264" s="57"/>
-      <c r="N264" s="57"/>
-      <c r="O264" s="57"/>
-      <c r="P264" s="57"/>
-      <c r="Q264" s="57"/>
-      <c r="R264" s="57"/>
-      <c r="S264" s="57"/>
-      <c r="T264" s="57"/>
-      <c r="U264" s="58"/>
+      <c r="H264" s="68"/>
+      <c r="I264" s="76"/>
+      <c r="J264" s="76"/>
+      <c r="K264" s="76"/>
+      <c r="L264" s="76"/>
+      <c r="M264" s="76"/>
+      <c r="N264" s="76"/>
+      <c r="O264" s="76"/>
+      <c r="P264" s="76"/>
+      <c r="Q264" s="76"/>
+      <c r="R264" s="76"/>
+      <c r="S264" s="76"/>
+      <c r="T264" s="76"/>
+      <c r="U264" s="69"/>
     </row>
     <row r="265" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A265" s="27"/>
@@ -31799,20 +31799,20 @@
       <c r="E265" s="28"/>
       <c r="F265" s="28"/>
       <c r="G265" s="28"/>
-      <c r="H265" s="56"/>
-      <c r="I265" s="57"/>
-      <c r="J265" s="57"/>
-      <c r="K265" s="57"/>
-      <c r="L265" s="57"/>
-      <c r="M265" s="57"/>
-      <c r="N265" s="57"/>
-      <c r="O265" s="57"/>
-      <c r="P265" s="57"/>
-      <c r="Q265" s="57"/>
-      <c r="R265" s="57"/>
-      <c r="S265" s="57"/>
-      <c r="T265" s="57"/>
-      <c r="U265" s="58"/>
+      <c r="H265" s="68"/>
+      <c r="I265" s="76"/>
+      <c r="J265" s="76"/>
+      <c r="K265" s="76"/>
+      <c r="L265" s="76"/>
+      <c r="M265" s="76"/>
+      <c r="N265" s="76"/>
+      <c r="O265" s="76"/>
+      <c r="P265" s="76"/>
+      <c r="Q265" s="76"/>
+      <c r="R265" s="76"/>
+      <c r="S265" s="76"/>
+      <c r="T265" s="76"/>
+      <c r="U265" s="69"/>
     </row>
     <row r="266" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A266" s="27"/>
@@ -31828,20 +31828,20 @@
       <c r="E266" s="28"/>
       <c r="F266" s="28"/>
       <c r="G266" s="28"/>
-      <c r="H266" s="56"/>
-      <c r="I266" s="57"/>
-      <c r="J266" s="57"/>
-      <c r="K266" s="57"/>
-      <c r="L266" s="57"/>
-      <c r="M266" s="57"/>
-      <c r="N266" s="57"/>
-      <c r="O266" s="57"/>
-      <c r="P266" s="57"/>
-      <c r="Q266" s="57"/>
-      <c r="R266" s="57"/>
-      <c r="S266" s="57"/>
-      <c r="T266" s="57"/>
-      <c r="U266" s="58"/>
+      <c r="H266" s="68"/>
+      <c r="I266" s="76"/>
+      <c r="J266" s="76"/>
+      <c r="K266" s="76"/>
+      <c r="L266" s="76"/>
+      <c r="M266" s="76"/>
+      <c r="N266" s="76"/>
+      <c r="O266" s="76"/>
+      <c r="P266" s="76"/>
+      <c r="Q266" s="76"/>
+      <c r="R266" s="76"/>
+      <c r="S266" s="76"/>
+      <c r="T266" s="76"/>
+      <c r="U266" s="69"/>
     </row>
     <row r="267" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="27"/>
@@ -31857,20 +31857,20 @@
       <c r="E267" s="28"/>
       <c r="F267" s="28"/>
       <c r="G267" s="28"/>
-      <c r="H267" s="56"/>
-      <c r="I267" s="57"/>
-      <c r="J267" s="57"/>
-      <c r="K267" s="57"/>
-      <c r="L267" s="57"/>
-      <c r="M267" s="57"/>
-      <c r="N267" s="57"/>
-      <c r="O267" s="57"/>
-      <c r="P267" s="57"/>
-      <c r="Q267" s="57"/>
-      <c r="R267" s="57"/>
-      <c r="S267" s="57"/>
-      <c r="T267" s="57"/>
-      <c r="U267" s="58"/>
+      <c r="H267" s="68"/>
+      <c r="I267" s="76"/>
+      <c r="J267" s="76"/>
+      <c r="K267" s="76"/>
+      <c r="L267" s="76"/>
+      <c r="M267" s="76"/>
+      <c r="N267" s="76"/>
+      <c r="O267" s="76"/>
+      <c r="P267" s="76"/>
+      <c r="Q267" s="76"/>
+      <c r="R267" s="76"/>
+      <c r="S267" s="76"/>
+      <c r="T267" s="76"/>
+      <c r="U267" s="69"/>
     </row>
     <row r="268" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="27"/>
@@ -31886,22 +31886,22 @@
       <c r="E268" s="28"/>
       <c r="F268" s="28"/>
       <c r="G268" s="28"/>
-      <c r="H268" s="56" t="s">
+      <c r="H268" s="68" t="s">
         <v>1092</v>
       </c>
-      <c r="I268" s="57"/>
-      <c r="J268" s="57"/>
-      <c r="K268" s="57"/>
-      <c r="L268" s="57"/>
-      <c r="M268" s="57"/>
-      <c r="N268" s="57"/>
-      <c r="O268" s="57"/>
-      <c r="P268" s="57"/>
-      <c r="Q268" s="57"/>
-      <c r="R268" s="57"/>
-      <c r="S268" s="57"/>
-      <c r="T268" s="57"/>
-      <c r="U268" s="58"/>
+      <c r="I268" s="76"/>
+      <c r="J268" s="76"/>
+      <c r="K268" s="76"/>
+      <c r="L268" s="76"/>
+      <c r="M268" s="76"/>
+      <c r="N268" s="76"/>
+      <c r="O268" s="76"/>
+      <c r="P268" s="76"/>
+      <c r="Q268" s="76"/>
+      <c r="R268" s="76"/>
+      <c r="S268" s="76"/>
+      <c r="T268" s="76"/>
+      <c r="U268" s="69"/>
     </row>
     <row r="269" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="27"/>
@@ -31917,20 +31917,20 @@
       <c r="E269" s="28"/>
       <c r="F269" s="28"/>
       <c r="G269" s="28"/>
-      <c r="H269" s="56"/>
-      <c r="I269" s="57"/>
-      <c r="J269" s="57"/>
-      <c r="K269" s="57"/>
-      <c r="L269" s="57"/>
-      <c r="M269" s="57"/>
-      <c r="N269" s="57"/>
-      <c r="O269" s="57"/>
-      <c r="P269" s="57"/>
-      <c r="Q269" s="57"/>
-      <c r="R269" s="57"/>
-      <c r="S269" s="57"/>
-      <c r="T269" s="57"/>
-      <c r="U269" s="58"/>
+      <c r="H269" s="68"/>
+      <c r="I269" s="76"/>
+      <c r="J269" s="76"/>
+      <c r="K269" s="76"/>
+      <c r="L269" s="76"/>
+      <c r="M269" s="76"/>
+      <c r="N269" s="76"/>
+      <c r="O269" s="76"/>
+      <c r="P269" s="76"/>
+      <c r="Q269" s="76"/>
+      <c r="R269" s="76"/>
+      <c r="S269" s="76"/>
+      <c r="T269" s="76"/>
+      <c r="U269" s="69"/>
     </row>
     <row r="270" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A270" s="27"/>
@@ -31944,20 +31944,20 @@
       <c r="E270" s="28"/>
       <c r="F270" s="28"/>
       <c r="G270" s="28"/>
-      <c r="H270" s="56"/>
-      <c r="I270" s="57"/>
-      <c r="J270" s="57"/>
-      <c r="K270" s="57"/>
-      <c r="L270" s="57"/>
-      <c r="M270" s="57"/>
-      <c r="N270" s="57"/>
-      <c r="O270" s="57"/>
-      <c r="P270" s="57"/>
-      <c r="Q270" s="57"/>
-      <c r="R270" s="57"/>
-      <c r="S270" s="57"/>
-      <c r="T270" s="57"/>
-      <c r="U270" s="58"/>
+      <c r="H270" s="68"/>
+      <c r="I270" s="76"/>
+      <c r="J270" s="76"/>
+      <c r="K270" s="76"/>
+      <c r="L270" s="76"/>
+      <c r="M270" s="76"/>
+      <c r="N270" s="76"/>
+      <c r="O270" s="76"/>
+      <c r="P270" s="76"/>
+      <c r="Q270" s="76"/>
+      <c r="R270" s="76"/>
+      <c r="S270" s="76"/>
+      <c r="T270" s="76"/>
+      <c r="U270" s="69"/>
     </row>
     <row r="271" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="27"/>
@@ -31971,20 +31971,20 @@
       <c r="E271" s="28"/>
       <c r="F271" s="28"/>
       <c r="G271" s="28"/>
-      <c r="H271" s="56"/>
-      <c r="I271" s="57"/>
-      <c r="J271" s="57"/>
-      <c r="K271" s="57"/>
-      <c r="L271" s="57"/>
-      <c r="M271" s="57"/>
-      <c r="N271" s="57"/>
-      <c r="O271" s="57"/>
-      <c r="P271" s="57"/>
-      <c r="Q271" s="57"/>
-      <c r="R271" s="57"/>
-      <c r="S271" s="57"/>
-      <c r="T271" s="57"/>
-      <c r="U271" s="58"/>
+      <c r="H271" s="68"/>
+      <c r="I271" s="76"/>
+      <c r="J271" s="76"/>
+      <c r="K271" s="76"/>
+      <c r="L271" s="76"/>
+      <c r="M271" s="76"/>
+      <c r="N271" s="76"/>
+      <c r="O271" s="76"/>
+      <c r="P271" s="76"/>
+      <c r="Q271" s="76"/>
+      <c r="R271" s="76"/>
+      <c r="S271" s="76"/>
+      <c r="T271" s="76"/>
+      <c r="U271" s="69"/>
     </row>
     <row r="272" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="27"/>
@@ -31998,60 +31998,34 @@
       <c r="E272" s="28"/>
       <c r="F272" s="28"/>
       <c r="G272" s="28"/>
-      <c r="H272" s="56"/>
-      <c r="I272" s="57"/>
-      <c r="J272" s="57"/>
-      <c r="K272" s="57"/>
-      <c r="L272" s="57"/>
-      <c r="M272" s="57"/>
-      <c r="N272" s="57"/>
-      <c r="O272" s="57"/>
-      <c r="P272" s="57"/>
-      <c r="Q272" s="57"/>
-      <c r="R272" s="57"/>
-      <c r="S272" s="57"/>
-      <c r="T272" s="57"/>
-      <c r="U272" s="58"/>
+      <c r="H272" s="68"/>
+      <c r="I272" s="76"/>
+      <c r="J272" s="76"/>
+      <c r="K272" s="76"/>
+      <c r="L272" s="76"/>
+      <c r="M272" s="76"/>
+      <c r="N272" s="76"/>
+      <c r="O272" s="76"/>
+      <c r="P272" s="76"/>
+      <c r="Q272" s="76"/>
+      <c r="R272" s="76"/>
+      <c r="S272" s="76"/>
+      <c r="T272" s="76"/>
+      <c r="U272" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="H271:U271"/>
-    <mergeCell ref="H272:U272"/>
-    <mergeCell ref="H265:U265"/>
-    <mergeCell ref="H266:U266"/>
-    <mergeCell ref="H267:U267"/>
-    <mergeCell ref="H268:U268"/>
-    <mergeCell ref="H269:U269"/>
-    <mergeCell ref="H270:U270"/>
-    <mergeCell ref="H264:U264"/>
-    <mergeCell ref="C248:I248"/>
-    <mergeCell ref="A254:U254"/>
-    <mergeCell ref="H255:U255"/>
-    <mergeCell ref="H256:U256"/>
-    <mergeCell ref="H257:U257"/>
-    <mergeCell ref="H258:U258"/>
-    <mergeCell ref="H259:U259"/>
-    <mergeCell ref="H260:U260"/>
-    <mergeCell ref="H261:U261"/>
-    <mergeCell ref="H262:U262"/>
-    <mergeCell ref="H263:U263"/>
-    <mergeCell ref="C203:I203"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C119:I119"/>
-    <mergeCell ref="C122:I122"/>
-    <mergeCell ref="C123:I123"/>
-    <mergeCell ref="C163:I163"/>
-    <mergeCell ref="C164:I164"/>
-    <mergeCell ref="C184:I184"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A3:U3"/>
+    <mergeCell ref="A4:U4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="G5:G7"/>
     <mergeCell ref="C21:I21"/>
     <mergeCell ref="R6:R7"/>
     <mergeCell ref="S6:T6"/>
@@ -32068,17 +32042,43 @@
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:U3"/>
-    <mergeCell ref="A4:U4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="C203:I203"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C119:I119"/>
+    <mergeCell ref="C122:I122"/>
+    <mergeCell ref="C123:I123"/>
+    <mergeCell ref="C163:I163"/>
+    <mergeCell ref="C164:I164"/>
+    <mergeCell ref="C184:I184"/>
+    <mergeCell ref="H264:U264"/>
+    <mergeCell ref="C248:I248"/>
+    <mergeCell ref="A254:U254"/>
+    <mergeCell ref="H255:U255"/>
+    <mergeCell ref="H256:U256"/>
+    <mergeCell ref="H257:U257"/>
+    <mergeCell ref="H258:U258"/>
+    <mergeCell ref="H259:U259"/>
+    <mergeCell ref="H260:U260"/>
+    <mergeCell ref="H261:U261"/>
+    <mergeCell ref="H262:U262"/>
+    <mergeCell ref="H263:U263"/>
+    <mergeCell ref="H271:U271"/>
+    <mergeCell ref="H272:U272"/>
+    <mergeCell ref="H265:U265"/>
+    <mergeCell ref="H266:U266"/>
+    <mergeCell ref="H267:U267"/>
+    <mergeCell ref="H268:U268"/>
+    <mergeCell ref="H269:U269"/>
+    <mergeCell ref="H270:U270"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/school_lublino/lublino_KP.xlsx
+++ b/school_lublino/lublino_KP.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3338" uniqueCount="1105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3340" uniqueCount="1106">
   <si>
     <t>Указать название организации (на бланке организации)</t>
   </si>
@@ -3465,6 +3465,9 @@
   </si>
   <si>
     <t>сделать</t>
+  </si>
+  <si>
+    <t>базовая</t>
   </si>
 </sst>
 </file>
@@ -3913,6 +3916,39 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3943,40 +3979,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4376,79 +4379,79 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="56"/>
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
-      <c r="U2" s="56"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
+      <c r="P3" s="68"/>
+      <c r="Q3" s="68"/>
+      <c r="R3" s="68"/>
+      <c r="S3" s="68"/>
+      <c r="T3" s="68"/>
+      <c r="U3" s="68"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="58" t="s">
+      <c r="A4" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="58"/>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="58"/>
-      <c r="S4" s="58"/>
-      <c r="T4" s="58"/>
-      <c r="U4" s="58"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="69"/>
+      <c r="Q4" s="69"/>
+      <c r="R4" s="69"/>
+      <c r="S4" s="69"/>
+      <c r="T4" s="69"/>
+      <c r="U4" s="69"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="65" t="s">
@@ -4478,115 +4481,115 @@
       <c r="I5" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="59" t="s">
+      <c r="J5" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="61"/>
-      <c r="P5" s="62" t="s">
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="72"/>
+      <c r="P5" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="64"/>
-      <c r="S5" s="62" t="s">
+      <c r="Q5" s="74"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="63"/>
-      <c r="U5" s="64"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="75"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="68" t="s">
+      <c r="A6" s="76"/>
+      <c r="B6" s="76"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="69"/>
+      <c r="K6" s="58"/>
       <c r="L6" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="68" t="s">
+      <c r="M6" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="69"/>
+      <c r="N6" s="58"/>
       <c r="O6" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="69"/>
+      <c r="Q6" s="58"/>
       <c r="R6" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="S6" s="68" t="s">
+      <c r="S6" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="69"/>
+      <c r="T6" s="58"/>
       <c r="U6" s="65" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="67"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
+      <c r="A7" s="66"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
       <c r="J7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="67"/>
+      <c r="L7" s="66"/>
       <c r="M7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="67"/>
+      <c r="O7" s="66"/>
       <c r="P7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="67"/>
+      <c r="R7" s="66"/>
       <c r="S7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="U7" s="67"/>
+      <c r="U7" s="66"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="70" t="s">
+      <c r="A8" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="72"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="64"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -4628,15 +4631,15 @@
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="73" t="s">
+      <c r="C9" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="75"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="61"/>
       <c r="M9" s="6">
         <f>SUM(M10,M20)</f>
         <v>18303819.899999999</v>
@@ -4672,15 +4675,15 @@
       <c r="B10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="73" t="s">
+      <c r="C10" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="75"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="61"/>
       <c r="M10" s="6">
         <f t="shared" ref="M10:O14" si="0">SUM(M11)</f>
         <v>126283.29</v>
@@ -4716,15 +4719,15 @@
       <c r="B11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="73" t="s">
+      <c r="C11" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="75"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="61"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4760,15 +4763,15 @@
       <c r="B12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="C12" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="75"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="61"/>
       <c r="M12" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4804,15 +4807,15 @@
       <c r="B13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="73" t="s">
+      <c r="C13" s="59" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="75"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="61"/>
       <c r="M13" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4848,15 +4851,15 @@
       <c r="B14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="73" t="s">
+      <c r="C14" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="75"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="61"/>
       <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -5147,15 +5150,15 @@
       <c r="B20" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="73" t="s">
+      <c r="C20" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="75"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="61"/>
       <c r="M20" s="6">
         <f t="shared" ref="M20:O21" si="1">SUM(M21)</f>
         <v>18177536.609999999</v>
@@ -5191,15 +5194,15 @@
       <c r="B21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="73" t="s">
+      <c r="C21" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="74"/>
-      <c r="E21" s="74"/>
-      <c r="F21" s="74"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="75"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="61"/>
       <c r="M21" s="6">
         <f t="shared" si="1"/>
         <v>18177536.609999999</v>
@@ -5235,15 +5238,15 @@
       <c r="B22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="73" t="s">
+      <c r="C22" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="74"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="75"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="61"/>
       <c r="M22" s="6">
         <f>SUM(M23,M122,M163,M203,M248)</f>
         <v>18177536.609999999</v>
@@ -5279,15 +5282,15 @@
       <c r="B23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="73" t="s">
+      <c r="C23" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="74"/>
-      <c r="E23" s="74"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="74"/>
-      <c r="I23" s="75"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="61"/>
       <c r="M23" s="6">
         <f>SUM(M24,M67,M76,M119)</f>
         <v>12831032.07</v>
@@ -5323,15 +5326,15 @@
       <c r="B24" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="73" t="s">
+      <c r="C24" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="74"/>
-      <c r="I24" s="75"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="61"/>
       <c r="M24" s="6">
         <f>SUM(M25,M29,M31,M34,M36,M41,M46,M51,M57,M62)</f>
         <v>7808423.3099999996</v>
@@ -7555,15 +7558,15 @@
       <c r="B67" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="73" t="s">
+      <c r="C67" s="59" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="74"/>
-      <c r="E67" s="74"/>
-      <c r="F67" s="74"/>
-      <c r="G67" s="74"/>
-      <c r="H67" s="74"/>
-      <c r="I67" s="75"/>
+      <c r="D67" s="60"/>
+      <c r="E67" s="60"/>
+      <c r="F67" s="60"/>
+      <c r="G67" s="60"/>
+      <c r="H67" s="60"/>
+      <c r="I67" s="61"/>
       <c r="M67" s="6">
         <f>SUM(M68,M72,M74)</f>
         <v>748533.11</v>
@@ -8061,15 +8064,15 @@
       <c r="B76" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C76" s="73" t="s">
+      <c r="C76" s="59" t="s">
         <v>325</v>
       </c>
-      <c r="D76" s="74"/>
-      <c r="E76" s="74"/>
-      <c r="F76" s="74"/>
-      <c r="G76" s="74"/>
-      <c r="H76" s="74"/>
-      <c r="I76" s="75"/>
+      <c r="D76" s="60"/>
+      <c r="E76" s="60"/>
+      <c r="F76" s="60"/>
+      <c r="G76" s="60"/>
+      <c r="H76" s="60"/>
+      <c r="I76" s="61"/>
       <c r="M76" s="6">
         <f>SUM(M77,M82,M87,M93,M96,M99,M104,M109,M114,M117)</f>
         <v>3831185.6499999994</v>
@@ -10319,15 +10322,15 @@
       <c r="B119" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C119" s="73" t="s">
+      <c r="C119" s="59" t="s">
         <v>526</v>
       </c>
-      <c r="D119" s="74"/>
-      <c r="E119" s="74"/>
-      <c r="F119" s="74"/>
-      <c r="G119" s="74"/>
-      <c r="H119" s="74"/>
-      <c r="I119" s="75"/>
+      <c r="D119" s="60"/>
+      <c r="E119" s="60"/>
+      <c r="F119" s="60"/>
+      <c r="G119" s="60"/>
+      <c r="H119" s="60"/>
+      <c r="I119" s="61"/>
       <c r="M119" s="6">
         <f>SUM(M120)</f>
         <v>442890</v>
@@ -10489,15 +10492,15 @@
       <c r="B122" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="C122" s="73" t="s">
+      <c r="C122" s="59" t="s">
         <v>541</v>
       </c>
-      <c r="D122" s="74"/>
-      <c r="E122" s="74"/>
-      <c r="F122" s="74"/>
-      <c r="G122" s="74"/>
-      <c r="H122" s="74"/>
-      <c r="I122" s="75"/>
+      <c r="D122" s="60"/>
+      <c r="E122" s="60"/>
+      <c r="F122" s="60"/>
+      <c r="G122" s="60"/>
+      <c r="H122" s="60"/>
+      <c r="I122" s="61"/>
       <c r="M122" s="6">
         <f>SUM(M123)</f>
         <v>4016037.31</v>
@@ -10533,15 +10536,15 @@
       <c r="B123" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="C123" s="73" t="s">
+      <c r="C123" s="59" t="s">
         <v>544</v>
       </c>
-      <c r="D123" s="74"/>
-      <c r="E123" s="74"/>
-      <c r="F123" s="74"/>
-      <c r="G123" s="74"/>
-      <c r="H123" s="74"/>
-      <c r="I123" s="75"/>
+      <c r="D123" s="60"/>
+      <c r="E123" s="60"/>
+      <c r="F123" s="60"/>
+      <c r="G123" s="60"/>
+      <c r="H123" s="60"/>
+      <c r="I123" s="61"/>
       <c r="M123" s="6">
         <f>SUM(M124,M127,M131,M136,M140,M143,M148,M153,M158)</f>
         <v>4016037.31</v>
@@ -11283,7 +11286,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="137" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A137" s="9" t="s">
         <v>613</v>
       </c>
@@ -12622,15 +12625,15 @@
       <c r="B163" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C163" s="73" t="s">
+      <c r="C163" s="59" t="s">
         <v>710</v>
       </c>
-      <c r="D163" s="74"/>
-      <c r="E163" s="74"/>
-      <c r="F163" s="74"/>
-      <c r="G163" s="74"/>
-      <c r="H163" s="74"/>
-      <c r="I163" s="75"/>
+      <c r="D163" s="60"/>
+      <c r="E163" s="60"/>
+      <c r="F163" s="60"/>
+      <c r="G163" s="60"/>
+      <c r="H163" s="60"/>
+      <c r="I163" s="61"/>
       <c r="M163" s="6">
         <f>SUM(M164,M184)</f>
         <v>611422.71999999997</v>
@@ -12666,15 +12669,15 @@
       <c r="B164" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="C164" s="73" t="s">
+      <c r="C164" s="59" t="s">
         <v>713</v>
       </c>
-      <c r="D164" s="74"/>
-      <c r="E164" s="74"/>
-      <c r="F164" s="74"/>
-      <c r="G164" s="74"/>
-      <c r="H164" s="74"/>
-      <c r="I164" s="75"/>
+      <c r="D164" s="60"/>
+      <c r="E164" s="60"/>
+      <c r="F164" s="60"/>
+      <c r="G164" s="60"/>
+      <c r="H164" s="60"/>
+      <c r="I164" s="61"/>
       <c r="M164" s="6">
         <f>SUM(M165,M171,M174,M178,M182)</f>
         <v>415021.23999999993</v>
@@ -13084,7 +13087,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="172" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A172" s="9" t="s">
         <v>749</v>
       </c>
@@ -13251,7 +13254,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="175" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A175" s="9" t="s">
         <v>759</v>
       </c>
@@ -13547,7 +13550,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="181" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
         <v>776</v>
       </c>
@@ -13721,15 +13724,15 @@
       <c r="B184" s="9" t="s">
         <v>789</v>
       </c>
-      <c r="C184" s="73" t="s">
+      <c r="C184" s="59" t="s">
         <v>790</v>
       </c>
-      <c r="D184" s="74"/>
-      <c r="E184" s="74"/>
-      <c r="F184" s="74"/>
-      <c r="G184" s="74"/>
-      <c r="H184" s="74"/>
-      <c r="I184" s="75"/>
+      <c r="D184" s="60"/>
+      <c r="E184" s="60"/>
+      <c r="F184" s="60"/>
+      <c r="G184" s="60"/>
+      <c r="H184" s="60"/>
+      <c r="I184" s="61"/>
       <c r="M184" s="6">
         <f>SUM(M185,M188,M191,M194,M197,M200)</f>
         <v>196401.48</v>
@@ -14779,15 +14782,15 @@
       <c r="B203" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="C203" s="73" t="s">
+      <c r="C203" s="59" t="s">
         <v>856</v>
       </c>
-      <c r="D203" s="74"/>
-      <c r="E203" s="74"/>
-      <c r="F203" s="74"/>
-      <c r="G203" s="74"/>
-      <c r="H203" s="74"/>
-      <c r="I203" s="75"/>
+      <c r="D203" s="60"/>
+      <c r="E203" s="60"/>
+      <c r="F203" s="60"/>
+      <c r="G203" s="60"/>
+      <c r="H203" s="60"/>
+      <c r="I203" s="61"/>
       <c r="M203" s="6">
         <f>SUM(M204,M206,M221,M236,M238,M240,M242,M243,M244,M245,M246,M247)</f>
         <v>719044.50999999989</v>
@@ -15367,7 +15370,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="215" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A215" s="9" t="s">
         <v>913</v>
       </c>
@@ -15964,7 +15967,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="228" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A228" s="9" t="s">
         <v>963</v>
       </c>
@@ -17169,15 +17172,15 @@
       <c r="B248" s="9" t="s">
         <v>1031</v>
       </c>
-      <c r="C248" s="73" t="s">
+      <c r="C248" s="59" t="s">
         <v>1032</v>
       </c>
-      <c r="D248" s="74"/>
-      <c r="E248" s="74"/>
-      <c r="F248" s="74"/>
-      <c r="G248" s="74"/>
-      <c r="H248" s="74"/>
-      <c r="I248" s="75"/>
+      <c r="D248" s="60"/>
+      <c r="E248" s="60"/>
+      <c r="F248" s="60"/>
+      <c r="G248" s="60"/>
+      <c r="H248" s="60"/>
+      <c r="I248" s="61"/>
       <c r="M248" s="6">
         <f>SUM(M249,M250,M251,M252)</f>
         <v>0</v>
@@ -17564,29 +17567,29 @@
       </c>
     </row>
     <row r="254" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="70" t="s">
+      <c r="A254" s="62" t="s">
         <v>1050</v>
       </c>
-      <c r="B254" s="71"/>
-      <c r="C254" s="71"/>
-      <c r="D254" s="71"/>
-      <c r="E254" s="71"/>
-      <c r="F254" s="71"/>
-      <c r="G254" s="71"/>
-      <c r="H254" s="71"/>
-      <c r="I254" s="71"/>
-      <c r="J254" s="71"/>
-      <c r="K254" s="71"/>
-      <c r="L254" s="71"/>
-      <c r="M254" s="71"/>
-      <c r="N254" s="71"/>
-      <c r="O254" s="71"/>
-      <c r="P254" s="71"/>
-      <c r="Q254" s="71"/>
-      <c r="R254" s="71"/>
-      <c r="S254" s="71"/>
-      <c r="T254" s="71"/>
-      <c r="U254" s="72"/>
+      <c r="B254" s="63"/>
+      <c r="C254" s="63"/>
+      <c r="D254" s="63"/>
+      <c r="E254" s="63"/>
+      <c r="F254" s="63"/>
+      <c r="G254" s="63"/>
+      <c r="H254" s="63"/>
+      <c r="I254" s="63"/>
+      <c r="J254" s="63"/>
+      <c r="K254" s="63"/>
+      <c r="L254" s="63"/>
+      <c r="M254" s="63"/>
+      <c r="N254" s="63"/>
+      <c r="O254" s="63"/>
+      <c r="P254" s="63"/>
+      <c r="Q254" s="63"/>
+      <c r="R254" s="63"/>
+      <c r="S254" s="63"/>
+      <c r="T254" s="63"/>
+      <c r="U254" s="64"/>
     </row>
     <row r="255" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="27"/>
@@ -17602,20 +17605,20 @@
       <c r="E255" s="28"/>
       <c r="F255" s="28"/>
       <c r="G255" s="28"/>
-      <c r="H255" s="68"/>
-      <c r="I255" s="76"/>
-      <c r="J255" s="76"/>
-      <c r="K255" s="76"/>
-      <c r="L255" s="76"/>
-      <c r="M255" s="76"/>
-      <c r="N255" s="76"/>
-      <c r="O255" s="76"/>
-      <c r="P255" s="76"/>
-      <c r="Q255" s="76"/>
-      <c r="R255" s="76"/>
-      <c r="S255" s="76"/>
-      <c r="T255" s="76"/>
-      <c r="U255" s="69"/>
+      <c r="H255" s="56"/>
+      <c r="I255" s="57"/>
+      <c r="J255" s="57"/>
+      <c r="K255" s="57"/>
+      <c r="L255" s="57"/>
+      <c r="M255" s="57"/>
+      <c r="N255" s="57"/>
+      <c r="O255" s="57"/>
+      <c r="P255" s="57"/>
+      <c r="Q255" s="57"/>
+      <c r="R255" s="57"/>
+      <c r="S255" s="57"/>
+      <c r="T255" s="57"/>
+      <c r="U255" s="58"/>
     </row>
     <row r="256" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="27"/>
@@ -17631,20 +17634,20 @@
       <c r="E256" s="28"/>
       <c r="F256" s="28"/>
       <c r="G256" s="28"/>
-      <c r="H256" s="68"/>
-      <c r="I256" s="76"/>
-      <c r="J256" s="76"/>
-      <c r="K256" s="76"/>
-      <c r="L256" s="76"/>
-      <c r="M256" s="76"/>
-      <c r="N256" s="76"/>
-      <c r="O256" s="76"/>
-      <c r="P256" s="76"/>
-      <c r="Q256" s="76"/>
-      <c r="R256" s="76"/>
-      <c r="S256" s="76"/>
-      <c r="T256" s="76"/>
-      <c r="U256" s="69"/>
+      <c r="H256" s="56"/>
+      <c r="I256" s="57"/>
+      <c r="J256" s="57"/>
+      <c r="K256" s="57"/>
+      <c r="L256" s="57"/>
+      <c r="M256" s="57"/>
+      <c r="N256" s="57"/>
+      <c r="O256" s="57"/>
+      <c r="P256" s="57"/>
+      <c r="Q256" s="57"/>
+      <c r="R256" s="57"/>
+      <c r="S256" s="57"/>
+      <c r="T256" s="57"/>
+      <c r="U256" s="58"/>
     </row>
     <row r="257" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A257" s="27"/>
@@ -17660,20 +17663,20 @@
       <c r="E257" s="28"/>
       <c r="F257" s="28"/>
       <c r="G257" s="28"/>
-      <c r="H257" s="68"/>
-      <c r="I257" s="76"/>
-      <c r="J257" s="76"/>
-      <c r="K257" s="76"/>
-      <c r="L257" s="76"/>
-      <c r="M257" s="76"/>
-      <c r="N257" s="76"/>
-      <c r="O257" s="76"/>
-      <c r="P257" s="76"/>
-      <c r="Q257" s="76"/>
-      <c r="R257" s="76"/>
-      <c r="S257" s="76"/>
-      <c r="T257" s="76"/>
-      <c r="U257" s="69"/>
+      <c r="H257" s="56"/>
+      <c r="I257" s="57"/>
+      <c r="J257" s="57"/>
+      <c r="K257" s="57"/>
+      <c r="L257" s="57"/>
+      <c r="M257" s="57"/>
+      <c r="N257" s="57"/>
+      <c r="O257" s="57"/>
+      <c r="P257" s="57"/>
+      <c r="Q257" s="57"/>
+      <c r="R257" s="57"/>
+      <c r="S257" s="57"/>
+      <c r="T257" s="57"/>
+      <c r="U257" s="58"/>
     </row>
     <row r="258" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="27"/>
@@ -17689,20 +17692,20 @@
       <c r="E258" s="28"/>
       <c r="F258" s="28"/>
       <c r="G258" s="28"/>
-      <c r="H258" s="68"/>
-      <c r="I258" s="76"/>
-      <c r="J258" s="76"/>
-      <c r="K258" s="76"/>
-      <c r="L258" s="76"/>
-      <c r="M258" s="76"/>
-      <c r="N258" s="76"/>
-      <c r="O258" s="76"/>
-      <c r="P258" s="76"/>
-      <c r="Q258" s="76"/>
-      <c r="R258" s="76"/>
-      <c r="S258" s="76"/>
-      <c r="T258" s="76"/>
-      <c r="U258" s="69"/>
+      <c r="H258" s="56"/>
+      <c r="I258" s="57"/>
+      <c r="J258" s="57"/>
+      <c r="K258" s="57"/>
+      <c r="L258" s="57"/>
+      <c r="M258" s="57"/>
+      <c r="N258" s="57"/>
+      <c r="O258" s="57"/>
+      <c r="P258" s="57"/>
+      <c r="Q258" s="57"/>
+      <c r="R258" s="57"/>
+      <c r="S258" s="57"/>
+      <c r="T258" s="57"/>
+      <c r="U258" s="58"/>
     </row>
     <row r="259" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="27"/>
@@ -17718,20 +17721,20 @@
       <c r="E259" s="28"/>
       <c r="F259" s="28"/>
       <c r="G259" s="28"/>
-      <c r="H259" s="68"/>
-      <c r="I259" s="76"/>
-      <c r="J259" s="76"/>
-      <c r="K259" s="76"/>
-      <c r="L259" s="76"/>
-      <c r="M259" s="76"/>
-      <c r="N259" s="76"/>
-      <c r="O259" s="76"/>
-      <c r="P259" s="76"/>
-      <c r="Q259" s="76"/>
-      <c r="R259" s="76"/>
-      <c r="S259" s="76"/>
-      <c r="T259" s="76"/>
-      <c r="U259" s="69"/>
+      <c r="H259" s="56"/>
+      <c r="I259" s="57"/>
+      <c r="J259" s="57"/>
+      <c r="K259" s="57"/>
+      <c r="L259" s="57"/>
+      <c r="M259" s="57"/>
+      <c r="N259" s="57"/>
+      <c r="O259" s="57"/>
+      <c r="P259" s="57"/>
+      <c r="Q259" s="57"/>
+      <c r="R259" s="57"/>
+      <c r="S259" s="57"/>
+      <c r="T259" s="57"/>
+      <c r="U259" s="58"/>
     </row>
     <row r="260" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A260" s="27"/>
@@ -17747,20 +17750,20 @@
       <c r="E260" s="28"/>
       <c r="F260" s="28"/>
       <c r="G260" s="28"/>
-      <c r="H260" s="68"/>
-      <c r="I260" s="76"/>
-      <c r="J260" s="76"/>
-      <c r="K260" s="76"/>
-      <c r="L260" s="76"/>
-      <c r="M260" s="76"/>
-      <c r="N260" s="76"/>
-      <c r="O260" s="76"/>
-      <c r="P260" s="76"/>
-      <c r="Q260" s="76"/>
-      <c r="R260" s="76"/>
-      <c r="S260" s="76"/>
-      <c r="T260" s="76"/>
-      <c r="U260" s="69"/>
+      <c r="H260" s="56"/>
+      <c r="I260" s="57"/>
+      <c r="J260" s="57"/>
+      <c r="K260" s="57"/>
+      <c r="L260" s="57"/>
+      <c r="M260" s="57"/>
+      <c r="N260" s="57"/>
+      <c r="O260" s="57"/>
+      <c r="P260" s="57"/>
+      <c r="Q260" s="57"/>
+      <c r="R260" s="57"/>
+      <c r="S260" s="57"/>
+      <c r="T260" s="57"/>
+      <c r="U260" s="58"/>
     </row>
     <row r="261" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A261" s="27"/>
@@ -17776,20 +17779,20 @@
       <c r="E261" s="28"/>
       <c r="F261" s="28"/>
       <c r="G261" s="28"/>
-      <c r="H261" s="68"/>
-      <c r="I261" s="76"/>
-      <c r="J261" s="76"/>
-      <c r="K261" s="76"/>
-      <c r="L261" s="76"/>
-      <c r="M261" s="76"/>
-      <c r="N261" s="76"/>
-      <c r="O261" s="76"/>
-      <c r="P261" s="76"/>
-      <c r="Q261" s="76"/>
-      <c r="R261" s="76"/>
-      <c r="S261" s="76"/>
-      <c r="T261" s="76"/>
-      <c r="U261" s="69"/>
+      <c r="H261" s="56"/>
+      <c r="I261" s="57"/>
+      <c r="J261" s="57"/>
+      <c r="K261" s="57"/>
+      <c r="L261" s="57"/>
+      <c r="M261" s="57"/>
+      <c r="N261" s="57"/>
+      <c r="O261" s="57"/>
+      <c r="P261" s="57"/>
+      <c r="Q261" s="57"/>
+      <c r="R261" s="57"/>
+      <c r="S261" s="57"/>
+      <c r="T261" s="57"/>
+      <c r="U261" s="58"/>
     </row>
     <row r="262" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="27"/>
@@ -17805,20 +17808,20 @@
       <c r="E262" s="28"/>
       <c r="F262" s="28"/>
       <c r="G262" s="28"/>
-      <c r="H262" s="68"/>
-      <c r="I262" s="76"/>
-      <c r="J262" s="76"/>
-      <c r="K262" s="76"/>
-      <c r="L262" s="76"/>
-      <c r="M262" s="76"/>
-      <c r="N262" s="76"/>
-      <c r="O262" s="76"/>
-      <c r="P262" s="76"/>
-      <c r="Q262" s="76"/>
-      <c r="R262" s="76"/>
-      <c r="S262" s="76"/>
-      <c r="T262" s="76"/>
-      <c r="U262" s="69"/>
+      <c r="H262" s="56"/>
+      <c r="I262" s="57"/>
+      <c r="J262" s="57"/>
+      <c r="K262" s="57"/>
+      <c r="L262" s="57"/>
+      <c r="M262" s="57"/>
+      <c r="N262" s="57"/>
+      <c r="O262" s="57"/>
+      <c r="P262" s="57"/>
+      <c r="Q262" s="57"/>
+      <c r="R262" s="57"/>
+      <c r="S262" s="57"/>
+      <c r="T262" s="57"/>
+      <c r="U262" s="58"/>
     </row>
     <row r="263" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="27"/>
@@ -17834,20 +17837,20 @@
       <c r="E263" s="28"/>
       <c r="F263" s="28"/>
       <c r="G263" s="28"/>
-      <c r="H263" s="68"/>
-      <c r="I263" s="76"/>
-      <c r="J263" s="76"/>
-      <c r="K263" s="76"/>
-      <c r="L263" s="76"/>
-      <c r="M263" s="76"/>
-      <c r="N263" s="76"/>
-      <c r="O263" s="76"/>
-      <c r="P263" s="76"/>
-      <c r="Q263" s="76"/>
-      <c r="R263" s="76"/>
-      <c r="S263" s="76"/>
-      <c r="T263" s="76"/>
-      <c r="U263" s="69"/>
+      <c r="H263" s="56"/>
+      <c r="I263" s="57"/>
+      <c r="J263" s="57"/>
+      <c r="K263" s="57"/>
+      <c r="L263" s="57"/>
+      <c r="M263" s="57"/>
+      <c r="N263" s="57"/>
+      <c r="O263" s="57"/>
+      <c r="P263" s="57"/>
+      <c r="Q263" s="57"/>
+      <c r="R263" s="57"/>
+      <c r="S263" s="57"/>
+      <c r="T263" s="57"/>
+      <c r="U263" s="58"/>
     </row>
     <row r="264" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A264" s="27"/>
@@ -17863,20 +17866,20 @@
       <c r="E264" s="28"/>
       <c r="F264" s="28"/>
       <c r="G264" s="28"/>
-      <c r="H264" s="68"/>
-      <c r="I264" s="76"/>
-      <c r="J264" s="76"/>
-      <c r="K264" s="76"/>
-      <c r="L264" s="76"/>
-      <c r="M264" s="76"/>
-      <c r="N264" s="76"/>
-      <c r="O264" s="76"/>
-      <c r="P264" s="76"/>
-      <c r="Q264" s="76"/>
-      <c r="R264" s="76"/>
-      <c r="S264" s="76"/>
-      <c r="T264" s="76"/>
-      <c r="U264" s="69"/>
+      <c r="H264" s="56"/>
+      <c r="I264" s="57"/>
+      <c r="J264" s="57"/>
+      <c r="K264" s="57"/>
+      <c r="L264" s="57"/>
+      <c r="M264" s="57"/>
+      <c r="N264" s="57"/>
+      <c r="O264" s="57"/>
+      <c r="P264" s="57"/>
+      <c r="Q264" s="57"/>
+      <c r="R264" s="57"/>
+      <c r="S264" s="57"/>
+      <c r="T264" s="57"/>
+      <c r="U264" s="58"/>
     </row>
     <row r="265" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A265" s="27"/>
@@ -17892,20 +17895,20 @@
       <c r="E265" s="28"/>
       <c r="F265" s="28"/>
       <c r="G265" s="28"/>
-      <c r="H265" s="68"/>
-      <c r="I265" s="76"/>
-      <c r="J265" s="76"/>
-      <c r="K265" s="76"/>
-      <c r="L265" s="76"/>
-      <c r="M265" s="76"/>
-      <c r="N265" s="76"/>
-      <c r="O265" s="76"/>
-      <c r="P265" s="76"/>
-      <c r="Q265" s="76"/>
-      <c r="R265" s="76"/>
-      <c r="S265" s="76"/>
-      <c r="T265" s="76"/>
-      <c r="U265" s="69"/>
+      <c r="H265" s="56"/>
+      <c r="I265" s="57"/>
+      <c r="J265" s="57"/>
+      <c r="K265" s="57"/>
+      <c r="L265" s="57"/>
+      <c r="M265" s="57"/>
+      <c r="N265" s="57"/>
+      <c r="O265" s="57"/>
+      <c r="P265" s="57"/>
+      <c r="Q265" s="57"/>
+      <c r="R265" s="57"/>
+      <c r="S265" s="57"/>
+      <c r="T265" s="57"/>
+      <c r="U265" s="58"/>
     </row>
     <row r="266" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A266" s="27"/>
@@ -17921,20 +17924,20 @@
       <c r="E266" s="28"/>
       <c r="F266" s="28"/>
       <c r="G266" s="28"/>
-      <c r="H266" s="68"/>
-      <c r="I266" s="76"/>
-      <c r="J266" s="76"/>
-      <c r="K266" s="76"/>
-      <c r="L266" s="76"/>
-      <c r="M266" s="76"/>
-      <c r="N266" s="76"/>
-      <c r="O266" s="76"/>
-      <c r="P266" s="76"/>
-      <c r="Q266" s="76"/>
-      <c r="R266" s="76"/>
-      <c r="S266" s="76"/>
-      <c r="T266" s="76"/>
-      <c r="U266" s="69"/>
+      <c r="H266" s="56"/>
+      <c r="I266" s="57"/>
+      <c r="J266" s="57"/>
+      <c r="K266" s="57"/>
+      <c r="L266" s="57"/>
+      <c r="M266" s="57"/>
+      <c r="N266" s="57"/>
+      <c r="O266" s="57"/>
+      <c r="P266" s="57"/>
+      <c r="Q266" s="57"/>
+      <c r="R266" s="57"/>
+      <c r="S266" s="57"/>
+      <c r="T266" s="57"/>
+      <c r="U266" s="58"/>
     </row>
     <row r="267" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="27"/>
@@ -17950,20 +17953,20 @@
       <c r="E267" s="28"/>
       <c r="F267" s="28"/>
       <c r="G267" s="28"/>
-      <c r="H267" s="68"/>
-      <c r="I267" s="76"/>
-      <c r="J267" s="76"/>
-      <c r="K267" s="76"/>
-      <c r="L267" s="76"/>
-      <c r="M267" s="76"/>
-      <c r="N267" s="76"/>
-      <c r="O267" s="76"/>
-      <c r="P267" s="76"/>
-      <c r="Q267" s="76"/>
-      <c r="R267" s="76"/>
-      <c r="S267" s="76"/>
-      <c r="T267" s="76"/>
-      <c r="U267" s="69"/>
+      <c r="H267" s="56"/>
+      <c r="I267" s="57"/>
+      <c r="J267" s="57"/>
+      <c r="K267" s="57"/>
+      <c r="L267" s="57"/>
+      <c r="M267" s="57"/>
+      <c r="N267" s="57"/>
+      <c r="O267" s="57"/>
+      <c r="P267" s="57"/>
+      <c r="Q267" s="57"/>
+      <c r="R267" s="57"/>
+      <c r="S267" s="57"/>
+      <c r="T267" s="57"/>
+      <c r="U267" s="58"/>
     </row>
     <row r="268" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="27"/>
@@ -17979,22 +17982,22 @@
       <c r="E268" s="28"/>
       <c r="F268" s="28"/>
       <c r="G268" s="28"/>
-      <c r="H268" s="68" t="s">
+      <c r="H268" s="56" t="s">
         <v>1092</v>
       </c>
-      <c r="I268" s="76"/>
-      <c r="J268" s="76"/>
-      <c r="K268" s="76"/>
-      <c r="L268" s="76"/>
-      <c r="M268" s="76"/>
-      <c r="N268" s="76"/>
-      <c r="O268" s="76"/>
-      <c r="P268" s="76"/>
-      <c r="Q268" s="76"/>
-      <c r="R268" s="76"/>
-      <c r="S268" s="76"/>
-      <c r="T268" s="76"/>
-      <c r="U268" s="69"/>
+      <c r="I268" s="57"/>
+      <c r="J268" s="57"/>
+      <c r="K268" s="57"/>
+      <c r="L268" s="57"/>
+      <c r="M268" s="57"/>
+      <c r="N268" s="57"/>
+      <c r="O268" s="57"/>
+      <c r="P268" s="57"/>
+      <c r="Q268" s="57"/>
+      <c r="R268" s="57"/>
+      <c r="S268" s="57"/>
+      <c r="T268" s="57"/>
+      <c r="U268" s="58"/>
     </row>
     <row r="269" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="27"/>
@@ -18010,20 +18013,20 @@
       <c r="E269" s="28"/>
       <c r="F269" s="28"/>
       <c r="G269" s="28"/>
-      <c r="H269" s="68"/>
-      <c r="I269" s="76"/>
-      <c r="J269" s="76"/>
-      <c r="K269" s="76"/>
-      <c r="L269" s="76"/>
-      <c r="M269" s="76"/>
-      <c r="N269" s="76"/>
-      <c r="O269" s="76"/>
-      <c r="P269" s="76"/>
-      <c r="Q269" s="76"/>
-      <c r="R269" s="76"/>
-      <c r="S269" s="76"/>
-      <c r="T269" s="76"/>
-      <c r="U269" s="69"/>
+      <c r="H269" s="56"/>
+      <c r="I269" s="57"/>
+      <c r="J269" s="57"/>
+      <c r="K269" s="57"/>
+      <c r="L269" s="57"/>
+      <c r="M269" s="57"/>
+      <c r="N269" s="57"/>
+      <c r="O269" s="57"/>
+      <c r="P269" s="57"/>
+      <c r="Q269" s="57"/>
+      <c r="R269" s="57"/>
+      <c r="S269" s="57"/>
+      <c r="T269" s="57"/>
+      <c r="U269" s="58"/>
     </row>
     <row r="270" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A270" s="27"/>
@@ -18037,20 +18040,20 @@
       <c r="E270" s="28"/>
       <c r="F270" s="28"/>
       <c r="G270" s="28"/>
-      <c r="H270" s="68"/>
-      <c r="I270" s="76"/>
-      <c r="J270" s="76"/>
-      <c r="K270" s="76"/>
-      <c r="L270" s="76"/>
-      <c r="M270" s="76"/>
-      <c r="N270" s="76"/>
-      <c r="O270" s="76"/>
-      <c r="P270" s="76"/>
-      <c r="Q270" s="76"/>
-      <c r="R270" s="76"/>
-      <c r="S270" s="76"/>
-      <c r="T270" s="76"/>
-      <c r="U270" s="69"/>
+      <c r="H270" s="56"/>
+      <c r="I270" s="57"/>
+      <c r="J270" s="57"/>
+      <c r="K270" s="57"/>
+      <c r="L270" s="57"/>
+      <c r="M270" s="57"/>
+      <c r="N270" s="57"/>
+      <c r="O270" s="57"/>
+      <c r="P270" s="57"/>
+      <c r="Q270" s="57"/>
+      <c r="R270" s="57"/>
+      <c r="S270" s="57"/>
+      <c r="T270" s="57"/>
+      <c r="U270" s="58"/>
     </row>
     <row r="271" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="27"/>
@@ -18064,20 +18067,20 @@
       <c r="E271" s="28"/>
       <c r="F271" s="28"/>
       <c r="G271" s="28"/>
-      <c r="H271" s="68"/>
-      <c r="I271" s="76"/>
-      <c r="J271" s="76"/>
-      <c r="K271" s="76"/>
-      <c r="L271" s="76"/>
-      <c r="M271" s="76"/>
-      <c r="N271" s="76"/>
-      <c r="O271" s="76"/>
-      <c r="P271" s="76"/>
-      <c r="Q271" s="76"/>
-      <c r="R271" s="76"/>
-      <c r="S271" s="76"/>
-      <c r="T271" s="76"/>
-      <c r="U271" s="69"/>
+      <c r="H271" s="56"/>
+      <c r="I271" s="57"/>
+      <c r="J271" s="57"/>
+      <c r="K271" s="57"/>
+      <c r="L271" s="57"/>
+      <c r="M271" s="57"/>
+      <c r="N271" s="57"/>
+      <c r="O271" s="57"/>
+      <c r="P271" s="57"/>
+      <c r="Q271" s="57"/>
+      <c r="R271" s="57"/>
+      <c r="S271" s="57"/>
+      <c r="T271" s="57"/>
+      <c r="U271" s="58"/>
     </row>
     <row r="272" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="27"/>
@@ -18091,73 +18094,25 @@
       <c r="E272" s="28"/>
       <c r="F272" s="28"/>
       <c r="G272" s="28"/>
-      <c r="H272" s="68"/>
-      <c r="I272" s="76"/>
-      <c r="J272" s="76"/>
-      <c r="K272" s="76"/>
-      <c r="L272" s="76"/>
-      <c r="M272" s="76"/>
-      <c r="N272" s="76"/>
-      <c r="O272" s="76"/>
-      <c r="P272" s="76"/>
-      <c r="Q272" s="76"/>
-      <c r="R272" s="76"/>
-      <c r="S272" s="76"/>
-      <c r="T272" s="76"/>
-      <c r="U272" s="69"/>
+      <c r="H272" s="56"/>
+      <c r="I272" s="57"/>
+      <c r="J272" s="57"/>
+      <c r="K272" s="57"/>
+      <c r="L272" s="57"/>
+      <c r="M272" s="57"/>
+      <c r="N272" s="57"/>
+      <c r="O272" s="57"/>
+      <c r="P272" s="57"/>
+      <c r="Q272" s="57"/>
+      <c r="R272" s="57"/>
+      <c r="S272" s="57"/>
+      <c r="T272" s="57"/>
+      <c r="U272" s="58"/>
     </row>
   </sheetData>
   <sheetProtection password="C644" sheet="1" formatColumns="0" autoFilter="0"/>
   <autoFilter ref="A7:U7"/>
   <mergeCells count="64">
-    <mergeCell ref="H270:U270"/>
-    <mergeCell ref="H271:U271"/>
-    <mergeCell ref="H272:U272"/>
-    <mergeCell ref="H265:U265"/>
-    <mergeCell ref="H266:U266"/>
-    <mergeCell ref="H267:U267"/>
-    <mergeCell ref="H268:U268"/>
-    <mergeCell ref="H269:U269"/>
-    <mergeCell ref="H260:U260"/>
-    <mergeCell ref="H261:U261"/>
-    <mergeCell ref="H262:U262"/>
-    <mergeCell ref="H263:U263"/>
-    <mergeCell ref="H264:U264"/>
-    <mergeCell ref="H255:U255"/>
-    <mergeCell ref="H256:U256"/>
-    <mergeCell ref="H257:U257"/>
-    <mergeCell ref="H258:U258"/>
-    <mergeCell ref="H259:U259"/>
-    <mergeCell ref="C164:I164"/>
-    <mergeCell ref="C184:I184"/>
-    <mergeCell ref="C203:I203"/>
-    <mergeCell ref="C248:I248"/>
-    <mergeCell ref="A254:U254"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C119:I119"/>
-    <mergeCell ref="C122:I122"/>
-    <mergeCell ref="C123:I123"/>
-    <mergeCell ref="C163:I163"/>
-    <mergeCell ref="C21:I21"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:R7"/>
     <mergeCell ref="A2:U2"/>
     <mergeCell ref="A3:U3"/>
     <mergeCell ref="A4:U4"/>
@@ -18174,6 +18129,54 @@
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="I5:I7"/>
     <mergeCell ref="J6:K6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C119:I119"/>
+    <mergeCell ref="C122:I122"/>
+    <mergeCell ref="C123:I123"/>
+    <mergeCell ref="C163:I163"/>
+    <mergeCell ref="C164:I164"/>
+    <mergeCell ref="C184:I184"/>
+    <mergeCell ref="C203:I203"/>
+    <mergeCell ref="C248:I248"/>
+    <mergeCell ref="A254:U254"/>
+    <mergeCell ref="H255:U255"/>
+    <mergeCell ref="H256:U256"/>
+    <mergeCell ref="H257:U257"/>
+    <mergeCell ref="H258:U258"/>
+    <mergeCell ref="H259:U259"/>
+    <mergeCell ref="H260:U260"/>
+    <mergeCell ref="H261:U261"/>
+    <mergeCell ref="H262:U262"/>
+    <mergeCell ref="H263:U263"/>
+    <mergeCell ref="H264:U264"/>
+    <mergeCell ref="H270:U270"/>
+    <mergeCell ref="H271:U271"/>
+    <mergeCell ref="H272:U272"/>
+    <mergeCell ref="H265:U265"/>
+    <mergeCell ref="H266:U266"/>
+    <mergeCell ref="H267:U267"/>
+    <mergeCell ref="H268:U268"/>
+    <mergeCell ref="H269:U269"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18265,79 +18268,79 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="56"/>
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
-      <c r="U2" s="56"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
+      <c r="P3" s="68"/>
+      <c r="Q3" s="68"/>
+      <c r="R3" s="68"/>
+      <c r="S3" s="68"/>
+      <c r="T3" s="68"/>
+      <c r="U3" s="68"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="58" t="s">
+      <c r="A4" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="58"/>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="58"/>
-      <c r="S4" s="58"/>
-      <c r="T4" s="58"/>
-      <c r="U4" s="58"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="69"/>
+      <c r="Q4" s="69"/>
+      <c r="R4" s="69"/>
+      <c r="S4" s="69"/>
+      <c r="T4" s="69"/>
+      <c r="U4" s="69"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="65" t="s">
@@ -18367,115 +18370,115 @@
       <c r="I5" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="59" t="s">
+      <c r="J5" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="61"/>
-      <c r="P5" s="62" t="s">
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="72"/>
+      <c r="P5" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="64"/>
-      <c r="S5" s="62" t="s">
+      <c r="Q5" s="74"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="63"/>
-      <c r="U5" s="64"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="75"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="68" t="s">
+      <c r="A6" s="76"/>
+      <c r="B6" s="76"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="69"/>
+      <c r="K6" s="58"/>
       <c r="L6" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="68" t="s">
+      <c r="M6" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="69"/>
+      <c r="N6" s="58"/>
       <c r="O6" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="69"/>
+      <c r="Q6" s="58"/>
       <c r="R6" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="S6" s="68" t="s">
+      <c r="S6" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="69"/>
+      <c r="T6" s="58"/>
       <c r="U6" s="65" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="67"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
+      <c r="A7" s="66"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
       <c r="J7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="67"/>
+      <c r="L7" s="66"/>
       <c r="M7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="67"/>
+      <c r="O7" s="66"/>
       <c r="P7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="67"/>
+      <c r="R7" s="66"/>
       <c r="S7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="U7" s="67"/>
+      <c r="U7" s="66"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="70" t="s">
+      <c r="A8" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="72"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="64"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -18517,15 +18520,15 @@
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="73" t="s">
+      <c r="C9" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="75"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="61"/>
       <c r="M9" s="6">
         <f>SUM(M10,M20)</f>
         <v>18303819.899999999</v>
@@ -18561,15 +18564,15 @@
       <c r="B10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="73" t="s">
+      <c r="C10" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="75"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="61"/>
       <c r="M10" s="6">
         <f t="shared" ref="M10:O14" si="0">SUM(M11)</f>
         <v>126283.29</v>
@@ -18605,15 +18608,15 @@
       <c r="B11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="73" t="s">
+      <c r="C11" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="75"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="61"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18649,15 +18652,15 @@
       <c r="B12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="C12" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="75"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="61"/>
       <c r="M12" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18693,15 +18696,15 @@
       <c r="B13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="73" t="s">
+      <c r="C13" s="59" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="75"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="61"/>
       <c r="M13" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18737,15 +18740,15 @@
       <c r="B14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="73" t="s">
+      <c r="C14" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="75"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="61"/>
       <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -19036,15 +19039,15 @@
       <c r="B20" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="73" t="s">
+      <c r="C20" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="75"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="61"/>
       <c r="M20" s="6">
         <f t="shared" ref="M20:O21" si="1">SUM(M21)</f>
         <v>18177536.609999999</v>
@@ -19080,15 +19083,15 @@
       <c r="B21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="73" t="s">
+      <c r="C21" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="74"/>
-      <c r="E21" s="74"/>
-      <c r="F21" s="74"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="75"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="61"/>
       <c r="M21" s="6">
         <f t="shared" si="1"/>
         <v>18177536.609999999</v>
@@ -19124,15 +19127,15 @@
       <c r="B22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="73" t="s">
+      <c r="C22" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="74"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="75"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="61"/>
       <c r="M22" s="6">
         <f>SUM(M23,M122,M163,M203,M248)</f>
         <v>18177536.609999999</v>
@@ -19168,15 +19171,15 @@
       <c r="B23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="73" t="s">
+      <c r="C23" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="74"/>
-      <c r="E23" s="74"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="74"/>
-      <c r="I23" s="75"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="61"/>
       <c r="M23" s="6">
         <f>SUM(M24,M67,M76,M119)</f>
         <v>12831032.07</v>
@@ -19212,15 +19215,15 @@
       <c r="B24" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="73" t="s">
+      <c r="C24" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="74"/>
-      <c r="I24" s="75"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="61"/>
       <c r="M24" s="6">
         <f>SUM(M25,M29,M31,M34,M36,M41,M46,M51,M57,M62)</f>
         <v>7808423.3099999996</v>
@@ -19249,7 +19252,7 @@
         <v>16983851</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>100</v>
       </c>
@@ -21449,15 +21452,15 @@
       <c r="B67" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="73" t="s">
+      <c r="C67" s="59" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="74"/>
-      <c r="E67" s="74"/>
-      <c r="F67" s="74"/>
-      <c r="G67" s="74"/>
-      <c r="H67" s="74"/>
-      <c r="I67" s="75"/>
+      <c r="D67" s="60"/>
+      <c r="E67" s="60"/>
+      <c r="F67" s="60"/>
+      <c r="G67" s="60"/>
+      <c r="H67" s="60"/>
+      <c r="I67" s="61"/>
       <c r="M67" s="6">
         <f>SUM(M68,M72,M74)</f>
         <v>748533.11</v>
@@ -21957,15 +21960,15 @@
       <c r="B76" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C76" s="73" t="s">
+      <c r="C76" s="59" t="s">
         <v>325</v>
       </c>
-      <c r="D76" s="74"/>
-      <c r="E76" s="74"/>
-      <c r="F76" s="74"/>
-      <c r="G76" s="74"/>
-      <c r="H76" s="74"/>
-      <c r="I76" s="75"/>
+      <c r="D76" s="60"/>
+      <c r="E76" s="60"/>
+      <c r="F76" s="60"/>
+      <c r="G76" s="60"/>
+      <c r="H76" s="60"/>
+      <c r="I76" s="61"/>
       <c r="M76" s="6">
         <f>SUM(M77,M82,M87,M93,M96,M99,M104,M109,M114,M117)</f>
         <v>3831185.6499999994</v>
@@ -21994,7 +21997,7 @@
         <v>17000002</v>
       </c>
     </row>
-    <row r="77" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="s">
         <v>326</v>
       </c>
@@ -22675,7 +22678,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="90" spans="1:35" ht="150" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" ht="131.25" x14ac:dyDescent="0.25">
       <c r="A90" s="9" t="s">
         <v>396</v>
       </c>
@@ -22720,7 +22723,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="91" spans="1:35" ht="150" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" ht="131.25" x14ac:dyDescent="0.25">
       <c r="A91" s="9" t="s">
         <v>402</v>
       </c>
@@ -23144,7 +23147,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="99" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A99" s="9" t="s">
         <v>441</v>
       </c>
@@ -23225,7 +23228,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="100" spans="1:35" ht="131.25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A100" s="9" t="s">
         <v>447</v>
       </c>
@@ -23401,7 +23404,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="104" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A104" s="9" t="s">
         <v>465</v>
       </c>
@@ -23656,7 +23659,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="109" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A109" s="9" t="s">
         <v>481</v>
       </c>
@@ -24163,7 +24166,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="118" spans="1:35" ht="150" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" ht="131.25" x14ac:dyDescent="0.25">
       <c r="A118" s="9" t="s">
         <v>518</v>
       </c>
@@ -24215,15 +24218,15 @@
       <c r="B119" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C119" s="73" t="s">
+      <c r="C119" s="59" t="s">
         <v>526</v>
       </c>
-      <c r="D119" s="74"/>
-      <c r="E119" s="74"/>
-      <c r="F119" s="74"/>
-      <c r="G119" s="74"/>
-      <c r="H119" s="74"/>
-      <c r="I119" s="75"/>
+      <c r="D119" s="60"/>
+      <c r="E119" s="60"/>
+      <c r="F119" s="60"/>
+      <c r="G119" s="60"/>
+      <c r="H119" s="60"/>
+      <c r="I119" s="61"/>
       <c r="M119" s="6">
         <f>SUM(M120)</f>
         <v>442890</v>
@@ -24633,7 +24636,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="127" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A127" s="9" t="s">
         <v>560</v>
       </c>
@@ -25400,7 +25403,9 @@
         <v>631</v>
       </c>
       <c r="D141" s="11"/>
-      <c r="E141" s="11"/>
+      <c r="E141" s="11" t="s">
+        <v>1105</v>
+      </c>
       <c r="F141" s="16" t="s">
         <v>110</v>
       </c>
@@ -25443,7 +25448,9 @@
         <v>120</v>
       </c>
       <c r="D142" s="11"/>
-      <c r="E142" s="11"/>
+      <c r="E142" s="11" t="s">
+        <v>1105</v>
+      </c>
       <c r="F142" s="16" t="s">
         <v>110</v>
       </c>
@@ -26529,15 +26536,15 @@
       <c r="B163" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C163" s="73" t="s">
+      <c r="C163" s="59" t="s">
         <v>710</v>
       </c>
-      <c r="D163" s="74"/>
-      <c r="E163" s="74"/>
-      <c r="F163" s="74"/>
-      <c r="G163" s="74"/>
-      <c r="H163" s="74"/>
-      <c r="I163" s="75"/>
+      <c r="D163" s="60"/>
+      <c r="E163" s="60"/>
+      <c r="F163" s="60"/>
+      <c r="G163" s="60"/>
+      <c r="H163" s="60"/>
+      <c r="I163" s="61"/>
       <c r="M163" s="6">
         <f>SUM(M164,M184)</f>
         <v>611422.71999999997</v>
@@ -26573,15 +26580,15 @@
       <c r="B164" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="C164" s="73" t="s">
+      <c r="C164" s="59" t="s">
         <v>713</v>
       </c>
-      <c r="D164" s="74"/>
-      <c r="E164" s="74"/>
-      <c r="F164" s="74"/>
-      <c r="G164" s="74"/>
-      <c r="H164" s="74"/>
-      <c r="I164" s="75"/>
+      <c r="D164" s="60"/>
+      <c r="E164" s="60"/>
+      <c r="F164" s="60"/>
+      <c r="G164" s="60"/>
+      <c r="H164" s="60"/>
+      <c r="I164" s="61"/>
       <c r="M164" s="6">
         <f>SUM(M165,M171,M174,M178,M182)</f>
         <v>415021.23999999993</v>
@@ -27628,15 +27635,15 @@
       <c r="B184" s="9" t="s">
         <v>789</v>
       </c>
-      <c r="C184" s="73" t="s">
+      <c r="C184" s="59" t="s">
         <v>790</v>
       </c>
-      <c r="D184" s="74"/>
-      <c r="E184" s="74"/>
-      <c r="F184" s="74"/>
-      <c r="G184" s="74"/>
-      <c r="H184" s="74"/>
-      <c r="I184" s="75"/>
+      <c r="D184" s="60"/>
+      <c r="E184" s="60"/>
+      <c r="F184" s="60"/>
+      <c r="G184" s="60"/>
+      <c r="H184" s="60"/>
+      <c r="I184" s="61"/>
       <c r="M184" s="6">
         <f>SUM(M185,M188,M191,M194,M197,M200)</f>
         <v>196401.48</v>
@@ -28686,15 +28693,15 @@
       <c r="B203" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="C203" s="73" t="s">
+      <c r="C203" s="59" t="s">
         <v>856</v>
       </c>
-      <c r="D203" s="74"/>
-      <c r="E203" s="74"/>
-      <c r="F203" s="74"/>
-      <c r="G203" s="74"/>
-      <c r="H203" s="74"/>
-      <c r="I203" s="75"/>
+      <c r="D203" s="60"/>
+      <c r="E203" s="60"/>
+      <c r="F203" s="60"/>
+      <c r="G203" s="60"/>
+      <c r="H203" s="60"/>
+      <c r="I203" s="61"/>
       <c r="M203" s="6">
         <f>SUM(M204,M206,M221,M236,M238,M240,M242,M243,M244,M245,M246,M247)</f>
         <v>719044.50999999989</v>
@@ -29102,7 +29109,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="211" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A211" s="9" t="s">
         <v>893</v>
       </c>
@@ -30045,7 +30052,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="232" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A232" s="9" t="s">
         <v>978</v>
       </c>
@@ -30550,7 +30557,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="241" spans="1:35" ht="300" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:35" ht="281.25" x14ac:dyDescent="0.25">
       <c r="A241" s="9" t="s">
         <v>1014</v>
       </c>
@@ -31076,15 +31083,15 @@
       <c r="B248" s="9" t="s">
         <v>1031</v>
       </c>
-      <c r="C248" s="73" t="s">
+      <c r="C248" s="59" t="s">
         <v>1032</v>
       </c>
-      <c r="D248" s="74"/>
-      <c r="E248" s="74"/>
-      <c r="F248" s="74"/>
-      <c r="G248" s="74"/>
-      <c r="H248" s="74"/>
-      <c r="I248" s="75"/>
+      <c r="D248" s="60"/>
+      <c r="E248" s="60"/>
+      <c r="F248" s="60"/>
+      <c r="G248" s="60"/>
+      <c r="H248" s="60"/>
+      <c r="I248" s="61"/>
       <c r="M248" s="6">
         <f>SUM(M249,M250,M251,M252)</f>
         <v>0</v>
@@ -31346,7 +31353,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="252" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A252" s="9" t="s">
         <v>1041</v>
       </c>
@@ -31471,29 +31478,29 @@
       </c>
     </row>
     <row r="254" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="70" t="s">
+      <c r="A254" s="62" t="s">
         <v>1050</v>
       </c>
-      <c r="B254" s="71"/>
-      <c r="C254" s="71"/>
-      <c r="D254" s="71"/>
-      <c r="E254" s="71"/>
-      <c r="F254" s="71"/>
-      <c r="G254" s="71"/>
-      <c r="H254" s="71"/>
-      <c r="I254" s="71"/>
-      <c r="J254" s="71"/>
-      <c r="K254" s="71"/>
-      <c r="L254" s="71"/>
-      <c r="M254" s="71"/>
-      <c r="N254" s="71"/>
-      <c r="O254" s="71"/>
-      <c r="P254" s="71"/>
-      <c r="Q254" s="71"/>
-      <c r="R254" s="71"/>
-      <c r="S254" s="71"/>
-      <c r="T254" s="71"/>
-      <c r="U254" s="72"/>
+      <c r="B254" s="63"/>
+      <c r="C254" s="63"/>
+      <c r="D254" s="63"/>
+      <c r="E254" s="63"/>
+      <c r="F254" s="63"/>
+      <c r="G254" s="63"/>
+      <c r="H254" s="63"/>
+      <c r="I254" s="63"/>
+      <c r="J254" s="63"/>
+      <c r="K254" s="63"/>
+      <c r="L254" s="63"/>
+      <c r="M254" s="63"/>
+      <c r="N254" s="63"/>
+      <c r="O254" s="63"/>
+      <c r="P254" s="63"/>
+      <c r="Q254" s="63"/>
+      <c r="R254" s="63"/>
+      <c r="S254" s="63"/>
+      <c r="T254" s="63"/>
+      <c r="U254" s="64"/>
     </row>
     <row r="255" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="27"/>
@@ -31509,20 +31516,20 @@
       <c r="E255" s="28"/>
       <c r="F255" s="28"/>
       <c r="G255" s="28"/>
-      <c r="H255" s="68"/>
-      <c r="I255" s="76"/>
-      <c r="J255" s="76"/>
-      <c r="K255" s="76"/>
-      <c r="L255" s="76"/>
-      <c r="M255" s="76"/>
-      <c r="N255" s="76"/>
-      <c r="O255" s="76"/>
-      <c r="P255" s="76"/>
-      <c r="Q255" s="76"/>
-      <c r="R255" s="76"/>
-      <c r="S255" s="76"/>
-      <c r="T255" s="76"/>
-      <c r="U255" s="69"/>
+      <c r="H255" s="56"/>
+      <c r="I255" s="57"/>
+      <c r="J255" s="57"/>
+      <c r="K255" s="57"/>
+      <c r="L255" s="57"/>
+      <c r="M255" s="57"/>
+      <c r="N255" s="57"/>
+      <c r="O255" s="57"/>
+      <c r="P255" s="57"/>
+      <c r="Q255" s="57"/>
+      <c r="R255" s="57"/>
+      <c r="S255" s="57"/>
+      <c r="T255" s="57"/>
+      <c r="U255" s="58"/>
     </row>
     <row r="256" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="27"/>
@@ -31538,20 +31545,20 @@
       <c r="E256" s="28"/>
       <c r="F256" s="28"/>
       <c r="G256" s="28"/>
-      <c r="H256" s="68"/>
-      <c r="I256" s="76"/>
-      <c r="J256" s="76"/>
-      <c r="K256" s="76"/>
-      <c r="L256" s="76"/>
-      <c r="M256" s="76"/>
-      <c r="N256" s="76"/>
-      <c r="O256" s="76"/>
-      <c r="P256" s="76"/>
-      <c r="Q256" s="76"/>
-      <c r="R256" s="76"/>
-      <c r="S256" s="76"/>
-      <c r="T256" s="76"/>
-      <c r="U256" s="69"/>
+      <c r="H256" s="56"/>
+      <c r="I256" s="57"/>
+      <c r="J256" s="57"/>
+      <c r="K256" s="57"/>
+      <c r="L256" s="57"/>
+      <c r="M256" s="57"/>
+      <c r="N256" s="57"/>
+      <c r="O256" s="57"/>
+      <c r="P256" s="57"/>
+      <c r="Q256" s="57"/>
+      <c r="R256" s="57"/>
+      <c r="S256" s="57"/>
+      <c r="T256" s="57"/>
+      <c r="U256" s="58"/>
     </row>
     <row r="257" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A257" s="27"/>
@@ -31567,20 +31574,20 @@
       <c r="E257" s="28"/>
       <c r="F257" s="28"/>
       <c r="G257" s="28"/>
-      <c r="H257" s="68"/>
-      <c r="I257" s="76"/>
-      <c r="J257" s="76"/>
-      <c r="K257" s="76"/>
-      <c r="L257" s="76"/>
-      <c r="M257" s="76"/>
-      <c r="N257" s="76"/>
-      <c r="O257" s="76"/>
-      <c r="P257" s="76"/>
-      <c r="Q257" s="76"/>
-      <c r="R257" s="76"/>
-      <c r="S257" s="76"/>
-      <c r="T257" s="76"/>
-      <c r="U257" s="69"/>
+      <c r="H257" s="56"/>
+      <c r="I257" s="57"/>
+      <c r="J257" s="57"/>
+      <c r="K257" s="57"/>
+      <c r="L257" s="57"/>
+      <c r="M257" s="57"/>
+      <c r="N257" s="57"/>
+      <c r="O257" s="57"/>
+      <c r="P257" s="57"/>
+      <c r="Q257" s="57"/>
+      <c r="R257" s="57"/>
+      <c r="S257" s="57"/>
+      <c r="T257" s="57"/>
+      <c r="U257" s="58"/>
     </row>
     <row r="258" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="27"/>
@@ -31596,20 +31603,20 @@
       <c r="E258" s="28"/>
       <c r="F258" s="28"/>
       <c r="G258" s="28"/>
-      <c r="H258" s="68"/>
-      <c r="I258" s="76"/>
-      <c r="J258" s="76"/>
-      <c r="K258" s="76"/>
-      <c r="L258" s="76"/>
-      <c r="M258" s="76"/>
-      <c r="N258" s="76"/>
-      <c r="O258" s="76"/>
-      <c r="P258" s="76"/>
-      <c r="Q258" s="76"/>
-      <c r="R258" s="76"/>
-      <c r="S258" s="76"/>
-      <c r="T258" s="76"/>
-      <c r="U258" s="69"/>
+      <c r="H258" s="56"/>
+      <c r="I258" s="57"/>
+      <c r="J258" s="57"/>
+      <c r="K258" s="57"/>
+      <c r="L258" s="57"/>
+      <c r="M258" s="57"/>
+      <c r="N258" s="57"/>
+      <c r="O258" s="57"/>
+      <c r="P258" s="57"/>
+      <c r="Q258" s="57"/>
+      <c r="R258" s="57"/>
+      <c r="S258" s="57"/>
+      <c r="T258" s="57"/>
+      <c r="U258" s="58"/>
     </row>
     <row r="259" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="27"/>
@@ -31625,20 +31632,20 @@
       <c r="E259" s="28"/>
       <c r="F259" s="28"/>
       <c r="G259" s="28"/>
-      <c r="H259" s="68"/>
-      <c r="I259" s="76"/>
-      <c r="J259" s="76"/>
-      <c r="K259" s="76"/>
-      <c r="L259" s="76"/>
-      <c r="M259" s="76"/>
-      <c r="N259" s="76"/>
-      <c r="O259" s="76"/>
-      <c r="P259" s="76"/>
-      <c r="Q259" s="76"/>
-      <c r="R259" s="76"/>
-      <c r="S259" s="76"/>
-      <c r="T259" s="76"/>
-      <c r="U259" s="69"/>
+      <c r="H259" s="56"/>
+      <c r="I259" s="57"/>
+      <c r="J259" s="57"/>
+      <c r="K259" s="57"/>
+      <c r="L259" s="57"/>
+      <c r="M259" s="57"/>
+      <c r="N259" s="57"/>
+      <c r="O259" s="57"/>
+      <c r="P259" s="57"/>
+      <c r="Q259" s="57"/>
+      <c r="R259" s="57"/>
+      <c r="S259" s="57"/>
+      <c r="T259" s="57"/>
+      <c r="U259" s="58"/>
     </row>
     <row r="260" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A260" s="27"/>
@@ -31654,20 +31661,20 @@
       <c r="E260" s="28"/>
       <c r="F260" s="28"/>
       <c r="G260" s="28"/>
-      <c r="H260" s="68"/>
-      <c r="I260" s="76"/>
-      <c r="J260" s="76"/>
-      <c r="K260" s="76"/>
-      <c r="L260" s="76"/>
-      <c r="M260" s="76"/>
-      <c r="N260" s="76"/>
-      <c r="O260" s="76"/>
-      <c r="P260" s="76"/>
-      <c r="Q260" s="76"/>
-      <c r="R260" s="76"/>
-      <c r="S260" s="76"/>
-      <c r="T260" s="76"/>
-      <c r="U260" s="69"/>
+      <c r="H260" s="56"/>
+      <c r="I260" s="57"/>
+      <c r="J260" s="57"/>
+      <c r="K260" s="57"/>
+      <c r="L260" s="57"/>
+      <c r="M260" s="57"/>
+      <c r="N260" s="57"/>
+      <c r="O260" s="57"/>
+      <c r="P260" s="57"/>
+      <c r="Q260" s="57"/>
+      <c r="R260" s="57"/>
+      <c r="S260" s="57"/>
+      <c r="T260" s="57"/>
+      <c r="U260" s="58"/>
     </row>
     <row r="261" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A261" s="27"/>
@@ -31683,22 +31690,22 @@
       <c r="E261" s="28"/>
       <c r="F261" s="28"/>
       <c r="G261" s="28"/>
-      <c r="H261" s="68"/>
-      <c r="I261" s="76"/>
-      <c r="J261" s="76"/>
-      <c r="K261" s="76"/>
-      <c r="L261" s="76"/>
-      <c r="M261" s="76"/>
-      <c r="N261" s="76"/>
-      <c r="O261" s="76"/>
-      <c r="P261" s="76"/>
-      <c r="Q261" s="76"/>
-      <c r="R261" s="76"/>
-      <c r="S261" s="76"/>
-      <c r="T261" s="76"/>
-      <c r="U261" s="69"/>
-    </row>
-    <row r="262" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="H261" s="56"/>
+      <c r="I261" s="57"/>
+      <c r="J261" s="57"/>
+      <c r="K261" s="57"/>
+      <c r="L261" s="57"/>
+      <c r="M261" s="57"/>
+      <c r="N261" s="57"/>
+      <c r="O261" s="57"/>
+      <c r="P261" s="57"/>
+      <c r="Q261" s="57"/>
+      <c r="R261" s="57"/>
+      <c r="S261" s="57"/>
+      <c r="T261" s="57"/>
+      <c r="U261" s="58"/>
+    </row>
+    <row r="262" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="27"/>
       <c r="B262" s="5" t="s">
         <v>1071</v>
@@ -31712,20 +31719,20 @@
       <c r="E262" s="28"/>
       <c r="F262" s="28"/>
       <c r="G262" s="28"/>
-      <c r="H262" s="68"/>
-      <c r="I262" s="76"/>
-      <c r="J262" s="76"/>
-      <c r="K262" s="76"/>
-      <c r="L262" s="76"/>
-      <c r="M262" s="76"/>
-      <c r="N262" s="76"/>
-      <c r="O262" s="76"/>
-      <c r="P262" s="76"/>
-      <c r="Q262" s="76"/>
-      <c r="R262" s="76"/>
-      <c r="S262" s="76"/>
-      <c r="T262" s="76"/>
-      <c r="U262" s="69"/>
+      <c r="H262" s="56"/>
+      <c r="I262" s="57"/>
+      <c r="J262" s="57"/>
+      <c r="K262" s="57"/>
+      <c r="L262" s="57"/>
+      <c r="M262" s="57"/>
+      <c r="N262" s="57"/>
+      <c r="O262" s="57"/>
+      <c r="P262" s="57"/>
+      <c r="Q262" s="57"/>
+      <c r="R262" s="57"/>
+      <c r="S262" s="57"/>
+      <c r="T262" s="57"/>
+      <c r="U262" s="58"/>
     </row>
     <row r="263" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="27"/>
@@ -31741,20 +31748,20 @@
       <c r="E263" s="28"/>
       <c r="F263" s="28"/>
       <c r="G263" s="28"/>
-      <c r="H263" s="68"/>
-      <c r="I263" s="76"/>
-      <c r="J263" s="76"/>
-      <c r="K263" s="76"/>
-      <c r="L263" s="76"/>
-      <c r="M263" s="76"/>
-      <c r="N263" s="76"/>
-      <c r="O263" s="76"/>
-      <c r="P263" s="76"/>
-      <c r="Q263" s="76"/>
-      <c r="R263" s="76"/>
-      <c r="S263" s="76"/>
-      <c r="T263" s="76"/>
-      <c r="U263" s="69"/>
+      <c r="H263" s="56"/>
+      <c r="I263" s="57"/>
+      <c r="J263" s="57"/>
+      <c r="K263" s="57"/>
+      <c r="L263" s="57"/>
+      <c r="M263" s="57"/>
+      <c r="N263" s="57"/>
+      <c r="O263" s="57"/>
+      <c r="P263" s="57"/>
+      <c r="Q263" s="57"/>
+      <c r="R263" s="57"/>
+      <c r="S263" s="57"/>
+      <c r="T263" s="57"/>
+      <c r="U263" s="58"/>
     </row>
     <row r="264" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A264" s="27"/>
@@ -31770,20 +31777,20 @@
       <c r="E264" s="28"/>
       <c r="F264" s="28"/>
       <c r="G264" s="28"/>
-      <c r="H264" s="68"/>
-      <c r="I264" s="76"/>
-      <c r="J264" s="76"/>
-      <c r="K264" s="76"/>
-      <c r="L264" s="76"/>
-      <c r="M264" s="76"/>
-      <c r="N264" s="76"/>
-      <c r="O264" s="76"/>
-      <c r="P264" s="76"/>
-      <c r="Q264" s="76"/>
-      <c r="R264" s="76"/>
-      <c r="S264" s="76"/>
-      <c r="T264" s="76"/>
-      <c r="U264" s="69"/>
+      <c r="H264" s="56"/>
+      <c r="I264" s="57"/>
+      <c r="J264" s="57"/>
+      <c r="K264" s="57"/>
+      <c r="L264" s="57"/>
+      <c r="M264" s="57"/>
+      <c r="N264" s="57"/>
+      <c r="O264" s="57"/>
+      <c r="P264" s="57"/>
+      <c r="Q264" s="57"/>
+      <c r="R264" s="57"/>
+      <c r="S264" s="57"/>
+      <c r="T264" s="57"/>
+      <c r="U264" s="58"/>
     </row>
     <row r="265" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A265" s="27"/>
@@ -31799,20 +31806,20 @@
       <c r="E265" s="28"/>
       <c r="F265" s="28"/>
       <c r="G265" s="28"/>
-      <c r="H265" s="68"/>
-      <c r="I265" s="76"/>
-      <c r="J265" s="76"/>
-      <c r="K265" s="76"/>
-      <c r="L265" s="76"/>
-      <c r="M265" s="76"/>
-      <c r="N265" s="76"/>
-      <c r="O265" s="76"/>
-      <c r="P265" s="76"/>
-      <c r="Q265" s="76"/>
-      <c r="R265" s="76"/>
-      <c r="S265" s="76"/>
-      <c r="T265" s="76"/>
-      <c r="U265" s="69"/>
+      <c r="H265" s="56"/>
+      <c r="I265" s="57"/>
+      <c r="J265" s="57"/>
+      <c r="K265" s="57"/>
+      <c r="L265" s="57"/>
+      <c r="M265" s="57"/>
+      <c r="N265" s="57"/>
+      <c r="O265" s="57"/>
+      <c r="P265" s="57"/>
+      <c r="Q265" s="57"/>
+      <c r="R265" s="57"/>
+      <c r="S265" s="57"/>
+      <c r="T265" s="57"/>
+      <c r="U265" s="58"/>
     </row>
     <row r="266" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A266" s="27"/>
@@ -31828,20 +31835,20 @@
       <c r="E266" s="28"/>
       <c r="F266" s="28"/>
       <c r="G266" s="28"/>
-      <c r="H266" s="68"/>
-      <c r="I266" s="76"/>
-      <c r="J266" s="76"/>
-      <c r="K266" s="76"/>
-      <c r="L266" s="76"/>
-      <c r="M266" s="76"/>
-      <c r="N266" s="76"/>
-      <c r="O266" s="76"/>
-      <c r="P266" s="76"/>
-      <c r="Q266" s="76"/>
-      <c r="R266" s="76"/>
-      <c r="S266" s="76"/>
-      <c r="T266" s="76"/>
-      <c r="U266" s="69"/>
+      <c r="H266" s="56"/>
+      <c r="I266" s="57"/>
+      <c r="J266" s="57"/>
+      <c r="K266" s="57"/>
+      <c r="L266" s="57"/>
+      <c r="M266" s="57"/>
+      <c r="N266" s="57"/>
+      <c r="O266" s="57"/>
+      <c r="P266" s="57"/>
+      <c r="Q266" s="57"/>
+      <c r="R266" s="57"/>
+      <c r="S266" s="57"/>
+      <c r="T266" s="57"/>
+      <c r="U266" s="58"/>
     </row>
     <row r="267" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="27"/>
@@ -31857,20 +31864,20 @@
       <c r="E267" s="28"/>
       <c r="F267" s="28"/>
       <c r="G267" s="28"/>
-      <c r="H267" s="68"/>
-      <c r="I267" s="76"/>
-      <c r="J267" s="76"/>
-      <c r="K267" s="76"/>
-      <c r="L267" s="76"/>
-      <c r="M267" s="76"/>
-      <c r="N267" s="76"/>
-      <c r="O267" s="76"/>
-      <c r="P267" s="76"/>
-      <c r="Q267" s="76"/>
-      <c r="R267" s="76"/>
-      <c r="S267" s="76"/>
-      <c r="T267" s="76"/>
-      <c r="U267" s="69"/>
+      <c r="H267" s="56"/>
+      <c r="I267" s="57"/>
+      <c r="J267" s="57"/>
+      <c r="K267" s="57"/>
+      <c r="L267" s="57"/>
+      <c r="M267" s="57"/>
+      <c r="N267" s="57"/>
+      <c r="O267" s="57"/>
+      <c r="P267" s="57"/>
+      <c r="Q267" s="57"/>
+      <c r="R267" s="57"/>
+      <c r="S267" s="57"/>
+      <c r="T267" s="57"/>
+      <c r="U267" s="58"/>
     </row>
     <row r="268" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="27"/>
@@ -31886,22 +31893,22 @@
       <c r="E268" s="28"/>
       <c r="F268" s="28"/>
       <c r="G268" s="28"/>
-      <c r="H268" s="68" t="s">
+      <c r="H268" s="56" t="s">
         <v>1092</v>
       </c>
-      <c r="I268" s="76"/>
-      <c r="J268" s="76"/>
-      <c r="K268" s="76"/>
-      <c r="L268" s="76"/>
-      <c r="M268" s="76"/>
-      <c r="N268" s="76"/>
-      <c r="O268" s="76"/>
-      <c r="P268" s="76"/>
-      <c r="Q268" s="76"/>
-      <c r="R268" s="76"/>
-      <c r="S268" s="76"/>
-      <c r="T268" s="76"/>
-      <c r="U268" s="69"/>
+      <c r="I268" s="57"/>
+      <c r="J268" s="57"/>
+      <c r="K268" s="57"/>
+      <c r="L268" s="57"/>
+      <c r="M268" s="57"/>
+      <c r="N268" s="57"/>
+      <c r="O268" s="57"/>
+      <c r="P268" s="57"/>
+      <c r="Q268" s="57"/>
+      <c r="R268" s="57"/>
+      <c r="S268" s="57"/>
+      <c r="T268" s="57"/>
+      <c r="U268" s="58"/>
     </row>
     <row r="269" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="27"/>
@@ -31917,20 +31924,20 @@
       <c r="E269" s="28"/>
       <c r="F269" s="28"/>
       <c r="G269" s="28"/>
-      <c r="H269" s="68"/>
-      <c r="I269" s="76"/>
-      <c r="J269" s="76"/>
-      <c r="K269" s="76"/>
-      <c r="L269" s="76"/>
-      <c r="M269" s="76"/>
-      <c r="N269" s="76"/>
-      <c r="O269" s="76"/>
-      <c r="P269" s="76"/>
-      <c r="Q269" s="76"/>
-      <c r="R269" s="76"/>
-      <c r="S269" s="76"/>
-      <c r="T269" s="76"/>
-      <c r="U269" s="69"/>
+      <c r="H269" s="56"/>
+      <c r="I269" s="57"/>
+      <c r="J269" s="57"/>
+      <c r="K269" s="57"/>
+      <c r="L269" s="57"/>
+      <c r="M269" s="57"/>
+      <c r="N269" s="57"/>
+      <c r="O269" s="57"/>
+      <c r="P269" s="57"/>
+      <c r="Q269" s="57"/>
+      <c r="R269" s="57"/>
+      <c r="S269" s="57"/>
+      <c r="T269" s="57"/>
+      <c r="U269" s="58"/>
     </row>
     <row r="270" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A270" s="27"/>
@@ -31944,20 +31951,20 @@
       <c r="E270" s="28"/>
       <c r="F270" s="28"/>
       <c r="G270" s="28"/>
-      <c r="H270" s="68"/>
-      <c r="I270" s="76"/>
-      <c r="J270" s="76"/>
-      <c r="K270" s="76"/>
-      <c r="L270" s="76"/>
-      <c r="M270" s="76"/>
-      <c r="N270" s="76"/>
-      <c r="O270" s="76"/>
-      <c r="P270" s="76"/>
-      <c r="Q270" s="76"/>
-      <c r="R270" s="76"/>
-      <c r="S270" s="76"/>
-      <c r="T270" s="76"/>
-      <c r="U270" s="69"/>
+      <c r="H270" s="56"/>
+      <c r="I270" s="57"/>
+      <c r="J270" s="57"/>
+      <c r="K270" s="57"/>
+      <c r="L270" s="57"/>
+      <c r="M270" s="57"/>
+      <c r="N270" s="57"/>
+      <c r="O270" s="57"/>
+      <c r="P270" s="57"/>
+      <c r="Q270" s="57"/>
+      <c r="R270" s="57"/>
+      <c r="S270" s="57"/>
+      <c r="T270" s="57"/>
+      <c r="U270" s="58"/>
     </row>
     <row r="271" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="27"/>
@@ -31971,20 +31978,20 @@
       <c r="E271" s="28"/>
       <c r="F271" s="28"/>
       <c r="G271" s="28"/>
-      <c r="H271" s="68"/>
-      <c r="I271" s="76"/>
-      <c r="J271" s="76"/>
-      <c r="K271" s="76"/>
-      <c r="L271" s="76"/>
-      <c r="M271" s="76"/>
-      <c r="N271" s="76"/>
-      <c r="O271" s="76"/>
-      <c r="P271" s="76"/>
-      <c r="Q271" s="76"/>
-      <c r="R271" s="76"/>
-      <c r="S271" s="76"/>
-      <c r="T271" s="76"/>
-      <c r="U271" s="69"/>
+      <c r="H271" s="56"/>
+      <c r="I271" s="57"/>
+      <c r="J271" s="57"/>
+      <c r="K271" s="57"/>
+      <c r="L271" s="57"/>
+      <c r="M271" s="57"/>
+      <c r="N271" s="57"/>
+      <c r="O271" s="57"/>
+      <c r="P271" s="57"/>
+      <c r="Q271" s="57"/>
+      <c r="R271" s="57"/>
+      <c r="S271" s="57"/>
+      <c r="T271" s="57"/>
+      <c r="U271" s="58"/>
     </row>
     <row r="272" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="27"/>
@@ -31998,34 +32005,60 @@
       <c r="E272" s="28"/>
       <c r="F272" s="28"/>
       <c r="G272" s="28"/>
-      <c r="H272" s="68"/>
-      <c r="I272" s="76"/>
-      <c r="J272" s="76"/>
-      <c r="K272" s="76"/>
-      <c r="L272" s="76"/>
-      <c r="M272" s="76"/>
-      <c r="N272" s="76"/>
-      <c r="O272" s="76"/>
-      <c r="P272" s="76"/>
-      <c r="Q272" s="76"/>
-      <c r="R272" s="76"/>
-      <c r="S272" s="76"/>
-      <c r="T272" s="76"/>
-      <c r="U272" s="69"/>
+      <c r="H272" s="56"/>
+      <c r="I272" s="57"/>
+      <c r="J272" s="57"/>
+      <c r="K272" s="57"/>
+      <c r="L272" s="57"/>
+      <c r="M272" s="57"/>
+      <c r="N272" s="57"/>
+      <c r="O272" s="57"/>
+      <c r="P272" s="57"/>
+      <c r="Q272" s="57"/>
+      <c r="R272" s="57"/>
+      <c r="S272" s="57"/>
+      <c r="T272" s="57"/>
+      <c r="U272" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:U3"/>
-    <mergeCell ref="A4:U4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="H271:U271"/>
+    <mergeCell ref="H272:U272"/>
+    <mergeCell ref="H265:U265"/>
+    <mergeCell ref="H266:U266"/>
+    <mergeCell ref="H267:U267"/>
+    <mergeCell ref="H268:U268"/>
+    <mergeCell ref="H269:U269"/>
+    <mergeCell ref="H270:U270"/>
+    <mergeCell ref="H264:U264"/>
+    <mergeCell ref="C248:I248"/>
+    <mergeCell ref="A254:U254"/>
+    <mergeCell ref="H255:U255"/>
+    <mergeCell ref="H256:U256"/>
+    <mergeCell ref="H257:U257"/>
+    <mergeCell ref="H258:U258"/>
+    <mergeCell ref="H259:U259"/>
+    <mergeCell ref="H260:U260"/>
+    <mergeCell ref="H261:U261"/>
+    <mergeCell ref="H262:U262"/>
+    <mergeCell ref="H263:U263"/>
+    <mergeCell ref="C203:I203"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C119:I119"/>
+    <mergeCell ref="C122:I122"/>
+    <mergeCell ref="C123:I123"/>
+    <mergeCell ref="C163:I163"/>
+    <mergeCell ref="C164:I164"/>
+    <mergeCell ref="C184:I184"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C20:I20"/>
     <mergeCell ref="C21:I21"/>
     <mergeCell ref="R6:R7"/>
     <mergeCell ref="S6:T6"/>
@@ -32042,44 +32075,19 @@
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="O6:O7"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="C203:I203"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C119:I119"/>
-    <mergeCell ref="C122:I122"/>
-    <mergeCell ref="C123:I123"/>
-    <mergeCell ref="C163:I163"/>
-    <mergeCell ref="C164:I164"/>
-    <mergeCell ref="C184:I184"/>
-    <mergeCell ref="H264:U264"/>
-    <mergeCell ref="C248:I248"/>
-    <mergeCell ref="A254:U254"/>
-    <mergeCell ref="H255:U255"/>
-    <mergeCell ref="H256:U256"/>
-    <mergeCell ref="H257:U257"/>
-    <mergeCell ref="H258:U258"/>
-    <mergeCell ref="H259:U259"/>
-    <mergeCell ref="H260:U260"/>
-    <mergeCell ref="H261:U261"/>
-    <mergeCell ref="H262:U262"/>
-    <mergeCell ref="H263:U263"/>
-    <mergeCell ref="H271:U271"/>
-    <mergeCell ref="H272:U272"/>
-    <mergeCell ref="H265:U265"/>
-    <mergeCell ref="H266:U266"/>
-    <mergeCell ref="H267:U267"/>
-    <mergeCell ref="H268:U268"/>
-    <mergeCell ref="H269:U269"/>
-    <mergeCell ref="H270:U270"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A3:U3"/>
+    <mergeCell ref="A4:U4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="G5:G7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/school_lublino/lublino_KP.xlsx
+++ b/school_lublino/lublino_KP.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ТКП!$A$7:$U$7</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" calcMode="manual"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -3916,39 +3916,6 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3979,7 +3946,40 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4379,79 +4379,79 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
-      <c r="U3" s="68"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
-      <c r="P4" s="69"/>
-      <c r="Q4" s="69"/>
-      <c r="R4" s="69"/>
-      <c r="S4" s="69"/>
-      <c r="T4" s="69"/>
-      <c r="U4" s="69"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
+      <c r="U4" s="58"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="65" t="s">
@@ -4481,115 +4481,115 @@
       <c r="I5" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="70" t="s">
+      <c r="J5" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="72"/>
-      <c r="P5" s="73" t="s">
+      <c r="K5" s="60"/>
+      <c r="L5" s="60"/>
+      <c r="M5" s="60"/>
+      <c r="N5" s="60"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="75"/>
-      <c r="S5" s="73" t="s">
+      <c r="Q5" s="63"/>
+      <c r="R5" s="64"/>
+      <c r="S5" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="74"/>
-      <c r="U5" s="75"/>
+      <c r="T5" s="63"/>
+      <c r="U5" s="64"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="76"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="56" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="58"/>
+      <c r="K6" s="69"/>
       <c r="L6" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="56" t="s">
+      <c r="M6" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="58"/>
+      <c r="N6" s="69"/>
       <c r="O6" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="56" t="s">
+      <c r="P6" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="58"/>
+      <c r="Q6" s="69"/>
       <c r="R6" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="S6" s="56" t="s">
+      <c r="S6" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="58"/>
+      <c r="T6" s="69"/>
       <c r="U6" s="65" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="66"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
+      <c r="A7" s="67"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="67"/>
       <c r="J7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="66"/>
+      <c r="L7" s="67"/>
       <c r="M7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="66"/>
+      <c r="O7" s="67"/>
       <c r="P7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="66"/>
+      <c r="R7" s="67"/>
       <c r="S7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="U7" s="66"/>
+      <c r="U7" s="67"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="64"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="72"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -4631,15 +4631,15 @@
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="61"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="74"/>
+      <c r="H9" s="74"/>
+      <c r="I9" s="75"/>
       <c r="M9" s="6">
         <f>SUM(M10,M20)</f>
         <v>18303819.899999999</v>
@@ -4675,15 +4675,15 @@
       <c r="B10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="61"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="75"/>
       <c r="M10" s="6">
         <f t="shared" ref="M10:O14" si="0">SUM(M11)</f>
         <v>126283.29</v>
@@ -4719,15 +4719,15 @@
       <c r="B11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="61"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="74"/>
+      <c r="I11" s="75"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4763,15 +4763,15 @@
       <c r="B12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="61"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="75"/>
       <c r="M12" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4807,15 +4807,15 @@
       <c r="B13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="61"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="75"/>
       <c r="M13" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -4851,15 +4851,15 @@
       <c r="B14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="61"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="75"/>
       <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -5150,15 +5150,15 @@
       <c r="B20" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="59" t="s">
+      <c r="C20" s="73" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="61"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="75"/>
       <c r="M20" s="6">
         <f t="shared" ref="M20:O21" si="1">SUM(M21)</f>
         <v>18177536.609999999</v>
@@ -5194,15 +5194,15 @@
       <c r="B21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="59" t="s">
+      <c r="C21" s="73" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="61"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="75"/>
       <c r="M21" s="6">
         <f t="shared" si="1"/>
         <v>18177536.609999999</v>
@@ -5238,15 +5238,15 @@
       <c r="B22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="59" t="s">
+      <c r="C22" s="73" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="61"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="75"/>
       <c r="M22" s="6">
         <f>SUM(M23,M122,M163,M203,M248)</f>
         <v>18177536.609999999</v>
@@ -5282,15 +5282,15 @@
       <c r="B23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="73" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="61"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="74"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="74"/>
+      <c r="I23" s="75"/>
       <c r="M23" s="6">
         <f>SUM(M24,M67,M76,M119)</f>
         <v>12831032.07</v>
@@ -5326,15 +5326,15 @@
       <c r="B24" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="73" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="60"/>
-      <c r="E24" s="60"/>
-      <c r="F24" s="60"/>
-      <c r="G24" s="60"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="61"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="74"/>
+      <c r="I24" s="75"/>
       <c r="M24" s="6">
         <f>SUM(M25,M29,M31,M34,M36,M41,M46,M51,M57,M62)</f>
         <v>7808423.3099999996</v>
@@ -7558,15 +7558,15 @@
       <c r="B67" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="59" t="s">
+      <c r="C67" s="73" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="60"/>
-      <c r="E67" s="60"/>
-      <c r="F67" s="60"/>
-      <c r="G67" s="60"/>
-      <c r="H67" s="60"/>
-      <c r="I67" s="61"/>
+      <c r="D67" s="74"/>
+      <c r="E67" s="74"/>
+      <c r="F67" s="74"/>
+      <c r="G67" s="74"/>
+      <c r="H67" s="74"/>
+      <c r="I67" s="75"/>
       <c r="M67" s="6">
         <f>SUM(M68,M72,M74)</f>
         <v>748533.11</v>
@@ -8064,15 +8064,15 @@
       <c r="B76" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C76" s="59" t="s">
+      <c r="C76" s="73" t="s">
         <v>325</v>
       </c>
-      <c r="D76" s="60"/>
-      <c r="E76" s="60"/>
-      <c r="F76" s="60"/>
-      <c r="G76" s="60"/>
-      <c r="H76" s="60"/>
-      <c r="I76" s="61"/>
+      <c r="D76" s="74"/>
+      <c r="E76" s="74"/>
+      <c r="F76" s="74"/>
+      <c r="G76" s="74"/>
+      <c r="H76" s="74"/>
+      <c r="I76" s="75"/>
       <c r="M76" s="6">
         <f>SUM(M77,M82,M87,M93,M96,M99,M104,M109,M114,M117)</f>
         <v>3831185.6499999994</v>
@@ -10322,15 +10322,15 @@
       <c r="B119" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C119" s="59" t="s">
+      <c r="C119" s="73" t="s">
         <v>526</v>
       </c>
-      <c r="D119" s="60"/>
-      <c r="E119" s="60"/>
-      <c r="F119" s="60"/>
-      <c r="G119" s="60"/>
-      <c r="H119" s="60"/>
-      <c r="I119" s="61"/>
+      <c r="D119" s="74"/>
+      <c r="E119" s="74"/>
+      <c r="F119" s="74"/>
+      <c r="G119" s="74"/>
+      <c r="H119" s="74"/>
+      <c r="I119" s="75"/>
       <c r="M119" s="6">
         <f>SUM(M120)</f>
         <v>442890</v>
@@ -10492,15 +10492,15 @@
       <c r="B122" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="C122" s="59" t="s">
+      <c r="C122" s="73" t="s">
         <v>541</v>
       </c>
-      <c r="D122" s="60"/>
-      <c r="E122" s="60"/>
-      <c r="F122" s="60"/>
-      <c r="G122" s="60"/>
-      <c r="H122" s="60"/>
-      <c r="I122" s="61"/>
+      <c r="D122" s="74"/>
+      <c r="E122" s="74"/>
+      <c r="F122" s="74"/>
+      <c r="G122" s="74"/>
+      <c r="H122" s="74"/>
+      <c r="I122" s="75"/>
       <c r="M122" s="6">
         <f>SUM(M123)</f>
         <v>4016037.31</v>
@@ -10536,15 +10536,15 @@
       <c r="B123" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="C123" s="59" t="s">
+      <c r="C123" s="73" t="s">
         <v>544</v>
       </c>
-      <c r="D123" s="60"/>
-      <c r="E123" s="60"/>
-      <c r="F123" s="60"/>
-      <c r="G123" s="60"/>
-      <c r="H123" s="60"/>
-      <c r="I123" s="61"/>
+      <c r="D123" s="74"/>
+      <c r="E123" s="74"/>
+      <c r="F123" s="74"/>
+      <c r="G123" s="74"/>
+      <c r="H123" s="74"/>
+      <c r="I123" s="75"/>
       <c r="M123" s="6">
         <f>SUM(M124,M127,M131,M136,M140,M143,M148,M153,M158)</f>
         <v>4016037.31</v>
@@ -11286,7 +11286,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="137" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A137" s="9" t="s">
         <v>613</v>
       </c>
@@ -12625,15 +12625,15 @@
       <c r="B163" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C163" s="59" t="s">
+      <c r="C163" s="73" t="s">
         <v>710</v>
       </c>
-      <c r="D163" s="60"/>
-      <c r="E163" s="60"/>
-      <c r="F163" s="60"/>
-      <c r="G163" s="60"/>
-      <c r="H163" s="60"/>
-      <c r="I163" s="61"/>
+      <c r="D163" s="74"/>
+      <c r="E163" s="74"/>
+      <c r="F163" s="74"/>
+      <c r="G163" s="74"/>
+      <c r="H163" s="74"/>
+      <c r="I163" s="75"/>
       <c r="M163" s="6">
         <f>SUM(M164,M184)</f>
         <v>611422.71999999997</v>
@@ -12669,15 +12669,15 @@
       <c r="B164" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="C164" s="59" t="s">
+      <c r="C164" s="73" t="s">
         <v>713</v>
       </c>
-      <c r="D164" s="60"/>
-      <c r="E164" s="60"/>
-      <c r="F164" s="60"/>
-      <c r="G164" s="60"/>
-      <c r="H164" s="60"/>
-      <c r="I164" s="61"/>
+      <c r="D164" s="74"/>
+      <c r="E164" s="74"/>
+      <c r="F164" s="74"/>
+      <c r="G164" s="74"/>
+      <c r="H164" s="74"/>
+      <c r="I164" s="75"/>
       <c r="M164" s="6">
         <f>SUM(M165,M171,M174,M178,M182)</f>
         <v>415021.23999999993</v>
@@ -13087,7 +13087,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="172" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A172" s="9" t="s">
         <v>749</v>
       </c>
@@ -13254,7 +13254,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="175" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A175" s="9" t="s">
         <v>759</v>
       </c>
@@ -13550,7 +13550,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="181" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
         <v>776</v>
       </c>
@@ -13724,15 +13724,15 @@
       <c r="B184" s="9" t="s">
         <v>789</v>
       </c>
-      <c r="C184" s="59" t="s">
+      <c r="C184" s="73" t="s">
         <v>790</v>
       </c>
-      <c r="D184" s="60"/>
-      <c r="E184" s="60"/>
-      <c r="F184" s="60"/>
-      <c r="G184" s="60"/>
-      <c r="H184" s="60"/>
-      <c r="I184" s="61"/>
+      <c r="D184" s="74"/>
+      <c r="E184" s="74"/>
+      <c r="F184" s="74"/>
+      <c r="G184" s="74"/>
+      <c r="H184" s="74"/>
+      <c r="I184" s="75"/>
       <c r="M184" s="6">
         <f>SUM(M185,M188,M191,M194,M197,M200)</f>
         <v>196401.48</v>
@@ -14782,15 +14782,15 @@
       <c r="B203" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="C203" s="59" t="s">
+      <c r="C203" s="73" t="s">
         <v>856</v>
       </c>
-      <c r="D203" s="60"/>
-      <c r="E203" s="60"/>
-      <c r="F203" s="60"/>
-      <c r="G203" s="60"/>
-      <c r="H203" s="60"/>
-      <c r="I203" s="61"/>
+      <c r="D203" s="74"/>
+      <c r="E203" s="74"/>
+      <c r="F203" s="74"/>
+      <c r="G203" s="74"/>
+      <c r="H203" s="74"/>
+      <c r="I203" s="75"/>
       <c r="M203" s="6">
         <f>SUM(M204,M206,M221,M236,M238,M240,M242,M243,M244,M245,M246,M247)</f>
         <v>719044.50999999989</v>
@@ -15370,7 +15370,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="215" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A215" s="9" t="s">
         <v>913</v>
       </c>
@@ -15967,7 +15967,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="228" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A228" s="9" t="s">
         <v>963</v>
       </c>
@@ -17172,15 +17172,15 @@
       <c r="B248" s="9" t="s">
         <v>1031</v>
       </c>
-      <c r="C248" s="59" t="s">
+      <c r="C248" s="73" t="s">
         <v>1032</v>
       </c>
-      <c r="D248" s="60"/>
-      <c r="E248" s="60"/>
-      <c r="F248" s="60"/>
-      <c r="G248" s="60"/>
-      <c r="H248" s="60"/>
-      <c r="I248" s="61"/>
+      <c r="D248" s="74"/>
+      <c r="E248" s="74"/>
+      <c r="F248" s="74"/>
+      <c r="G248" s="74"/>
+      <c r="H248" s="74"/>
+      <c r="I248" s="75"/>
       <c r="M248" s="6">
         <f>SUM(M249,M250,M251,M252)</f>
         <v>0</v>
@@ -17567,29 +17567,29 @@
       </c>
     </row>
     <row r="254" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="62" t="s">
+      <c r="A254" s="70" t="s">
         <v>1050</v>
       </c>
-      <c r="B254" s="63"/>
-      <c r="C254" s="63"/>
-      <c r="D254" s="63"/>
-      <c r="E254" s="63"/>
-      <c r="F254" s="63"/>
-      <c r="G254" s="63"/>
-      <c r="H254" s="63"/>
-      <c r="I254" s="63"/>
-      <c r="J254" s="63"/>
-      <c r="K254" s="63"/>
-      <c r="L254" s="63"/>
-      <c r="M254" s="63"/>
-      <c r="N254" s="63"/>
-      <c r="O254" s="63"/>
-      <c r="P254" s="63"/>
-      <c r="Q254" s="63"/>
-      <c r="R254" s="63"/>
-      <c r="S254" s="63"/>
-      <c r="T254" s="63"/>
-      <c r="U254" s="64"/>
+      <c r="B254" s="71"/>
+      <c r="C254" s="71"/>
+      <c r="D254" s="71"/>
+      <c r="E254" s="71"/>
+      <c r="F254" s="71"/>
+      <c r="G254" s="71"/>
+      <c r="H254" s="71"/>
+      <c r="I254" s="71"/>
+      <c r="J254" s="71"/>
+      <c r="K254" s="71"/>
+      <c r="L254" s="71"/>
+      <c r="M254" s="71"/>
+      <c r="N254" s="71"/>
+      <c r="O254" s="71"/>
+      <c r="P254" s="71"/>
+      <c r="Q254" s="71"/>
+      <c r="R254" s="71"/>
+      <c r="S254" s="71"/>
+      <c r="T254" s="71"/>
+      <c r="U254" s="72"/>
     </row>
     <row r="255" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="27"/>
@@ -17605,20 +17605,20 @@
       <c r="E255" s="28"/>
       <c r="F255" s="28"/>
       <c r="G255" s="28"/>
-      <c r="H255" s="56"/>
-      <c r="I255" s="57"/>
-      <c r="J255" s="57"/>
-      <c r="K255" s="57"/>
-      <c r="L255" s="57"/>
-      <c r="M255" s="57"/>
-      <c r="N255" s="57"/>
-      <c r="O255" s="57"/>
-      <c r="P255" s="57"/>
-      <c r="Q255" s="57"/>
-      <c r="R255" s="57"/>
-      <c r="S255" s="57"/>
-      <c r="T255" s="57"/>
-      <c r="U255" s="58"/>
+      <c r="H255" s="68"/>
+      <c r="I255" s="76"/>
+      <c r="J255" s="76"/>
+      <c r="K255" s="76"/>
+      <c r="L255" s="76"/>
+      <c r="M255" s="76"/>
+      <c r="N255" s="76"/>
+      <c r="O255" s="76"/>
+      <c r="P255" s="76"/>
+      <c r="Q255" s="76"/>
+      <c r="R255" s="76"/>
+      <c r="S255" s="76"/>
+      <c r="T255" s="76"/>
+      <c r="U255" s="69"/>
     </row>
     <row r="256" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="27"/>
@@ -17634,20 +17634,20 @@
       <c r="E256" s="28"/>
       <c r="F256" s="28"/>
       <c r="G256" s="28"/>
-      <c r="H256" s="56"/>
-      <c r="I256" s="57"/>
-      <c r="J256" s="57"/>
-      <c r="K256" s="57"/>
-      <c r="L256" s="57"/>
-      <c r="M256" s="57"/>
-      <c r="N256" s="57"/>
-      <c r="O256" s="57"/>
-      <c r="P256" s="57"/>
-      <c r="Q256" s="57"/>
-      <c r="R256" s="57"/>
-      <c r="S256" s="57"/>
-      <c r="T256" s="57"/>
-      <c r="U256" s="58"/>
+      <c r="H256" s="68"/>
+      <c r="I256" s="76"/>
+      <c r="J256" s="76"/>
+      <c r="K256" s="76"/>
+      <c r="L256" s="76"/>
+      <c r="M256" s="76"/>
+      <c r="N256" s="76"/>
+      <c r="O256" s="76"/>
+      <c r="P256" s="76"/>
+      <c r="Q256" s="76"/>
+      <c r="R256" s="76"/>
+      <c r="S256" s="76"/>
+      <c r="T256" s="76"/>
+      <c r="U256" s="69"/>
     </row>
     <row r="257" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A257" s="27"/>
@@ -17663,20 +17663,20 @@
       <c r="E257" s="28"/>
       <c r="F257" s="28"/>
       <c r="G257" s="28"/>
-      <c r="H257" s="56"/>
-      <c r="I257" s="57"/>
-      <c r="J257" s="57"/>
-      <c r="K257" s="57"/>
-      <c r="L257" s="57"/>
-      <c r="M257" s="57"/>
-      <c r="N257" s="57"/>
-      <c r="O257" s="57"/>
-      <c r="P257" s="57"/>
-      <c r="Q257" s="57"/>
-      <c r="R257" s="57"/>
-      <c r="S257" s="57"/>
-      <c r="T257" s="57"/>
-      <c r="U257" s="58"/>
+      <c r="H257" s="68"/>
+      <c r="I257" s="76"/>
+      <c r="J257" s="76"/>
+      <c r="K257" s="76"/>
+      <c r="L257" s="76"/>
+      <c r="M257" s="76"/>
+      <c r="N257" s="76"/>
+      <c r="O257" s="76"/>
+      <c r="P257" s="76"/>
+      <c r="Q257" s="76"/>
+      <c r="R257" s="76"/>
+      <c r="S257" s="76"/>
+      <c r="T257" s="76"/>
+      <c r="U257" s="69"/>
     </row>
     <row r="258" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="27"/>
@@ -17692,20 +17692,20 @@
       <c r="E258" s="28"/>
       <c r="F258" s="28"/>
       <c r="G258" s="28"/>
-      <c r="H258" s="56"/>
-      <c r="I258" s="57"/>
-      <c r="J258" s="57"/>
-      <c r="K258" s="57"/>
-      <c r="L258" s="57"/>
-      <c r="M258" s="57"/>
-      <c r="N258" s="57"/>
-      <c r="O258" s="57"/>
-      <c r="P258" s="57"/>
-      <c r="Q258" s="57"/>
-      <c r="R258" s="57"/>
-      <c r="S258" s="57"/>
-      <c r="T258" s="57"/>
-      <c r="U258" s="58"/>
+      <c r="H258" s="68"/>
+      <c r="I258" s="76"/>
+      <c r="J258" s="76"/>
+      <c r="K258" s="76"/>
+      <c r="L258" s="76"/>
+      <c r="M258" s="76"/>
+      <c r="N258" s="76"/>
+      <c r="O258" s="76"/>
+      <c r="P258" s="76"/>
+      <c r="Q258" s="76"/>
+      <c r="R258" s="76"/>
+      <c r="S258" s="76"/>
+      <c r="T258" s="76"/>
+      <c r="U258" s="69"/>
     </row>
     <row r="259" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="27"/>
@@ -17721,20 +17721,20 @@
       <c r="E259" s="28"/>
       <c r="F259" s="28"/>
       <c r="G259" s="28"/>
-      <c r="H259" s="56"/>
-      <c r="I259" s="57"/>
-      <c r="J259" s="57"/>
-      <c r="K259" s="57"/>
-      <c r="L259" s="57"/>
-      <c r="M259" s="57"/>
-      <c r="N259" s="57"/>
-      <c r="O259" s="57"/>
-      <c r="P259" s="57"/>
-      <c r="Q259" s="57"/>
-      <c r="R259" s="57"/>
-      <c r="S259" s="57"/>
-      <c r="T259" s="57"/>
-      <c r="U259" s="58"/>
+      <c r="H259" s="68"/>
+      <c r="I259" s="76"/>
+      <c r="J259" s="76"/>
+      <c r="K259" s="76"/>
+      <c r="L259" s="76"/>
+      <c r="M259" s="76"/>
+      <c r="N259" s="76"/>
+      <c r="O259" s="76"/>
+      <c r="P259" s="76"/>
+      <c r="Q259" s="76"/>
+      <c r="R259" s="76"/>
+      <c r="S259" s="76"/>
+      <c r="T259" s="76"/>
+      <c r="U259" s="69"/>
     </row>
     <row r="260" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A260" s="27"/>
@@ -17750,20 +17750,20 @@
       <c r="E260" s="28"/>
       <c r="F260" s="28"/>
       <c r="G260" s="28"/>
-      <c r="H260" s="56"/>
-      <c r="I260" s="57"/>
-      <c r="J260" s="57"/>
-      <c r="K260" s="57"/>
-      <c r="L260" s="57"/>
-      <c r="M260" s="57"/>
-      <c r="N260" s="57"/>
-      <c r="O260" s="57"/>
-      <c r="P260" s="57"/>
-      <c r="Q260" s="57"/>
-      <c r="R260" s="57"/>
-      <c r="S260" s="57"/>
-      <c r="T260" s="57"/>
-      <c r="U260" s="58"/>
+      <c r="H260" s="68"/>
+      <c r="I260" s="76"/>
+      <c r="J260" s="76"/>
+      <c r="K260" s="76"/>
+      <c r="L260" s="76"/>
+      <c r="M260" s="76"/>
+      <c r="N260" s="76"/>
+      <c r="O260" s="76"/>
+      <c r="P260" s="76"/>
+      <c r="Q260" s="76"/>
+      <c r="R260" s="76"/>
+      <c r="S260" s="76"/>
+      <c r="T260" s="76"/>
+      <c r="U260" s="69"/>
     </row>
     <row r="261" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A261" s="27"/>
@@ -17779,20 +17779,20 @@
       <c r="E261" s="28"/>
       <c r="F261" s="28"/>
       <c r="G261" s="28"/>
-      <c r="H261" s="56"/>
-      <c r="I261" s="57"/>
-      <c r="J261" s="57"/>
-      <c r="K261" s="57"/>
-      <c r="L261" s="57"/>
-      <c r="M261" s="57"/>
-      <c r="N261" s="57"/>
-      <c r="O261" s="57"/>
-      <c r="P261" s="57"/>
-      <c r="Q261" s="57"/>
-      <c r="R261" s="57"/>
-      <c r="S261" s="57"/>
-      <c r="T261" s="57"/>
-      <c r="U261" s="58"/>
+      <c r="H261" s="68"/>
+      <c r="I261" s="76"/>
+      <c r="J261" s="76"/>
+      <c r="K261" s="76"/>
+      <c r="L261" s="76"/>
+      <c r="M261" s="76"/>
+      <c r="N261" s="76"/>
+      <c r="O261" s="76"/>
+      <c r="P261" s="76"/>
+      <c r="Q261" s="76"/>
+      <c r="R261" s="76"/>
+      <c r="S261" s="76"/>
+      <c r="T261" s="76"/>
+      <c r="U261" s="69"/>
     </row>
     <row r="262" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="27"/>
@@ -17808,20 +17808,20 @@
       <c r="E262" s="28"/>
       <c r="F262" s="28"/>
       <c r="G262" s="28"/>
-      <c r="H262" s="56"/>
-      <c r="I262" s="57"/>
-      <c r="J262" s="57"/>
-      <c r="K262" s="57"/>
-      <c r="L262" s="57"/>
-      <c r="M262" s="57"/>
-      <c r="N262" s="57"/>
-      <c r="O262" s="57"/>
-      <c r="P262" s="57"/>
-      <c r="Q262" s="57"/>
-      <c r="R262" s="57"/>
-      <c r="S262" s="57"/>
-      <c r="T262" s="57"/>
-      <c r="U262" s="58"/>
+      <c r="H262" s="68"/>
+      <c r="I262" s="76"/>
+      <c r="J262" s="76"/>
+      <c r="K262" s="76"/>
+      <c r="L262" s="76"/>
+      <c r="M262" s="76"/>
+      <c r="N262" s="76"/>
+      <c r="O262" s="76"/>
+      <c r="P262" s="76"/>
+      <c r="Q262" s="76"/>
+      <c r="R262" s="76"/>
+      <c r="S262" s="76"/>
+      <c r="T262" s="76"/>
+      <c r="U262" s="69"/>
     </row>
     <row r="263" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="27"/>
@@ -17837,20 +17837,20 @@
       <c r="E263" s="28"/>
       <c r="F263" s="28"/>
       <c r="G263" s="28"/>
-      <c r="H263" s="56"/>
-      <c r="I263" s="57"/>
-      <c r="J263" s="57"/>
-      <c r="K263" s="57"/>
-      <c r="L263" s="57"/>
-      <c r="M263" s="57"/>
-      <c r="N263" s="57"/>
-      <c r="O263" s="57"/>
-      <c r="P263" s="57"/>
-      <c r="Q263" s="57"/>
-      <c r="R263" s="57"/>
-      <c r="S263" s="57"/>
-      <c r="T263" s="57"/>
-      <c r="U263" s="58"/>
+      <c r="H263" s="68"/>
+      <c r="I263" s="76"/>
+      <c r="J263" s="76"/>
+      <c r="K263" s="76"/>
+      <c r="L263" s="76"/>
+      <c r="M263" s="76"/>
+      <c r="N263" s="76"/>
+      <c r="O263" s="76"/>
+      <c r="P263" s="76"/>
+      <c r="Q263" s="76"/>
+      <c r="R263" s="76"/>
+      <c r="S263" s="76"/>
+      <c r="T263" s="76"/>
+      <c r="U263" s="69"/>
     </row>
     <row r="264" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A264" s="27"/>
@@ -17866,20 +17866,20 @@
       <c r="E264" s="28"/>
       <c r="F264" s="28"/>
       <c r="G264" s="28"/>
-      <c r="H264" s="56"/>
-      <c r="I264" s="57"/>
-      <c r="J264" s="57"/>
-      <c r="K264" s="57"/>
-      <c r="L264" s="57"/>
-      <c r="M264" s="57"/>
-      <c r="N264" s="57"/>
-      <c r="O264" s="57"/>
-      <c r="P264" s="57"/>
-      <c r="Q264" s="57"/>
-      <c r="R264" s="57"/>
-      <c r="S264" s="57"/>
-      <c r="T264" s="57"/>
-      <c r="U264" s="58"/>
+      <c r="H264" s="68"/>
+      <c r="I264" s="76"/>
+      <c r="J264" s="76"/>
+      <c r="K264" s="76"/>
+      <c r="L264" s="76"/>
+      <c r="M264" s="76"/>
+      <c r="N264" s="76"/>
+      <c r="O264" s="76"/>
+      <c r="P264" s="76"/>
+      <c r="Q264" s="76"/>
+      <c r="R264" s="76"/>
+      <c r="S264" s="76"/>
+      <c r="T264" s="76"/>
+      <c r="U264" s="69"/>
     </row>
     <row r="265" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A265" s="27"/>
@@ -17895,20 +17895,20 @@
       <c r="E265" s="28"/>
       <c r="F265" s="28"/>
       <c r="G265" s="28"/>
-      <c r="H265" s="56"/>
-      <c r="I265" s="57"/>
-      <c r="J265" s="57"/>
-      <c r="K265" s="57"/>
-      <c r="L265" s="57"/>
-      <c r="M265" s="57"/>
-      <c r="N265" s="57"/>
-      <c r="O265" s="57"/>
-      <c r="P265" s="57"/>
-      <c r="Q265" s="57"/>
-      <c r="R265" s="57"/>
-      <c r="S265" s="57"/>
-      <c r="T265" s="57"/>
-      <c r="U265" s="58"/>
+      <c r="H265" s="68"/>
+      <c r="I265" s="76"/>
+      <c r="J265" s="76"/>
+      <c r="K265" s="76"/>
+      <c r="L265" s="76"/>
+      <c r="M265" s="76"/>
+      <c r="N265" s="76"/>
+      <c r="O265" s="76"/>
+      <c r="P265" s="76"/>
+      <c r="Q265" s="76"/>
+      <c r="R265" s="76"/>
+      <c r="S265" s="76"/>
+      <c r="T265" s="76"/>
+      <c r="U265" s="69"/>
     </row>
     <row r="266" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A266" s="27"/>
@@ -17924,20 +17924,20 @@
       <c r="E266" s="28"/>
       <c r="F266" s="28"/>
       <c r="G266" s="28"/>
-      <c r="H266" s="56"/>
-      <c r="I266" s="57"/>
-      <c r="J266" s="57"/>
-      <c r="K266" s="57"/>
-      <c r="L266" s="57"/>
-      <c r="M266" s="57"/>
-      <c r="N266" s="57"/>
-      <c r="O266" s="57"/>
-      <c r="P266" s="57"/>
-      <c r="Q266" s="57"/>
-      <c r="R266" s="57"/>
-      <c r="S266" s="57"/>
-      <c r="T266" s="57"/>
-      <c r="U266" s="58"/>
+      <c r="H266" s="68"/>
+      <c r="I266" s="76"/>
+      <c r="J266" s="76"/>
+      <c r="K266" s="76"/>
+      <c r="L266" s="76"/>
+      <c r="M266" s="76"/>
+      <c r="N266" s="76"/>
+      <c r="O266" s="76"/>
+      <c r="P266" s="76"/>
+      <c r="Q266" s="76"/>
+      <c r="R266" s="76"/>
+      <c r="S266" s="76"/>
+      <c r="T266" s="76"/>
+      <c r="U266" s="69"/>
     </row>
     <row r="267" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="27"/>
@@ -17953,20 +17953,20 @@
       <c r="E267" s="28"/>
       <c r="F267" s="28"/>
       <c r="G267" s="28"/>
-      <c r="H267" s="56"/>
-      <c r="I267" s="57"/>
-      <c r="J267" s="57"/>
-      <c r="K267" s="57"/>
-      <c r="L267" s="57"/>
-      <c r="M267" s="57"/>
-      <c r="N267" s="57"/>
-      <c r="O267" s="57"/>
-      <c r="P267" s="57"/>
-      <c r="Q267" s="57"/>
-      <c r="R267" s="57"/>
-      <c r="S267" s="57"/>
-      <c r="T267" s="57"/>
-      <c r="U267" s="58"/>
+      <c r="H267" s="68"/>
+      <c r="I267" s="76"/>
+      <c r="J267" s="76"/>
+      <c r="K267" s="76"/>
+      <c r="L267" s="76"/>
+      <c r="M267" s="76"/>
+      <c r="N267" s="76"/>
+      <c r="O267" s="76"/>
+      <c r="P267" s="76"/>
+      <c r="Q267" s="76"/>
+      <c r="R267" s="76"/>
+      <c r="S267" s="76"/>
+      <c r="T267" s="76"/>
+      <c r="U267" s="69"/>
     </row>
     <row r="268" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="27"/>
@@ -17982,22 +17982,22 @@
       <c r="E268" s="28"/>
       <c r="F268" s="28"/>
       <c r="G268" s="28"/>
-      <c r="H268" s="56" t="s">
+      <c r="H268" s="68" t="s">
         <v>1092</v>
       </c>
-      <c r="I268" s="57"/>
-      <c r="J268" s="57"/>
-      <c r="K268" s="57"/>
-      <c r="L268" s="57"/>
-      <c r="M268" s="57"/>
-      <c r="N268" s="57"/>
-      <c r="O268" s="57"/>
-      <c r="P268" s="57"/>
-      <c r="Q268" s="57"/>
-      <c r="R268" s="57"/>
-      <c r="S268" s="57"/>
-      <c r="T268" s="57"/>
-      <c r="U268" s="58"/>
+      <c r="I268" s="76"/>
+      <c r="J268" s="76"/>
+      <c r="K268" s="76"/>
+      <c r="L268" s="76"/>
+      <c r="M268" s="76"/>
+      <c r="N268" s="76"/>
+      <c r="O268" s="76"/>
+      <c r="P268" s="76"/>
+      <c r="Q268" s="76"/>
+      <c r="R268" s="76"/>
+      <c r="S268" s="76"/>
+      <c r="T268" s="76"/>
+      <c r="U268" s="69"/>
     </row>
     <row r="269" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="27"/>
@@ -18013,20 +18013,20 @@
       <c r="E269" s="28"/>
       <c r="F269" s="28"/>
       <c r="G269" s="28"/>
-      <c r="H269" s="56"/>
-      <c r="I269" s="57"/>
-      <c r="J269" s="57"/>
-      <c r="K269" s="57"/>
-      <c r="L269" s="57"/>
-      <c r="M269" s="57"/>
-      <c r="N269" s="57"/>
-      <c r="O269" s="57"/>
-      <c r="P269" s="57"/>
-      <c r="Q269" s="57"/>
-      <c r="R269" s="57"/>
-      <c r="S269" s="57"/>
-      <c r="T269" s="57"/>
-      <c r="U269" s="58"/>
+      <c r="H269" s="68"/>
+      <c r="I269" s="76"/>
+      <c r="J269" s="76"/>
+      <c r="K269" s="76"/>
+      <c r="L269" s="76"/>
+      <c r="M269" s="76"/>
+      <c r="N269" s="76"/>
+      <c r="O269" s="76"/>
+      <c r="P269" s="76"/>
+      <c r="Q269" s="76"/>
+      <c r="R269" s="76"/>
+      <c r="S269" s="76"/>
+      <c r="T269" s="76"/>
+      <c r="U269" s="69"/>
     </row>
     <row r="270" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A270" s="27"/>
@@ -18040,20 +18040,20 @@
       <c r="E270" s="28"/>
       <c r="F270" s="28"/>
       <c r="G270" s="28"/>
-      <c r="H270" s="56"/>
-      <c r="I270" s="57"/>
-      <c r="J270" s="57"/>
-      <c r="K270" s="57"/>
-      <c r="L270" s="57"/>
-      <c r="M270" s="57"/>
-      <c r="N270" s="57"/>
-      <c r="O270" s="57"/>
-      <c r="P270" s="57"/>
-      <c r="Q270" s="57"/>
-      <c r="R270" s="57"/>
-      <c r="S270" s="57"/>
-      <c r="T270" s="57"/>
-      <c r="U270" s="58"/>
+      <c r="H270" s="68"/>
+      <c r="I270" s="76"/>
+      <c r="J270" s="76"/>
+      <c r="K270" s="76"/>
+      <c r="L270" s="76"/>
+      <c r="M270" s="76"/>
+      <c r="N270" s="76"/>
+      <c r="O270" s="76"/>
+      <c r="P270" s="76"/>
+      <c r="Q270" s="76"/>
+      <c r="R270" s="76"/>
+      <c r="S270" s="76"/>
+      <c r="T270" s="76"/>
+      <c r="U270" s="69"/>
     </row>
     <row r="271" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="27"/>
@@ -18067,20 +18067,20 @@
       <c r="E271" s="28"/>
       <c r="F271" s="28"/>
       <c r="G271" s="28"/>
-      <c r="H271" s="56"/>
-      <c r="I271" s="57"/>
-      <c r="J271" s="57"/>
-      <c r="K271" s="57"/>
-      <c r="L271" s="57"/>
-      <c r="M271" s="57"/>
-      <c r="N271" s="57"/>
-      <c r="O271" s="57"/>
-      <c r="P271" s="57"/>
-      <c r="Q271" s="57"/>
-      <c r="R271" s="57"/>
-      <c r="S271" s="57"/>
-      <c r="T271" s="57"/>
-      <c r="U271" s="58"/>
+      <c r="H271" s="68"/>
+      <c r="I271" s="76"/>
+      <c r="J271" s="76"/>
+      <c r="K271" s="76"/>
+      <c r="L271" s="76"/>
+      <c r="M271" s="76"/>
+      <c r="N271" s="76"/>
+      <c r="O271" s="76"/>
+      <c r="P271" s="76"/>
+      <c r="Q271" s="76"/>
+      <c r="R271" s="76"/>
+      <c r="S271" s="76"/>
+      <c r="T271" s="76"/>
+      <c r="U271" s="69"/>
     </row>
     <row r="272" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="27"/>
@@ -18094,25 +18094,73 @@
       <c r="E272" s="28"/>
       <c r="F272" s="28"/>
       <c r="G272" s="28"/>
-      <c r="H272" s="56"/>
-      <c r="I272" s="57"/>
-      <c r="J272" s="57"/>
-      <c r="K272" s="57"/>
-      <c r="L272" s="57"/>
-      <c r="M272" s="57"/>
-      <c r="N272" s="57"/>
-      <c r="O272" s="57"/>
-      <c r="P272" s="57"/>
-      <c r="Q272" s="57"/>
-      <c r="R272" s="57"/>
-      <c r="S272" s="57"/>
-      <c r="T272" s="57"/>
-      <c r="U272" s="58"/>
+      <c r="H272" s="68"/>
+      <c r="I272" s="76"/>
+      <c r="J272" s="76"/>
+      <c r="K272" s="76"/>
+      <c r="L272" s="76"/>
+      <c r="M272" s="76"/>
+      <c r="N272" s="76"/>
+      <c r="O272" s="76"/>
+      <c r="P272" s="76"/>
+      <c r="Q272" s="76"/>
+      <c r="R272" s="76"/>
+      <c r="S272" s="76"/>
+      <c r="T272" s="76"/>
+      <c r="U272" s="69"/>
     </row>
   </sheetData>
   <sheetProtection password="C644" sheet="1" formatColumns="0" autoFilter="0"/>
   <autoFilter ref="A7:U7"/>
   <mergeCells count="64">
+    <mergeCell ref="H270:U270"/>
+    <mergeCell ref="H271:U271"/>
+    <mergeCell ref="H272:U272"/>
+    <mergeCell ref="H265:U265"/>
+    <mergeCell ref="H266:U266"/>
+    <mergeCell ref="H267:U267"/>
+    <mergeCell ref="H268:U268"/>
+    <mergeCell ref="H269:U269"/>
+    <mergeCell ref="H260:U260"/>
+    <mergeCell ref="H261:U261"/>
+    <mergeCell ref="H262:U262"/>
+    <mergeCell ref="H263:U263"/>
+    <mergeCell ref="H264:U264"/>
+    <mergeCell ref="H255:U255"/>
+    <mergeCell ref="H256:U256"/>
+    <mergeCell ref="H257:U257"/>
+    <mergeCell ref="H258:U258"/>
+    <mergeCell ref="H259:U259"/>
+    <mergeCell ref="C164:I164"/>
+    <mergeCell ref="C184:I184"/>
+    <mergeCell ref="C203:I203"/>
+    <mergeCell ref="C248:I248"/>
+    <mergeCell ref="A254:U254"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C119:I119"/>
+    <mergeCell ref="C122:I122"/>
+    <mergeCell ref="C123:I123"/>
+    <mergeCell ref="C163:I163"/>
+    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:R7"/>
     <mergeCell ref="A2:U2"/>
     <mergeCell ref="A3:U3"/>
     <mergeCell ref="A4:U4"/>
@@ -18129,54 +18177,6 @@
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="I5:I7"/>
     <mergeCell ref="J6:K6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:R7"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="C21:I21"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C119:I119"/>
-    <mergeCell ref="C122:I122"/>
-    <mergeCell ref="C123:I123"/>
-    <mergeCell ref="C163:I163"/>
-    <mergeCell ref="C164:I164"/>
-    <mergeCell ref="C184:I184"/>
-    <mergeCell ref="C203:I203"/>
-    <mergeCell ref="C248:I248"/>
-    <mergeCell ref="A254:U254"/>
-    <mergeCell ref="H255:U255"/>
-    <mergeCell ref="H256:U256"/>
-    <mergeCell ref="H257:U257"/>
-    <mergeCell ref="H258:U258"/>
-    <mergeCell ref="H259:U259"/>
-    <mergeCell ref="H260:U260"/>
-    <mergeCell ref="H261:U261"/>
-    <mergeCell ref="H262:U262"/>
-    <mergeCell ref="H263:U263"/>
-    <mergeCell ref="H264:U264"/>
-    <mergeCell ref="H270:U270"/>
-    <mergeCell ref="H271:U271"/>
-    <mergeCell ref="H272:U272"/>
-    <mergeCell ref="H265:U265"/>
-    <mergeCell ref="H266:U266"/>
-    <mergeCell ref="H267:U267"/>
-    <mergeCell ref="H268:U268"/>
-    <mergeCell ref="H269:U269"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18268,79 +18268,79 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
-      <c r="U3" s="68"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
-      <c r="P4" s="69"/>
-      <c r="Q4" s="69"/>
-      <c r="R4" s="69"/>
-      <c r="S4" s="69"/>
-      <c r="T4" s="69"/>
-      <c r="U4" s="69"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
+      <c r="U4" s="58"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="65" t="s">
@@ -18370,115 +18370,115 @@
       <c r="I5" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="70" t="s">
+      <c r="J5" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="72"/>
-      <c r="P5" s="73" t="s">
+      <c r="K5" s="60"/>
+      <c r="L5" s="60"/>
+      <c r="M5" s="60"/>
+      <c r="N5" s="60"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="75"/>
-      <c r="S5" s="73" t="s">
+      <c r="Q5" s="63"/>
+      <c r="R5" s="64"/>
+      <c r="S5" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="74"/>
-      <c r="U5" s="75"/>
+      <c r="T5" s="63"/>
+      <c r="U5" s="64"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="76"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="56" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="58"/>
+      <c r="K6" s="69"/>
       <c r="L6" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="56" t="s">
+      <c r="M6" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="58"/>
+      <c r="N6" s="69"/>
       <c r="O6" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="56" t="s">
+      <c r="P6" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="58"/>
+      <c r="Q6" s="69"/>
       <c r="R6" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="S6" s="56" t="s">
+      <c r="S6" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="58"/>
+      <c r="T6" s="69"/>
       <c r="U6" s="65" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="66"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
+      <c r="A7" s="67"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="67"/>
       <c r="J7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="66"/>
+      <c r="L7" s="67"/>
       <c r="M7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="66"/>
+      <c r="O7" s="67"/>
       <c r="P7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="66"/>
+      <c r="R7" s="67"/>
       <c r="S7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="U7" s="66"/>
+      <c r="U7" s="67"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="64"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="72"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -18520,15 +18520,15 @@
       <c r="B9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="61"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="74"/>
+      <c r="H9" s="74"/>
+      <c r="I9" s="75"/>
       <c r="M9" s="6">
         <f>SUM(M10,M20)</f>
         <v>18303819.899999999</v>
@@ -18564,15 +18564,15 @@
       <c r="B10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="61"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="75"/>
       <c r="M10" s="6">
         <f t="shared" ref="M10:O14" si="0">SUM(M11)</f>
         <v>126283.29</v>
@@ -18608,15 +18608,15 @@
       <c r="B11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="61"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="74"/>
+      <c r="I11" s="75"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18652,15 +18652,15 @@
       <c r="B12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="61"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="75"/>
       <c r="M12" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18696,15 +18696,15 @@
       <c r="B13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="61"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="75"/>
       <c r="M13" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -18740,15 +18740,15 @@
       <c r="B14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="61"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="75"/>
       <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>126283.29</v>
@@ -19039,15 +19039,15 @@
       <c r="B20" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="59" t="s">
+      <c r="C20" s="73" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="61"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="75"/>
       <c r="M20" s="6">
         <f t="shared" ref="M20:O21" si="1">SUM(M21)</f>
         <v>18177536.609999999</v>
@@ -19083,15 +19083,15 @@
       <c r="B21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="59" t="s">
+      <c r="C21" s="73" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="61"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="75"/>
       <c r="M21" s="6">
         <f t="shared" si="1"/>
         <v>18177536.609999999</v>
@@ -19127,15 +19127,15 @@
       <c r="B22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="59" t="s">
+      <c r="C22" s="73" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="61"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="75"/>
       <c r="M22" s="6">
         <f>SUM(M23,M122,M163,M203,M248)</f>
         <v>18177536.609999999</v>
@@ -19171,15 +19171,15 @@
       <c r="B23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="C23" s="73" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="61"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="74"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="74"/>
+      <c r="I23" s="75"/>
       <c r="M23" s="6">
         <f>SUM(M24,M67,M76,M119)</f>
         <v>12831032.07</v>
@@ -19215,15 +19215,15 @@
       <c r="B24" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="73" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="60"/>
-      <c r="E24" s="60"/>
-      <c r="F24" s="60"/>
-      <c r="G24" s="60"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="61"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="74"/>
+      <c r="I24" s="75"/>
       <c r="M24" s="6">
         <f>SUM(M25,M29,M31,M34,M36,M41,M46,M51,M57,M62)</f>
         <v>7808423.3099999996</v>
@@ -21452,15 +21452,15 @@
       <c r="B67" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="59" t="s">
+      <c r="C67" s="73" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="60"/>
-      <c r="E67" s="60"/>
-      <c r="F67" s="60"/>
-      <c r="G67" s="60"/>
-      <c r="H67" s="60"/>
-      <c r="I67" s="61"/>
+      <c r="D67" s="74"/>
+      <c r="E67" s="74"/>
+      <c r="F67" s="74"/>
+      <c r="G67" s="74"/>
+      <c r="H67" s="74"/>
+      <c r="I67" s="75"/>
       <c r="M67" s="6">
         <f>SUM(M68,M72,M74)</f>
         <v>748533.11</v>
@@ -21960,15 +21960,15 @@
       <c r="B76" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C76" s="59" t="s">
+      <c r="C76" s="73" t="s">
         <v>325</v>
       </c>
-      <c r="D76" s="60"/>
-      <c r="E76" s="60"/>
-      <c r="F76" s="60"/>
-      <c r="G76" s="60"/>
-      <c r="H76" s="60"/>
-      <c r="I76" s="61"/>
+      <c r="D76" s="74"/>
+      <c r="E76" s="74"/>
+      <c r="F76" s="74"/>
+      <c r="G76" s="74"/>
+      <c r="H76" s="74"/>
+      <c r="I76" s="75"/>
       <c r="M76" s="6">
         <f>SUM(M77,M82,M87,M93,M96,M99,M104,M109,M114,M117)</f>
         <v>3831185.6499999994</v>
@@ -24218,15 +24218,15 @@
       <c r="B119" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C119" s="59" t="s">
+      <c r="C119" s="73" t="s">
         <v>526</v>
       </c>
-      <c r="D119" s="60"/>
-      <c r="E119" s="60"/>
-      <c r="F119" s="60"/>
-      <c r="G119" s="60"/>
-      <c r="H119" s="60"/>
-      <c r="I119" s="61"/>
+      <c r="D119" s="74"/>
+      <c r="E119" s="74"/>
+      <c r="F119" s="74"/>
+      <c r="G119" s="74"/>
+      <c r="H119" s="74"/>
+      <c r="I119" s="75"/>
       <c r="M119" s="6">
         <f>SUM(M120)</f>
         <v>442890</v>
@@ -26536,15 +26536,15 @@
       <c r="B163" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="C163" s="59" t="s">
+      <c r="C163" s="73" t="s">
         <v>710</v>
       </c>
-      <c r="D163" s="60"/>
-      <c r="E163" s="60"/>
-      <c r="F163" s="60"/>
-      <c r="G163" s="60"/>
-      <c r="H163" s="60"/>
-      <c r="I163" s="61"/>
+      <c r="D163" s="74"/>
+      <c r="E163" s="74"/>
+      <c r="F163" s="74"/>
+      <c r="G163" s="74"/>
+      <c r="H163" s="74"/>
+      <c r="I163" s="75"/>
       <c r="M163" s="6">
         <f>SUM(M164,M184)</f>
         <v>611422.71999999997</v>
@@ -26580,15 +26580,15 @@
       <c r="B164" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="C164" s="59" t="s">
+      <c r="C164" s="73" t="s">
         <v>713</v>
       </c>
-      <c r="D164" s="60"/>
-      <c r="E164" s="60"/>
-      <c r="F164" s="60"/>
-      <c r="G164" s="60"/>
-      <c r="H164" s="60"/>
-      <c r="I164" s="61"/>
+      <c r="D164" s="74"/>
+      <c r="E164" s="74"/>
+      <c r="F164" s="74"/>
+      <c r="G164" s="74"/>
+      <c r="H164" s="74"/>
+      <c r="I164" s="75"/>
       <c r="M164" s="6">
         <f>SUM(M165,M171,M174,M178,M182)</f>
         <v>415021.23999999993</v>
@@ -27635,15 +27635,15 @@
       <c r="B184" s="9" t="s">
         <v>789</v>
       </c>
-      <c r="C184" s="59" t="s">
+      <c r="C184" s="73" t="s">
         <v>790</v>
       </c>
-      <c r="D184" s="60"/>
-      <c r="E184" s="60"/>
-      <c r="F184" s="60"/>
-      <c r="G184" s="60"/>
-      <c r="H184" s="60"/>
-      <c r="I184" s="61"/>
+      <c r="D184" s="74"/>
+      <c r="E184" s="74"/>
+      <c r="F184" s="74"/>
+      <c r="G184" s="74"/>
+      <c r="H184" s="74"/>
+      <c r="I184" s="75"/>
       <c r="M184" s="6">
         <f>SUM(M185,M188,M191,M194,M197,M200)</f>
         <v>196401.48</v>
@@ -28693,15 +28693,15 @@
       <c r="B203" s="9" t="s">
         <v>855</v>
       </c>
-      <c r="C203" s="59" t="s">
+      <c r="C203" s="73" t="s">
         <v>856</v>
       </c>
-      <c r="D203" s="60"/>
-      <c r="E203" s="60"/>
-      <c r="F203" s="60"/>
-      <c r="G203" s="60"/>
-      <c r="H203" s="60"/>
-      <c r="I203" s="61"/>
+      <c r="D203" s="74"/>
+      <c r="E203" s="74"/>
+      <c r="F203" s="74"/>
+      <c r="G203" s="74"/>
+      <c r="H203" s="74"/>
+      <c r="I203" s="75"/>
       <c r="M203" s="6">
         <f>SUM(M204,M206,M221,M236,M238,M240,M242,M243,M244,M245,M246,M247)</f>
         <v>719044.50999999989</v>
@@ -31083,15 +31083,15 @@
       <c r="B248" s="9" t="s">
         <v>1031</v>
       </c>
-      <c r="C248" s="59" t="s">
+      <c r="C248" s="73" t="s">
         <v>1032</v>
       </c>
-      <c r="D248" s="60"/>
-      <c r="E248" s="60"/>
-      <c r="F248" s="60"/>
-      <c r="G248" s="60"/>
-      <c r="H248" s="60"/>
-      <c r="I248" s="61"/>
+      <c r="D248" s="74"/>
+      <c r="E248" s="74"/>
+      <c r="F248" s="74"/>
+      <c r="G248" s="74"/>
+      <c r="H248" s="74"/>
+      <c r="I248" s="75"/>
       <c r="M248" s="6">
         <f>SUM(M249,M250,M251,M252)</f>
         <v>0</v>
@@ -31478,29 +31478,29 @@
       </c>
     </row>
     <row r="254" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="62" t="s">
+      <c r="A254" s="70" t="s">
         <v>1050</v>
       </c>
-      <c r="B254" s="63"/>
-      <c r="C254" s="63"/>
-      <c r="D254" s="63"/>
-      <c r="E254" s="63"/>
-      <c r="F254" s="63"/>
-      <c r="G254" s="63"/>
-      <c r="H254" s="63"/>
-      <c r="I254" s="63"/>
-      <c r="J254" s="63"/>
-      <c r="K254" s="63"/>
-      <c r="L254" s="63"/>
-      <c r="M254" s="63"/>
-      <c r="N254" s="63"/>
-      <c r="O254" s="63"/>
-      <c r="P254" s="63"/>
-      <c r="Q254" s="63"/>
-      <c r="R254" s="63"/>
-      <c r="S254" s="63"/>
-      <c r="T254" s="63"/>
-      <c r="U254" s="64"/>
+      <c r="B254" s="71"/>
+      <c r="C254" s="71"/>
+      <c r="D254" s="71"/>
+      <c r="E254" s="71"/>
+      <c r="F254" s="71"/>
+      <c r="G254" s="71"/>
+      <c r="H254" s="71"/>
+      <c r="I254" s="71"/>
+      <c r="J254" s="71"/>
+      <c r="K254" s="71"/>
+      <c r="L254" s="71"/>
+      <c r="M254" s="71"/>
+      <c r="N254" s="71"/>
+      <c r="O254" s="71"/>
+      <c r="P254" s="71"/>
+      <c r="Q254" s="71"/>
+      <c r="R254" s="71"/>
+      <c r="S254" s="71"/>
+      <c r="T254" s="71"/>
+      <c r="U254" s="72"/>
     </row>
     <row r="255" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="27"/>
@@ -31516,20 +31516,20 @@
       <c r="E255" s="28"/>
       <c r="F255" s="28"/>
       <c r="G255" s="28"/>
-      <c r="H255" s="56"/>
-      <c r="I255" s="57"/>
-      <c r="J255" s="57"/>
-      <c r="K255" s="57"/>
-      <c r="L255" s="57"/>
-      <c r="M255" s="57"/>
-      <c r="N255" s="57"/>
-      <c r="O255" s="57"/>
-      <c r="P255" s="57"/>
-      <c r="Q255" s="57"/>
-      <c r="R255" s="57"/>
-      <c r="S255" s="57"/>
-      <c r="T255" s="57"/>
-      <c r="U255" s="58"/>
+      <c r="H255" s="68"/>
+      <c r="I255" s="76"/>
+      <c r="J255" s="76"/>
+      <c r="K255" s="76"/>
+      <c r="L255" s="76"/>
+      <c r="M255" s="76"/>
+      <c r="N255" s="76"/>
+      <c r="O255" s="76"/>
+      <c r="P255" s="76"/>
+      <c r="Q255" s="76"/>
+      <c r="R255" s="76"/>
+      <c r="S255" s="76"/>
+      <c r="T255" s="76"/>
+      <c r="U255" s="69"/>
     </row>
     <row r="256" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="27"/>
@@ -31545,20 +31545,20 @@
       <c r="E256" s="28"/>
       <c r="F256" s="28"/>
       <c r="G256" s="28"/>
-      <c r="H256" s="56"/>
-      <c r="I256" s="57"/>
-      <c r="J256" s="57"/>
-      <c r="K256" s="57"/>
-      <c r="L256" s="57"/>
-      <c r="M256" s="57"/>
-      <c r="N256" s="57"/>
-      <c r="O256" s="57"/>
-      <c r="P256" s="57"/>
-      <c r="Q256" s="57"/>
-      <c r="R256" s="57"/>
-      <c r="S256" s="57"/>
-      <c r="T256" s="57"/>
-      <c r="U256" s="58"/>
+      <c r="H256" s="68"/>
+      <c r="I256" s="76"/>
+      <c r="J256" s="76"/>
+      <c r="K256" s="76"/>
+      <c r="L256" s="76"/>
+      <c r="M256" s="76"/>
+      <c r="N256" s="76"/>
+      <c r="O256" s="76"/>
+      <c r="P256" s="76"/>
+      <c r="Q256" s="76"/>
+      <c r="R256" s="76"/>
+      <c r="S256" s="76"/>
+      <c r="T256" s="76"/>
+      <c r="U256" s="69"/>
     </row>
     <row r="257" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A257" s="27"/>
@@ -31574,20 +31574,20 @@
       <c r="E257" s="28"/>
       <c r="F257" s="28"/>
       <c r="G257" s="28"/>
-      <c r="H257" s="56"/>
-      <c r="I257" s="57"/>
-      <c r="J257" s="57"/>
-      <c r="K257" s="57"/>
-      <c r="L257" s="57"/>
-      <c r="M257" s="57"/>
-      <c r="N257" s="57"/>
-      <c r="O257" s="57"/>
-      <c r="P257" s="57"/>
-      <c r="Q257" s="57"/>
-      <c r="R257" s="57"/>
-      <c r="S257" s="57"/>
-      <c r="T257" s="57"/>
-      <c r="U257" s="58"/>
+      <c r="H257" s="68"/>
+      <c r="I257" s="76"/>
+      <c r="J257" s="76"/>
+      <c r="K257" s="76"/>
+      <c r="L257" s="76"/>
+      <c r="M257" s="76"/>
+      <c r="N257" s="76"/>
+      <c r="O257" s="76"/>
+      <c r="P257" s="76"/>
+      <c r="Q257" s="76"/>
+      <c r="R257" s="76"/>
+      <c r="S257" s="76"/>
+      <c r="T257" s="76"/>
+      <c r="U257" s="69"/>
     </row>
     <row r="258" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="27"/>
@@ -31603,20 +31603,20 @@
       <c r="E258" s="28"/>
       <c r="F258" s="28"/>
       <c r="G258" s="28"/>
-      <c r="H258" s="56"/>
-      <c r="I258" s="57"/>
-      <c r="J258" s="57"/>
-      <c r="K258" s="57"/>
-      <c r="L258" s="57"/>
-      <c r="M258" s="57"/>
-      <c r="N258" s="57"/>
-      <c r="O258" s="57"/>
-      <c r="P258" s="57"/>
-      <c r="Q258" s="57"/>
-      <c r="R258" s="57"/>
-      <c r="S258" s="57"/>
-      <c r="T258" s="57"/>
-      <c r="U258" s="58"/>
+      <c r="H258" s="68"/>
+      <c r="I258" s="76"/>
+      <c r="J258" s="76"/>
+      <c r="K258" s="76"/>
+      <c r="L258" s="76"/>
+      <c r="M258" s="76"/>
+      <c r="N258" s="76"/>
+      <c r="O258" s="76"/>
+      <c r="P258" s="76"/>
+      <c r="Q258" s="76"/>
+      <c r="R258" s="76"/>
+      <c r="S258" s="76"/>
+      <c r="T258" s="76"/>
+      <c r="U258" s="69"/>
     </row>
     <row r="259" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="27"/>
@@ -31632,20 +31632,20 @@
       <c r="E259" s="28"/>
       <c r="F259" s="28"/>
       <c r="G259" s="28"/>
-      <c r="H259" s="56"/>
-      <c r="I259" s="57"/>
-      <c r="J259" s="57"/>
-      <c r="K259" s="57"/>
-      <c r="L259" s="57"/>
-      <c r="M259" s="57"/>
-      <c r="N259" s="57"/>
-      <c r="O259" s="57"/>
-      <c r="P259" s="57"/>
-      <c r="Q259" s="57"/>
-      <c r="R259" s="57"/>
-      <c r="S259" s="57"/>
-      <c r="T259" s="57"/>
-      <c r="U259" s="58"/>
+      <c r="H259" s="68"/>
+      <c r="I259" s="76"/>
+      <c r="J259" s="76"/>
+      <c r="K259" s="76"/>
+      <c r="L259" s="76"/>
+      <c r="M259" s="76"/>
+      <c r="N259" s="76"/>
+      <c r="O259" s="76"/>
+      <c r="P259" s="76"/>
+      <c r="Q259" s="76"/>
+      <c r="R259" s="76"/>
+      <c r="S259" s="76"/>
+      <c r="T259" s="76"/>
+      <c r="U259" s="69"/>
     </row>
     <row r="260" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A260" s="27"/>
@@ -31661,20 +31661,20 @@
       <c r="E260" s="28"/>
       <c r="F260" s="28"/>
       <c r="G260" s="28"/>
-      <c r="H260" s="56"/>
-      <c r="I260" s="57"/>
-      <c r="J260" s="57"/>
-      <c r="K260" s="57"/>
-      <c r="L260" s="57"/>
-      <c r="M260" s="57"/>
-      <c r="N260" s="57"/>
-      <c r="O260" s="57"/>
-      <c r="P260" s="57"/>
-      <c r="Q260" s="57"/>
-      <c r="R260" s="57"/>
-      <c r="S260" s="57"/>
-      <c r="T260" s="57"/>
-      <c r="U260" s="58"/>
+      <c r="H260" s="68"/>
+      <c r="I260" s="76"/>
+      <c r="J260" s="76"/>
+      <c r="K260" s="76"/>
+      <c r="L260" s="76"/>
+      <c r="M260" s="76"/>
+      <c r="N260" s="76"/>
+      <c r="O260" s="76"/>
+      <c r="P260" s="76"/>
+      <c r="Q260" s="76"/>
+      <c r="R260" s="76"/>
+      <c r="S260" s="76"/>
+      <c r="T260" s="76"/>
+      <c r="U260" s="69"/>
     </row>
     <row r="261" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A261" s="27"/>
@@ -31690,20 +31690,20 @@
       <c r="E261" s="28"/>
       <c r="F261" s="28"/>
       <c r="G261" s="28"/>
-      <c r="H261" s="56"/>
-      <c r="I261" s="57"/>
-      <c r="J261" s="57"/>
-      <c r="K261" s="57"/>
-      <c r="L261" s="57"/>
-      <c r="M261" s="57"/>
-      <c r="N261" s="57"/>
-      <c r="O261" s="57"/>
-      <c r="P261" s="57"/>
-      <c r="Q261" s="57"/>
-      <c r="R261" s="57"/>
-      <c r="S261" s="57"/>
-      <c r="T261" s="57"/>
-      <c r="U261" s="58"/>
+      <c r="H261" s="68"/>
+      <c r="I261" s="76"/>
+      <c r="J261" s="76"/>
+      <c r="K261" s="76"/>
+      <c r="L261" s="76"/>
+      <c r="M261" s="76"/>
+      <c r="N261" s="76"/>
+      <c r="O261" s="76"/>
+      <c r="P261" s="76"/>
+      <c r="Q261" s="76"/>
+      <c r="R261" s="76"/>
+      <c r="S261" s="76"/>
+      <c r="T261" s="76"/>
+      <c r="U261" s="69"/>
     </row>
     <row r="262" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="27"/>
@@ -31719,20 +31719,20 @@
       <c r="E262" s="28"/>
       <c r="F262" s="28"/>
       <c r="G262" s="28"/>
-      <c r="H262" s="56"/>
-      <c r="I262" s="57"/>
-      <c r="J262" s="57"/>
-      <c r="K262" s="57"/>
-      <c r="L262" s="57"/>
-      <c r="M262" s="57"/>
-      <c r="N262" s="57"/>
-      <c r="O262" s="57"/>
-      <c r="P262" s="57"/>
-      <c r="Q262" s="57"/>
-      <c r="R262" s="57"/>
-      <c r="S262" s="57"/>
-      <c r="T262" s="57"/>
-      <c r="U262" s="58"/>
+      <c r="H262" s="68"/>
+      <c r="I262" s="76"/>
+      <c r="J262" s="76"/>
+      <c r="K262" s="76"/>
+      <c r="L262" s="76"/>
+      <c r="M262" s="76"/>
+      <c r="N262" s="76"/>
+      <c r="O262" s="76"/>
+      <c r="P262" s="76"/>
+      <c r="Q262" s="76"/>
+      <c r="R262" s="76"/>
+      <c r="S262" s="76"/>
+      <c r="T262" s="76"/>
+      <c r="U262" s="69"/>
     </row>
     <row r="263" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="27"/>
@@ -31748,20 +31748,20 @@
       <c r="E263" s="28"/>
       <c r="F263" s="28"/>
       <c r="G263" s="28"/>
-      <c r="H263" s="56"/>
-      <c r="I263" s="57"/>
-      <c r="J263" s="57"/>
-      <c r="K263" s="57"/>
-      <c r="L263" s="57"/>
-      <c r="M263" s="57"/>
-      <c r="N263" s="57"/>
-      <c r="O263" s="57"/>
-      <c r="P263" s="57"/>
-      <c r="Q263" s="57"/>
-      <c r="R263" s="57"/>
-      <c r="S263" s="57"/>
-      <c r="T263" s="57"/>
-      <c r="U263" s="58"/>
+      <c r="H263" s="68"/>
+      <c r="I263" s="76"/>
+      <c r="J263" s="76"/>
+      <c r="K263" s="76"/>
+      <c r="L263" s="76"/>
+      <c r="M263" s="76"/>
+      <c r="N263" s="76"/>
+      <c r="O263" s="76"/>
+      <c r="P263" s="76"/>
+      <c r="Q263" s="76"/>
+      <c r="R263" s="76"/>
+      <c r="S263" s="76"/>
+      <c r="T263" s="76"/>
+      <c r="U263" s="69"/>
     </row>
     <row r="264" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A264" s="27"/>
@@ -31777,20 +31777,20 @@
       <c r="E264" s="28"/>
       <c r="F264" s="28"/>
       <c r="G264" s="28"/>
-      <c r="H264" s="56"/>
-      <c r="I264" s="57"/>
-      <c r="J264" s="57"/>
-      <c r="K264" s="57"/>
-      <c r="L264" s="57"/>
-      <c r="M264" s="57"/>
-      <c r="N264" s="57"/>
-      <c r="O264" s="57"/>
-      <c r="P264" s="57"/>
-      <c r="Q264" s="57"/>
-      <c r="R264" s="57"/>
-      <c r="S264" s="57"/>
-      <c r="T264" s="57"/>
-      <c r="U264" s="58"/>
+      <c r="H264" s="68"/>
+      <c r="I264" s="76"/>
+      <c r="J264" s="76"/>
+      <c r="K264" s="76"/>
+      <c r="L264" s="76"/>
+      <c r="M264" s="76"/>
+      <c r="N264" s="76"/>
+      <c r="O264" s="76"/>
+      <c r="P264" s="76"/>
+      <c r="Q264" s="76"/>
+      <c r="R264" s="76"/>
+      <c r="S264" s="76"/>
+      <c r="T264" s="76"/>
+      <c r="U264" s="69"/>
     </row>
     <row r="265" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A265" s="27"/>
@@ -31806,20 +31806,20 @@
       <c r="E265" s="28"/>
       <c r="F265" s="28"/>
       <c r="G265" s="28"/>
-      <c r="H265" s="56"/>
-      <c r="I265" s="57"/>
-      <c r="J265" s="57"/>
-      <c r="K265" s="57"/>
-      <c r="L265" s="57"/>
-      <c r="M265" s="57"/>
-      <c r="N265" s="57"/>
-      <c r="O265" s="57"/>
-      <c r="P265" s="57"/>
-      <c r="Q265" s="57"/>
-      <c r="R265" s="57"/>
-      <c r="S265" s="57"/>
-      <c r="T265" s="57"/>
-      <c r="U265" s="58"/>
+      <c r="H265" s="68"/>
+      <c r="I265" s="76"/>
+      <c r="J265" s="76"/>
+      <c r="K265" s="76"/>
+      <c r="L265" s="76"/>
+      <c r="M265" s="76"/>
+      <c r="N265" s="76"/>
+      <c r="O265" s="76"/>
+      <c r="P265" s="76"/>
+      <c r="Q265" s="76"/>
+      <c r="R265" s="76"/>
+      <c r="S265" s="76"/>
+      <c r="T265" s="76"/>
+      <c r="U265" s="69"/>
     </row>
     <row r="266" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A266" s="27"/>
@@ -31835,20 +31835,20 @@
       <c r="E266" s="28"/>
       <c r="F266" s="28"/>
       <c r="G266" s="28"/>
-      <c r="H266" s="56"/>
-      <c r="I266" s="57"/>
-      <c r="J266" s="57"/>
-      <c r="K266" s="57"/>
-      <c r="L266" s="57"/>
-      <c r="M266" s="57"/>
-      <c r="N266" s="57"/>
-      <c r="O266" s="57"/>
-      <c r="P266" s="57"/>
-      <c r="Q266" s="57"/>
-      <c r="R266" s="57"/>
-      <c r="S266" s="57"/>
-      <c r="T266" s="57"/>
-      <c r="U266" s="58"/>
+      <c r="H266" s="68"/>
+      <c r="I266" s="76"/>
+      <c r="J266" s="76"/>
+      <c r="K266" s="76"/>
+      <c r="L266" s="76"/>
+      <c r="M266" s="76"/>
+      <c r="N266" s="76"/>
+      <c r="O266" s="76"/>
+      <c r="P266" s="76"/>
+      <c r="Q266" s="76"/>
+      <c r="R266" s="76"/>
+      <c r="S266" s="76"/>
+      <c r="T266" s="76"/>
+      <c r="U266" s="69"/>
     </row>
     <row r="267" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="27"/>
@@ -31864,20 +31864,20 @@
       <c r="E267" s="28"/>
       <c r="F267" s="28"/>
       <c r="G267" s="28"/>
-      <c r="H267" s="56"/>
-      <c r="I267" s="57"/>
-      <c r="J267" s="57"/>
-      <c r="K267" s="57"/>
-      <c r="L267" s="57"/>
-      <c r="M267" s="57"/>
-      <c r="N267" s="57"/>
-      <c r="O267" s="57"/>
-      <c r="P267" s="57"/>
-      <c r="Q267" s="57"/>
-      <c r="R267" s="57"/>
-      <c r="S267" s="57"/>
-      <c r="T267" s="57"/>
-      <c r="U267" s="58"/>
+      <c r="H267" s="68"/>
+      <c r="I267" s="76"/>
+      <c r="J267" s="76"/>
+      <c r="K267" s="76"/>
+      <c r="L267" s="76"/>
+      <c r="M267" s="76"/>
+      <c r="N267" s="76"/>
+      <c r="O267" s="76"/>
+      <c r="P267" s="76"/>
+      <c r="Q267" s="76"/>
+      <c r="R267" s="76"/>
+      <c r="S267" s="76"/>
+      <c r="T267" s="76"/>
+      <c r="U267" s="69"/>
     </row>
     <row r="268" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="27"/>
@@ -31893,22 +31893,22 @@
       <c r="E268" s="28"/>
       <c r="F268" s="28"/>
       <c r="G268" s="28"/>
-      <c r="H268" s="56" t="s">
+      <c r="H268" s="68" t="s">
         <v>1092</v>
       </c>
-      <c r="I268" s="57"/>
-      <c r="J268" s="57"/>
-      <c r="K268" s="57"/>
-      <c r="L268" s="57"/>
-      <c r="M268" s="57"/>
-      <c r="N268" s="57"/>
-      <c r="O268" s="57"/>
-      <c r="P268" s="57"/>
-      <c r="Q268" s="57"/>
-      <c r="R268" s="57"/>
-      <c r="S268" s="57"/>
-      <c r="T268" s="57"/>
-      <c r="U268" s="58"/>
+      <c r="I268" s="76"/>
+      <c r="J268" s="76"/>
+      <c r="K268" s="76"/>
+      <c r="L268" s="76"/>
+      <c r="M268" s="76"/>
+      <c r="N268" s="76"/>
+      <c r="O268" s="76"/>
+      <c r="P268" s="76"/>
+      <c r="Q268" s="76"/>
+      <c r="R268" s="76"/>
+      <c r="S268" s="76"/>
+      <c r="T268" s="76"/>
+      <c r="U268" s="69"/>
     </row>
     <row r="269" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="27"/>
@@ -31924,20 +31924,20 @@
       <c r="E269" s="28"/>
       <c r="F269" s="28"/>
       <c r="G269" s="28"/>
-      <c r="H269" s="56"/>
-      <c r="I269" s="57"/>
-      <c r="J269" s="57"/>
-      <c r="K269" s="57"/>
-      <c r="L269" s="57"/>
-      <c r="M269" s="57"/>
-      <c r="N269" s="57"/>
-      <c r="O269" s="57"/>
-      <c r="P269" s="57"/>
-      <c r="Q269" s="57"/>
-      <c r="R269" s="57"/>
-      <c r="S269" s="57"/>
-      <c r="T269" s="57"/>
-      <c r="U269" s="58"/>
+      <c r="H269" s="68"/>
+      <c r="I269" s="76"/>
+      <c r="J269" s="76"/>
+      <c r="K269" s="76"/>
+      <c r="L269" s="76"/>
+      <c r="M269" s="76"/>
+      <c r="N269" s="76"/>
+      <c r="O269" s="76"/>
+      <c r="P269" s="76"/>
+      <c r="Q269" s="76"/>
+      <c r="R269" s="76"/>
+      <c r="S269" s="76"/>
+      <c r="T269" s="76"/>
+      <c r="U269" s="69"/>
     </row>
     <row r="270" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A270" s="27"/>
@@ -31951,20 +31951,20 @@
       <c r="E270" s="28"/>
       <c r="F270" s="28"/>
       <c r="G270" s="28"/>
-      <c r="H270" s="56"/>
-      <c r="I270" s="57"/>
-      <c r="J270" s="57"/>
-      <c r="K270" s="57"/>
-      <c r="L270" s="57"/>
-      <c r="M270" s="57"/>
-      <c r="N270" s="57"/>
-      <c r="O270" s="57"/>
-      <c r="P270" s="57"/>
-      <c r="Q270" s="57"/>
-      <c r="R270" s="57"/>
-      <c r="S270" s="57"/>
-      <c r="T270" s="57"/>
-      <c r="U270" s="58"/>
+      <c r="H270" s="68"/>
+      <c r="I270" s="76"/>
+      <c r="J270" s="76"/>
+      <c r="K270" s="76"/>
+      <c r="L270" s="76"/>
+      <c r="M270" s="76"/>
+      <c r="N270" s="76"/>
+      <c r="O270" s="76"/>
+      <c r="P270" s="76"/>
+      <c r="Q270" s="76"/>
+      <c r="R270" s="76"/>
+      <c r="S270" s="76"/>
+      <c r="T270" s="76"/>
+      <c r="U270" s="69"/>
     </row>
     <row r="271" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="27"/>
@@ -31978,20 +31978,20 @@
       <c r="E271" s="28"/>
       <c r="F271" s="28"/>
       <c r="G271" s="28"/>
-      <c r="H271" s="56"/>
-      <c r="I271" s="57"/>
-      <c r="J271" s="57"/>
-      <c r="K271" s="57"/>
-      <c r="L271" s="57"/>
-      <c r="M271" s="57"/>
-      <c r="N271" s="57"/>
-      <c r="O271" s="57"/>
-      <c r="P271" s="57"/>
-      <c r="Q271" s="57"/>
-      <c r="R271" s="57"/>
-      <c r="S271" s="57"/>
-      <c r="T271" s="57"/>
-      <c r="U271" s="58"/>
+      <c r="H271" s="68"/>
+      <c r="I271" s="76"/>
+      <c r="J271" s="76"/>
+      <c r="K271" s="76"/>
+      <c r="L271" s="76"/>
+      <c r="M271" s="76"/>
+      <c r="N271" s="76"/>
+      <c r="O271" s="76"/>
+      <c r="P271" s="76"/>
+      <c r="Q271" s="76"/>
+      <c r="R271" s="76"/>
+      <c r="S271" s="76"/>
+      <c r="T271" s="76"/>
+      <c r="U271" s="69"/>
     </row>
     <row r="272" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="27"/>
@@ -32005,60 +32005,34 @@
       <c r="E272" s="28"/>
       <c r="F272" s="28"/>
       <c r="G272" s="28"/>
-      <c r="H272" s="56"/>
-      <c r="I272" s="57"/>
-      <c r="J272" s="57"/>
-      <c r="K272" s="57"/>
-      <c r="L272" s="57"/>
-      <c r="M272" s="57"/>
-      <c r="N272" s="57"/>
-      <c r="O272" s="57"/>
-      <c r="P272" s="57"/>
-      <c r="Q272" s="57"/>
-      <c r="R272" s="57"/>
-      <c r="S272" s="57"/>
-      <c r="T272" s="57"/>
-      <c r="U272" s="58"/>
+      <c r="H272" s="68"/>
+      <c r="I272" s="76"/>
+      <c r="J272" s="76"/>
+      <c r="K272" s="76"/>
+      <c r="L272" s="76"/>
+      <c r="M272" s="76"/>
+      <c r="N272" s="76"/>
+      <c r="O272" s="76"/>
+      <c r="P272" s="76"/>
+      <c r="Q272" s="76"/>
+      <c r="R272" s="76"/>
+      <c r="S272" s="76"/>
+      <c r="T272" s="76"/>
+      <c r="U272" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="H271:U271"/>
-    <mergeCell ref="H272:U272"/>
-    <mergeCell ref="H265:U265"/>
-    <mergeCell ref="H266:U266"/>
-    <mergeCell ref="H267:U267"/>
-    <mergeCell ref="H268:U268"/>
-    <mergeCell ref="H269:U269"/>
-    <mergeCell ref="H270:U270"/>
-    <mergeCell ref="H264:U264"/>
-    <mergeCell ref="C248:I248"/>
-    <mergeCell ref="A254:U254"/>
-    <mergeCell ref="H255:U255"/>
-    <mergeCell ref="H256:U256"/>
-    <mergeCell ref="H257:U257"/>
-    <mergeCell ref="H258:U258"/>
-    <mergeCell ref="H259:U259"/>
-    <mergeCell ref="H260:U260"/>
-    <mergeCell ref="H261:U261"/>
-    <mergeCell ref="H262:U262"/>
-    <mergeCell ref="H263:U263"/>
-    <mergeCell ref="C203:I203"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C119:I119"/>
-    <mergeCell ref="C122:I122"/>
-    <mergeCell ref="C123:I123"/>
-    <mergeCell ref="C163:I163"/>
-    <mergeCell ref="C164:I164"/>
-    <mergeCell ref="C184:I184"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A3:U3"/>
+    <mergeCell ref="A4:U4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="G5:G7"/>
     <mergeCell ref="C21:I21"/>
     <mergeCell ref="R6:R7"/>
     <mergeCell ref="S6:T6"/>
@@ -32075,17 +32049,43 @@
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:U3"/>
-    <mergeCell ref="A4:U4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="C203:I203"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C119:I119"/>
+    <mergeCell ref="C122:I122"/>
+    <mergeCell ref="C123:I123"/>
+    <mergeCell ref="C163:I163"/>
+    <mergeCell ref="C164:I164"/>
+    <mergeCell ref="C184:I184"/>
+    <mergeCell ref="H264:U264"/>
+    <mergeCell ref="C248:I248"/>
+    <mergeCell ref="A254:U254"/>
+    <mergeCell ref="H255:U255"/>
+    <mergeCell ref="H256:U256"/>
+    <mergeCell ref="H257:U257"/>
+    <mergeCell ref="H258:U258"/>
+    <mergeCell ref="H259:U259"/>
+    <mergeCell ref="H260:U260"/>
+    <mergeCell ref="H261:U261"/>
+    <mergeCell ref="H262:U262"/>
+    <mergeCell ref="H263:U263"/>
+    <mergeCell ref="H271:U271"/>
+    <mergeCell ref="H272:U272"/>
+    <mergeCell ref="H265:U265"/>
+    <mergeCell ref="H266:U266"/>
+    <mergeCell ref="H267:U267"/>
+    <mergeCell ref="H268:U268"/>
+    <mergeCell ref="H269:U269"/>
+    <mergeCell ref="H270:U270"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
